--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="M13" s="14" t="n"/>
       <c r="N13" s="15" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="P13" s="13" t="inlineStr">
         <is>
-          <t>★第1稿（0828版）を受領し令和7年8月版との全面突合を完了（doc23）。要修正：選択肢の順序が標準と逆になっている7か所（うち2か所は文字列の誤植）、標準様式の残骸3か所、問7の番号繰り上がり。村独自14問の採否を判定し、削除提案は問3(10)の1問のみ。★9/4：第2稿（0904版）を確認。指摘13件のうち11件が反映。ルビを57→105か所に拡充、通いの場の名称を現行事業名に修正、自由記述欄を新設。未対応は問1(2)①の選択肢順序と問7(7)の採用可否の2件。新たに保険外サービスの選択肢の不統一と個人情報の説明文の後退を検出（doc27）。</t>
+          <t>★第1稿（0828版）を受領し令和7年8月版との全面突合を完了（doc23）。要修正：選択肢の順序が標準と逆になっている7か所（うち2か所は文字列の誤植）、標準様式の残骸3か所、問7の番号繰り上がり。村独自14問の採否を判定し、削除提案は問3(10)の1問のみ。★9/4：第2稿（0904版）を確認。指摘13件のうち11件が反映。ルビを57→105か所に拡充、通いの場の名称を現行事業名に修正、自由記述欄を新設。未対応は問1(2)①の選択肢順序と問7(7)の採用可否の2件。新たに保険外サービスの選択肢の不統一と個人情報の説明文の後退を検出（doc27）。★9/14：0909校正版（doc34）を確認。問1(2)①の選択肢順序は解消。一方、問1(4)住まいの種類と問4(16)若い人に話しかけるが削除済み、問4(15)病人を見舞うに削除の指示。いずれも見える化の登録対象で、問4(15)(16)が落ちるとR09社会的役割の低下が算出できずR99が10領域→9領域に減る。印刷前の判断を要する。</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="M14" s="14" t="n"/>
       <c r="N14" s="15" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="O14" s="16" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="P14" s="13" t="inlineStr">
         <is>
-          <t>★第1稿を受領し手法Ⅲ標準様式との突合を完了（doc23）。要修正：標準の問13「訪問診療」が削除され問13が欠番、前回指摘2件（介護療養型医療施設の削除・傷病の選択肢13/14の入替）が未反映、基準月が空欄。村独自の問0・問6-1は番号体系を壊さない適切な設計。★9/4：第2稿で介護療養型医療施設の削除・傷病の選択肢13/14・基準月（問8）・訪問診療の復活がすべて反映。ただし訪問診療の番号が問12となり問12が重複・問13が欠番、問9の基準月が未修正、B票の案内文1行が削除された（doc27§3・§5-3）。</t>
+          <t>★第1稿を受領し手法Ⅲ標準様式との突合を完了（doc23）。要修正：標準の問13「訪問診療」が削除され問13が欠番、前回指摘2件（介護療養型医療施設の削除・傷病の選択肢13/14の入替）が未反映、基準月が空欄。村独自の問0・問6-1は番号体系を壊さない適切な設計。★9/4：第2稿で介護療養型医療施設の削除・傷病の選択肢13/14・基準月（問8）・訪問診療の復活がすべて反映。ただし訪問診療の番号が問12となり問12が重複・問13が欠番、問9の基準月が未修正、B票の案内文1行が削除された（doc27§3・§5-3）。★9/14：0909校正版（doc34）を確認。問12の重複・問13の欠番と問9の基準月は解消。傷病に「なし」「わからない」が追加され疾病数が算出可能に。サービスは12→9に整理（夜間対応型・定期巡回・看多機を削除。実績0で妥当）。残る印刷前の修正は問7-1の参照先「問6」→「問7」、問10の記号K→H・L→I、A票問15の分岐の食い違い。</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M19" s="14" t="n"/>
       <c r="N19" s="15" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="O19" s="16" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P19" s="13" t="inlineStr">
         <is>
-          <t>★議事録により9/3に第1稿提出、9/9頃に最終校了と確定。未決事項（手法・オプション項目・独自設問・依頼状名義・部数）は選択肢併記で提出する。★9/4：第2稿を受領しレビュー完了（doc27）。校了までの修正リスト11件を優先度付きで整理。必須3件（在宅の問13の番号・問9の基準月・ニーズ問1(2)①の選択肢順序）。</t>
+          <t>★議事録により9/3に第1稿提出、9/9頃に最終校了と確定。未決事項（手法・オプション項目・独自設問・依頼状名義・部数）は選択肢併記で提出する。★9/4：第2稿を受領しレビュー完了（doc27）。校了までの修正リスト11件を優先度付きで整理。必須3件（在宅の問13の番号・問9の基準月・ニーズ問1(2)①の選択肢順序）。★9/14：校了版の校正紙と対象者リスト・返信用封筒の版下を受領（doc34）。印刷前に決着が必要な事項6件を整理し依頼書に追加。返信用封筒の差出有効期間が回収期限と同日（2026年10月16日）で、期限翌日以降の投函が届かないため延長を要請。回収期限は手書きで10月16日（金）に確定。対象者はニーズ882人・在宅118人（在宅は想定150人を32人下回る）。</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7325,27 +7325,27 @@
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C8" s="34" t="inlineStr">
         <is>
-          <t>★ICFを用いたクロス分析の具体的な期待像（軸・アウトプットのイメージ）</t>
+          <t>★返信用封筒の差出有効期間の延長</t>
         </is>
       </c>
       <c r="D8" s="34" t="inlineStr">
         <is>
-          <t>★議事録の新規要件。「元気な高齢者」×「地域のニーズ」で共助・互助の必要性を示す分析。調査票の設計段階でクロス軸を確保しないと後から分析できない。9/3の第1稿に影響。</t>
+          <t>★★印刷前に要対応。版下は「差出有効期間 2026年10月16日まで」で回収期限（10月16日）と同日。期限翌日以降に投函された回答は料金受取人払が効かず届かない。通常は回収期限＋2週間程度。回収率に直結する。</t>
         </is>
       </c>
       <c r="E8" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-50</t>
+          <t>Ⅲ-70</t>
         </is>
       </c>
       <c r="F8" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-77</t>
+          <t>doc34§1-2</t>
         </is>
       </c>
       <c r="G8" s="35" t="inlineStr">
@@ -7363,27 +7363,27 @@
       </c>
       <c r="B9" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>★基金取崩額の確認（第9期計画の24,000,000円と議事録の「800万円程度」の関係。年額か期間合計か）</t>
+          <t>★在宅調査票の管理番号の印字形式（N付きか数字のみか）</t>
         </is>
       </c>
       <c r="D9" s="34" t="inlineStr">
         <is>
-          <t>★保険料試算の前提が3倍変わる。議事録で基金取崩を視野に入れる方針が示されたため、正確な残高と取崩実績の確認が必須。</t>
+          <t>★対象者リストはニーズが1〜882の数字、在宅がN1〜N118。調査票の印字見本はどちらも「1」。食い違うと回収後に名簿と回答を突き合わせられない。</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅲ-70</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-74</t>
+          <t>doc34§5-3</t>
         </is>
       </c>
       <c r="G9" s="35" t="inlineStr">
@@ -7401,27 +7401,27 @@
       </c>
       <c r="B10" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C10" s="34" t="inlineStr">
         <is>
-          <t>★第9期計画の第1号被保険者数の推計に用いたデータ（国配布の住基ベース推計か別の推計か）</t>
+          <t>★ICFを用いたクロス分析の具体的な期待像（軸・アウトプットのイメージ）</t>
         </is>
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>★国の事務連絡により、福島県では社人研の市町村別推計が公表されておらず第9期でも住基ベース推計が配布されていたことが判明。当方が示してきた「社人研推計をそのまま用いたため6.6%ずれた」という説明の前提が崩れた。第10期の説明の組み立てに影響する。</t>
+          <t>★議事録の新規要件。「元気な高齢者」×「地域のニーズ」で共助・互助の必要性を示す分析。調査票の設計段階でクロス軸を確保しないと後から分析できない。9/3の第1稿に影響。</t>
         </is>
       </c>
       <c r="E10" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-50</t>
         </is>
       </c>
       <c r="F10" s="35" t="inlineStr">
         <is>
-          <t>doc28§1-1 K-105</t>
+          <t>doc22 K-77</t>
         </is>
       </c>
       <c r="G10" s="35" t="inlineStr">
@@ -7444,22 +7444,22 @@
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>★第10期の第1号被保険者数をA案（配布データ）とB案（令和8年実績にリベース）のどちらで置くか</t>
+          <t>★ニーズ調査 問4(15)(16)（社会的役割）を削除するかどうか</t>
         </is>
       </c>
       <c r="D11" s="34" t="inlineStr">
         <is>
-          <t>★配布データの推計値（令和8年954人）が実績（1,012人）を58人・5.7%下回っており、そのまま用いると第9期と同じ過少推計になる。第10期を通じて約57人・6%の差が生じ、保険料の基準額に直接影響する。県通知は「参考として適切に設定願います」としており配布データの使用を義務づけていない。</t>
+          <t>★★印刷前に要決定。国の手引きは問4(13)〜(16)の4項目すべてが「いいえ」で「社会的役割の低下」と判定する。(16)は削除済み、(15)は0909校正で削除の指示。2項目が欠けるとR09が算出できず、見える化への登録も全国・県との比較も不可。R99が10領域→9領域に減るため第9期調査との比較も成立しない。左余白の「見える化関係」の書き込みは(10)〜(14)を指すとみられるが(15)(16)も登録対象である。</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-59,Ⅱ-64</t>
+          <t>Ⅲ-71,Ⅲ-72</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>doc28§1-4 K-106</t>
+          <t>doc34§1-1</t>
         </is>
       </c>
       <c r="G11" s="35" t="inlineStr">
@@ -7477,27 +7477,27 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C12" s="34" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の手法（手法Ⅲか、手法Ⅳ〈新版 在宅生活改善調査〉を加えるか）</t>
+          <t>★基金取崩額の確認（第9期計画の24,000,000円と議事録の「800万円程度」の関係。年額か期間合計か）</t>
         </is>
       </c>
       <c r="D12" s="34" t="inlineStr">
         <is>
-          <t>調査票の設計・印刷頁数・集計方法がすべて決まる。第10期の新設手法。</t>
+          <t>★保険料試算の前提が3倍変わる。議事録で基金取崩を視野に入れる方針が示されたため、正確な残高と取崩実績の確認が必須。</t>
         </is>
       </c>
       <c r="E12" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-07,Ⅰ-10</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F12" s="35" t="inlineStr">
         <is>
-          <t>doc03/doc05</t>
+          <t>doc22 K-74</t>
         </is>
       </c>
       <c r="G12" s="35" t="inlineStr">
@@ -7515,32 +7515,32 @@
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>ニーズ調査 約850人の抽出基準（要支援認定者を含むか／第9期との対比）</t>
+          <t>★第9期計画の第1号被保険者数の推計に用いたデータ（国配布の住基ベース推計か別の推計か）</t>
         </is>
       </c>
       <c r="D13" s="34" t="inlineStr">
         <is>
-          <t>議事録で在宅150件は「要支援1・2および要介護1〜5の在宅生活者等」と決着。ニーズ約850件の抽出基準（要支援を含むか）は未決着のため残置。</t>
+          <t>★国の事務連絡により、福島県では社人研の市町村別推計が公表されておらず第9期でも住基ベース推計が配布されていたことが判明。当方が示してきた「社人研推計をそのまま用いたため6.6%ずれた」という説明の前提が崩れた。第10期の説明の組み立てに影響する。</t>
         </is>
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>doc01-2,3／doc22</t>
+          <t>doc28§1-1 K-105</t>
         </is>
       </c>
       <c r="G13" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H13" s="34" t="inlineStr"/>
@@ -7553,27 +7553,27 @@
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>オプション項目の採否（「問6 就労について」ほか）</t>
+          <t>★第10期の第1号被保険者数をA案（配布データ）とB案（令和8年実績にリベース）のどちらで置くか</t>
         </is>
       </c>
       <c r="D14" s="34" t="inlineStr">
         <is>
-          <t>令和7年8月版で就労はオプションと確定。採否で頁数が変わる。</t>
+          <t>★配布データの推計値（令和8年954人）が実績（1,012人）を58人・5.7%下回っており、そのまま用いると第9期と同じ過少推計になる。第10期を通じて約57人・6%の差が生じ、保険料の基準額に直接影響する。県通知は「参考として適切に設定願います」としており配布データの使用を義務づけていない。</t>
         </is>
       </c>
       <c r="E14" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-12</t>
+          <t>Ⅱ-59,Ⅱ-64</t>
         </is>
       </c>
       <c r="F14" s="35" t="inlineStr">
         <is>
-          <t>doc05</t>
+          <t>doc28§1-4 K-106</t>
         </is>
       </c>
       <c r="G14" s="35" t="inlineStr">
@@ -7591,27 +7591,27 @@
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>村独自設問の採否（除雪・在宅医療・成年後見・歯科受診・服薬ほか）</t>
+          <t>★調査票の印刷前修正5件（p2投函期限の空欄・問7-1の「問6」・問10の記号K L・A票問15の分岐・URLとQRコード）</t>
         </is>
       </c>
       <c r="D15" s="34" t="inlineStr">
         <is>
-          <t>第9期との時系列比較を優先するか、新規論点を入れるかの判断。</t>
+          <t>★いずれも0909校正版で残っている。問7-1の参照先の誤りは分析編の中核クロス（X-15）に、A票問15の分岐はB票の回答対象者の確定に関わる。</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-13</t>
+          <t>Ⅲ-70,Ⅲ-71</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>doc03</t>
+          <t>doc34§1</t>
         </is>
       </c>
       <c r="G15" s="35" t="inlineStr">
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C16" s="34" t="inlineStr">
         <is>
-          <t>ウェブ回答フォームの仕様（回答期限・村HP掲載の有無・二次元コード印字位置）</t>
+          <t>在宅介護実態調査の手法（手法Ⅲか、手法Ⅳ〈新版 在宅生活改善調査〉を加えるか）</t>
         </is>
       </c>
       <c r="D16" s="34" t="inlineStr">
         <is>
-          <t>入稿データ作成の前提。</t>
+          <t>調査票の設計・印刷頁数・集計方法がすべて決まる。第10期の新設手法。</t>
         </is>
       </c>
       <c r="E16" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-16,Ⅰ-17</t>
+          <t>Ⅰ-07,Ⅰ-10</t>
         </is>
       </c>
       <c r="F16" s="35" t="inlineStr">
         <is>
-          <t>doc01-8</t>
+          <t>doc03/doc05</t>
         </is>
       </c>
       <c r="G16" s="35" t="inlineStr">
@@ -7672,27 +7672,27 @@
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>★発送日の確定（9/17前倒し／9/18のまま／9/24後ろ倒し）と回収期限</t>
+          <t>ニーズ調査 約850人の抽出基準（要支援認定者を含むか／第9期との対比）</t>
         </is>
       </c>
       <c r="D17" s="34" t="inlineStr">
         <is>
-          <t>★議事録は「9月18日頃」とするのみで、5連休の論点に触れていない。9/17（木）への前倒し可否と回収期限を9/3の第1稿提出時に併せて提起する。</t>
+          <t>議事録で在宅150件は「要支援1・2および要介護1〜5の在宅生活者等」と決着。ニーズ約850件の抽出基準（要支援を含むか）は未決着のため残置。</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-29,Ⅰ-32</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>doc19 指-1／doc22 A-4</t>
+          <t>doc01-2,3／doc22</t>
         </is>
       </c>
       <c r="G17" s="35" t="inlineStr">
         <is>
-          <t>再提起</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H17" s="34" t="inlineStr"/>
@@ -7710,22 +7710,22 @@
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>★ウェブ回答フォームにGoogleフォームを用いることの可否</t>
+          <t>オプション項目の採否（「問6 就労について」ほか）</t>
         </is>
       </c>
       <c r="D18" s="34" t="inlineStr">
         <is>
-          <t>★通信の暗号化とデータの保存先は別の論点。回答データが村外サーバに保存される。個人情報保護条例上の取扱いと、重複排除の実装・エクスポート後の元データ削除・公開期間管理の確認が必要。</t>
+          <t>令和7年8月版で就労はオプションと確定。採否で頁数が変わる。</t>
         </is>
       </c>
       <c r="E18" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-16,Ⅰ-18</t>
+          <t>Ⅰ-12</t>
         </is>
       </c>
       <c r="F18" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-3</t>
+          <t>doc05</t>
         </is>
       </c>
       <c r="G18" s="35" t="inlineStr">
@@ -7748,22 +7748,22 @@
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>調査票の印刷頁数の調整方針（仕様書はニーズ約12頁／在宅約8頁）</t>
+          <t>村独自設問の採否（除雪・在宅医療・成年後見・歯科受診・服薬ほか）</t>
         </is>
       </c>
       <c r="D19" s="34" t="inlineStr">
         <is>
-          <t>現在の調査票案は設問数が多く、レイアウト調整か設問の絞り込みが必要になる可能性。オプション項目の採否と一体。</t>
+          <t>第9期との時系列比較を優先するか、新規論点を入れるかの判断。</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-20,Ⅰ-21</t>
+          <t>Ⅰ-13</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>doc19 S-5</t>
+          <t>doc03</t>
         </is>
       </c>
       <c r="G19" s="35" t="inlineStr">
@@ -7786,27 +7786,27 @@
       </c>
       <c r="C20" s="34" t="inlineStr">
         <is>
-          <t>依頼状の差出人名義（村名義／村長名）</t>
+          <t>ウェブ回答フォームの仕様（回答期限・村HP掲載の有無・二次元コード印字位置）</t>
         </is>
       </c>
       <c r="D20" s="34" t="inlineStr">
         <is>
-          <t>★第1稿は「北塩原村長　遠藤　和夫」と村長名で作成済み。名義の可否と、あわせて現職の村長名が正しいかの確認が必要（当方が保有する平成30年の資料では別の方が村長）。</t>
+          <t>入稿データ作成の前提。</t>
         </is>
       </c>
       <c r="E20" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-16,Ⅰ-17</t>
         </is>
       </c>
       <c r="F20" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-4／doc23§5</t>
+          <t>doc01-8</t>
         </is>
       </c>
       <c r="G20" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H20" s="34" t="inlineStr"/>
@@ -7824,27 +7824,27 @@
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>調査票の印刷部数（予備を何部見込むか）</t>
+          <t>★発送日の確定（9/17前倒し／9/18のまま／9/24後ろ倒し）と回収期限</t>
         </is>
       </c>
       <c r="D21" s="34" t="inlineStr">
         <is>
-          <t>約1,000部＋予備。発送後の追加印刷は工程上困難。</t>
+          <t>★議事録は「9月18日頃」とするのみで、5連休の論点に触れていない。9/17（木）への前倒し可否と回収期限を9/3の第1稿提出時に併せて提起する。</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-21,Ⅰ-22</t>
+          <t>Ⅰ-29,Ⅰ-32</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-5</t>
+          <t>doc19 指-1／doc22 A-4</t>
         </is>
       </c>
       <c r="G21" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>再提起</t>
         </is>
       </c>
       <c r="H21" s="34" t="inlineStr"/>
@@ -7862,22 +7862,22 @@
       </c>
       <c r="C22" s="34" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 問8・問9の基準月</t>
+          <t>★ウェブ回答フォームにGoogleフォームを用いることの可否</t>
         </is>
       </c>
       <c r="D22" s="34" t="inlineStr">
         <is>
-          <t>発送月の前月が通常。発送日の確定とセット。</t>
+          <t>★通信の暗号化とデータの保存先は別の論点。回答データが村外サーバに保存される。個人情報保護条例上の取扱いと、重複排除の実装・エクスポート後の元データ削除・公開期間管理の確認が必要。</t>
         </is>
       </c>
       <c r="E22" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-16,Ⅰ-18</t>
         </is>
       </c>
       <c r="F22" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-2</t>
+          <t>doc19 追-3</t>
         </is>
       </c>
       <c r="G22" s="35" t="inlineStr">
@@ -7900,22 +7900,22 @@
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ調査 問7(7)「この1か月間に会った友人・知人の人数」の採用可否</t>
+          <t>調査票の印刷頁数の調整方針（仕様書はニーズ約12頁／在宅約8頁）</t>
         </is>
       </c>
       <c r="D23" s="34" t="inlineStr">
         <is>
-          <t>★第1稿では不採用のうえ以降の番号を繰り上げているため、見える化への入力時に設問の対応が崩れる。採用すれば番号ずれが解消し、かつICF分析の「参加」の量的指標としてそのまま使える。</t>
+          <t>現在の調査票案は設問数が多く、レイアウト調整か設問の絞り込みが必要になる可能性。オプション項目の採否と一体。</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-20,Ⅰ-21</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>doc23§1-2</t>
+          <t>doc19 S-5</t>
         </is>
       </c>
       <c r="G23" s="35" t="inlineStr">
@@ -7938,27 +7938,27 @@
       </c>
       <c r="C24" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ調査 村独自設問14問の採否と頁数（問3(10)の削除・問7(9)の簡素化）</t>
+          <t>依頼状の差出人名義（村名義／村長名）</t>
         </is>
       </c>
       <c r="D24" s="34" t="inlineStr">
         <is>
-          <t>★標準約66問＋村独自14問＝約79問。仕様書の目安A4約12頁を超える見込み。削除を提案するのは問3(10)「1日に何回食事をとりますか」の1問のみ（低栄養は問3(1)(7)(8)で把握可能）。他13問は施策・交付金の指標と結びついており残すべき。</t>
+          <t>★第1稿は「北塩原村長　遠藤　和夫」と村長名で作成済み。名義の可否と、あわせて現職の村長名が正しいかの確認が必要（当方が保有する平成30年の資料では別の方が村長）。</t>
         </is>
       </c>
       <c r="E24" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-12,Ⅰ-13</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F24" s="35" t="inlineStr">
         <is>
-          <t>doc23§4</t>
+          <t>doc19 追-4／doc23§5</t>
         </is>
       </c>
       <c r="G24" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H24" s="34" t="inlineStr"/>
@@ -7976,22 +7976,22 @@
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>★現職の村長名・所管課・役場の住所の確認</t>
+          <t>調査票の印刷部数（予備を何部見込むか）</t>
         </is>
       </c>
       <c r="D25" s="34" t="inlineStr">
         <is>
-          <t>★第1稿の依頼状に「北塩原村長 遠藤 和夫」「保健福祉課 福祉係」「大字北山字姥ヶ作3151番地」と記載。当方では現職の村長名を確認できない。所管課は住民課との別が未確認のまま（doc01 確認事項1）。</t>
+          <t>約1,000部＋予備。発送後の追加印刷は工程上困難。</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-21,Ⅰ-22</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>doc23§5</t>
+          <t>doc19 追-5</t>
         </is>
       </c>
       <c r="G25" s="35" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="C26" s="34" t="inlineStr">
         <is>
-          <t>★【必須】在宅A票 訪問診療の設問を問13に直す（問12が重複し問13が欠番）</t>
+          <t>在宅介護実態調査 問8・問9の基準月</t>
         </is>
       </c>
       <c r="D26" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で訪問診療が復活したが番号が問12となり、今後必要と感じる支援（問12）と重複している。回答者が混乱し集計時に設問を特定できない。9/9の校了までに必ず修正。</t>
+          <t>発送月の前月が通常。発送日の確定とセット。</t>
         </is>
       </c>
       <c r="E26" s="35" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="F26" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-1</t>
+          <t>doc19 追-2</t>
         </is>
       </c>
       <c r="G26" s="35" t="inlineStr">
@@ -8052,22 +8052,22 @@
       </c>
       <c r="C27" s="34" t="inlineStr">
         <is>
-          <t>★【必須】在宅A票 問9の基準月を「令和8年8月」に修正</t>
+          <t>★ニーズ調査 問7(7)「この1か月間に会った友人・知人の人数」の採用可否</t>
         </is>
       </c>
       <c r="D27" s="34" t="inlineStr">
         <is>
-          <t>★問8は修正されたが問9が「令和●年●月」のまま。</t>
+          <t>★第1稿では不採用のうえ以降の番号を繰り上げているため、見える化への入力時に設問の対応が崩れる。採用すれば番号ずれが解消し、かつICF分析の「参加」の量的指標としてそのまま使える。</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-2</t>
+          <t>doc23§1-2</t>
         </is>
       </c>
       <c r="G27" s="35" t="inlineStr">
@@ -8090,174 +8090,174 @@
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
+          <t>★ニーズ調査 村独自設問14問の採否と頁数（問3(10)の削除・問7(9)の簡素化）</t>
+        </is>
+      </c>
+      <c r="D28" s="34" t="inlineStr">
+        <is>
+          <t>★標準約66問＋村独自14問＝約79問。仕様書の目安A4約12頁を超える見込み。削除を提案するのは問3(10)「1日に何回食事をとりますか」の1問のみ（低栄養は問3(1)(7)(8)で把握可能）。他13問は施策・交付金の指標と結びついており残すべき。</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-12,Ⅰ-13</t>
+        </is>
+      </c>
+      <c r="F28" s="35" t="inlineStr">
+        <is>
+          <t>doc23§4</t>
+        </is>
+      </c>
+      <c r="G28" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H28" s="34" t="inlineStr"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="inlineStr">
+        <is>
+          <t>★現職の村長名・所管課・役場の住所の確認</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t>★第1稿の依頼状に「北塩原村長 遠藤 和夫」「保健福祉課 福祉係」「大字北山字姥ヶ作3151番地」と記載。当方では現職の村長名を確認できない。所管課は住民課との別が未確認のまま（doc01 確認事項1）。</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t>doc23§5</t>
+        </is>
+      </c>
+      <c r="G29" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H29" s="34" t="inlineStr"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C30" s="34" t="inlineStr">
+        <is>
+          <t>★【必須】在宅A票 訪問診療の設問を問13に直す（問12が重複し問13が欠番）</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で訪問診療が復活したが番号が問12となり、今後必要と感じる支援（問12）と重複している。回答者が混乱し集計時に設問を特定できない。9/9の校了までに必ず修正。</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>doc27§3-1</t>
+        </is>
+      </c>
+      <c r="G30" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H30" s="34" t="inlineStr"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t>★【必須】在宅A票 問9の基準月を「令和8年8月」に修正</t>
+        </is>
+      </c>
+      <c r="D31" s="34" t="inlineStr">
+        <is>
+          <t>★問8は修正されたが問9が「令和●年●月」のまま。</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F31" s="35" t="inlineStr">
+        <is>
+          <t>doc27§3-2</t>
+        </is>
+      </c>
+      <c r="G31" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H31" s="34" t="inlineStr"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="inlineStr">
+        <is>
           <t>★【必須】ニーズ 問1(2)① 選択肢14・15を「14．その他／15．不明」に修正</t>
         </is>
       </c>
-      <c r="D28" s="34" t="inlineStr">
+      <c r="D32" s="34" t="inlineStr">
         <is>
           <t>★選択肢の順序の修正7か所のうち、この1か所のみ修正漏れ。標準は13．高齢による衰弱／14．その他（　）／15．不明。</t>
         </is>
       </c>
-      <c r="E28" s="35" t="inlineStr">
+      <c r="E32" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F28" s="35" t="inlineStr">
+      <c r="F32" s="35" t="inlineStr">
         <is>
           <t>doc27§2-1</t>
-        </is>
-      </c>
-      <c r="G28" s="35" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H28" s="34" t="inlineStr"/>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>スケジュール</t>
-        </is>
-      </c>
-      <c r="C29" s="34" t="inlineStr">
-        <is>
-          <t>★第2回策定委員会の開催日（11月のいつか）</t>
-        </is>
-      </c>
-      <c r="D29" s="34" t="inlineStr">
-        <is>
-          <t>★資料の事前送付の期限が決まる。素案約90頁を当日配付では読めないため事前送付が前提。</t>
-        </is>
-      </c>
-      <c r="E29" s="35" t="inlineStr">
-        <is>
-          <t>Ⅱ-105</t>
-        </is>
-      </c>
-      <c r="F29" s="35" t="inlineStr">
-        <is>
-          <t>doc26§10 K-95</t>
-        </is>
-      </c>
-      <c r="G29" s="35" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H29" s="34" t="inlineStr"/>
-    </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C30" s="34" t="inlineStr">
-        <is>
-          <t>国の介護保険事業計画作成支援ツール（将来推計総括表）の出力一式</t>
-        </is>
-      </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>★★最優先。他案件（川崎町・金ケ崎町・大雪）はいずれも保険者が操作したツールの出力を受領し検証する立場にあるが、本村は見える化から独自算定しており国の様式との検算ができていない。他案件では令和8年度が実績でなく推計値、主要項目が未入力のまま保険料だけ数値が入る等の事例が実際に見つかっている。</t>
-        </is>
-      </c>
-      <c r="E30" s="35" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F30" s="35" t="inlineStr">
-        <is>
-          <t>doc33§5-1</t>
-        </is>
-      </c>
-      <c r="G30" s="35" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H30" s="34" t="inlineStr"/>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C31" s="34" t="inlineStr">
-        <is>
-          <t>第9期計画の本文（サービス別見込量の表を含む全体）</t>
-        </is>
-      </c>
-      <c r="D31" s="34" t="inlineStr">
-        <is>
-          <t>★★用途が2つある。①対計画比（サービス別の計画値と実績の対比）。他案件では総額が計画どおりでも内訳が11.5〜967.4％まで開くことが確認されており、本村は受給率を3か年平均で固定しているため偏りを持ち越す。②老人福祉事業の量の目標の記載位置の確認（doc32§4-1）。保有しているのは概要版のみでサービス別見込量がない。</t>
-        </is>
-      </c>
-      <c r="E31" s="35" t="inlineStr">
-        <is>
-          <t>Ⅱ-53,Ⅱ-55</t>
-        </is>
-      </c>
-      <c r="F31" s="35" t="inlineStr">
-        <is>
-          <t>doc33§5-2</t>
-        </is>
-      </c>
-      <c r="G31" s="35" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H31" s="34" t="inlineStr"/>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C32" s="34" t="inlineStr">
-        <is>
-          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
-        </is>
-      </c>
-      <c r="D32" s="34" t="inlineStr">
-        <is>
-          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
-        </is>
-      </c>
-      <c r="E32" s="35" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F32" s="35" t="inlineStr">
-        <is>
-          <t>doc20§8-2 K-61</t>
         </is>
       </c>
       <c r="G32" s="35" t="inlineStr">
@@ -8275,27 +8275,27 @@
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="C33" s="34" t="inlineStr">
         <is>
-          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
+          <t>★第2回策定委員会の開催日（11月のいつか）</t>
         </is>
       </c>
       <c r="D33" s="34" t="inlineStr">
         <is>
-          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
+          <t>★資料の事前送付の期限が決まる。素案約90頁を当日配付では読めないため事前送付が前提。</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61b</t>
+          <t>doc26§10 K-95</t>
         </is>
       </c>
       <c r="G33" s="35" t="inlineStr">
@@ -8318,22 +8318,22 @@
       </c>
       <c r="C34" s="34" t="inlineStr">
         <is>
-          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
+          <t>国の介護保険事業計画作成支援ツール（将来推計総括表）の出力一式</t>
         </is>
       </c>
       <c r="D34" s="34" t="inlineStr">
         <is>
-          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
+          <t>★★最優先。他案件（川崎町・金ケ崎町・大雪）はいずれも保険者が操作したツールの出力を受領し検証する立場にあるが、本村は見える化から独自算定しており国の様式との検算ができていない。他案件では令和8年度が実績でなく推計値、主要項目が未入力のまま保険料だけ数値が入る等の事例が実際に見つかっている。</t>
         </is>
       </c>
       <c r="E34" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-55,Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F34" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-62</t>
+          <t>doc33§5-1</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -8356,22 +8356,22 @@
       </c>
       <c r="C35" s="34" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
+          <t>第9期計画の本文（サービス別見込量の表を含む全体）</t>
         </is>
       </c>
       <c r="D35" s="34" t="inlineStr">
         <is>
-          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
+          <t>★★用途が2つある。①対計画比（サービス別の計画値と実績の対比）。他案件では総額が計画どおりでも内訳が11.5〜967.4％まで開くことが確認されており、本村は受給率を3か年平均で固定しているため偏りを持ち越す。②老人福祉事業の量の目標の記載位置の確認（doc32§4-1）。保有しているのは概要版のみでサービス別見込量がない。</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-53,Ⅱ-55</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-63</t>
+          <t>doc33§5-2</t>
         </is>
       </c>
       <c r="G35" s="35" t="inlineStr">
@@ -8394,22 +8394,22 @@
       </c>
       <c r="C36" s="34" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
+          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D36" s="34" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
+          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
         </is>
       </c>
       <c r="E36" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F36" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-64</t>
+          <t>doc20§8-2 K-61</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -8432,22 +8432,22 @@
       </c>
       <c r="C37" s="34" t="inlineStr">
         <is>
-          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
+          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D37" s="34" t="inlineStr">
         <is>
-          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
+          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-75</t>
+          <t>doc20§8-2 K-61b</t>
         </is>
       </c>
       <c r="G37" s="35" t="inlineStr">
@@ -8470,22 +8470,22 @@
       </c>
       <c r="C38" s="34" t="inlineStr">
         <is>
-          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
+          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
         </is>
       </c>
       <c r="D38" s="34" t="inlineStr">
         <is>
-          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
+          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
         </is>
       </c>
       <c r="E38" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-37</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F38" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-87</t>
+          <t>doc20§6-2 K-62</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="C39" s="34" t="inlineStr">
         <is>
-          <t>★会津権利擁護・成年後見センターへの相談が1年で件数−43%・時間−55%と減少した要因</t>
+          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
         </is>
       </c>
       <c r="D39" s="34" t="inlineStr">
         <is>
-          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
+          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>doc28§3-3 K-108</t>
+          <t>doc20§6-2 K-63</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -8541,27 +8541,27 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F40" s="35" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc20§6-2 K-64</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -8579,27 +8579,27 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C41" s="34" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
         </is>
       </c>
       <c r="D41" s="34" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>doc22 K-75</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -8617,27 +8617,27 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C42" s="34" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
         </is>
       </c>
       <c r="D42" s="34" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
         </is>
       </c>
       <c r="E42" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>Ⅰ-37</t>
         </is>
       </c>
       <c r="F42" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>doc24§12 K-87</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -8655,27 +8655,27 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C43" s="34" t="inlineStr">
         <is>
-          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
+          <t>★会津権利擁護・成年後見センターへの相談が1年で件数−43%・時間−55%と減少した要因</t>
         </is>
       </c>
       <c r="D43" s="34" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
+          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-89</t>
+          <t>doc28§3-3 K-108</t>
         </is>
       </c>
       <c r="G43" s="35" t="inlineStr">
@@ -8698,22 +8698,22 @@
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D44" s="34" t="inlineStr">
         <is>
-          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E44" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F44" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-97</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G44" s="35" t="inlineStr">
@@ -8731,27 +8731,27 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D45" s="34" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-50</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
@@ -8769,27 +8769,27 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D46" s="34" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E46" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F46" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -8807,27 +8807,27 @@
       </c>
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-46</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>doc25§4-2 K-91</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -8845,27 +8845,27 @@
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C48" s="34" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
         </is>
       </c>
       <c r="D48" s="34" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
         </is>
       </c>
       <c r="E48" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F48" s="35" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc26§10 K-97</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -8883,27 +8883,27 @@
       </c>
       <c r="B49" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅰ-50</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -8921,27 +8921,27 @@
       </c>
       <c r="B50" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F50" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -8959,27 +8959,27 @@
       </c>
       <c r="B51" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
+          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
+          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅰ-46</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>doc33§3-5</t>
+          <t>doc25§4-2 K-91</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -8997,27 +8997,27 @@
       </c>
       <c r="B52" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C52" s="34" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D52" s="34" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E52" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F52" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -9035,27 +9035,27 @@
       </c>
       <c r="B53" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D53" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -9073,27 +9073,27 @@
       </c>
       <c r="B54" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C54" s="34" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D54" s="34" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E54" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F54" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -9116,22 +9116,22 @@
       </c>
       <c r="C55" s="34" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>在宅介護実態調査の対象が118人（想定150人）であることへの集計設計の対応</t>
         </is>
       </c>
       <c r="D55" s="34" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+          <t>★回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかの判断が要る。</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅲ-72,Ⅲ-73</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-99</t>
+          <t>doc34§5-2</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -9154,22 +9154,22 @@
       </c>
       <c r="C56" s="34" t="inlineStr">
         <is>
-          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
+          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
         </is>
       </c>
       <c r="D56" s="34" t="inlineStr">
         <is>
-          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
+          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
         </is>
       </c>
       <c r="E56" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F56" s="35" t="inlineStr">
         <is>
-          <t>doc28§1-2 K-107</t>
+          <t>doc33§3-5</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -9187,27 +9187,27 @@
       </c>
       <c r="B57" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C57" s="34" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D57" s="34" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
@@ -9225,27 +9225,27 @@
       </c>
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C58" s="34" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D58" s="34" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E58" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F58" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -9263,27 +9263,27 @@
       </c>
       <c r="B59" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C59" s="34" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D59" s="34" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G59" s="35" t="inlineStr">
@@ -9301,32 +9301,32 @@
       </c>
       <c r="B60" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C60" s="34" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D60" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
         </is>
       </c>
       <c r="E60" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F60" s="35" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc26§10 K-99</t>
         </is>
       </c>
       <c r="G60" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H60" s="34" t="inlineStr"/>
@@ -9339,27 +9339,27 @@
       </c>
       <c r="B61" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C61" s="34" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
         </is>
       </c>
       <c r="D61" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc28§1-2 K-107</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -9377,27 +9377,27 @@
       </c>
       <c r="B62" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C62" s="34" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D62" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E62" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F62" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G62" s="35" t="inlineStr">
@@ -9415,27 +9415,27 @@
       </c>
       <c r="B63" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C63" s="34" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -9453,225 +9453,225 @@
       </c>
       <c r="B64" s="33" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C64" s="34" t="inlineStr">
+        <is>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+        </is>
+      </c>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+        </is>
+      </c>
+      <c r="E64" s="35" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F64" s="35" t="inlineStr">
+        <is>
+          <t>doc28§3-4 K-111</t>
+        </is>
+      </c>
+      <c r="G64" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H64" s="34" t="inlineStr"/>
+    </row>
+    <row r="65" ht="34" customHeight="1">
+      <c r="A65" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B65" s="33" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C64" s="34" t="inlineStr">
+      <c r="C65" s="34" t="inlineStr">
+        <is>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+        </is>
+      </c>
+      <c r="D65" s="34" t="inlineStr">
+        <is>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+        </is>
+      </c>
+      <c r="E65" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-19,Ⅰ-25</t>
+        </is>
+      </c>
+      <c r="F65" s="35" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G65" s="35" t="inlineStr">
+        <is>
+          <t>一部回答</t>
+        </is>
+      </c>
+      <c r="H65" s="34" t="inlineStr"/>
+    </row>
+    <row r="66" ht="34" customHeight="1">
+      <c r="A66" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B66" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C66" s="34" t="inlineStr">
+        <is>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+        </is>
+      </c>
+      <c r="D66" s="34" t="inlineStr">
+        <is>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+        </is>
+      </c>
+      <c r="E66" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F66" s="35" t="inlineStr">
+        <is>
+          <t>doc27§3-3</t>
+        </is>
+      </c>
+      <c r="G66" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H66" s="34" t="inlineStr"/>
+    </row>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B67" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C67" s="34" t="inlineStr">
+        <is>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+        </is>
+      </c>
+      <c r="D67" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+        </is>
+      </c>
+      <c r="E67" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F67" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-2</t>
+        </is>
+      </c>
+      <c r="G67" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H67" s="34" t="inlineStr"/>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B68" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C68" s="34" t="inlineStr">
+        <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D68" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E68" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F68" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G68" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H68" s="34" t="inlineStr"/>
+    </row>
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B69" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C69" s="34" t="inlineStr">
         <is>
           <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
-      <c r="D64" s="34" t="inlineStr">
+      <c r="D69" s="34" t="inlineStr">
         <is>
           <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
-      <c r="E64" s="35" t="inlineStr">
+      <c r="E69" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="F64" s="35" t="inlineStr">
+      <c r="F69" s="35" t="inlineStr">
         <is>
           <t>doc27§6</t>
         </is>
       </c>
-      <c r="G64" s="35" t="inlineStr">
+      <c r="G69" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H64" s="34" t="inlineStr"/>
-    </row>
-    <row r="65" ht="34" customHeight="1">
-      <c r="A65" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B65" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C65" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D65" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E65" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F65" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H65" s="25" t="inlineStr"/>
-    </row>
-    <row r="66" ht="34" customHeight="1">
-      <c r="A66" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B66" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C66" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D66" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
-        </is>
-      </c>
-      <c r="E66" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F66" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1,doc30§2-4</t>
-        </is>
-      </c>
-      <c r="G66" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H66" s="25" t="inlineStr"/>
-    </row>
-    <row r="67" ht="34" customHeight="1">
-      <c r="A67" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B67" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C67" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D67" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
-        </is>
-      </c>
-      <c r="E67" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F67" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H67" s="25" t="inlineStr"/>
-    </row>
-    <row r="68" ht="34" customHeight="1">
-      <c r="A68" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B68" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C68" s="25" t="inlineStr">
-        <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
-        </is>
-      </c>
-      <c r="D68" s="25" t="inlineStr">
-        <is>
-          <t>現行計画の評価に必要。</t>
-        </is>
-      </c>
-      <c r="E68" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F68" s="23" t="inlineStr">
-        <is>
-          <t>doc01-11</t>
-        </is>
-      </c>
-      <c r="G68" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H68" s="25" t="inlineStr"/>
-    </row>
-    <row r="69" ht="34" customHeight="1">
-      <c r="A69" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B69" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C69" s="25" t="inlineStr">
-        <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
-        </is>
-      </c>
-      <c r="D69" s="25" t="inlineStr">
-        <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
-        </is>
-      </c>
-      <c r="E69" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
-        </is>
-      </c>
-      <c r="F69" s="23" t="inlineStr">
-        <is>
-          <t>doc19 追-9</t>
-        </is>
-      </c>
-      <c r="G69" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H69" s="25" t="inlineStr"/>
+      <c r="H69" s="34" t="inlineStr"/>
     </row>
     <row r="70" ht="34" customHeight="1">
       <c r="A70" s="37" t="inlineStr">
@@ -9686,22 +9686,22 @@
       </c>
       <c r="C70" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F70" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G70" s="23" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="C71" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -9762,22 +9762,22 @@
       </c>
       <c r="C72" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr">
@@ -9800,22 +9800,22 @@
       </c>
       <c r="C73" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D73" s="25" t="inlineStr">
         <is>
-          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
@@ -9838,22 +9838,22 @@
       </c>
       <c r="C74" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
@@ -9876,22 +9876,22 @@
       </c>
       <c r="C75" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -9914,22 +9914,22 @@
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
@@ -9952,22 +9952,22 @@
       </c>
       <c r="C77" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -9990,22 +9990,22 @@
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F78" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -10066,22 +10066,22 @@
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10218,22 +10218,22 @@
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10294,22 +10294,22 @@
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -10332,22 +10332,22 @@
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -10370,22 +10370,22 @@
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -10408,22 +10408,22 @@
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10441,27 +10441,27 @@
       </c>
       <c r="B90" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -10479,27 +10479,27 @@
       </c>
       <c r="B91" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -10517,27 +10517,27 @@
       </c>
       <c r="B92" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -10555,27 +10555,27 @@
       </c>
       <c r="B93" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -10593,27 +10593,27 @@
       </c>
       <c r="B94" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -10631,27 +10631,27 @@
       </c>
       <c r="B95" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -10669,27 +10669,27 @@
       </c>
       <c r="B96" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -10707,27 +10707,27 @@
       </c>
       <c r="B97" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -10745,27 +10745,27 @@
       </c>
       <c r="B98" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -10783,27 +10783,27 @@
       </c>
       <c r="B99" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -10821,27 +10821,27 @@
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -10859,27 +10859,27 @@
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -10902,22 +10902,22 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -10940,22 +10940,22 @@
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -10978,22 +10978,22 @@
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11016,22 +11016,22 @@
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -11054,22 +11054,22 @@
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -11092,22 +11092,22 @@
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -11130,22 +11130,22 @@
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -11163,27 +11163,27 @@
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -11201,27 +11201,27 @@
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -11239,27 +11239,27 @@
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -11277,27 +11277,27 @@
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -11315,17 +11315,17 @@
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -11353,27 +11353,27 @@
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -11391,27 +11391,27 @@
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -11429,27 +11429,27 @@
       </c>
       <c r="B116" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -11467,27 +11467,27 @@
       </c>
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -11505,27 +11505,27 @@
       </c>
       <c r="B118" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -11543,27 +11543,27 @@
       </c>
       <c r="B119" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -11581,27 +11581,27 @@
       </c>
       <c r="B120" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -11619,27 +11619,27 @@
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -11657,27 +11657,27 @@
       </c>
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -11695,27 +11695,27 @@
       </c>
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -11733,27 +11733,27 @@
       </c>
       <c r="B124" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -11771,27 +11771,27 @@
       </c>
       <c r="B125" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -11809,27 +11809,27 @@
       </c>
       <c r="B126" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -11847,27 +11847,27 @@
       </c>
       <c r="B127" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -11885,346 +11885,346 @@
       </c>
       <c r="B128" s="24" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C128" s="25" t="inlineStr">
+        <is>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+        </is>
+      </c>
+      <c r="D128" s="25" t="inlineStr">
+        <is>
+          <t>施策の書きぶりに影響。</t>
+        </is>
+      </c>
+      <c r="E128" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F128" s="23" t="inlineStr">
+        <is>
+          <t>doc01-12</t>
+        </is>
+      </c>
+      <c r="G128" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H128" s="25" t="inlineStr"/>
+    </row>
+    <row r="129" ht="34" customHeight="1">
+      <c r="A129" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B129" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C129" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D129" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E129" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F129" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G129" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H129" s="25" t="inlineStr"/>
+    </row>
+    <row r="130" ht="34" customHeight="1">
+      <c r="A130" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B130" s="24" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C128" s="25" t="inlineStr">
+      <c r="C130" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D130" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E130" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F130" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G130" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H130" s="25" t="inlineStr"/>
+    </row>
+    <row r="131" ht="34" customHeight="1">
+      <c r="A131" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B131" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C131" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D131" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E131" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F131" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G131" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H131" s="25" t="inlineStr"/>
+    </row>
+    <row r="132" ht="34" customHeight="1">
+      <c r="A132" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B132" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C132" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D132" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E132" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F132" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G132" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H132" s="25" t="inlineStr"/>
+    </row>
+    <row r="133" ht="34" customHeight="1">
+      <c r="A133" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B133" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C133" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D133" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E133" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F133" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G133" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H133" s="25" t="inlineStr"/>
+    </row>
+    <row r="134" ht="34" customHeight="1">
+      <c r="A134" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B134" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C134" s="25" t="inlineStr">
         <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D128" s="25" t="inlineStr">
+      <c r="D134" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E128" s="23" t="inlineStr">
+      <c r="E134" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F128" s="23" t="inlineStr">
+      <c r="F134" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G128" s="23" t="inlineStr">
+      <c r="G134" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H128" s="25" t="inlineStr"/>
-    </row>
-    <row r="129" ht="34" customHeight="1">
-      <c r="A129" s="38" t="inlineStr">
+      <c r="H134" s="25" t="inlineStr"/>
+    </row>
+    <row r="135" ht="34" customHeight="1">
+      <c r="A135" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B129" s="24" t="inlineStr">
+      <c r="B135" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C129" s="25" t="inlineStr">
+      <c r="C135" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D129" s="25" t="inlineStr">
+      <c r="D135" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E129" s="23" t="inlineStr">
+      <c r="E135" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F129" s="23" t="inlineStr">
+      <c r="F135" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G129" s="23" t="inlineStr">
+      <c r="G135" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H129" s="25" t="inlineStr"/>
-    </row>
-    <row r="130" ht="34" customHeight="1">
-      <c r="A130" s="38" t="inlineStr">
+      <c r="H135" s="25" t="inlineStr"/>
+    </row>
+    <row r="136" ht="34" customHeight="1">
+      <c r="A136" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B130" s="24" t="inlineStr">
+      <c r="B136" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C130" s="25" t="inlineStr">
+      <c r="C136" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D130" s="25" t="inlineStr">
+      <c r="D136" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E130" s="23" t="inlineStr">
+      <c r="E136" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F130" s="23" t="inlineStr">
+      <c r="F136" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G130" s="23" t="inlineStr">
+      <c r="G136" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H130" s="25" t="inlineStr"/>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="39" t="inlineStr">
+      <c r="H136" s="25" t="inlineStr"/>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="133" ht="34" customHeight="1">
-      <c r="A133" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B133" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C133" s="42" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D133" s="42" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E133" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F133" s="40" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G133" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H133" s="42" t="inlineStr"/>
-    </row>
-    <row r="134" ht="34" customHeight="1">
-      <c r="A134" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B134" s="41" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C134" s="42" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D134" s="42" t="inlineStr">
-        <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
-        </is>
-      </c>
-      <c r="E134" s="40" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F134" s="40" t="inlineStr">
-        <is>
-          <t>doc28§4</t>
-        </is>
-      </c>
-      <c r="G134" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H134" s="42" t="inlineStr"/>
-    </row>
-    <row r="135" ht="34" customHeight="1">
-      <c r="A135" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B135" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C135" s="42" t="inlineStr">
-        <is>
-          <t>所得段階別の第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D135" s="42" t="inlineStr">
-        <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
-        </is>
-      </c>
-      <c r="E135" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F135" s="40" t="inlineStr">
-        <is>
-          <t>doc28§2</t>
-        </is>
-      </c>
-      <c r="G135" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H135" s="42" t="inlineStr"/>
-    </row>
-    <row r="136" ht="34" customHeight="1">
-      <c r="A136" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B136" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C136" s="42" t="inlineStr">
-        <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
-        </is>
-      </c>
-      <c r="D136" s="42" t="inlineStr">
-        <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
-        </is>
-      </c>
-      <c r="E136" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-59</t>
-        </is>
-      </c>
-      <c r="F136" s="40" t="inlineStr">
-        <is>
-          <t>doc28§1</t>
-        </is>
-      </c>
-      <c r="G136" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H136" s="42" t="inlineStr"/>
-    </row>
-    <row r="137" ht="34" customHeight="1">
-      <c r="A137" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B137" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C137" s="42" t="inlineStr">
-        <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
-        </is>
-      </c>
-      <c r="D137" s="42" t="inlineStr">
-        <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
-        </is>
-      </c>
-      <c r="E137" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-09</t>
-        </is>
-      </c>
-      <c r="F137" s="40" t="inlineStr">
-        <is>
-          <t>doc27§1-1</t>
-        </is>
-      </c>
-      <c r="G137" s="40" t="inlineStr">
-        <is>
-          <t>解決済（一部再掲）</t>
-        </is>
-      </c>
-      <c r="H137" s="42" t="inlineStr"/>
-    </row>
-    <row r="138" ht="34" customHeight="1">
-      <c r="A138" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B138" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C138" s="42" t="inlineStr">
-        <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
-        </is>
-      </c>
-      <c r="D138" s="42" t="inlineStr">
-        <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
-        </is>
-      </c>
-      <c r="E138" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-10</t>
-        </is>
-      </c>
-      <c r="F138" s="40" t="inlineStr">
-        <is>
-          <t>doc27§1-2</t>
-        </is>
-      </c>
-      <c r="G138" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H138" s="42" t="inlineStr"/>
     </row>
     <row r="139" ht="34" customHeight="1">
       <c r="A139" s="40" t="inlineStr">
@@ -12234,32 +12234,32 @@
       </c>
       <c r="B139" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C139" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D139" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E139" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F139" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G139" s="40" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H139" s="42" t="inlineStr"/>
@@ -12272,27 +12272,27 @@
       </c>
       <c r="B140" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C140" s="42" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D140" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E140" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F140" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G140" s="40" t="inlineStr">
@@ -12310,27 +12310,27 @@
       </c>
       <c r="B141" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C141" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D141" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E141" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F141" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G141" s="40" t="inlineStr">
@@ -12348,27 +12348,27 @@
       </c>
       <c r="B142" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C142" s="42" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D142" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E142" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F142" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G142" s="40" t="inlineStr">
@@ -12386,32 +12386,32 @@
       </c>
       <c r="B143" s="41" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C143" s="42" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D143" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E143" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F143" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G143" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H143" s="42" t="inlineStr"/>
@@ -12424,27 +12424,27 @@
       </c>
       <c r="B144" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C144" s="42" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D144" s="42" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E144" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F144" s="40" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G144" s="40" t="inlineStr">
@@ -12462,32 +12462,32 @@
       </c>
       <c r="B145" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C145" s="42" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D145" s="42" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E145" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F145" s="40" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G145" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H145" s="42" t="inlineStr"/>
@@ -12500,27 +12500,27 @@
       </c>
       <c r="B146" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C146" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D146" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E146" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F146" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G146" s="40" t="inlineStr">
@@ -12538,27 +12538,27 @@
       </c>
       <c r="B147" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C147" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D147" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E147" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F147" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G147" s="40" t="inlineStr">
@@ -12576,27 +12576,27 @@
       </c>
       <c r="B148" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C148" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D148" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E148" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F148" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G148" s="40" t="inlineStr">
@@ -12614,48 +12614,276 @@
       </c>
       <c r="B149" s="41" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C149" s="42" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の範囲</t>
+        </is>
+      </c>
+      <c r="D149" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+        </is>
+      </c>
+      <c r="E149" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F149" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G149" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H149" s="42" t="inlineStr"/>
+    </row>
+    <row r="150" ht="34" customHeight="1">
+      <c r="A150" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B150" s="41" t="inlineStr">
+        <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C149" s="42" t="inlineStr">
+      <c r="C150" s="42" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D150" s="42" t="inlineStr">
+        <is>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+        </is>
+      </c>
+      <c r="E150" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F150" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3,§4</t>
+        </is>
+      </c>
+      <c r="G150" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H150" s="42" t="inlineStr"/>
+    </row>
+    <row r="151" ht="34" customHeight="1">
+      <c r="A151" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B151" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C151" s="42" t="inlineStr">
+        <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D151" s="42" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E151" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F151" s="40" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G151" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H151" s="42" t="inlineStr"/>
+    </row>
+    <row r="152" ht="34" customHeight="1">
+      <c r="A152" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B152" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C152" s="42" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D152" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E152" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F152" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G152" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H152" s="42" t="inlineStr"/>
+    </row>
+    <row r="153" ht="34" customHeight="1">
+      <c r="A153" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B153" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C153" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D153" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E153" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F153" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G153" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H153" s="42" t="inlineStr"/>
+    </row>
+    <row r="154" ht="34" customHeight="1">
+      <c r="A154" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B154" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C154" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D154" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E154" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F154" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G154" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H154" s="42" t="inlineStr"/>
+    </row>
+    <row r="155" ht="34" customHeight="1">
+      <c r="A155" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B155" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C155" s="42" t="inlineStr">
         <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D149" s="42" t="inlineStr">
+      <c r="D155" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E149" s="40" t="inlineStr">
+      <c r="E155" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F149" s="40" t="inlineStr">
+      <c r="F155" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G149" s="40" t="inlineStr">
+      <c r="G155" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H149" s="42" t="inlineStr"/>
+      <c r="H155" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H130"/>
+  <autoFilter ref="A4:H136"/>
   <mergeCells count="3">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A132:H132"/>
+    <mergeCell ref="A138:H138"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A130" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G130" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$139</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="M65" s="14" t="n"/>
       <c r="N65" s="15" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O65" s="16" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="P65" s="13" t="inlineStr">
         <is>
-          <t>★9/8：doc30として推計の枠組みを確定。「見える化」システムのデータ定義（受給者数＝年度延べ、D45系の分母＝要介護度別認定者数）を検算のうえ確定し、estimate_services.py により区分別・サービス種類別の見込量を算定。全28サービスのうち令和7年度に実績のある16サービスについて受給者数・利用量・給付費の暫定値を doc18 第5章5-4に投入。施設・居住系の種類別人数は見える化に系列がなく給付費比の按分値のため、村の月報（第2表・第3表）で置き換えが必要。介護給付と予防給付の分離も同じく月報待ち。★9/12：他案件（川崎町・金ケ崎町・大雪）の到達水準と対照し（doc33）、基準年度を令和7年度と確定。見える化の系列別の月数を実測で確認し（D1はR7が11か月、D2/D3/D4は12か月相当）doc30の÷12が正しいことを裏付けて素案5-4に明記。令和9年4月新設4区分の枠と、国の推計ツールのワーニング判定式（閾値＝Q1−2Q〜Q3+2Q）による自己点検の手順を追加。国の推計ツールの出力は未受領で、依頼書18-2として最優先で追加した。</t>
+          <t>★9/8：doc30として推計の枠組みを確定。「見える化」システムのデータ定義（受給者数＝年度延べ、D45系の分母＝要介護度別認定者数）を検算のうえ確定し、estimate_services.py により区分別・サービス種類別の見込量を算定。全28サービスのうち令和7年度に実績のある16サービスについて受給者数・利用量・給付費の暫定値を doc18 第5章5-4に投入。施設・居住系の種類別人数は見える化に系列がなく給付費比の按分値のため、村の月報（第2表・第3表）で置き換えが必要。介護給付と予防給付の分離も同じく月報待ち。★9/12：他案件（川崎町・金ケ崎町・大雪）の到達水準と対照し（doc33）、基準年度を令和7年度と確定。見える化の系列別の月数を実測で確認し（D1はR7が11か月、D2/D3/D4は12か月相当）doc30の÷12が正しいことを裏付けて素案5-4に明記。令和9年4月新設4区分の枠と、国の推計ツールのワーニング判定式（閾値＝Q1−2Q〜Q3+2Q）による自己点検の手順を追加。国の推計ツールの出力は未受領で、依頼書18-2として最優先で追加した。★9/15：他案件（大雪・川崎・金ケ崎）の算定の進め方を確認し、本村に適用して第1次概算を実施（doc35）。(1)見込量は需要で置く／地域密着型と総合事業のみ村の供給力が上限、という原則を素案5-4に明記。(2)令和9年4月新設4区分を「―」「要協議」から0に立て直した。(3)夜間対応型訪問介護の令和9年3月末廃止を反映。(4)単価の趨勢を連鎖ラスパイレス指数で実測（R元→R7の年率+1.30%）。3か年平均で固定していることは給付費の5.32%過小＝保険料月額314円に当たる。(5)サービス別の受給者数の年率が▲13.12〜+54.88%と68ポイント開いていることを実測し、伸びをどこまで反映すべきかをバックテストで検証（backtest_growth.py）。φ=0.5・c=5%が最小（WMAPE19.11%）だが一律19.68%に対し改善は2.9%にとどまるため一律を採用すると決定。(6)一律の方法で3年先を予測したときの誤差は絶対値平均11.9%＝保険料月額約700円で、基金取崩24,000千円の効き（702円）と同規模。素案5-4(9)として新設。(7)在宅介護実態調査の施設入所申込みの反映シナリオの枠を素案5-4(3)に新設（+1人／月＝月額75円）。残るのは国の推計ワークシートによる基準年度の置き直しの分解のみ。</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="M66" s="14" t="n"/>
       <c r="N66" s="15" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="O66" s="16" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P66" s="13" t="inlineStr">
         <is>
-          <t>★9/8：サービス諸費（介護サービス等諸費＋介護予防サービス等諸費）の推計値を算定し doc18 第5章5-6に投入（令和9年度263,470千円／10年度263,505千円／11年度262,488千円）。見える化D48系に令和5年度までの決算が入っていることが判明し、令和3〜5年度の実績（244,097／247,333／258,848千円）と対比。決算の未入手は令和6・7年度の2か年に縮小。補足給付・高額介護サービス費・審査支払手数料は令和5年度決算まで把握済。★9/12：標準給付費見込額（3年計854,014千円）を算定。令和6・7年度決算が未受領のため割増率とその他給付費は令和5年度決算で代用している。</t>
+          <t>★9/8：サービス諸費（介護サービス等諸費＋介護予防サービス等諸費）の推計値を算定し doc18 第5章5-6に投入（令和9年度263,470千円／10年度263,505千円／11年度262,488千円）。見える化D48系に令和5年度までの決算が入っていることが判明し、令和3〜5年度の実績（244,097／247,333／258,848千円）と対比。決算の未入手は令和6・7年度の2か年に縮小。補足給付・高額介護サービス費・審査支払手数料は令和5年度決算まで把握済。★9/12：標準給付費見込額（3年計854,014千円）を算定。令和6・7年度決算が未受領のため割増率とその他給付費は令和5年度決算で代用している。★9/15：地域支援事業費を事業の対象別に3分して積み上げた（estimate_chiiki_shien.py）。介護予防・生活支援サービス事業は認定者数の伸び、一般介護予防事業と包括的支援事業・任意事業は第1号被保険者数の伸びによる。3か年計124,788千円で、令和5年度決算×3年の119,658千円を5,130千円上回り、保険料月額+36円に当たる。素案5-5(2)に投入。あわせて感応度表に3行（地域支援事業費+36円／単価の趨勢+314円／推計誤差±約700円）を追加し、据え置き項目31件を素案5-12として一覧化した。</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8318,22 +8318,22 @@
       </c>
       <c r="C34" s="34" t="inlineStr">
         <is>
-          <t>国の介護保険事業計画作成支援ツール（将来推計総括表）の出力一式</t>
+          <t>通いの場の参加者281人は実人数か延べ人数か（基準値の置き方）</t>
         </is>
       </c>
       <c r="D34" s="34" t="inlineStr">
         <is>
-          <t>★★最優先。他案件（川崎町・金ケ崎町・大雪）はいずれも保険者が操作したツールの出力を受領し検証する立場にあるが、本村は見える化から独自算定しており国の様式との検算ができていない。他案件では令和8年度が実績でなく推計値、主要項目が未入力のまま保険料だけ数値が入る等の事例が実際に見つかっている。</t>
+          <t>★9/15：参加率の分母を検算し、見える化F1・F4系の定義が「参加者実人数÷65歳以上人口」であることを確認した（H30は306÷961＝31.8%で公表値と一致）。令和6年度は281÷1,009＝27.8%（週1回以上は123÷1,009＝12.2%）となり、素案の12.2%・5.3%を訂正した。一方、第9期アンケートの自己申告による参加率11.2%とは16.6ポイント開く。281人が複数の通いの場への参加を重複計上しているのであれば実人数はこれより少ない。第10期の活動指標の基準値をどちらに置くかは把握方法の確認が前提。</t>
         </is>
       </c>
       <c r="E34" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F34" s="35" t="inlineStr">
         <is>
-          <t>doc33§5-1</t>
+          <t>doc35§2</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -8356,22 +8356,22 @@
       </c>
       <c r="C35" s="34" t="inlineStr">
         <is>
-          <t>第9期計画の本文（サービス別見込量の表を含む全体）</t>
+          <t>国の介護保険事業計画作成支援ツール（将来推計総括表）の出力一式</t>
         </is>
       </c>
       <c r="D35" s="34" t="inlineStr">
         <is>
-          <t>★★用途が2つある。①対計画比（サービス別の計画値と実績の対比）。他案件では総額が計画どおりでも内訳が11.5〜967.4％まで開くことが確認されており、本村は受給率を3か年平均で固定しているため偏りを持ち越す。②老人福祉事業の量の目標の記載位置の確認（doc32§4-1）。保有しているのは概要版のみでサービス別見込量がない。</t>
+          <t>★★最優先。他案件（川崎町・金ケ崎町・大雪）はいずれも保険者が操作したツールの出力を受領し検証する立場にあるが、本村は見える化から独自算定しており国の様式との検算ができていない。他案件では令和8年度が実績でなく推計値、主要項目が未入力のまま保険料だけ数値が入る等の事例が実際に見つかっている。</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>doc33§5-2</t>
+          <t>doc33§5-1</t>
         </is>
       </c>
       <c r="G35" s="35" t="inlineStr">
@@ -8394,22 +8394,22 @@
       </c>
       <c r="C36" s="34" t="inlineStr">
         <is>
-          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
+          <t>第9期計画の本文（サービス別見込量の表を含む全体）</t>
         </is>
       </c>
       <c r="D36" s="34" t="inlineStr">
         <is>
-          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
+          <t>★★用途が2つある。①対計画比（サービス別の計画値と実績の対比）。他案件では総額が計画どおりでも内訳が11.5〜967.4％まで開くことが確認されており、本村は受給率を3か年平均で固定しているため偏りを持ち越す。②老人福祉事業の量の目標の記載位置の確認（doc32§4-1）。保有しているのは概要版のみでサービス別見込量がない。</t>
         </is>
       </c>
       <c r="E36" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-53,Ⅱ-55</t>
         </is>
       </c>
       <c r="F36" s="35" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61</t>
+          <t>doc33§5-2</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="C37" s="34" t="inlineStr">
         <is>
-          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
+          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D37" s="34" t="inlineStr">
         <is>
-          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
+          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61b</t>
+          <t>doc20§8-2 K-61</t>
         </is>
       </c>
       <c r="G37" s="35" t="inlineStr">
@@ -8470,22 +8470,22 @@
       </c>
       <c r="C38" s="34" t="inlineStr">
         <is>
-          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
+          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D38" s="34" t="inlineStr">
         <is>
-          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
+          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
         </is>
       </c>
       <c r="E38" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F38" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-62</t>
+          <t>doc20§8-2 K-61b</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="C39" s="34" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
+          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
         </is>
       </c>
       <c r="D39" s="34" t="inlineStr">
         <is>
-          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
+          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-63</t>
+          <t>doc20§6-2 K-62</t>
         </is>
       </c>
       <c r="G39" s="35" t="inlineStr">
@@ -8546,22 +8546,22 @@
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
+          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
+          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F40" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-64</t>
+          <t>doc20§6-2 K-63</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -8584,22 +8584,22 @@
       </c>
       <c r="C41" s="34" t="inlineStr">
         <is>
-          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
+          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
         </is>
       </c>
       <c r="D41" s="34" t="inlineStr">
         <is>
-          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
+          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-75</t>
+          <t>doc20§6-2 K-64</t>
         </is>
       </c>
       <c r="G41" s="35" t="inlineStr">
@@ -8622,22 +8622,22 @@
       </c>
       <c r="C42" s="34" t="inlineStr">
         <is>
-          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
+          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
         </is>
       </c>
       <c r="D42" s="34" t="inlineStr">
         <is>
-          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
+          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
         </is>
       </c>
       <c r="E42" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-37</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F42" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-87</t>
+          <t>doc22 K-75</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -8660,22 +8660,22 @@
       </c>
       <c r="C43" s="34" t="inlineStr">
         <is>
-          <t>★会津権利擁護・成年後見センターへの相談が1年で件数−43%・時間−55%と減少した要因</t>
+          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
         </is>
       </c>
       <c r="D43" s="34" t="inlineStr">
         <is>
-          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
+          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-37</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>doc28§3-3 K-108</t>
+          <t>doc24§12 K-87</t>
         </is>
       </c>
       <c r="G43" s="35" t="inlineStr">
@@ -8693,27 +8693,27 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>★会津権利擁護・成年後見センターへの相談が1年で件数−43%・時間−55%と減少した要因</t>
         </is>
       </c>
       <c r="D44" s="34" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
         </is>
       </c>
       <c r="E44" s="35" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F44" s="35" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc28§3-3 K-108</t>
         </is>
       </c>
       <c r="G44" s="35" t="inlineStr">
@@ -8736,22 +8736,22 @@
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D45" s="34" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
@@ -8774,22 +8774,22 @@
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D46" s="34" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E46" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F46" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -8812,12 +8812,12 @@
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-89</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -8850,22 +8850,22 @@
       </c>
       <c r="C48" s="34" t="inlineStr">
         <is>
-          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D48" s="34" t="inlineStr">
         <is>
-          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
         </is>
       </c>
       <c r="E48" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F48" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-97</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -8883,27 +8883,27 @@
       </c>
       <c r="B49" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-50</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc26§10 K-97</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -8926,22 +8926,22 @@
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅰ-50</t>
         </is>
       </c>
       <c r="F50" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -8964,22 +8964,22 @@
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-46</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>doc25§4-2 K-91</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -8997,27 +8997,27 @@
       </c>
       <c r="B52" s="33" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C52" s="34" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
         </is>
       </c>
       <c r="D52" s="34" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
         </is>
       </c>
       <c r="E52" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅰ-46</t>
         </is>
       </c>
       <c r="F52" s="35" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc25§4-2 K-91</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -9035,27 +9035,27 @@
       </c>
       <c r="B53" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D53" s="34" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -9078,22 +9078,22 @@
       </c>
       <c r="C54" s="34" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D54" s="34" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E54" s="35" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F54" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -9111,27 +9111,27 @@
       </c>
       <c r="B55" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C55" s="34" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の対象が118人（想定150人）であることへの集計設計の対応</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D55" s="34" t="inlineStr">
         <is>
-          <t>★回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかの判断が要る。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Ⅲ-72,Ⅲ-73</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>doc34§5-2</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -9154,22 +9154,22 @@
       </c>
       <c r="C56" s="34" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
+          <t>在宅介護実態調査の対象が118人（想定150人）であることへの集計設計の対応</t>
         </is>
       </c>
       <c r="D56" s="34" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
+          <t>★回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかの判断が要る。</t>
         </is>
       </c>
       <c r="E56" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅲ-72,Ⅲ-73</t>
         </is>
       </c>
       <c r="F56" s="35" t="inlineStr">
         <is>
-          <t>doc33§3-5</t>
+          <t>doc34§5-2</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -9192,22 +9192,22 @@
       </c>
       <c r="C57" s="34" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
         </is>
       </c>
       <c r="D57" s="34" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc33§3-5</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
@@ -9230,22 +9230,22 @@
       </c>
       <c r="C58" s="34" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D58" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E58" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F58" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -9268,22 +9268,22 @@
       </c>
       <c r="C59" s="34" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D59" s="34" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G59" s="35" t="inlineStr">
@@ -9306,22 +9306,22 @@
       </c>
       <c r="C60" s="34" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D60" s="34" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E60" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F60" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-99</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G60" s="35" t="inlineStr">
@@ -9344,22 +9344,22 @@
       </c>
       <c r="C61" s="34" t="inlineStr">
         <is>
-          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D61" s="34" t="inlineStr">
         <is>
-          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>doc28§1-2 K-107</t>
+          <t>doc26§10 K-99</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -9377,27 +9377,27 @@
       </c>
       <c r="B62" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C62" s="34" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
         </is>
       </c>
       <c r="D62" s="34" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
         </is>
       </c>
       <c r="E62" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F62" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc28§1-2 K-107</t>
         </is>
       </c>
       <c r="G62" s="35" t="inlineStr">
@@ -9420,12 +9420,12 @@
       </c>
       <c r="C63" s="34" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D64" s="34" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E64" s="35" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="F64" s="35" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G64" s="35" t="inlineStr">
@@ -9491,32 +9491,32 @@
       </c>
       <c r="B65" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C65" s="34" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D65" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H65" s="34" t="inlineStr"/>
@@ -9534,27 +9534,27 @@
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
       <c r="D66" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
       <c r="E66" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
       <c r="F66" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H66" s="34" t="inlineStr"/>
@@ -9572,12 +9572,12 @@
       </c>
       <c r="C67" s="34" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
         </is>
       </c>
       <c r="D67" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc27§3-3</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
@@ -9610,22 +9610,22 @@
       </c>
       <c r="C68" s="34" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
         </is>
       </c>
       <c r="E68" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-09,Ⅰ-10</t>
         </is>
       </c>
       <c r="F68" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc27§5-2</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -9648,68 +9648,68 @@
       </c>
       <c r="C69" s="34" t="inlineStr">
         <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D69" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E69" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F69" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G69" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H69" s="34" t="inlineStr"/>
+    </row>
+    <row r="70" ht="34" customHeight="1">
+      <c r="A70" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B70" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C70" s="34" t="inlineStr">
+        <is>
           <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
-      <c r="D69" s="34" t="inlineStr">
+      <c r="D70" s="34" t="inlineStr">
         <is>
           <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
-      <c r="E69" s="35" t="inlineStr">
+      <c r="E70" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="F69" s="35" t="inlineStr">
+      <c r="F70" s="35" t="inlineStr">
         <is>
           <t>doc27§6</t>
         </is>
       </c>
-      <c r="G69" s="35" t="inlineStr">
+      <c r="G70" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H69" s="34" t="inlineStr"/>
-    </row>
-    <row r="70" ht="34" customHeight="1">
-      <c r="A70" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B70" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C70" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D70" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E70" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F70" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G70" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H70" s="25" t="inlineStr"/>
+      <c r="H70" s="34" t="inlineStr"/>
     </row>
     <row r="71" ht="34" customHeight="1">
       <c r="A71" s="37" t="inlineStr">
@@ -9724,22 +9724,22 @@
       </c>
       <c r="C71" s="25" t="inlineStr">
         <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-1,doc30§2-4</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
@@ -9762,22 +9762,22 @@
       </c>
       <c r="C72" s="25" t="inlineStr">
         <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
-          <t>doc02§16,§22</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr">
@@ -9800,27 +9800,27 @@
       </c>
       <c r="C73" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D73" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
         </is>
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F73" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H73" s="25" t="inlineStr"/>
@@ -9838,22 +9838,22 @@
       </c>
       <c r="C74" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
@@ -9876,22 +9876,22 @@
       </c>
       <c r="C75" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
@@ -9952,17 +9952,17 @@
       </c>
       <c r="C77" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
@@ -9990,12 +9990,12 @@
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
@@ -10028,22 +10028,22 @@
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -10066,22 +10066,22 @@
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
@@ -10104,22 +10104,22 @@
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
@@ -10180,22 +10180,22 @@
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10218,22 +10218,22 @@
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10294,22 +10294,22 @@
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -10332,17 +10332,17 @@
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
@@ -10370,17 +10370,17 @@
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10446,22 +10446,22 @@
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -10484,22 +10484,22 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -10560,22 +10560,22 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -10598,22 +10598,22 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -10636,22 +10636,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -10669,27 +10669,27 @@
       </c>
       <c r="B96" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -10712,22 +10712,22 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -10750,22 +10750,22 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -10783,27 +10783,27 @@
       </c>
       <c r="B99" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -10826,22 +10826,22 @@
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -10864,22 +10864,22 @@
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -10897,27 +10897,27 @@
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -10940,22 +10940,22 @@
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -10978,22 +10978,22 @@
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11016,22 +11016,22 @@
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -11054,22 +11054,22 @@
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -11092,22 +11092,22 @@
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -11130,22 +11130,22 @@
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -11168,22 +11168,22 @@
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -11206,22 +11206,22 @@
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -11244,22 +11244,22 @@
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -11282,22 +11282,22 @@
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -11320,22 +11320,22 @@
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -11358,22 +11358,22 @@
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -11391,27 +11391,27 @@
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -11429,27 +11429,27 @@
       </c>
       <c r="B116" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -11472,22 +11472,22 @@
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -11510,22 +11510,22 @@
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -11548,22 +11548,22 @@
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -11581,27 +11581,27 @@
       </c>
       <c r="B120" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -11619,27 +11619,27 @@
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -11657,27 +11657,27 @@
       </c>
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>第1号被保険者数の推計に2系列が併存している（社内）</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>★素案5-2（令和9〜11年度末1,002／997／990人）とestimate_premium.pyの前提（1,004／995／987人）が一致しない。3か年計で3人差、保険料基準額で月額約7円。年度末か年度平均かの定義の違いとみられる。保険料の確定計算の前に社内で統一する。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc35§8</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -11738,22 +11738,22 @@
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -11776,22 +11776,22 @@
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -11809,27 +11809,27 @@
       </c>
       <c r="B126" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -11847,27 +11847,27 @@
       </c>
       <c r="B127" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -11885,27 +11885,27 @@
       </c>
       <c r="B128" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -11928,12 +11928,12 @@
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -11961,27 +11961,27 @@
       </c>
       <c r="B130" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -11999,27 +11999,27 @@
       </c>
       <c r="B131" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12037,27 +12037,27 @@
       </c>
       <c r="B132" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -12080,22 +12080,22 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-31</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc19 追-6</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -12118,227 +12118,227 @@
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D134" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E134" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F134" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G134" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H134" s="25" t="inlineStr"/>
+    </row>
+    <row r="135" ht="34" customHeight="1">
+      <c r="A135" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B135" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C135" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D135" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E135" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F135" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G135" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H135" s="25" t="inlineStr"/>
+    </row>
+    <row r="136" ht="34" customHeight="1">
+      <c r="A136" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B136" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C136" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D136" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E136" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F136" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G136" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H136" s="25" t="inlineStr"/>
+    </row>
+    <row r="137" ht="34" customHeight="1">
+      <c r="A137" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B137" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C137" s="25" t="inlineStr">
+        <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D134" s="25" t="inlineStr">
+      <c r="D137" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E134" s="23" t="inlineStr">
+      <c r="E137" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F134" s="23" t="inlineStr">
+      <c r="F137" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G134" s="23" t="inlineStr">
+      <c r="G137" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H134" s="25" t="inlineStr"/>
-    </row>
-    <row r="135" ht="34" customHeight="1">
-      <c r="A135" s="38" t="inlineStr">
+      <c r="H137" s="25" t="inlineStr"/>
+    </row>
+    <row r="138" ht="34" customHeight="1">
+      <c r="A138" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B135" s="24" t="inlineStr">
+      <c r="B138" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C135" s="25" t="inlineStr">
+      <c r="C138" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D135" s="25" t="inlineStr">
+      <c r="D138" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E135" s="23" t="inlineStr">
+      <c r="E138" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F135" s="23" t="inlineStr">
+      <c r="F138" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G135" s="23" t="inlineStr">
+      <c r="G138" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H135" s="25" t="inlineStr"/>
-    </row>
-    <row r="136" ht="34" customHeight="1">
-      <c r="A136" s="38" t="inlineStr">
+      <c r="H138" s="25" t="inlineStr"/>
+    </row>
+    <row r="139" ht="34" customHeight="1">
+      <c r="A139" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B136" s="24" t="inlineStr">
+      <c r="B139" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C136" s="25" t="inlineStr">
+      <c r="C139" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D136" s="25" t="inlineStr">
+      <c r="D139" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E136" s="23" t="inlineStr">
+      <c r="E139" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F136" s="23" t="inlineStr">
+      <c r="F139" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G136" s="23" t="inlineStr">
+      <c r="G139" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H136" s="25" t="inlineStr"/>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="39" t="inlineStr">
+      <c r="H139" s="25" t="inlineStr"/>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="139" ht="34" customHeight="1">
-      <c r="A139" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B139" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C139" s="42" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D139" s="42" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E139" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F139" s="40" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G139" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H139" s="42" t="inlineStr"/>
-    </row>
-    <row r="140" ht="34" customHeight="1">
-      <c r="A140" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B140" s="41" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C140" s="42" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D140" s="42" t="inlineStr">
-        <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
-        </is>
-      </c>
-      <c r="E140" s="40" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F140" s="40" t="inlineStr">
-        <is>
-          <t>doc28§4</t>
-        </is>
-      </c>
-      <c r="G140" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H140" s="42" t="inlineStr"/>
-    </row>
-    <row r="141" ht="34" customHeight="1">
-      <c r="A141" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B141" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C141" s="42" t="inlineStr">
-        <is>
-          <t>所得段階別の第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D141" s="42" t="inlineStr">
-        <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
-        </is>
-      </c>
-      <c r="E141" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F141" s="40" t="inlineStr">
-        <is>
-          <t>doc28§2</t>
-        </is>
-      </c>
-      <c r="G141" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H141" s="42" t="inlineStr"/>
     </row>
     <row r="142" ht="34" customHeight="1">
       <c r="A142" s="40" t="inlineStr">
@@ -12353,22 +12353,22 @@
       </c>
       <c r="C142" s="42" t="inlineStr">
         <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D142" s="42" t="inlineStr">
         <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E142" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F142" s="40" t="inlineStr">
         <is>
-          <t>doc28§1</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G142" s="40" t="inlineStr">
@@ -12386,32 +12386,32 @@
       </c>
       <c r="B143" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C143" s="42" t="inlineStr">
         <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D143" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E143" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F143" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-1</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G143" s="40" t="inlineStr">
         <is>
-          <t>解決済（一部再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H143" s="42" t="inlineStr"/>
@@ -12424,27 +12424,27 @@
       </c>
       <c r="B144" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C144" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D144" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E144" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F144" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G144" s="40" t="inlineStr">
@@ -12462,32 +12462,32 @@
       </c>
       <c r="B145" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C145" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D145" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E145" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F145" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G145" s="40" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H145" s="42" t="inlineStr"/>
@@ -12505,27 +12505,27 @@
       </c>
       <c r="C146" s="42" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D146" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E146" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F146" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G146" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H146" s="42" t="inlineStr"/>
@@ -12543,22 +12543,22 @@
       </c>
       <c r="C147" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D147" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E147" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F147" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G147" s="40" t="inlineStr">
@@ -12581,27 +12581,27 @@
       </c>
       <c r="C148" s="42" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D148" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E148" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F148" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G148" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H148" s="42" t="inlineStr"/>
@@ -12614,22 +12614,22 @@
       </c>
       <c r="B149" s="41" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C149" s="42" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D149" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E149" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F149" s="40" t="inlineStr">
@@ -12652,27 +12652,27 @@
       </c>
       <c r="B150" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C150" s="42" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D150" s="42" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E150" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F150" s="40" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G150" s="40" t="inlineStr">
@@ -12690,27 +12690,27 @@
       </c>
       <c r="B151" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C151" s="42" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D151" s="42" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E151" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F151" s="40" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G151" s="40" t="inlineStr">
@@ -12728,27 +12728,27 @@
       </c>
       <c r="B152" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C152" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D152" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E152" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F152" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G152" s="40" t="inlineStr">
@@ -12771,22 +12771,22 @@
       </c>
       <c r="C153" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D153" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E153" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F153" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G153" s="40" t="inlineStr">
@@ -12809,22 +12809,22 @@
       </c>
       <c r="C154" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>交付要綱の配点表（満点）</t>
         </is>
       </c>
       <c r="D154" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
         </is>
       </c>
       <c r="E154" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F154" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc20§2</t>
         </is>
       </c>
       <c r="G154" s="40" t="inlineStr">
@@ -12847,43 +12847,157 @@
       </c>
       <c r="C155" s="42" t="inlineStr">
         <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D155" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E155" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F155" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G155" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H155" s="42" t="inlineStr"/>
+    </row>
+    <row r="156" ht="34" customHeight="1">
+      <c r="A156" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B156" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C156" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D156" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E156" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F156" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G156" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H156" s="42" t="inlineStr"/>
+    </row>
+    <row r="157" ht="34" customHeight="1">
+      <c r="A157" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B157" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C157" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D157" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E157" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F157" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G157" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H157" s="42" t="inlineStr"/>
+    </row>
+    <row r="158" ht="34" customHeight="1">
+      <c r="A158" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B158" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C158" s="42" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D155" s="42" t="inlineStr">
+      <c r="D158" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E155" s="40" t="inlineStr">
+      <c r="E158" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F155" s="40" t="inlineStr">
+      <c r="F158" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G155" s="40" t="inlineStr">
+      <c r="G158" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H155" s="42" t="inlineStr"/>
+      <c r="H158" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H136"/>
+  <autoFilter ref="A4:H139"/>
   <mergeCells count="3">
+    <mergeCell ref="A141:H141"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A138:H138"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G136" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13533,34 +13647,34 @@
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>★通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止</t>
-        </is>
-      </c>
-      <c r="D24" s="35" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>見える化は令和2年度で更新停止。令和6年度分のみ受領</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E24" s="34" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F24" s="35" t="inlineStr">
-        <is>
-          <t>未受領</t>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>一部受領</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は保険料（5-7）、地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。★9/15：見込量算定の第1次概算を反映（doc35）。あわせて素案の記述を令和8年度の交付金評価指標で検算し、複数の訂正を行った。(1)中長期の保険料を算定し5-11の【要確認】を解消（αを23%据え置くと令和22年度6,883円、3年ごとに1ポイント上がると8,379円）。(2)標準給付費の様式を埋め5-6を確定（3か年854,014千円）。5-7と完全に一致。(3)交付金の評価指標を令和8年度で検算したところ、素案の記述の多くが令和6年度または令和4年度の評価に基づいており実態と食い違っていた。通いの場への参加率は0→8点満点（最上位の段階は全国で約10%）、参加促進のアウトリーチは9点満点、地域リハビリテーションの推進は0→7点満点、計画の進捗管理（目標Ⅰの3項目）は0→48点満点。一方、要介護3〜5の状態の変化は2指標とも0点（35点減）、認知症サポーター数は12点中0点、難聴は20点中0点。施策1-1を「通いの場の再構築と参加率の向上」から「通いの場の開催頻度の向上と地区差の是正」に改称し、課題3の見出しも改めた。(4)6-3の成果目標・活動指標に令和8年度の得点と全国平均を併記し、維持6指標・引上げ5指標に整理。(5)認知症基本法13条1項・成年後見促進法14条1項を確認し1-2の【要確認】を解消。素案は2,197行→2,341行。</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8731,27 +8731,27 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
         </is>
       </c>
       <c r="D45" s="34" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
@@ -8769,27 +8769,27 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
         </is>
       </c>
       <c r="D46" s="34" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
         </is>
       </c>
       <c r="E46" s="35" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F46" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -8812,22 +8812,22 @@
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -8850,22 +8850,22 @@
       </c>
       <c r="C48" s="34" t="inlineStr">
         <is>
-          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D48" s="34" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E48" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F48" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-89</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -8888,22 +8888,22 @@
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-97</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -8921,27 +8921,27 @@
       </c>
       <c r="B50" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-50</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F50" s="35" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -8959,27 +8959,27 @@
       </c>
       <c r="B51" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc26§10 K-97</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -9002,22 +9002,22 @@
       </c>
       <c r="C52" s="34" t="inlineStr">
         <is>
-          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D52" s="34" t="inlineStr">
         <is>
-          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E52" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-46</t>
+          <t>Ⅰ-50</t>
         </is>
       </c>
       <c r="F52" s="35" t="inlineStr">
         <is>
-          <t>doc25§4-2 K-91</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -9035,27 +9035,27 @@
       </c>
       <c r="B53" s="33" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D53" s="34" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -9073,27 +9073,27 @@
       </c>
       <c r="B54" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C54" s="34" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
         </is>
       </c>
       <c r="D54" s="34" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
         </is>
       </c>
       <c r="E54" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅰ-46</t>
         </is>
       </c>
       <c r="F54" s="35" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc25§4-2 K-91</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -9111,27 +9111,27 @@
       </c>
       <c r="B55" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C55" s="34" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
         </is>
       </c>
       <c r="D55" s="34" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-70,Ⅱ-71</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -9149,27 +9149,27 @@
       </c>
       <c r="B56" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C56" s="34" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の対象が118人（想定150人）であることへの集計設計の対応</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D56" s="34" t="inlineStr">
         <is>
-          <t>★回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかの判断が要る。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E56" s="35" t="inlineStr">
         <is>
-          <t>Ⅲ-72,Ⅲ-73</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F56" s="35" t="inlineStr">
         <is>
-          <t>doc34§5-2</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -9187,27 +9187,27 @@
       </c>
       <c r="B57" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C57" s="34" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D57" s="34" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>doc33§3-5</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
@@ -9225,27 +9225,27 @@
       </c>
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C58" s="34" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D58" s="34" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E58" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F58" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -9268,22 +9268,22 @@
       </c>
       <c r="C59" s="34" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>在宅介護実態調査の対象が118人（想定150人）であることへの集計設計の対応</t>
         </is>
       </c>
       <c r="D59" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかの判断が要る。</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅲ-72,Ⅲ-73</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc34§5-2</t>
         </is>
       </c>
       <c r="G59" s="35" t="inlineStr">
@@ -9306,22 +9306,22 @@
       </c>
       <c r="C60" s="34" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
         </is>
       </c>
       <c r="D60" s="34" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
         </is>
       </c>
       <c r="E60" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F60" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc33§3-5</t>
         </is>
       </c>
       <c r="G60" s="35" t="inlineStr">
@@ -9344,22 +9344,22 @@
       </c>
       <c r="C61" s="34" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D61" s="34" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-99</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -9382,22 +9382,22 @@
       </c>
       <c r="C62" s="34" t="inlineStr">
         <is>
-          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D62" s="34" t="inlineStr">
         <is>
-          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E62" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F62" s="35" t="inlineStr">
         <is>
-          <t>doc28§1-2 K-107</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G62" s="35" t="inlineStr">
@@ -9415,27 +9415,27 @@
       </c>
       <c r="B63" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C63" s="34" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -9453,27 +9453,27 @@
       </c>
       <c r="B64" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D64" s="34" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
         </is>
       </c>
       <c r="E64" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F64" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc26§10 K-99</t>
         </is>
       </c>
       <c r="G64" s="35" t="inlineStr">
@@ -9491,27 +9491,27 @@
       </c>
       <c r="B65" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C65" s="34" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
         </is>
       </c>
       <c r="D65" s="34" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc28§1-2 K-107</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
@@ -9529,32 +9529,32 @@
       </c>
       <c r="B66" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D66" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E66" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F66" s="35" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H66" s="34" t="inlineStr"/>
@@ -9567,27 +9567,27 @@
       </c>
       <c r="B67" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C67" s="34" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D67" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
@@ -9605,27 +9605,27 @@
       </c>
       <c r="B68" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C68" s="34" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E68" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F68" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -9648,27 +9648,27 @@
       </c>
       <c r="C69" s="34" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
       <c r="D69" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H69" s="34" t="inlineStr"/>
@@ -9686,144 +9686,144 @@
       </c>
       <c r="C70" s="34" t="inlineStr">
         <is>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+        </is>
+      </c>
+      <c r="D70" s="34" t="inlineStr">
+        <is>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+        </is>
+      </c>
+      <c r="E70" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F70" s="35" t="inlineStr">
+        <is>
+          <t>doc27§3-3</t>
+        </is>
+      </c>
+      <c r="G70" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr"/>
+    </row>
+    <row r="71" ht="34" customHeight="1">
+      <c r="A71" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B71" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C71" s="34" t="inlineStr">
+        <is>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+        </is>
+      </c>
+      <c r="D71" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+        </is>
+      </c>
+      <c r="E71" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F71" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-2</t>
+        </is>
+      </c>
+      <c r="G71" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr"/>
+    </row>
+    <row r="72" ht="34" customHeight="1">
+      <c r="A72" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B72" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C72" s="34" t="inlineStr">
+        <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D72" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E72" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F72" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G72" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="inlineStr"/>
+    </row>
+    <row r="73" ht="34" customHeight="1">
+      <c r="A73" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B73" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C73" s="34" t="inlineStr">
+        <is>
           <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
-      <c r="D70" s="34" t="inlineStr">
+      <c r="D73" s="34" t="inlineStr">
         <is>
           <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
-      <c r="E70" s="35" t="inlineStr">
+      <c r="E73" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="F70" s="35" t="inlineStr">
+      <c r="F73" s="35" t="inlineStr">
         <is>
           <t>doc27§6</t>
         </is>
       </c>
-      <c r="G70" s="35" t="inlineStr">
+      <c r="G73" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H70" s="34" t="inlineStr"/>
-    </row>
-    <row r="71" ht="34" customHeight="1">
-      <c r="A71" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B71" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C71" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D71" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E71" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F71" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H71" s="25" t="inlineStr"/>
-    </row>
-    <row r="72" ht="34" customHeight="1">
-      <c r="A72" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B72" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C72" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D72" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
-        </is>
-      </c>
-      <c r="E72" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F72" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1,doc30§2-4</t>
-        </is>
-      </c>
-      <c r="G72" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H72" s="25" t="inlineStr"/>
-    </row>
-    <row r="73" ht="34" customHeight="1">
-      <c r="A73" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B73" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C73" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D73" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
-        </is>
-      </c>
-      <c r="E73" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F73" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G73" s="23" t="inlineStr">
-        <is>
-          <t>一部回答</t>
-        </is>
-      </c>
-      <c r="H73" s="25" t="inlineStr"/>
+      <c r="H73" s="34" t="inlineStr"/>
     </row>
     <row r="74" ht="34" customHeight="1">
       <c r="A74" s="37" t="inlineStr">
@@ -9838,22 +9838,22 @@
       </c>
       <c r="C74" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
@@ -9876,22 +9876,22 @@
       </c>
       <c r="C75" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -9914,27 +9914,27 @@
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H76" s="25" t="inlineStr"/>
@@ -9952,22 +9952,22 @@
       </c>
       <c r="C77" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
@@ -9990,22 +9990,22 @@
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F78" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
@@ -10028,22 +10028,22 @@
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -10066,22 +10066,22 @@
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
@@ -10104,22 +10104,22 @@
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10218,22 +10218,22 @@
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10256,22 +10256,22 @@
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -10332,12 +10332,12 @@
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -10370,22 +10370,22 @@
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -10408,22 +10408,22 @@
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -10484,22 +10484,22 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -10522,22 +10522,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -10560,22 +10560,22 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -10598,22 +10598,22 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -10636,22 +10636,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -10674,22 +10674,22 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -10707,27 +10707,27 @@
       </c>
       <c r="B97" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -10745,27 +10745,27 @@
       </c>
       <c r="B98" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -10783,27 +10783,27 @@
       </c>
       <c r="B99" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -10821,27 +10821,27 @@
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -10859,27 +10859,27 @@
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -10897,27 +10897,27 @@
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -10935,27 +10935,27 @@
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -10973,27 +10973,27 @@
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11011,27 +11011,27 @@
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -11049,27 +11049,27 @@
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -11092,22 +11092,22 @@
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -11130,22 +11130,22 @@
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -11168,22 +11168,22 @@
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -11206,22 +11206,22 @@
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -11244,22 +11244,22 @@
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -11282,22 +11282,22 @@
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -11320,22 +11320,22 @@
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -11358,22 +11358,22 @@
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -11396,22 +11396,22 @@
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -11434,22 +11434,22 @@
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -11467,27 +11467,27 @@
       </c>
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -11505,27 +11505,27 @@
       </c>
       <c r="B118" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -11543,27 +11543,27 @@
       </c>
       <c r="B119" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -11581,27 +11581,27 @@
       </c>
       <c r="B120" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -11619,27 +11619,27 @@
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -11662,22 +11662,22 @@
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計に2系列が併存している（社内）</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>★素案5-2（令和9〜11年度末1,002／997／990人）とestimate_premium.pyの前提（1,004／995／987人）が一致しない。3か年計で3人差、保険料基準額で月額約7円。年度末か年度平均かの定義の違いとみられる。保険料の確定計算の前に社内で統一する。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc35§8</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -11695,27 +11695,27 @@
       </c>
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -11733,27 +11733,27 @@
       </c>
       <c r="B124" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -11771,27 +11771,27 @@
       </c>
       <c r="B125" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -11809,27 +11809,27 @@
       </c>
       <c r="B126" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -11847,27 +11847,27 @@
       </c>
       <c r="B127" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>第1号被保険者数の推計に2系列が併存している（社内）</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>★素案5-2（令和9〜11年度末1,002／997／990人）とestimate_premium.pyの前提（1,004／995／987人）が一致しない。3か年計で3人差、保険料基準額で月額約7円。年度末か年度平均かの定義の違いとみられる。保険料の確定計算の前に社内で統一する。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc35§8</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -11890,22 +11890,22 @@
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -11923,27 +11923,27 @@
       </c>
       <c r="B129" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -11961,27 +11961,27 @@
       </c>
       <c r="B130" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -11999,27 +11999,27 @@
       </c>
       <c r="B131" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12037,27 +12037,27 @@
       </c>
       <c r="B132" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -12075,27 +12075,27 @@
       </c>
       <c r="B133" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -12113,27 +12113,27 @@
       </c>
       <c r="B134" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -12151,27 +12151,27 @@
       </c>
       <c r="B135" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -12189,27 +12189,27 @@
       </c>
       <c r="B136" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -12227,308 +12227,308 @@
       </c>
       <c r="B137" s="24" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C137" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D137" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E137" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F137" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G137" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H137" s="25" t="inlineStr"/>
+    </row>
+    <row r="138" ht="34" customHeight="1">
+      <c r="A138" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B138" s="24" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C137" s="25" t="inlineStr">
+      <c r="C138" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D138" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E138" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F138" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G138" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H138" s="25" t="inlineStr"/>
+    </row>
+    <row r="139" ht="34" customHeight="1">
+      <c r="A139" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B139" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C139" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D139" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E139" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F139" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G139" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H139" s="25" t="inlineStr"/>
+    </row>
+    <row r="140" ht="34" customHeight="1">
+      <c r="A140" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B140" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C140" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D140" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E140" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F140" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G140" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H140" s="25" t="inlineStr"/>
+    </row>
+    <row r="141" ht="34" customHeight="1">
+      <c r="A141" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B141" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C141" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D141" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E141" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F141" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G141" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H141" s="25" t="inlineStr"/>
+    </row>
+    <row r="142" ht="34" customHeight="1">
+      <c r="A142" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B142" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C142" s="25" t="inlineStr">
         <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D137" s="25" t="inlineStr">
+      <c r="D142" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E137" s="23" t="inlineStr">
+      <c r="E142" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F137" s="23" t="inlineStr">
+      <c r="F142" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G137" s="23" t="inlineStr">
+      <c r="G142" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H137" s="25" t="inlineStr"/>
-    </row>
-    <row r="138" ht="34" customHeight="1">
-      <c r="A138" s="38" t="inlineStr">
+      <c r="H142" s="25" t="inlineStr"/>
+    </row>
+    <row r="143" ht="34" customHeight="1">
+      <c r="A143" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B138" s="24" t="inlineStr">
+      <c r="B143" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C138" s="25" t="inlineStr">
+      <c r="C143" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D138" s="25" t="inlineStr">
+      <c r="D143" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E138" s="23" t="inlineStr">
+      <c r="E143" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F138" s="23" t="inlineStr">
+      <c r="F143" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G138" s="23" t="inlineStr">
+      <c r="G143" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H138" s="25" t="inlineStr"/>
-    </row>
-    <row r="139" ht="34" customHeight="1">
-      <c r="A139" s="38" t="inlineStr">
+      <c r="H143" s="25" t="inlineStr"/>
+    </row>
+    <row r="144" ht="34" customHeight="1">
+      <c r="A144" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B139" s="24" t="inlineStr">
+      <c r="B144" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C139" s="25" t="inlineStr">
+      <c r="C144" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D139" s="25" t="inlineStr">
+      <c r="D144" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E139" s="23" t="inlineStr">
+      <c r="E144" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F139" s="23" t="inlineStr">
+      <c r="F144" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G139" s="23" t="inlineStr">
+      <c r="G144" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H139" s="25" t="inlineStr"/>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="39" t="inlineStr">
+      <c r="H144" s="25" t="inlineStr"/>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="142" ht="34" customHeight="1">
-      <c r="A142" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B142" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C142" s="42" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D142" s="42" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E142" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F142" s="40" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G142" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H142" s="42" t="inlineStr"/>
-    </row>
-    <row r="143" ht="34" customHeight="1">
-      <c r="A143" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B143" s="41" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C143" s="42" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D143" s="42" t="inlineStr">
-        <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
-        </is>
-      </c>
-      <c r="E143" s="40" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F143" s="40" t="inlineStr">
-        <is>
-          <t>doc28§4</t>
-        </is>
-      </c>
-      <c r="G143" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H143" s="42" t="inlineStr"/>
-    </row>
-    <row r="144" ht="34" customHeight="1">
-      <c r="A144" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B144" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C144" s="42" t="inlineStr">
-        <is>
-          <t>所得段階別の第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D144" s="42" t="inlineStr">
-        <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
-        </is>
-      </c>
-      <c r="E144" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F144" s="40" t="inlineStr">
-        <is>
-          <t>doc28§2</t>
-        </is>
-      </c>
-      <c r="G144" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H144" s="42" t="inlineStr"/>
-    </row>
-    <row r="145" ht="34" customHeight="1">
-      <c r="A145" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B145" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C145" s="42" t="inlineStr">
-        <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
-        </is>
-      </c>
-      <c r="D145" s="42" t="inlineStr">
-        <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
-        </is>
-      </c>
-      <c r="E145" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-59</t>
-        </is>
-      </c>
-      <c r="F145" s="40" t="inlineStr">
-        <is>
-          <t>doc28§1</t>
-        </is>
-      </c>
-      <c r="G145" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H145" s="42" t="inlineStr"/>
-    </row>
-    <row r="146" ht="34" customHeight="1">
-      <c r="A146" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B146" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C146" s="42" t="inlineStr">
-        <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
-        </is>
-      </c>
-      <c r="D146" s="42" t="inlineStr">
-        <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
-        </is>
-      </c>
-      <c r="E146" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-09</t>
-        </is>
-      </c>
-      <c r="F146" s="40" t="inlineStr">
-        <is>
-          <t>doc27§1-1</t>
-        </is>
-      </c>
-      <c r="G146" s="40" t="inlineStr">
-        <is>
-          <t>解決済（一部再掲）</t>
-        </is>
-      </c>
-      <c r="H146" s="42" t="inlineStr"/>
     </row>
     <row r="147" ht="34" customHeight="1">
       <c r="A147" s="40" t="inlineStr">
@@ -12538,27 +12538,27 @@
       </c>
       <c r="B147" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C147" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D147" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E147" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F147" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G147" s="40" t="inlineStr">
@@ -12576,32 +12576,32 @@
       </c>
       <c r="B148" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C148" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D148" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E148" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F148" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G148" s="40" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H148" s="42" t="inlineStr"/>
@@ -12614,27 +12614,27 @@
       </c>
       <c r="B149" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C149" s="42" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D149" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E149" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F149" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G149" s="40" t="inlineStr">
@@ -12652,27 +12652,27 @@
       </c>
       <c r="B150" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C150" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D150" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E150" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F150" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G150" s="40" t="inlineStr">
@@ -12695,27 +12695,27 @@
       </c>
       <c r="C151" s="42" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D151" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E151" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F151" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G151" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H151" s="42" t="inlineStr"/>
@@ -12728,27 +12728,27 @@
       </c>
       <c r="B152" s="41" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C152" s="42" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D152" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E152" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F152" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G152" s="40" t="inlineStr">
@@ -12766,32 +12766,32 @@
       </c>
       <c r="B153" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C153" s="42" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D153" s="42" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E153" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F153" s="40" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G153" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H153" s="42" t="inlineStr"/>
@@ -12804,27 +12804,27 @@
       </c>
       <c r="B154" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C154" s="42" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D154" s="42" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E154" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F154" s="40" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G154" s="40" t="inlineStr">
@@ -12842,27 +12842,27 @@
       </c>
       <c r="B155" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C155" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D155" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E155" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F155" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G155" s="40" t="inlineStr">
@@ -12880,27 +12880,27 @@
       </c>
       <c r="B156" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C156" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D156" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E156" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F156" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G156" s="40" t="inlineStr">
@@ -12918,27 +12918,27 @@
       </c>
       <c r="B157" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C157" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D157" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E157" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F157" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G157" s="40" t="inlineStr">
@@ -12961,43 +12961,233 @@
       </c>
       <c r="C158" s="42" t="inlineStr">
         <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D158" s="42" t="inlineStr">
+        <is>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+        </is>
+      </c>
+      <c r="E158" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F158" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3,§4</t>
+        </is>
+      </c>
+      <c r="G158" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H158" s="42" t="inlineStr"/>
+    </row>
+    <row r="159" ht="34" customHeight="1">
+      <c r="A159" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B159" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C159" s="42" t="inlineStr">
+        <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D159" s="42" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E159" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F159" s="40" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G159" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H159" s="42" t="inlineStr"/>
+    </row>
+    <row r="160" ht="34" customHeight="1">
+      <c r="A160" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B160" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C160" s="42" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D160" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E160" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F160" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G160" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H160" s="42" t="inlineStr"/>
+    </row>
+    <row r="161" ht="34" customHeight="1">
+      <c r="A161" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B161" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C161" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D161" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E161" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F161" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G161" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H161" s="42" t="inlineStr"/>
+    </row>
+    <row r="162" ht="34" customHeight="1">
+      <c r="A162" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B162" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C162" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D162" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E162" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F162" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G162" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H162" s="42" t="inlineStr"/>
+    </row>
+    <row r="163" ht="34" customHeight="1">
+      <c r="A163" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B163" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C163" s="42" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D158" s="42" t="inlineStr">
+      <c r="D163" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E158" s="40" t="inlineStr">
+      <c r="E163" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F158" s="40" t="inlineStr">
+      <c r="F163" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G158" s="40" t="inlineStr">
+      <c r="G163" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H158" s="42" t="inlineStr"/>
+      <c r="H163" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H139"/>
+  <autoFilter ref="A4:H144"/>
   <mergeCells count="3">
-    <mergeCell ref="A141:H141"/>
+    <mergeCell ref="A146:H146"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="M65" s="14" t="n"/>
       <c r="N65" s="15" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="O65" s="16" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="P65" s="13" t="inlineStr">
         <is>
-          <t>★9/8：doc30として推計の枠組みを確定。「見える化」システムのデータ定義（受給者数＝年度延べ、D45系の分母＝要介護度別認定者数）を検算のうえ確定し、estimate_services.py により区分別・サービス種類別の見込量を算定。全28サービスのうち令和7年度に実績のある16サービスについて受給者数・利用量・給付費の暫定値を doc18 第5章5-4に投入。施設・居住系の種類別人数は見える化に系列がなく給付費比の按分値のため、村の月報（第2表・第3表）で置き換えが必要。介護給付と予防給付の分離も同じく月報待ち。★9/12：他案件（川崎町・金ケ崎町・大雪）の到達水準と対照し（doc33）、基準年度を令和7年度と確定。見える化の系列別の月数を実測で確認し（D1はR7が11か月、D2/D3/D4は12か月相当）doc30の÷12が正しいことを裏付けて素案5-4に明記。令和9年4月新設4区分の枠と、国の推計ツールのワーニング判定式（閾値＝Q1−2Q〜Q3+2Q）による自己点検の手順を追加。国の推計ツールの出力は未受領で、依頼書18-2として最優先で追加した。★9/15：他案件（大雪・川崎・金ケ崎）の算定の進め方を確認し、本村に適用して第1次概算を実施（doc35）。(1)見込量は需要で置く／地域密着型と総合事業のみ村の供給力が上限、という原則を素案5-4に明記。(2)令和9年4月新設4区分を「―」「要協議」から0に立て直した。(3)夜間対応型訪問介護の令和9年3月末廃止を反映。(4)単価の趨勢を連鎖ラスパイレス指数で実測（R元→R7の年率+1.30%）。3か年平均で固定していることは給付費の5.32%過小＝保険料月額314円に当たる。(5)サービス別の受給者数の年率が▲13.12〜+54.88%と68ポイント開いていることを実測し、伸びをどこまで反映すべきかをバックテストで検証（backtest_growth.py）。φ=0.5・c=5%が最小（WMAPE19.11%）だが一律19.68%に対し改善は2.9%にとどまるため一律を採用すると決定。(6)一律の方法で3年先を予測したときの誤差は絶対値平均11.9%＝保険料月額約700円で、基金取崩24,000千円の効き（702円）と同規模。素案5-4(9)として新設。(7)在宅介護実態調査の施設入所申込みの反映シナリオの枠を素案5-4(3)に新設（+1人／月＝月額75円）。残るのは国の推計ワークシートによる基準年度の置き直しの分解のみ。</t>
+          <t>★9/8：doc30として推計の枠組みを確定。「見える化」システムのデータ定義（受給者数＝年度延べ、D45系の分母＝要介護度別認定者数）を検算のうえ確定し、estimate_services.py により区分別・サービス種類別の見込量を算定。全28サービスのうち令和7年度に実績のある16サービスについて受給者数・利用量・給付費の暫定値を doc18 第5章5-4に投入。施設・居住系の種類別人数は見える化に系列がなく給付費比の按分値のため、村の月報（第2表・第3表）で置き換えが必要。介護給付と予防給付の分離も同じく月報待ち。★9/12：他案件（川崎町・金ケ崎町・大雪）の到達水準と対照し（doc33）、基準年度を令和7年度と確定。見える化の系列別の月数を実測で確認し（D1はR7が11か月、D2/D3/D4は12か月相当）doc30の÷12が正しいことを裏付けて素案5-4に明記。令和9年4月新設4区分の枠と、国の推計ツールのワーニング判定式（閾値＝Q1−2Q〜Q3+2Q）による自己点検の手順を追加。国の推計ツールの出力は未受領で、依頼書18-2として最優先で追加した。★9/15：他案件（大雪・川崎・金ケ崎）の算定の進め方を確認し、本村に適用して第1次概算を実施（doc35）。(1)見込量は需要で置く／地域密着型と総合事業のみ村の供給力が上限、という原則を素案5-4に明記。(2)令和9年4月新設4区分を「―」「要協議」から0に立て直した。(3)夜間対応型訪問介護の令和9年3月末廃止を反映。(4)単価の趨勢を連鎖ラスパイレス指数で実測（R元→R7の年率+1.30%）。3か年平均で固定していることは給付費の5.32%過小＝保険料月額314円に当たる。(5)サービス別の受給者数の年率が▲13.12〜+54.88%と68ポイント開いていることを実測し、伸びをどこまで反映すべきかをバックテストで検証（backtest_growth.py）。φ=0.5・c=5%が最小（WMAPE19.11%）だが一律19.68%に対し改善は2.9%にとどまるため一律を採用すると決定。(6)一律の方法で3年先を予測したときの誤差は絶対値平均11.9%＝保険料月額約700円で、基金取崩24,000千円の効き（702円）と同規模。素案5-4(9)として新設。(7)在宅介護実態調査の施設入所申込みの反映シナリオの枠を素案5-4(3)に新設（+1人／月＝月額75円）。残るのは国の推計ワークシートによる基準年度の置き直しの分解のみ。★9/15（第3次）：推計の系列を統一し、給付費を分離した（doc35§7-3）。(1)素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し5-1・5-2・5-3を全面改訂。5-1に①第1号被保険者数→②認定者数→③受給者数→④利用量→⑤給付費→⑥標準給付費→⑦保険料の連なりを表で明示した。(2)決算（D48-b）の介護サービス等諸費／介護予防サービス等諸費と要介護度別受給者数を突き合わせ、予防給付19,002円・介護給付175,230円の1人あたり給付月額を復元（令和3〜5年度で±1.6%以内の安定）。第10期3か年で介護給付費755,119千円・予防給付費34,344千円に分離し、5-6の空欄を埋めた。(3)見込量の自己点検を実施（check_warning.py）。年度間の変化率は3区分とも4%以内。令和7年度実績→令和9年度見込で±10%超は4件（居宅療養管理指導▲25.3%、短期入所生活介護▲20.8%、訪問入浴介護・地域密着型通所介護は新規計上）。いずれも3か年平均で置くことの副作用であり委員会にお諮りする。(4)地域支援事業費を新系列で置き直し3か年122,737千円（保険料月額+22円）。</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="M66" s="14" t="n"/>
       <c r="N66" s="15" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O66" s="16" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9529,27 +9529,27 @@
       </c>
       <c r="B66" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
         </is>
       </c>
       <c r="D66" s="34" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
         </is>
       </c>
       <c r="E66" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F66" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="C67" s="34" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D67" s="34" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="C68" s="34" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E68" s="35" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="F68" s="35" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -9643,32 +9643,32 @@
       </c>
       <c r="B69" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C69" s="34" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D69" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H69" s="34" t="inlineStr"/>
@@ -9686,27 +9686,27 @@
       </c>
       <c r="C70" s="34" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
       <c r="E70" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
       <c r="F70" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G70" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H70" s="34" t="inlineStr"/>
@@ -9724,12 +9724,12 @@
       </c>
       <c r="C71" s="34" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
         </is>
       </c>
       <c r="D71" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc27§3-3</t>
         </is>
       </c>
       <c r="G71" s="35" t="inlineStr">
@@ -9762,22 +9762,22 @@
       </c>
       <c r="C72" s="34" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
         </is>
       </c>
       <c r="D72" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
         </is>
       </c>
       <c r="E72" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-09,Ⅰ-10</t>
         </is>
       </c>
       <c r="F72" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc27§5-2</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -9800,68 +9800,68 @@
       </c>
       <c r="C73" s="34" t="inlineStr">
         <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D73" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E73" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F73" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G73" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr"/>
+    </row>
+    <row r="74" ht="34" customHeight="1">
+      <c r="A74" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B74" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C74" s="34" t="inlineStr">
+        <is>
           <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
-      <c r="D73" s="34" t="inlineStr">
+      <c r="D74" s="34" t="inlineStr">
         <is>
           <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
-      <c r="E73" s="35" t="inlineStr">
+      <c r="E74" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="F73" s="35" t="inlineStr">
+      <c r="F74" s="35" t="inlineStr">
         <is>
           <t>doc27§6</t>
         </is>
       </c>
-      <c r="G73" s="35" t="inlineStr">
+      <c r="G74" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H73" s="34" t="inlineStr"/>
-    </row>
-    <row r="74" ht="34" customHeight="1">
-      <c r="A74" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B74" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C74" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D74" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E74" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F74" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G74" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H74" s="25" t="inlineStr"/>
+      <c r="H74" s="34" t="inlineStr"/>
     </row>
     <row r="75" ht="34" customHeight="1">
       <c r="A75" s="37" t="inlineStr">
@@ -9876,22 +9876,22 @@
       </c>
       <c r="C75" s="25" t="inlineStr">
         <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F75" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-1,doc30§2-4</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
@@ -9914,27 +9914,27 @@
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F76" s="23" t="inlineStr">
         <is>
-          <t>doc02§16,§22</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H76" s="25" t="inlineStr"/>
@@ -9952,27 +9952,27 @@
       </c>
       <c r="C77" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F77" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H77" s="25" t="inlineStr"/>
@@ -9990,22 +9990,22 @@
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F78" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
@@ -10028,22 +10028,22 @@
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
@@ -10104,17 +10104,17 @@
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
@@ -10180,22 +10180,22 @@
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10218,22 +10218,22 @@
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10256,22 +10256,22 @@
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10294,22 +10294,22 @@
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -10332,22 +10332,22 @@
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -10370,22 +10370,22 @@
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10446,22 +10446,22 @@
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -10484,17 +10484,17 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
@@ -10522,17 +10522,17 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
@@ -10560,12 +10560,12 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -10598,22 +10598,22 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -10636,22 +10636,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -10712,22 +10712,22 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -10750,22 +10750,22 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -10788,22 +10788,22 @@
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -10821,27 +10821,27 @@
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -10859,27 +10859,27 @@
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc35§7-3(2),doc18 5-6</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -10902,22 +10902,22 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -10935,27 +10935,27 @@
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -10973,27 +10973,27 @@
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11011,27 +11011,27 @@
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -11054,22 +11054,22 @@
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -11087,27 +11087,27 @@
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -11125,27 +11125,27 @@
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -11168,22 +11168,22 @@
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -11206,22 +11206,22 @@
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -11244,22 +11244,22 @@
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -11282,22 +11282,22 @@
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -11320,22 +11320,22 @@
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -11396,22 +11396,22 @@
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -11434,22 +11434,22 @@
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -11472,22 +11472,22 @@
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -11510,22 +11510,22 @@
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -11548,22 +11548,22 @@
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -11586,22 +11586,22 @@
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -11624,22 +11624,22 @@
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -11657,27 +11657,27 @@
       </c>
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -11695,27 +11695,27 @@
       </c>
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -11733,27 +11733,27 @@
       </c>
       <c r="B124" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -11776,22 +11776,22 @@
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -11814,22 +11814,22 @@
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -11852,22 +11852,22 @@
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計に2系列が併存している（社内）</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>★素案5-2（令和9〜11年度末1,002／997／990人）とestimate_premium.pyの前提（1,004／995／987人）が一致しない。3か年計で3人差、保険料基準額で月額約7円。年度末か年度平均かの定義の違いとみられる。保険料の確定計算の前に社内で統一する。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc35§8</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -11885,27 +11885,27 @@
       </c>
       <c r="B128" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -11923,27 +11923,27 @@
       </c>
       <c r="B129" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -11966,22 +11966,22 @@
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -12004,22 +12004,22 @@
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12042,22 +12042,22 @@
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -12080,22 +12080,22 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -12113,27 +12113,27 @@
       </c>
       <c r="B134" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -12151,27 +12151,27 @@
       </c>
       <c r="B135" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -12194,22 +12194,22 @@
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -12232,22 +12232,22 @@
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -12265,27 +12265,27 @@
       </c>
       <c r="B138" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
@@ -12303,27 +12303,27 @@
       </c>
       <c r="B139" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
@@ -12346,22 +12346,22 @@
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-31</t>
         </is>
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc19 追-6</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
@@ -12384,22 +12384,22 @@
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
         </is>
       </c>
       <c r="E141" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-40,Ⅰ-42</t>
         </is>
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc19 追-7</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
@@ -12422,189 +12422,189 @@
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D142" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E142" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F142" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G142" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H142" s="25" t="inlineStr"/>
+    </row>
+    <row r="143" ht="34" customHeight="1">
+      <c r="A143" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B143" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C143" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D143" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E143" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F143" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G143" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H143" s="25" t="inlineStr"/>
+    </row>
+    <row r="144" ht="34" customHeight="1">
+      <c r="A144" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B144" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C144" s="25" t="inlineStr">
+        <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D142" s="25" t="inlineStr">
+      <c r="D144" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E142" s="23" t="inlineStr">
+      <c r="E144" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F142" s="23" t="inlineStr">
+      <c r="F144" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G142" s="23" t="inlineStr">
+      <c r="G144" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H142" s="25" t="inlineStr"/>
-    </row>
-    <row r="143" ht="34" customHeight="1">
-      <c r="A143" s="38" t="inlineStr">
+      <c r="H144" s="25" t="inlineStr"/>
+    </row>
+    <row r="145" ht="34" customHeight="1">
+      <c r="A145" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B143" s="24" t="inlineStr">
+      <c r="B145" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C143" s="25" t="inlineStr">
+      <c r="C145" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D143" s="25" t="inlineStr">
+      <c r="D145" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E143" s="23" t="inlineStr">
+      <c r="E145" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F143" s="23" t="inlineStr">
+      <c r="F145" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G143" s="23" t="inlineStr">
+      <c r="G145" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H143" s="25" t="inlineStr"/>
-    </row>
-    <row r="144" ht="34" customHeight="1">
-      <c r="A144" s="38" t="inlineStr">
+      <c r="H145" s="25" t="inlineStr"/>
+    </row>
+    <row r="146" ht="34" customHeight="1">
+      <c r="A146" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B144" s="24" t="inlineStr">
+      <c r="B146" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C144" s="25" t="inlineStr">
+      <c r="C146" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D144" s="25" t="inlineStr">
+      <c r="D146" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E144" s="23" t="inlineStr">
+      <c r="E146" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F144" s="23" t="inlineStr">
+      <c r="F146" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G144" s="23" t="inlineStr">
+      <c r="G146" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H144" s="25" t="inlineStr"/>
-    </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="39" t="inlineStr">
+      <c r="H146" s="25" t="inlineStr"/>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="147" ht="34" customHeight="1">
-      <c r="A147" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B147" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C147" s="42" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D147" s="42" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E147" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F147" s="40" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G147" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H147" s="42" t="inlineStr"/>
-    </row>
-    <row r="148" ht="34" customHeight="1">
-      <c r="A148" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B148" s="41" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C148" s="42" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D148" s="42" t="inlineStr">
-        <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
-        </is>
-      </c>
-      <c r="E148" s="40" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F148" s="40" t="inlineStr">
-        <is>
-          <t>doc28§4</t>
-        </is>
-      </c>
-      <c r="G148" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H148" s="42" t="inlineStr"/>
     </row>
     <row r="149" ht="34" customHeight="1">
       <c r="A149" s="40" t="inlineStr">
@@ -12614,27 +12614,27 @@
       </c>
       <c r="B149" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C149" s="42" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数</t>
+          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
         </is>
       </c>
       <c r="D149" s="42" t="inlineStr">
         <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
+          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
         </is>
       </c>
       <c r="E149" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F149" s="40" t="inlineStr">
         <is>
-          <t>doc28§2</t>
+          <t>doc35§7-3(1)</t>
         </is>
       </c>
       <c r="G149" s="40" t="inlineStr">
@@ -12657,22 +12657,22 @@
       </c>
       <c r="C150" s="42" t="inlineStr">
         <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D150" s="42" t="inlineStr">
         <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E150" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F150" s="40" t="inlineStr">
         <is>
-          <t>doc28§1</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G150" s="40" t="inlineStr">
@@ -12690,32 +12690,32 @@
       </c>
       <c r="B151" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C151" s="42" t="inlineStr">
         <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D151" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E151" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F151" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-1</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G151" s="40" t="inlineStr">
         <is>
-          <t>解決済（一部再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H151" s="42" t="inlineStr"/>
@@ -12728,27 +12728,27 @@
       </c>
       <c r="B152" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C152" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D152" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E152" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F152" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G152" s="40" t="inlineStr">
@@ -12766,32 +12766,32 @@
       </c>
       <c r="B153" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C153" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D153" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E153" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F153" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G153" s="40" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H153" s="42" t="inlineStr"/>
@@ -12809,27 +12809,27 @@
       </c>
       <c r="C154" s="42" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D154" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E154" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F154" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G154" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H154" s="42" t="inlineStr"/>
@@ -12847,22 +12847,22 @@
       </c>
       <c r="C155" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D155" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E155" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F155" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G155" s="40" t="inlineStr">
@@ -12885,27 +12885,27 @@
       </c>
       <c r="C156" s="42" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D156" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E156" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F156" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G156" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H156" s="42" t="inlineStr"/>
@@ -12918,22 +12918,22 @@
       </c>
       <c r="B157" s="41" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C157" s="42" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D157" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E157" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F157" s="40" t="inlineStr">
@@ -12956,27 +12956,27 @@
       </c>
       <c r="B158" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C158" s="42" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D158" s="42" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E158" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F158" s="40" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G158" s="40" t="inlineStr">
@@ -12994,27 +12994,27 @@
       </c>
       <c r="B159" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C159" s="42" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D159" s="42" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E159" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F159" s="40" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G159" s="40" t="inlineStr">
@@ -13032,27 +13032,27 @@
       </c>
       <c r="B160" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C160" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D160" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E160" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F160" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G160" s="40" t="inlineStr">
@@ -13075,22 +13075,22 @@
       </c>
       <c r="C161" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D161" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E161" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F161" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G161" s="40" t="inlineStr">
@@ -13113,22 +13113,22 @@
       </c>
       <c r="C162" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>交付要綱の配点表（満点）</t>
         </is>
       </c>
       <c r="D162" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
         </is>
       </c>
       <c r="E162" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F162" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc20§2</t>
         </is>
       </c>
       <c r="G162" s="40" t="inlineStr">
@@ -13151,43 +13151,157 @@
       </c>
       <c r="C163" s="42" t="inlineStr">
         <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D163" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E163" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F163" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G163" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H163" s="42" t="inlineStr"/>
+    </row>
+    <row r="164" ht="34" customHeight="1">
+      <c r="A164" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B164" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C164" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D164" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E164" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F164" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G164" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H164" s="42" t="inlineStr"/>
+    </row>
+    <row r="165" ht="34" customHeight="1">
+      <c r="A165" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B165" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C165" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D165" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E165" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F165" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G165" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H165" s="42" t="inlineStr"/>
+    </row>
+    <row r="166" ht="34" customHeight="1">
+      <c r="A166" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B166" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C166" s="42" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D163" s="42" t="inlineStr">
+      <c r="D166" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E163" s="40" t="inlineStr">
+      <c r="E166" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F163" s="40" t="inlineStr">
+      <c r="F166" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G163" s="40" t="inlineStr">
+      <c r="G166" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H163" s="42" t="inlineStr"/>
+      <c r="H166" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H144"/>
+  <autoFilter ref="A4:H146"/>
   <mergeCells count="3">
-    <mergeCell ref="A146:H146"/>
+    <mergeCell ref="A148:H148"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P19" s="13" t="inlineStr">
         <is>
-          <t>★議事録により9/3に第1稿提出、9/9頃に最終校了と確定。未決事項（手法・オプション項目・独自設問・依頼状名義・部数）は選択肢併記で提出する。★9/4：第2稿を受領しレビュー完了（doc27）。校了までの修正リスト11件を優先度付きで整理。必須3件（在宅の問13の番号・問9の基準月・ニーズ問1(2)①の選択肢順序）。★9/14：校了版の校正紙と対象者リスト・返信用封筒の版下を受領（doc34）。印刷前に決着が必要な事項6件を整理し依頼書に追加。返信用封筒の差出有効期間が回収期限と同日（2026年10月16日）で、期限翌日以降の投函が届かないため延長を要請。回収期限は手書きで10月16日（金）に確定。対象者はニーズ882人・在宅118人（在宅は想定150人を32人下回る）。</t>
+          <t>★議事録により9/3に第1稿提出、9/9頃に最終校了と確定。未決事項（手法・オプション項目・独自設問・依頼状名義・部数）は選択肢併記で提出する。★9/4：第2稿を受領しレビュー完了（doc27）。校了までの修正リスト11件を優先度付きで整理。必須3件（在宅の問13の番号・問9の基準月・ニーズ問1(2)①の選択肢順序）。★9/14：校了版の校正紙と対象者リスト・返信用封筒の版下を受領（doc34）。印刷前に決着が必要な事項6件を整理し依頼書に追加。返信用封筒の差出有効期間が回収期限と同日（2026年10月16日）で、期限翌日以降の投函が届かないため延長を要請。回収期限は手書きで10月16日（金）に確定。対象者はニーズ882人・在宅118人（在宅は想定150人を32人下回る）。★9/16：発送予定日（9/18）まで2日。印刷前に決着が必要な6件はいずれも未回答であり、本業務で現時点の最大のリスクである。とくに問4(15)(16)の削除は、見える化システムのR09（社会的役割の低下）が算出できなくなり、R99が10領域→9領域となって第9期との比較が成立しなくなる。印刷後は取り返しがつかない。返信用封筒の差出有効期間（2026年10月16日）も回収期限と同日で、期限翌日以降の投函が届かない。村へ至急の判断を要請している（確認事項 優先度S）。</t>
         </is>
       </c>
     </row>
@@ -2073,64 +2073,66 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-2 印刷・発送準備</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>入稿データの作成</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(3)</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G24" s="20" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>入稿データ</t>
         </is>
       </c>
-      <c r="H24" s="20" t="inlineStr">
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>調査票の確定が前提</t>
         </is>
       </c>
-      <c r="I24" s="18" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>R8.9中</t>
         </is>
       </c>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="21" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P24" s="20" t="inlineStr">
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="14" t="n">
+        <v>46279</v>
+      </c>
+      <c r="M24" s="14" t="n"/>
+      <c r="N24" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O24" s="16" t="inlineStr">
+        <is>
+          <t>確認中</t>
+        </is>
+      </c>
+      <c r="P24" s="13" t="inlineStr">
         <is>
           <t>★9/9頃の校了・印刷依頼が目標（議事録）。9/3の第1稿提出→修正・確認を経て確定する。</t>
         </is>
@@ -4519,7 +4521,7 @@
       </c>
       <c r="M63" s="14" t="n"/>
       <c r="N63" s="15" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="O63" s="16" t="inlineStr">
         <is>
@@ -4528,7 +4530,7 @@
       </c>
       <c r="P63" s="13" t="inlineStr">
         <is>
-          <t>doc13で前期・後期別の乖離率補正により令和9〜11年度末を算定（1,002／997／990人）。scripts/estimate_population.pyで再現可能。補正手法の村合意と国ワークシートで確定。</t>
+          <t>doc13で前期・後期別の乖離率補正により令和9〜11年度末を算定（1,002／997／990人）。scripts/estimate_population.pyで再現可能。★9/15：素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており2系列が併存していたことが判明。厚生労働省配布の系列（B案・令和7年12月末実績にリベース）に統一し、素案5-1・5-2を全面改訂した（1,004／995／987人）。2つの方法の差は最大3人（0.3%・保険料月額約7円）であり、検証として素案5-2に併記。残るのは補正手法の村合意と国ワークシートによる確定のみ。</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4587,7 @@
       </c>
       <c r="M64" s="14" t="n"/>
       <c r="N64" s="15" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O64" s="16" t="inlineStr">
         <is>
@@ -4594,7 +4596,7 @@
       </c>
       <c r="P64" s="13" t="inlineStr">
         <is>
-          <t>★9/7：doc29／scripts/estimate_certified.py として要介護度別の推計を確立。見える化のB4-a（全体）とB4-d（75歳以上）から前期・後期別の要介護度別認定率を分解（前期5.86%／後期34.70%）。B案×令和8年の認定率で基準年が実績と完全一致（211人・要支援1=51・要支援2=29・要介護1=50）。令和9年214人／令和10年217人／令和11年220人。認定率の基準2種×被保険者数2案の4通りを出力し、令和11年度で最大12人・5.8%の幅。</t>
+          <t>★9/7：doc29／scripts/estimate_certified.py として要介護度別の推計を確立。見える化のB4-a（全体）とB4-d（75歳以上）から前期・後期別の要介護度別認定率を分解（前期5.86%／後期34.70%）。B案×令和8年の認定率で基準年が実績と完全一致（211人・要支援1=51・要支援2=29・要介護1=50）。令和9年214人／令和10年217人／令和11年220人。認定率の基準2種×被保険者数2案の4通りを出力し、令和11年度で最大12人・5.8%の幅。★9/15：素案5-3に要介護度別（要支援1〜要介護5）の見込みを掲載し、認定率の置き方3とおりの幅を明示した（令和11年で①3か年平均220人〈採用〉・②直近年度固定224人・③年0.62pt上昇226人、保険料で月額約170円の幅）。国ワークシートの受領で確定する。</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4851,7 @@
       </c>
       <c r="M68" s="14" t="n"/>
       <c r="N68" s="15" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O68" s="16" t="inlineStr">
         <is>
@@ -4858,7 +4860,7 @@
       </c>
       <c r="P68" s="13" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：第9期で県内平均を上回ったため急激な負担増を抑えたい意向。基金取崩も視野。令和9年度の介護報酬改定を見据え現行単価で一旦試算し単価確定後に補正。doc18 第5章5-7に様式と所得段階13段階の枠を作成済。★9/8：サービス諸費の推計（doc30）が出たため、残る停止要因は基金残高と令和6・7年度決算の2件に絞られた。★9/12：保険料算定の5式（金ケ崎町で第9期公表値と一致を確認した構造）と調整交付金見込交付割合の式（α+0.05）−α×F×Gを導入し、本村の第9期を0.32%で再現。限界率23.79%・F×G=1.034を復元。感応度9項目（給付費1%＝月額59円、第1号負担割合1pt＝294円、基金24,000千円＝▲702円）と12パターン（5,936〜7,341円・幅1,406円）を算定し素案5-7に投入（scripts/estimate_premium.py）。保険料の幅のうち702円は基金取崩の判断で決まるため、給付費推計の精緻化より基金方針の決定が先。</t>
+          <t>★議事録で方針決着：第9期で県内平均を上回ったため急激な負担増を抑えたい意向。基金取崩も視野。令和9年度の介護報酬改定を見据え現行単価で一旦試算し単価確定後に補正。doc18 第5章5-7に様式と所得段階13段階の枠を作成済。★9/8：サービス諸費の推計（doc30）が出たため、残る停止要因は基金残高と令和6・7年度決算の2件に絞られた。★9/12：保険料算定の5式（金ケ崎町で第9期公表値と一致を確認した構造）と調整交付金見込交付割合の式（α+0.05）−α×F×Gを導入し、本村の第9期を0.32%で再現。限界率23.79%・F×G=1.034を復元。感応度9項目（給付費1%＝月額59円、第1号負担割合1pt＝294円、基金24,000千円＝▲702円）と12パターン（5,936〜7,341円・幅1,406円）を算定し素案5-7に投入（scripts/estimate_premium.py）。保険料の幅のうち702円は基金取崩の判断で決まるため、給付費推計の精緻化より基金方針の決定が先。★9/15：中長期（令和17年度・令和22年度）の保険料をαの2案で算定し素案5-11の【要確認】を解消（据え置き23%なら令和22年度6,883円、3年ごと1pt上昇なら8,379円。scripts/estimate_longterm.py）。素案5-6の標準給付費の様式を埋め3か年854,014千円を確定。5-7の感応度に3行（地域支援事業費+22円／単価の趨勢+314円／推計誤差±約700円）を追加した。残るのはα政令・基金残高・令和6-7年度決算の受領。</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4917,7 @@
       </c>
       <c r="M69" s="14" t="n"/>
       <c r="N69" s="15" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="O69" s="16" t="inlineStr">
         <is>
@@ -4924,7 +4926,7 @@
       </c>
       <c r="P69" s="13" t="inlineStr">
         <is>
-          <t>★交付金の配点表・全国集計3か年の受領により、満点・全国平均・県平均・全国順位が判明（doc20）。★9/3：資料7として成果目標6指標・活動指標13指標を設定し、うち11指標の現状値を確定（通いの場23か所281人・参加率12.2%、多様なサービス事業費割合0.0%、サポーター約237人、ステップアップ講座0人、縦覧点検4帳票、給付費通知300件/年、地域ケア会議年6回、SC参加割合50.0%、認定率21.1%、要支援1が51人 ほか）。目標値は調査結果の確定後に設定。交付金の得点は数値目標に置かず進捗管理の仕組みを書く方針。</t>
+          <t>★交付金の配点表・全国集計3か年の受領により、満点・全国平均・県平均・全国順位が判明（doc20）。★9/3：資料7として成果目標6指標・活動指標13指標を設定し、うち11指標の現状値を確定（通いの場23か所281人・参加率12.2%、多様なサービス事業費割合0.0%、サポーター約237人、ステップアップ講座0人、縦覧点検4帳票、給付費通知300件/年、地域ケア会議年6回、SC参加割合50.0%、認定率21.1%、要支援1が51人 ほか）。目標値は調査結果の確定後に設定。交付金の得点は数値目標に置かず進捗管理の仕組みを書く方針。★9/15：令和8年度の交付金評価指標で検算し、素案6-3に本村の得点と全国平均を併記。全国平均を上回る6指標は「維持」、下回る5指標は「引上げ」に整理した。引上げを要するのは要介護3〜5の状態の変化（0点／40点・20点）、総合事業の多様なサービス（0点／13点）、認知症サポーターのステップアップ講座（0点／12点）。目標値は第2回策定委員会で設定する。</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5563,7 @@
       </c>
       <c r="M79" s="14" t="n"/>
       <c r="N79" s="15" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="O79" s="16" t="inlineStr">
         <is>
@@ -5570,7 +5572,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。★9/15：見込量算定の第1次概算を反映（doc35）。あわせて素案の記述を令和8年度の交付金評価指標で検算し、複数の訂正を行った。(1)中長期の保険料を算定し5-11の【要確認】を解消（αを23%据え置くと令和22年度6,883円、3年ごとに1ポイント上がると8,379円）。(2)標準給付費の様式を埋め5-6を確定（3か年854,014千円）。5-7と完全に一致。(3)交付金の評価指標を令和8年度で検算したところ、素案の記述の多くが令和6年度または令和4年度の評価に基づいており実態と食い違っていた。通いの場への参加率は0→8点満点（最上位の段階は全国で約10%）、参加促進のアウトリーチは9点満点、地域リハビリテーションの推進は0→7点満点、計画の進捗管理（目標Ⅰの3項目）は0→48点満点。一方、要介護3〜5の状態の変化は2指標とも0点（35点減）、認知症サポーター数は12点中0点、難聴は20点中0点。施策1-1を「通いの場の再構築と参加率の向上」から「通いの場の開催頻度の向上と地区差の是正」に改称し、課題3の見出しも改めた。(4)6-3の成果目標・活動指標に令和8年度の得点と全国平均を併記し、維持6指標・引上げ5指標に整理。(5)認知症基本法13条1項・成年後見促進法14条1項を確認し1-2の【要確認】を解消。素案は2,197行→2,341行。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。★9/15：見込量算定の第1次概算を反映（doc35）。あわせて素案の記述を令和8年度の交付金評価指標で検算し、複数の訂正を行った。(1)中長期の保険料を算定し5-11の【要確認】を解消（αを23%据え置くと令和22年度6,883円、3年ごとに1ポイント上がると8,379円）。(2)標準給付費の様式を埋め5-6を確定（3か年854,014千円）。5-7と完全に一致。(3)交付金の評価指標を令和8年度で検算したところ、素案の記述の多くが令和6年度または令和4年度の評価に基づいており実態と食い違っていた。通いの場への参加率は0→8点満点（最上位の段階は全国で約10%）、参加促進のアウトリーチは9点満点、地域リハビリテーションの推進は0→7点満点、計画の進捗管理（目標Ⅰの3項目）は0→48点満点。一方、要介護3〜5の状態の変化は2指標とも0点（35点減）、認知症サポーター数は12点中0点、難聴は20点中0点。施策1-1を「通いの場の再構築と参加率の向上」から「通いの場の開催頻度の向上と地区差の是正」に改称し、課題3の見出しも改めた。(4)6-3の成果目標・活動指標に令和8年度の得点と全国平均を併記し、維持6指標・引上げ5指標に整理。(5)認知症基本法13条1項・成年後見促進法14条1項を確認し1-2の【要確認】を解消。素案は2,197行→2,341行。★9/15：3次にわたり修正。(1)見込量算定の第1次概算を反映（doc35）。(2)令和8年度の交付金評価指標で全記述を検算し、施策1-1の名称と課題3の見出しを改めた。(3)推計の系列を統一し、介護給付費と予防給付費を分離、見込量の自己点検を実施。5-12（据え置き項目31件）を新設。素案は約115頁→2,449行（段落約4,400・表約125・図20）。残る空欄は交付金の交付見込額、高齢者福祉サービスの量の目標の一部、委員名簿・パブコメなど確定後に記入するもの。★9/16：交付金の目標別に全国平均と対比したところ、素案2-8の「認知症総合支援が全国平均を下回る唯一の目標」が誤りと判明（上回るのは3目標、下回るのは5目標。認知症総合支援は差が最大の▲19.1点）。2-8に目標別の対比表を新設し関係箇所を訂正した。あわせて薄い節を埋めた（1-5日常生活圏域・4-2〜4-4基本目標の導入・5-10低所得者）。6-4に乖離の検証の見直しの目安（±5%以内／±5〜12%／±12%超）を、6-5に計画期間中に確定する5項目を新設。±12%は推計の誤差の絶対値の平均11.9%（保険料月額約700円）によるもので、この幅を超える乖離は基金の取崩しでは吸収できない。素案は2,449行→2,509行。</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6053,7 @@
       </c>
       <c r="M87" s="14" t="n"/>
       <c r="N87" s="15" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="O87" s="16" t="inlineStr">
         <is>
@@ -6060,7 +6062,7 @@
       </c>
       <c r="P87" s="13" t="inlineStr">
         <is>
-          <t>★doc26で資料構成を確定（資料1〜8・約53頁＋素案別冊）。合意を得たい事項5点を先頭に置く構成。★9/3：output/08_第2回策定委員会資料.docx として資料2（本体完成）・資料5（骨格）・資料6（骨格）・資料7（本体完成）を作成。★9/4：資料4（第10期の基本理念・基本目標・施策体系）を追加し本体完成（全体で39表・A4約40頁）。基本理念は2案併記、基本目標5本、施策28本（新規10）。残るは資料3（調査結果速報）のみで、調査結果の確定後に作成。資料4に差し込む住民ニーズの数値も資料3から供給する。LibreOfficeが動作しないためレイアウトの目視確認は未実施。</t>
+          <t>★doc26で資料構成を確定（資料1〜8・約53頁＋素案別冊）。合意を得たい事項5点を先頭に置く構成。★9/3：output/08_第2回策定委員会資料.docx として資料2（本体完成）・資料5（骨格）・資料6（骨格）・資料7（本体完成）を作成。★9/4：資料4（第10期の基本理念・基本目標・施策体系）を追加し本体完成（全体で39表・A4約40頁）。基本理念は2案併記、基本目標5本、施策28本（新規10）。残るは資料3（調査結果速報）のみで、調査結果の確定後に作成。資料4に差し込む住民ニーズの数値も資料3から供給する。LibreOfficeが動作しないためレイアウトの目視確認は未実施。★9/16：資料5を骨格から本体に引き上げ（8頁→14頁）。5-3にサービス種類別の見込量と給付費の分離を、5-4に推計の幅（単価の趨勢+314円・伸びの偏りのバックテスト・推計誤差±約700円・自己点検の4件）を、5-5に令和9年4月の新設区分を新設した。資料6も本体に引き上げ（6頁→10頁）。6-3に算定の5式と感応度9項目、6-3bに12パターン（5,936〜7,341円）、6-5に中長期の保険料（αの2案）を投入。資料7に7-3bとして令和8年度の得点と全国平均の対比（維持6指標・引上げ5指標）を追加。算定の進展により委員の判断を要する論点が4つ増えたため、合意事項を5点→8点に改訂し、当日の進行案（2時間）を doc26§12 に作成した。資料は26表→43表・約65頁。残る律速は委員の改選・基金残高・調査の回収集計の3つ。</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P65" s="13" t="inlineStr">
         <is>
-          <t>★9/8：doc30として推計の枠組みを確定。「見える化」システムのデータ定義（受給者数＝年度延べ、D45系の分母＝要介護度別認定者数）を検算のうえ確定し、estimate_services.py により区分別・サービス種類別の見込量を算定。全28サービスのうち令和7年度に実績のある16サービスについて受給者数・利用量・給付費の暫定値を doc18 第5章5-4に投入。施設・居住系の種類別人数は見える化に系列がなく給付費比の按分値のため、村の月報（第2表・第3表）で置き換えが必要。介護給付と予防給付の分離も同じく月報待ち。★9/12：他案件（川崎町・金ケ崎町・大雪）の到達水準と対照し（doc33）、基準年度を令和7年度と確定。見える化の系列別の月数を実測で確認し（D1はR7が11か月、D2/D3/D4は12か月相当）doc30の÷12が正しいことを裏付けて素案5-4に明記。令和9年4月新設4区分の枠と、国の推計ツールのワーニング判定式（閾値＝Q1−2Q〜Q3+2Q）による自己点検の手順を追加。国の推計ツールの出力は未受領で、依頼書18-2として最優先で追加した。★9/15：他案件（大雪・川崎・金ケ崎）の算定の進め方を確認し、本村に適用して第1次概算を実施（doc35）。(1)見込量は需要で置く／地域密着型と総合事業のみ村の供給力が上限、という原則を素案5-4に明記。(2)令和9年4月新設4区分を「―」「要協議」から0に立て直した。(3)夜間対応型訪問介護の令和9年3月末廃止を反映。(4)単価の趨勢を連鎖ラスパイレス指数で実測（R元→R7の年率+1.30%）。3か年平均で固定していることは給付費の5.32%過小＝保険料月額314円に当たる。(5)サービス別の受給者数の年率が▲13.12〜+54.88%と68ポイント開いていることを実測し、伸びをどこまで反映すべきかをバックテストで検証（backtest_growth.py）。φ=0.5・c=5%が最小（WMAPE19.11%）だが一律19.68%に対し改善は2.9%にとどまるため一律を採用すると決定。(6)一律の方法で3年先を予測したときの誤差は絶対値平均11.9%＝保険料月額約700円で、基金取崩24,000千円の効き（702円）と同規模。素案5-4(9)として新設。(7)在宅介護実態調査の施設入所申込みの反映シナリオの枠を素案5-4(3)に新設（+1人／月＝月額75円）。残るのは国の推計ワークシートによる基準年度の置き直しの分解のみ。★9/15（第3次）：推計の系列を統一し、給付費を分離した（doc35§7-3）。(1)素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し5-1・5-2・5-3を全面改訂。5-1に①第1号被保険者数→②認定者数→③受給者数→④利用量→⑤給付費→⑥標準給付費→⑦保険料の連なりを表で明示した。(2)決算（D48-b）の介護サービス等諸費／介護予防サービス等諸費と要介護度別受給者数を突き合わせ、予防給付19,002円・介護給付175,230円の1人あたり給付月額を復元（令和3〜5年度で±1.6%以内の安定）。第10期3か年で介護給付費755,119千円・予防給付費34,344千円に分離し、5-6の空欄を埋めた。(3)見込量の自己点検を実施（check_warning.py）。年度間の変化率は3区分とも4%以内。令和7年度実績→令和9年度見込で±10%超は4件（居宅療養管理指導▲25.3%、短期入所生活介護▲20.8%、訪問入浴介護・地域密着型通所介護は新規計上）。いずれも3か年平均で置くことの副作用であり委員会にお諮りする。(4)地域支援事業費を新系列で置き直し3か年122,737千円（保険料月額+22円）。</t>
+          <t>★9/8：doc30として推計の枠組みを確定。「見える化」システムのデータ定義（受給者数＝年度延べ、D45系の分母＝要介護度別認定者数）を検算のうえ確定し、estimate_services.py により区分別・サービス種類別の見込量を算定。全28サービスのうち令和7年度に実績のある16サービスについて受給者数・利用量・給付費の暫定値を doc18 第5章5-4に投入。施設・居住系の種類別人数は見える化に系列がなく給付費比の按分値のため、村の月報（第2表・第3表）で置き換えが必要。介護給付と予防給付の分離も同じく月報待ち。★9/12：他案件（川崎町・金ケ崎町・大雪）の到達水準と対照し（doc33）、基準年度を令和7年度と確定。見える化の系列別の月数を実測で確認し（D1はR7が11か月、D2/D3/D4は12か月相当）doc30の÷12が正しいことを裏付けて素案5-4に明記。令和9年4月新設4区分の枠と、国の推計ツールのワーニング判定式（閾値＝Q1−2Q〜Q3+2Q）による自己点検の手順を追加。国の推計ツールの出力は未受領で、依頼書18-2として最優先で追加した。★9/15：他案件（大雪・川崎・金ケ崎）の算定の進め方を確認し、本村に適用して第1次概算を実施（doc35）。(1)見込量は需要で置く／地域密着型と総合事業のみ村の供給力が上限、という原則を素案5-4に明記。(2)令和9年4月新設4区分を「―」「要協議」から0に立て直した。(3)夜間対応型訪問介護の令和9年3月末廃止を反映。(4)単価の趨勢を連鎖ラスパイレス指数で実測（R元→R7の年率+1.30%）。3か年平均で固定していることは給付費の5.32%過小＝保険料月額314円に当たる。(5)サービス別の受給者数の年率が▲13.12〜+54.88%と68ポイント開いていることを実測し、伸びをどこまで反映すべきかをバックテストで検証（backtest_growth.py）。φ=0.5・c=5%が最小（WMAPE19.11%）だが一律19.68%に対し改善は2.9%にとどまるため一律を採用すると決定。(6)一律の方法で3年先を予測したときの誤差は絶対値平均11.9%＝保険料月額約700円で、基金取崩24,000千円の効き（702円）と同規模。素案5-4(9)として新設。(7)在宅介護実態調査の施設入所申込みの反映シナリオの枠を素案5-4(3)に新設（+1人／月＝月額75円）。残るのは国の推計ワークシートによる基準年度の置き直しの分解のみ。★9/15（第3次）：推計の系列を統一し、給付費を分離した（doc35§7-3）。(1)素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し5-1・5-2・5-3を全面改訂。5-1に①第1号被保険者数→②認定者数→③受給者数→④利用量→⑤給付費→⑥標準給付費→⑦保険料の連なりを表で明示した。(2)決算（D48-b）の介護サービス等諸費／介護予防サービス等諸費と要介護度別受給者数を突き合わせ、予防給付19,002円・介護給付175,230円の1人あたり給付月額を復元（令和3〜5年度で±1.6%以内の安定）。第10期3か年で介護給付費755,119千円・予防給付費34,344千円に分離し、5-6の空欄を埋めた。(3)見込量の自己点検を実施（check_warning.py）。年度間の変化率は3区分とも4%以内。令和7年度実績→令和9年度見込で±10%超は4件（居宅療養管理指導▲25.3%、短期入所生活介護▲20.8%、訪問入浴介護・地域密着型通所介護は新規計上）。いずれも3か年平均で置くことの副作用であり委員会にお諮りする。(4)地域支援事業費を新系列で置き直し3か年122,737千円（保険料月額+22円）。★9/16：認知症関連を反映（doc36§4）。5-4(7)の必要利用定員総数に認知症高齢者数との対比を追加（自立度Ⅱ以上1人あたりの定員は令和2年0.178人分→令和6年0.168人分。定員は平成28年度以降27人で固定、稼働率93%）。5-5(1)に認知症総合支援事業の6行（初期集中支援推進事業の対象者数・地域支援推進員・認知症カフェ・サポーター養成講座・養成者数・チームオレンジ）を新設。大半が実績未受領のため空欄。村内GHの待機者数と村外GH利用者数が未受領で、定員の増減を委員会に諮れない状態である（優先度A）。</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="P71" s="13" t="inlineStr">
         <is>
-          <t>doc14・doc18として施策案を整理。第4章は26施策。住民ニーズ第1位の除雪を独立施策（2-6）として新設。基本目標5「計画の推進と進捗管理」の新設を提案。国の基本指針で追加・修正の可能性。</t>
+          <t>doc14・doc18として施策案を整理。第4章は26施策。住民ニーズ第1位の除雪を独立施策（2-6）として新設。基本目標5「計画の推進と進捗管理」の新設を提案。国の基本指針で追加・修正の可能性。★9/16：認知症基本法の基本的施策10項目と本計画の施策を対応させたところ、第15条（認知症の人の生活におけるバリアフリー化の推進）を受ける施策がないことが判明。移動・住まい・除雪の各施策が実質的な受け皿になるが、認知症の人に着目した記述はない。外出・買い物・金融機関の利用など介護保険の枠組みの外にある領域であり、庁内の関係部署および事業者との連携の範囲を村と協議する。</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。★9/15：見込量算定の第1次概算を反映（doc35）。あわせて素案の記述を令和8年度の交付金評価指標で検算し、複数の訂正を行った。(1)中長期の保険料を算定し5-11の【要確認】を解消（αを23%据え置くと令和22年度6,883円、3年ごとに1ポイント上がると8,379円）。(2)標準給付費の様式を埋め5-6を確定（3か年854,014千円）。5-7と完全に一致。(3)交付金の評価指標を令和8年度で検算したところ、素案の記述の多くが令和6年度または令和4年度の評価に基づいており実態と食い違っていた。通いの場への参加率は0→8点満点（最上位の段階は全国で約10%）、参加促進のアウトリーチは9点満点、地域リハビリテーションの推進は0→7点満点、計画の進捗管理（目標Ⅰの3項目）は0→48点満点。一方、要介護3〜5の状態の変化は2指標とも0点（35点減）、認知症サポーター数は12点中0点、難聴は20点中0点。施策1-1を「通いの場の再構築と参加率の向上」から「通いの場の開催頻度の向上と地区差の是正」に改称し、課題3の見出しも改めた。(4)6-3の成果目標・活動指標に令和8年度の得点と全国平均を併記し、維持6指標・引上げ5指標に整理。(5)認知症基本法13条1項・成年後見促進法14条1項を確認し1-2の【要確認】を解消。素案は2,197行→2,341行。★9/15：3次にわたり修正。(1)見込量算定の第1次概算を反映（doc35）。(2)令和8年度の交付金評価指標で全記述を検算し、施策1-1の名称と課題3の見出しを改めた。(3)推計の系列を統一し、介護給付費と予防給付費を分離、見込量の自己点検を実施。5-12（据え置き項目31件）を新設。素案は約115頁→2,449行（段落約4,400・表約125・図20）。残る空欄は交付金の交付見込額、高齢者福祉サービスの量の目標の一部、委員名簿・パブコメなど確定後に記入するもの。★9/16：交付金の目標別に全国平均と対比したところ、素案2-8の「認知症総合支援が全国平均を下回る唯一の目標」が誤りと判明（上回るのは3目標、下回るのは5目標。認知症総合支援は差が最大の▲19.1点）。2-8に目標別の対比表を新設し関係箇所を訂正した。あわせて薄い節を埋めた（1-5日常生活圏域・4-2〜4-4基本目標の導入・5-10低所得者）。6-4に乖離の検証の見直しの目安（±5%以内／±5〜12%／±12%超）を、6-5に計画期間中に確定する5項目を新設。±12%は推計の誤差の絶対値の平均11.9%（保険料月額約700円）によるもので、この幅を超える乖離は基金の取崩しでは吸収できない。素案は2,449行→2,509行。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。★9/15：見込量算定の第1次概算を反映（doc35）。あわせて素案の記述を令和8年度の交付金評価指標で検算し、複数の訂正を行った。(1)中長期の保険料を算定し5-11の【要確認】を解消（αを23%据え置くと令和22年度6,883円、3年ごとに1ポイント上がると8,379円）。(2)標準給付費の様式を埋め5-6を確定（3か年854,014千円）。5-7と完全に一致。(3)交付金の評価指標を令和8年度で検算したところ、素案の記述の多くが令和6年度または令和4年度の評価に基づいており実態と食い違っていた。通いの場への参加率は0→8点満点（最上位の段階は全国で約10%）、参加促進のアウトリーチは9点満点、地域リハビリテーションの推進は0→7点満点、計画の進捗管理（目標Ⅰの3項目）は0→48点満点。一方、要介護3〜5の状態の変化は2指標とも0点（35点減）、認知症サポーター数は12点中0点、難聴は20点中0点。施策1-1を「通いの場の再構築と参加率の向上」から「通いの場の開催頻度の向上と地区差の是正」に改称し、課題3の見出しも改めた。(4)6-3の成果目標・活動指標に令和8年度の得点と全国平均を併記し、維持6指標・引上げ5指標に整理。(5)認知症基本法13条1項・成年後見促進法14条1項を確認し1-2の【要確認】を解消。素案は2,197行→2,341行。★9/15：3次にわたり修正。(1)見込量算定の第1次概算を反映（doc35）。(2)令和8年度の交付金評価指標で全記述を検算し、施策1-1の名称と課題3の見出しを改めた。(3)推計の系列を統一し、介護給付費と予防給付費を分離、見込量の自己点検を実施。5-12（据え置き項目31件）を新設。素案は約115頁→2,449行（段落約4,400・表約125・図20）。残る空欄は交付金の交付見込額、高齢者福祉サービスの量の目標の一部、委員名簿・パブコメなど確定後に記入するもの。★9/16：交付金の目標別に全国平均と対比したところ、素案2-8の「認知症総合支援が全国平均を下回る唯一の目標」が誤りと判明（上回るのは3目標、下回るのは5目標。認知症総合支援は差が最大の▲19.1点）。2-8に目標別の対比表を新設し関係箇所を訂正した。あわせて薄い節を埋めた（1-5日常生活圏域・4-2〜4-4基本目標の導入・5-10低所得者）。6-4に乖離の検証の見直しの目安（±5%以内／±5〜12%／±12%超）を、6-5に計画期間中に確定する5項目を新設。±12%は推計の誤差の絶対値の平均11.9%（保険料月額約700円）によるもので、この幅を超える乖離は基金の取崩しでは吸収できない。素案は2,449行→2,509行。★9/16：認知症施策推進計画としての検討（doc36）。本計画は認知症基本法第13条第1項の市町村計画を兼ねるが、認知症施策は施策4-4の1本のみで基本法の基本的施策との対応が示されていなかった。第4章に4-7「認知症施策推進計画としての位置づけ」を新設し、3つの基本的な考え方（新しい認知症観・本人および家族等の参画・共生社会）、基本法第14〜23条の10項目と本計画の施策との対応表、本村の状況、本人・家族の参画の方法、指標8件を掲載した。2-3に認知症高齢者の状況（自立度Ⅱ以上161人・2年間で22.0%増・認定者に占める割合63.6%）を新設。あわせて第4章の施策番号に「施策」を冠し、基本目標の節番号との衝突（4-4が基本目標4と施策4-4の両方を指す状態）を解消した。素案は2,509行→2,633行。</t>
         </is>
       </c>
     </row>
@@ -7136,7 +7136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8738,22 +8738,22 @@
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
+          <t>認知症対応型共同生活介護（村内27人分）の待機者数と、村外のグループホームを利用している方の人数</t>
         </is>
       </c>
       <c r="D45" s="34" t="inlineStr">
         <is>
-          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
+          <t>★施策3-2・5-4(7)の必要利用定員総数の判断に必須。認知症高齢者（自立度Ⅱ以上）は2年間で132人→161人と22.0%増えた一方、定員は平成28年度以降27人のまま。稼働率93%。増床の要否は待機と村外利用の実態がなければ判断できない。</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc36§3,doc18 5-4(7)</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
@@ -8776,22 +8776,22 @@
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
+          <t>認知症関連事業の実績（認知症カフェの箇所数、認知症初期集中支援推進事業の対象者数、認知症地域支援推進員の活動実績）</t>
         </is>
       </c>
       <c r="D46" s="34" t="inlineStr">
         <is>
-          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
+          <t>★素案5-5(1)の地域支援事業の量に認知症総合支援事業の行を新設したが、いずれも実績が未受領。国の様式では認知症総合支援事業の量を定めることが求められる。</t>
         </is>
       </c>
       <c r="E46" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-53,Ⅱ-68</t>
         </is>
       </c>
       <c r="F46" s="35" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc36§4,doc18 5-5(1)</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -8809,27 +8809,27 @@
       </c>
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
         </is>
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -8847,27 +8847,27 @@
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C48" s="34" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
         </is>
       </c>
       <c r="D48" s="34" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
         </is>
       </c>
       <c r="E48" s="35" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F48" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -8890,22 +8890,22 @@
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -8928,22 +8928,22 @@
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F50" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-89</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -8966,22 +8966,22 @@
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-97</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -8999,27 +8999,27 @@
       </c>
       <c r="B52" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C52" s="34" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D52" s="34" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
         </is>
       </c>
       <c r="E52" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-50</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F52" s="35" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -9037,27 +9037,27 @@
       </c>
       <c r="B53" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
         </is>
       </c>
       <c r="D53" s="34" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc26§10 K-97</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -9080,22 +9080,22 @@
       </c>
       <c r="C54" s="34" t="inlineStr">
         <is>
-          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D54" s="34" t="inlineStr">
         <is>
-          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E54" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-46</t>
+          <t>Ⅰ-50</t>
         </is>
       </c>
       <c r="F54" s="35" t="inlineStr">
         <is>
-          <t>doc25§4-2 K-91</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -9113,27 +9113,27 @@
       </c>
       <c r="B55" s="33" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C55" s="34" t="inlineStr">
         <is>
-          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D55" s="34" t="inlineStr">
         <is>
-          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-70,Ⅱ-71</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -9151,27 +9151,27 @@
       </c>
       <c r="B56" s="33" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C56" s="34" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
         </is>
       </c>
       <c r="D56" s="34" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
         </is>
       </c>
       <c r="E56" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅰ-46</t>
         </is>
       </c>
       <c r="F56" s="35" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc25§4-2 K-91</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -9189,27 +9189,27 @@
       </c>
       <c r="B57" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C57" s="34" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
         </is>
       </c>
       <c r="D57" s="34" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅱ-70,Ⅱ-71</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C58" s="34" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D58" s="34" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E58" s="35" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F58" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -9265,27 +9265,27 @@
       </c>
       <c r="B59" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C59" s="34" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の対象が118人（想定150人）であることへの集計設計の対応</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D59" s="34" t="inlineStr">
         <is>
-          <t>★回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかの判断が要る。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Ⅲ-72,Ⅲ-73</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>doc34§5-2</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G59" s="35" t="inlineStr">
@@ -9303,27 +9303,27 @@
       </c>
       <c r="B60" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C60" s="34" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D60" s="34" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E60" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F60" s="35" t="inlineStr">
         <is>
-          <t>doc33§3-5</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G60" s="35" t="inlineStr">
@@ -9346,22 +9346,22 @@
       </c>
       <c r="C61" s="34" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>在宅介護実態調査の対象が118人（想定150人）であることへの集計設計の対応</t>
         </is>
       </c>
       <c r="D61" s="34" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかの判断が要る。</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅲ-72,Ⅲ-73</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc34§5-2</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -9384,22 +9384,22 @@
       </c>
       <c r="C62" s="34" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
         </is>
       </c>
       <c r="D62" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
         </is>
       </c>
       <c r="E62" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F62" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc33§3-5</t>
         </is>
       </c>
       <c r="G62" s="35" t="inlineStr">
@@ -9422,22 +9422,22 @@
       </c>
       <c r="C63" s="34" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -9460,22 +9460,22 @@
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D64" s="34" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E64" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F64" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-99</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G64" s="35" t="inlineStr">
@@ -9498,22 +9498,22 @@
       </c>
       <c r="C65" s="34" t="inlineStr">
         <is>
-          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D65" s="34" t="inlineStr">
         <is>
-          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>doc28§1-2 K-107</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
@@ -9536,22 +9536,22 @@
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
-          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D66" s="34" t="inlineStr">
         <is>
-          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
         </is>
       </c>
       <c r="E66" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F66" s="35" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc26§10 K-99</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -9569,27 +9569,27 @@
       </c>
       <c r="B67" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C67" s="34" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
         </is>
       </c>
       <c r="D67" s="34" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc28§1-2 K-107</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
@@ -9607,27 +9607,27 @@
       </c>
       <c r="B68" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C68" s="34" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>認知症の人およびご家族から意見を聴く方法</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
         </is>
       </c>
       <c r="E68" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F68" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc36§5,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -9645,27 +9645,27 @@
       </c>
       <c r="B69" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C69" s="34" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
         </is>
       </c>
       <c r="D69" s="34" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="B70" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C70" s="34" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E70" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F70" s="35" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G70" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H70" s="34" t="inlineStr"/>
@@ -9721,27 +9721,27 @@
       </c>
       <c r="B71" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C71" s="34" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D71" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G71" s="35" t="inlineStr">
@@ -9759,27 +9759,27 @@
       </c>
       <c r="B72" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C72" s="34" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D72" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E72" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F72" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -9802,27 +9802,27 @@
       </c>
       <c r="C73" s="34" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
       <c r="D73" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G73" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H73" s="34" t="inlineStr"/>
@@ -9840,144 +9840,144 @@
       </c>
       <c r="C74" s="34" t="inlineStr">
         <is>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+        </is>
+      </c>
+      <c r="D74" s="34" t="inlineStr">
+        <is>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+        </is>
+      </c>
+      <c r="E74" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F74" s="35" t="inlineStr">
+        <is>
+          <t>doc27§3-3</t>
+        </is>
+      </c>
+      <c r="G74" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr"/>
+    </row>
+    <row r="75" ht="34" customHeight="1">
+      <c r="A75" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B75" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C75" s="34" t="inlineStr">
+        <is>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+        </is>
+      </c>
+      <c r="D75" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+        </is>
+      </c>
+      <c r="E75" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F75" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-2</t>
+        </is>
+      </c>
+      <c r="G75" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H75" s="34" t="inlineStr"/>
+    </row>
+    <row r="76" ht="34" customHeight="1">
+      <c r="A76" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B76" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C76" s="34" t="inlineStr">
+        <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D76" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E76" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F76" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G76" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H76" s="34" t="inlineStr"/>
+    </row>
+    <row r="77" ht="34" customHeight="1">
+      <c r="A77" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B77" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C77" s="34" t="inlineStr">
+        <is>
           <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
-      <c r="D74" s="34" t="inlineStr">
+      <c r="D77" s="34" t="inlineStr">
         <is>
           <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
-      <c r="E74" s="35" t="inlineStr">
+      <c r="E77" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="F74" s="35" t="inlineStr">
+      <c r="F77" s="35" t="inlineStr">
         <is>
           <t>doc27§6</t>
         </is>
       </c>
-      <c r="G74" s="35" t="inlineStr">
+      <c r="G77" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H74" s="34" t="inlineStr"/>
-    </row>
-    <row r="75" ht="34" customHeight="1">
-      <c r="A75" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B75" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C75" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D75" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E75" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F75" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G75" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H75" s="25" t="inlineStr"/>
-    </row>
-    <row r="76" ht="34" customHeight="1">
-      <c r="A76" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B76" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C76" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D76" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
-        </is>
-      </c>
-      <c r="E76" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F76" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1,doc30§2-4</t>
-        </is>
-      </c>
-      <c r="G76" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H76" s="25" t="inlineStr"/>
-    </row>
-    <row r="77" ht="34" customHeight="1">
-      <c r="A77" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B77" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C77" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D77" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
-        </is>
-      </c>
-      <c r="E77" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F77" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="inlineStr">
-        <is>
-          <t>一部回答</t>
-        </is>
-      </c>
-      <c r="H77" s="25" t="inlineStr"/>
+      <c r="H77" s="34" t="inlineStr"/>
     </row>
     <row r="78" ht="34" customHeight="1">
       <c r="A78" s="37" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F78" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
@@ -10030,22 +10030,22 @@
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -10068,27 +10068,27 @@
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H80" s="25" t="inlineStr"/>
@@ -10106,22 +10106,22 @@
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
@@ -10144,22 +10144,22 @@
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
@@ -10182,22 +10182,22 @@
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10220,22 +10220,22 @@
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10258,22 +10258,22 @@
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -10372,22 +10372,22 @@
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -10410,22 +10410,22 @@
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -10524,22 +10524,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -10562,22 +10562,22 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -10638,22 +10638,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -10676,22 +10676,22 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -10714,22 +10714,22 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -10752,22 +10752,22 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -10790,22 +10790,22 @@
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -10828,22 +10828,22 @@
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -10866,22 +10866,22 @@
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(2),doc18 5-6</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -10899,27 +10899,27 @@
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -10937,27 +10937,27 @@
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -10975,27 +10975,27 @@
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc35§7-3(2),doc18 5-6</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11013,27 +11013,27 @@
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -11051,27 +11051,27 @@
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -11089,27 +11089,27 @@
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -11127,27 +11127,27 @@
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -11165,27 +11165,27 @@
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -11203,27 +11203,27 @@
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -11241,27 +11241,27 @@
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -11284,22 +11284,22 @@
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -11322,22 +11322,22 @@
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -11360,22 +11360,22 @@
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -11398,22 +11398,22 @@
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -11436,22 +11436,22 @@
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -11474,22 +11474,22 @@
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -11512,22 +11512,22 @@
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -11626,22 +11626,22 @@
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -11664,22 +11664,22 @@
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -11702,22 +11702,22 @@
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -11740,22 +11740,22 @@
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -11773,27 +11773,27 @@
       </c>
       <c r="B125" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>認知症対応型通所介護を再開するかどうか</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc36§3,doc18 施策3-2</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -11811,27 +11811,27 @@
       </c>
       <c r="B126" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc36§3,doc18 4-7(2)</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -11849,27 +11849,27 @@
       </c>
       <c r="B127" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -11887,27 +11887,27 @@
       </c>
       <c r="B128" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -11925,27 +11925,27 @@
       </c>
       <c r="B129" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -11963,27 +11963,27 @@
       </c>
       <c r="B130" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -12001,27 +12001,27 @@
       </c>
       <c r="B131" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12039,27 +12039,27 @@
       </c>
       <c r="B132" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -12077,27 +12077,27 @@
       </c>
       <c r="B133" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -12115,27 +12115,27 @@
       </c>
       <c r="B134" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -12153,27 +12153,27 @@
       </c>
       <c r="B135" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc36§2,doc18 2-3</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -12191,27 +12191,27 @@
       </c>
       <c r="B136" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -12229,27 +12229,27 @@
       </c>
       <c r="B137" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -12267,27 +12267,27 @@
       </c>
       <c r="B138" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
@@ -12305,27 +12305,27 @@
       </c>
       <c r="B139" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
@@ -12343,27 +12343,27 @@
       </c>
       <c r="B140" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
@@ -12381,27 +12381,27 @@
       </c>
       <c r="B141" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E141" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
@@ -12419,27 +12419,27 @@
       </c>
       <c r="B142" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G142" s="23" t="inlineStr">
@@ -12457,27 +12457,27 @@
       </c>
       <c r="B143" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C143" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E143" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G143" s="23" t="inlineStr">
@@ -12495,346 +12495,346 @@
       </c>
       <c r="B144" s="24" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C144" s="25" t="inlineStr">
+        <is>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+        </is>
+      </c>
+      <c r="D144" s="25" t="inlineStr">
+        <is>
+          <t>施策の書きぶりに影響。</t>
+        </is>
+      </c>
+      <c r="E144" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F144" s="23" t="inlineStr">
+        <is>
+          <t>doc01-12</t>
+        </is>
+      </c>
+      <c r="G144" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H144" s="25" t="inlineStr"/>
+    </row>
+    <row r="145" ht="34" customHeight="1">
+      <c r="A145" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B145" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C145" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D145" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E145" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F145" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G145" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H145" s="25" t="inlineStr"/>
+    </row>
+    <row r="146" ht="34" customHeight="1">
+      <c r="A146" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B146" s="24" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C144" s="25" t="inlineStr">
+      <c r="C146" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D146" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E146" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F146" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G146" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H146" s="25" t="inlineStr"/>
+    </row>
+    <row r="147" ht="34" customHeight="1">
+      <c r="A147" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B147" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C147" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D147" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E147" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F147" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G147" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H147" s="25" t="inlineStr"/>
+    </row>
+    <row r="148" ht="34" customHeight="1">
+      <c r="A148" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B148" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C148" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D148" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E148" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F148" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G148" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H148" s="25" t="inlineStr"/>
+    </row>
+    <row r="149" ht="34" customHeight="1">
+      <c r="A149" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B149" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C149" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D149" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E149" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F149" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G149" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H149" s="25" t="inlineStr"/>
+    </row>
+    <row r="150" ht="34" customHeight="1">
+      <c r="A150" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B150" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C150" s="25" t="inlineStr">
         <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D144" s="25" t="inlineStr">
+      <c r="D150" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E144" s="23" t="inlineStr">
+      <c r="E150" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F144" s="23" t="inlineStr">
+      <c r="F150" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G144" s="23" t="inlineStr">
+      <c r="G150" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H144" s="25" t="inlineStr"/>
-    </row>
-    <row r="145" ht="34" customHeight="1">
-      <c r="A145" s="38" t="inlineStr">
+      <c r="H150" s="25" t="inlineStr"/>
+    </row>
+    <row r="151" ht="34" customHeight="1">
+      <c r="A151" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B145" s="24" t="inlineStr">
+      <c r="B151" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C145" s="25" t="inlineStr">
+      <c r="C151" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D145" s="25" t="inlineStr">
+      <c r="D151" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E145" s="23" t="inlineStr">
+      <c r="E151" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F145" s="23" t="inlineStr">
+      <c r="F151" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G145" s="23" t="inlineStr">
+      <c r="G151" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H145" s="25" t="inlineStr"/>
-    </row>
-    <row r="146" ht="34" customHeight="1">
-      <c r="A146" s="38" t="inlineStr">
+      <c r="H151" s="25" t="inlineStr"/>
+    </row>
+    <row r="152" ht="34" customHeight="1">
+      <c r="A152" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B146" s="24" t="inlineStr">
+      <c r="B152" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C146" s="25" t="inlineStr">
+      <c r="C152" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D146" s="25" t="inlineStr">
+      <c r="D152" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E146" s="23" t="inlineStr">
+      <c r="E152" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F146" s="23" t="inlineStr">
+      <c r="F152" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G146" s="23" t="inlineStr">
+      <c r="G152" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H146" s="25" t="inlineStr"/>
-    </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="39" t="inlineStr">
+      <c r="H152" s="25" t="inlineStr"/>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="149" ht="34" customHeight="1">
-      <c r="A149" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B149" s="41" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C149" s="42" t="inlineStr">
-        <is>
-          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
-        </is>
-      </c>
-      <c r="D149" s="42" t="inlineStr">
-        <is>
-          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
-        </is>
-      </c>
-      <c r="E149" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F149" s="40" t="inlineStr">
-        <is>
-          <t>doc35§7-3(1)</t>
-        </is>
-      </c>
-      <c r="G149" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H149" s="42" t="inlineStr"/>
-    </row>
-    <row r="150" ht="34" customHeight="1">
-      <c r="A150" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B150" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C150" s="42" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D150" s="42" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E150" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F150" s="40" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G150" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H150" s="42" t="inlineStr"/>
-    </row>
-    <row r="151" ht="34" customHeight="1">
-      <c r="A151" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B151" s="41" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C151" s="42" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D151" s="42" t="inlineStr">
-        <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
-        </is>
-      </c>
-      <c r="E151" s="40" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F151" s="40" t="inlineStr">
-        <is>
-          <t>doc28§4</t>
-        </is>
-      </c>
-      <c r="G151" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H151" s="42" t="inlineStr"/>
-    </row>
-    <row r="152" ht="34" customHeight="1">
-      <c r="A152" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B152" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C152" s="42" t="inlineStr">
-        <is>
-          <t>所得段階別の第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D152" s="42" t="inlineStr">
-        <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
-        </is>
-      </c>
-      <c r="E152" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F152" s="40" t="inlineStr">
-        <is>
-          <t>doc28§2</t>
-        </is>
-      </c>
-      <c r="G152" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H152" s="42" t="inlineStr"/>
-    </row>
-    <row r="153" ht="34" customHeight="1">
-      <c r="A153" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B153" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C153" s="42" t="inlineStr">
-        <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
-        </is>
-      </c>
-      <c r="D153" s="42" t="inlineStr">
-        <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
-        </is>
-      </c>
-      <c r="E153" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-59</t>
-        </is>
-      </c>
-      <c r="F153" s="40" t="inlineStr">
-        <is>
-          <t>doc28§1</t>
-        </is>
-      </c>
-      <c r="G153" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H153" s="42" t="inlineStr"/>
-    </row>
-    <row r="154" ht="34" customHeight="1">
-      <c r="A154" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B154" s="41" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C154" s="42" t="inlineStr">
-        <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
-        </is>
-      </c>
-      <c r="D154" s="42" t="inlineStr">
-        <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
-        </is>
-      </c>
-      <c r="E154" s="40" t="inlineStr">
-        <is>
-          <t>Ⅰ-09</t>
-        </is>
-      </c>
-      <c r="F154" s="40" t="inlineStr">
-        <is>
-          <t>doc27§1-1</t>
-        </is>
-      </c>
-      <c r="G154" s="40" t="inlineStr">
-        <is>
-          <t>解決済（一部再掲）</t>
-        </is>
-      </c>
-      <c r="H154" s="42" t="inlineStr"/>
     </row>
     <row r="155" ht="34" customHeight="1">
       <c r="A155" s="40" t="inlineStr">
@@ -12844,27 +12844,27 @@
       </c>
       <c r="B155" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C155" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
         </is>
       </c>
       <c r="D155" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
         </is>
       </c>
       <c r="E155" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F155" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc35§7-3(1)</t>
         </is>
       </c>
       <c r="G155" s="40" t="inlineStr">
@@ -12882,32 +12882,32 @@
       </c>
       <c r="B156" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C156" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D156" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E156" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F156" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G156" s="40" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H156" s="42" t="inlineStr"/>
@@ -12920,27 +12920,27 @@
       </c>
       <c r="B157" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C157" s="42" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D157" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E157" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F157" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G157" s="40" t="inlineStr">
@@ -12958,27 +12958,27 @@
       </c>
       <c r="B158" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C158" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D158" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E158" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F158" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G158" s="40" t="inlineStr">
@@ -12996,27 +12996,27 @@
       </c>
       <c r="B159" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C159" s="42" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D159" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E159" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F159" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G159" s="40" t="inlineStr">
@@ -13034,32 +13034,32 @@
       </c>
       <c r="B160" s="41" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C160" s="42" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D160" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E160" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F160" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G160" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H160" s="42" t="inlineStr"/>
@@ -13072,27 +13072,27 @@
       </c>
       <c r="B161" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C161" s="42" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D161" s="42" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E161" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F161" s="40" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G161" s="40" t="inlineStr">
@@ -13110,32 +13110,32 @@
       </c>
       <c r="B162" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C162" s="42" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D162" s="42" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E162" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F162" s="40" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G162" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H162" s="42" t="inlineStr"/>
@@ -13148,27 +13148,27 @@
       </c>
       <c r="B163" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C163" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D163" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E163" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F163" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G163" s="40" t="inlineStr">
@@ -13186,27 +13186,27 @@
       </c>
       <c r="B164" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C164" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D164" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E164" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F164" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G164" s="40" t="inlineStr">
@@ -13224,27 +13224,27 @@
       </c>
       <c r="B165" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C165" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D165" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E165" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F165" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G165" s="40" t="inlineStr">
@@ -13262,48 +13262,276 @@
       </c>
       <c r="B166" s="41" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C166" s="42" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の範囲</t>
+        </is>
+      </c>
+      <c r="D166" s="42" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+        </is>
+      </c>
+      <c r="E166" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F166" s="40" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G166" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H166" s="42" t="inlineStr"/>
+    </row>
+    <row r="167" ht="34" customHeight="1">
+      <c r="A167" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B167" s="41" t="inlineStr">
+        <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C166" s="42" t="inlineStr">
+      <c r="C167" s="42" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D167" s="42" t="inlineStr">
+        <is>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+        </is>
+      </c>
+      <c r="E167" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F167" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3,§4</t>
+        </is>
+      </c>
+      <c r="G167" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H167" s="42" t="inlineStr"/>
+    </row>
+    <row r="168" ht="34" customHeight="1">
+      <c r="A168" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B168" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C168" s="42" t="inlineStr">
+        <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D168" s="42" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E168" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F168" s="40" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G168" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H168" s="42" t="inlineStr"/>
+    </row>
+    <row r="169" ht="34" customHeight="1">
+      <c r="A169" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B169" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C169" s="42" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D169" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E169" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F169" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G169" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H169" s="42" t="inlineStr"/>
+    </row>
+    <row r="170" ht="34" customHeight="1">
+      <c r="A170" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B170" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C170" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D170" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E170" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F170" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G170" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H170" s="42" t="inlineStr"/>
+    </row>
+    <row r="171" ht="34" customHeight="1">
+      <c r="A171" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B171" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C171" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D171" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E171" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F171" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G171" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H171" s="42" t="inlineStr"/>
+    </row>
+    <row r="172" ht="34" customHeight="1">
+      <c r="A172" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B172" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C172" s="42" t="inlineStr">
         <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D166" s="42" t="inlineStr">
+      <c r="D172" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E166" s="40" t="inlineStr">
+      <c r="E172" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F166" s="40" t="inlineStr">
+      <c r="F172" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G166" s="40" t="inlineStr">
+      <c r="G172" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H166" s="42" t="inlineStr"/>
+      <c r="H172" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H146"/>
+  <autoFilter ref="A4:H152"/>
   <mergeCells count="3">
-    <mergeCell ref="A148:H148"/>
+    <mergeCell ref="A154:H154"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$156</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。★9/15：見込量算定の第1次概算を反映（doc35）。あわせて素案の記述を令和8年度の交付金評価指標で検算し、複数の訂正を行った。(1)中長期の保険料を算定し5-11の【要確認】を解消（αを23%据え置くと令和22年度6,883円、3年ごとに1ポイント上がると8,379円）。(2)標準給付費の様式を埋め5-6を確定（3か年854,014千円）。5-7と完全に一致。(3)交付金の評価指標を令和8年度で検算したところ、素案の記述の多くが令和6年度または令和4年度の評価に基づいており実態と食い違っていた。通いの場への参加率は0→8点満点（最上位の段階は全国で約10%）、参加促進のアウトリーチは9点満点、地域リハビリテーションの推進は0→7点満点、計画の進捗管理（目標Ⅰの3項目）は0→48点満点。一方、要介護3〜5の状態の変化は2指標とも0点（35点減）、認知症サポーター数は12点中0点、難聴は20点中0点。施策1-1を「通いの場の再構築と参加率の向上」から「通いの場の開催頻度の向上と地区差の是正」に改称し、課題3の見出しも改めた。(4)6-3の成果目標・活動指標に令和8年度の得点と全国平均を併記し、維持6指標・引上げ5指標に整理。(5)認知症基本法13条1項・成年後見促進法14条1項を確認し1-2の【要確認】を解消。素案は2,197行→2,341行。★9/15：3次にわたり修正。(1)見込量算定の第1次概算を反映（doc35）。(2)令和8年度の交付金評価指標で全記述を検算し、施策1-1の名称と課題3の見出しを改めた。(3)推計の系列を統一し、介護給付費と予防給付費を分離、見込量の自己点検を実施。5-12（据え置き項目31件）を新設。素案は約115頁→2,449行（段落約4,400・表約125・図20）。残る空欄は交付金の交付見込額、高齢者福祉サービスの量の目標の一部、委員名簿・パブコメなど確定後に記入するもの。★9/16：交付金の目標別に全国平均と対比したところ、素案2-8の「認知症総合支援が全国平均を下回る唯一の目標」が誤りと判明（上回るのは3目標、下回るのは5目標。認知症総合支援は差が最大の▲19.1点）。2-8に目標別の対比表を新設し関係箇所を訂正した。あわせて薄い節を埋めた（1-5日常生活圏域・4-2〜4-4基本目標の導入・5-10低所得者）。6-4に乖離の検証の見直しの目安（±5%以内／±5〜12%／±12%超）を、6-5に計画期間中に確定する5項目を新設。±12%は推計の誤差の絶対値の平均11.9%（保険料月額約700円）によるもので、この幅を超える乖離は基金の取崩しでは吸収できない。素案は2,449行→2,509行。★9/16：認知症施策推進計画としての検討（doc36）。本計画は認知症基本法第13条第1項の市町村計画を兼ねるが、認知症施策は施策4-4の1本のみで基本法の基本的施策との対応が示されていなかった。第4章に4-7「認知症施策推進計画としての位置づけ」を新設し、3つの基本的な考え方（新しい認知症観・本人および家族等の参画・共生社会）、基本法第14〜23条の10項目と本計画の施策との対応表、本村の状況、本人・家族の参画の方法、指標8件を掲載した。2-3に認知症高齢者の状況（自立度Ⅱ以上161人・2年間で22.0%増・認定者に占める割合63.6%）を新設。あわせて第4章の施策番号に「施策」を冠し、基本目標の節番号との衝突（4-4が基本目標4と施策4-4の両方を指す状態）を解消した。素案は2,509行→2,633行。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。★9/15：見込量算定の第1次概算を反映（doc35）。あわせて素案の記述を令和8年度の交付金評価指標で検算し、複数の訂正を行った。(1)中長期の保険料を算定し5-11の【要確認】を解消（αを23%据え置くと令和22年度6,883円、3年ごとに1ポイント上がると8,379円）。(2)標準給付費の様式を埋め5-6を確定（3か年854,014千円）。5-7と完全に一致。(3)交付金の評価指標を令和8年度で検算したところ、素案の記述の多くが令和6年度または令和4年度の評価に基づいており実態と食い違っていた。通いの場への参加率は0→8点満点（最上位の段階は全国で約10%）、参加促進のアウトリーチは9点満点、地域リハビリテーションの推進は0→7点満点、計画の進捗管理（目標Ⅰの3項目）は0→48点満点。一方、要介護3〜5の状態の変化は2指標とも0点（35点減）、認知症サポーター数は12点中0点、難聴は20点中0点。施策1-1を「通いの場の再構築と参加率の向上」から「通いの場の開催頻度の向上と地区差の是正」に改称し、課題3の見出しも改めた。(4)6-3の成果目標・活動指標に令和8年度の得点と全国平均を併記し、維持6指標・引上げ5指標に整理。(5)認知症基本法13条1項・成年後見促進法14条1項を確認し1-2の【要確認】を解消。素案は2,197行→2,341行。★9/15：3次にわたり修正。(1)見込量算定の第1次概算を反映（doc35）。(2)令和8年度の交付金評価指標で全記述を検算し、施策1-1の名称と課題3の見出しを改めた。(3)推計の系列を統一し、介護給付費と予防給付費を分離、見込量の自己点検を実施。5-12（据え置き項目31件）を新設。素案は約115頁→2,449行（段落約4,400・表約125・図20）。残る空欄は交付金の交付見込額、高齢者福祉サービスの量の目標の一部、委員名簿・パブコメなど確定後に記入するもの。★9/16：交付金の目標別に全国平均と対比したところ、素案2-8の「認知症総合支援が全国平均を下回る唯一の目標」が誤りと判明（上回るのは3目標、下回るのは5目標。認知症総合支援は差が最大の▲19.1点）。2-8に目標別の対比表を新設し関係箇所を訂正した。あわせて薄い節を埋めた（1-5日常生活圏域・4-2〜4-4基本目標の導入・5-10低所得者）。6-4に乖離の検証の見直しの目安（±5%以内／±5〜12%／±12%超）を、6-5に計画期間中に確定する5項目を新設。±12%は推計の誤差の絶対値の平均11.9%（保険料月額約700円）によるもので、この幅を超える乖離は基金の取崩しでは吸収できない。素案は2,449行→2,509行。★9/16：認知症施策推進計画としての検討（doc36）。本計画は認知症基本法第13条第1項の市町村計画を兼ねるが、認知症施策は施策4-4の1本のみで基本法の基本的施策との対応が示されていなかった。第4章に4-7「認知症施策推進計画としての位置づけ」を新設し、3つの基本的な考え方（新しい認知症観・本人および家族等の参画・共生社会）、基本法第14〜23条の10項目と本計画の施策との対応表、本村の状況、本人・家族の参画の方法、指標8件を掲載した。2-3に認知症高齢者の状況（自立度Ⅱ以上161人・2年間で22.0%増・認定者に占める割合63.6%）を新設。あわせて第4章の施策番号に「施策」を冠し、基本目標の節番号との衝突（4-4が基本目標4と施策4-4の両方を指す状態）を解消した。素案は2,509行→2,633行。★9/16（第2次）：認知症基本法の条文（令和5年法律第65号）と厚生労働省の概要資料を受領し、素案4-7を検算した。3件の誤りを訂正——(1)市町村が計画に位置づけるのは第14〜23条の10項目ではなく第14〜21条の8項目（第22条以降は主語が「国は」）、(2)意見聴取の根拠は第13条第3項ではなく「第13条第3項において準用する第12条第3項」、(3)第15条バリアフリー化の対応施策は住まい・除雪ではなく移動・見守り（条文の例示による）。あわせて条文から新たに4件を素案に追加——第13条第3項が準用する第12条第4〜7項（計画の公表・実施状況の評価と公表・5年ごとの検討・評価結果の取りまとめ時の意見聴取）、第9条（認知症の日9月21日・認知症月間9月）、第7条（公共交通・金融機関・小売業者等の合理的配慮）、第16条第2項（若年性認知症の雇用継続）。4-7を全面改訂し8つの見出しに再構成した。素案は2,633行→2,677行。</t>
         </is>
       </c>
     </row>
@@ -7136,7 +7136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9612,12 +9612,12 @@
       </c>
       <c r="C68" s="34" t="inlineStr">
         <is>
-          <t>認知症の人およびご家族から意見を聴く方法</t>
+          <t>認知症施策の実施状況の評価と公表の運用</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
+          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
         </is>
       </c>
       <c r="E68" s="35" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="F68" s="35" t="inlineStr">
         <is>
-          <t>doc36§5,doc18 4-7(4)</t>
+          <t>doc36§10-1,doc18 4-7(6)</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -9650,22 +9650,22 @@
       </c>
       <c r="C69" s="34" t="inlineStr">
         <is>
-          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
+          <t>認知症の人およびご家族から意見を聴く方法</t>
         </is>
       </c>
       <c r="D69" s="34" t="inlineStr">
         <is>
-          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
+          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§5,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
@@ -9683,27 +9683,27 @@
       </c>
       <c r="B70" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C70" s="34" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
         </is>
       </c>
       <c r="E70" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F70" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G70" s="35" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="C71" s="34" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D71" s="34" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G71" s="35" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="C72" s="34" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D72" s="34" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E72" s="35" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="F72" s="35" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -9797,32 +9797,32 @@
       </c>
       <c r="B73" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C73" s="34" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D73" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G73" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H73" s="34" t="inlineStr"/>
@@ -9840,27 +9840,27 @@
       </c>
       <c r="C74" s="34" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
       <c r="D74" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
       <c r="E74" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
       <c r="F74" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G74" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H74" s="34" t="inlineStr"/>
@@ -9878,12 +9878,12 @@
       </c>
       <c r="C75" s="34" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
         </is>
       </c>
       <c r="D75" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
         </is>
       </c>
       <c r="E75" s="35" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc27§3-3</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
@@ -9916,22 +9916,22 @@
       </c>
       <c r="C76" s="34" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
         </is>
       </c>
       <c r="D76" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
         </is>
       </c>
       <c r="E76" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-09,Ⅰ-10</t>
         </is>
       </c>
       <c r="F76" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc27§5-2</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -9954,68 +9954,68 @@
       </c>
       <c r="C77" s="34" t="inlineStr">
         <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D77" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E77" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F77" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G77" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H77" s="34" t="inlineStr"/>
+    </row>
+    <row r="78" ht="34" customHeight="1">
+      <c r="A78" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B78" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C78" s="34" t="inlineStr">
+        <is>
           <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
-      <c r="D77" s="34" t="inlineStr">
+      <c r="D78" s="34" t="inlineStr">
         <is>
           <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
-      <c r="E77" s="35" t="inlineStr">
+      <c r="E78" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="F77" s="35" t="inlineStr">
+      <c r="F78" s="35" t="inlineStr">
         <is>
           <t>doc27§6</t>
         </is>
       </c>
-      <c r="G77" s="35" t="inlineStr">
+      <c r="G78" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H77" s="34" t="inlineStr"/>
-    </row>
-    <row r="78" ht="34" customHeight="1">
-      <c r="A78" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B78" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C78" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D78" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E78" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F78" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G78" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H78" s="25" t="inlineStr"/>
+      <c r="H78" s="34" t="inlineStr"/>
     </row>
     <row r="79" ht="34" customHeight="1">
       <c r="A79" s="37" t="inlineStr">
@@ -10030,22 +10030,22 @@
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F79" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-1,doc30§2-4</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
@@ -10068,27 +10068,27 @@
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc02§16,§22</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H80" s="25" t="inlineStr"/>
@@ -10106,27 +10106,27 @@
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H81" s="25" t="inlineStr"/>
@@ -10144,22 +10144,22 @@
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
@@ -10182,22 +10182,22 @@
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10258,17 +10258,17 @@
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
@@ -10334,22 +10334,22 @@
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -10372,22 +10372,22 @@
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -10410,22 +10410,22 @@
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10448,22 +10448,22 @@
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -10486,22 +10486,22 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -10524,22 +10524,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -10600,22 +10600,22 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -10638,17 +10638,17 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
@@ -10676,17 +10676,17 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -10752,22 +10752,22 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -10790,22 +10790,22 @@
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -10866,22 +10866,22 @@
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -10904,22 +10904,22 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -10942,22 +10942,22 @@
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -10980,22 +10980,22 @@
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(2),doc18 5-6</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11013,27 +11013,27 @@
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc36§10-4,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -11051,27 +11051,27 @@
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc35§7-3(2),doc18 5-6</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -11094,22 +11094,22 @@
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -11127,27 +11127,27 @@
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -11165,27 +11165,27 @@
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -11203,27 +11203,27 @@
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -11246,22 +11246,22 @@
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -11279,27 +11279,27 @@
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -11317,27 +11317,27 @@
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -11360,22 +11360,22 @@
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -11398,22 +11398,22 @@
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -11436,22 +11436,22 @@
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -11474,22 +11474,22 @@
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -11512,22 +11512,22 @@
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -11626,22 +11626,22 @@
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -11664,22 +11664,22 @@
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -11702,22 +11702,22 @@
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -11740,22 +11740,22 @@
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -11778,22 +11778,22 @@
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護を再開するかどうか</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 施策3-2</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -11816,22 +11816,22 @@
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 4-7(2)</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -11854,22 +11854,22 @@
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
+          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
+          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§10-2,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -11892,22 +11892,22 @@
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc36§10-3,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -11930,22 +11930,22 @@
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>認知症対応型通所介護を再開するかどうか</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc36§3,doc18 施策3-2</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -11963,27 +11963,27 @@
       </c>
       <c r="B130" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc36§3,doc18 4-7(2)</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -12001,27 +12001,27 @@
       </c>
       <c r="B131" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12039,27 +12039,27 @@
       </c>
       <c r="B132" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -12077,27 +12077,27 @@
       </c>
       <c r="B133" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -12120,22 +12120,22 @@
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -12158,22 +12158,22 @@
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc36§2,doc18 2-3</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -12191,27 +12191,27 @@
       </c>
       <c r="B136" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -12229,27 +12229,27 @@
       </c>
       <c r="B137" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -12267,27 +12267,27 @@
       </c>
       <c r="B138" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
@@ -12305,27 +12305,27 @@
       </c>
       <c r="B139" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc36§2,doc18 2-3</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
@@ -12348,12 +12348,12 @@
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E141" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
@@ -12419,27 +12419,27 @@
       </c>
       <c r="B142" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G142" s="23" t="inlineStr">
@@ -12457,27 +12457,27 @@
       </c>
       <c r="B143" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C143" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E143" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G143" s="23" t="inlineStr">
@@ -12495,27 +12495,27 @@
       </c>
       <c r="B144" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C144" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F144" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G144" s="23" t="inlineStr">
@@ -12533,27 +12533,27 @@
       </c>
       <c r="B145" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C145" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E145" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F145" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G145" s="23" t="inlineStr">
@@ -12571,27 +12571,27 @@
       </c>
       <c r="B146" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C146" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E146" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F146" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G146" s="23" t="inlineStr">
@@ -12609,27 +12609,27 @@
       </c>
       <c r="B147" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C147" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E147" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F147" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G147" s="23" t="inlineStr">
@@ -12647,27 +12647,27 @@
       </c>
       <c r="B148" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C148" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F148" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G148" s="23" t="inlineStr">
@@ -12685,27 +12685,27 @@
       </c>
       <c r="B149" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C149" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E149" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F149" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G149" s="23" t="inlineStr">
@@ -12728,265 +12728,265 @@
       </c>
       <c r="C150" s="25" t="inlineStr">
         <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D150" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E150" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F150" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G150" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H150" s="25" t="inlineStr"/>
+    </row>
+    <row r="151" ht="34" customHeight="1">
+      <c r="A151" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B151" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C151" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D151" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E151" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F151" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G151" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H151" s="25" t="inlineStr"/>
+    </row>
+    <row r="152" ht="34" customHeight="1">
+      <c r="A152" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B152" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C152" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D152" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E152" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F152" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G152" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H152" s="25" t="inlineStr"/>
+    </row>
+    <row r="153" ht="34" customHeight="1">
+      <c r="A153" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B153" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C153" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D153" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E153" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F153" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G153" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H153" s="25" t="inlineStr"/>
+    </row>
+    <row r="154" ht="34" customHeight="1">
+      <c r="A154" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B154" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C154" s="25" t="inlineStr">
+        <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D150" s="25" t="inlineStr">
+      <c r="D154" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E150" s="23" t="inlineStr">
+      <c r="E154" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F150" s="23" t="inlineStr">
+      <c r="F154" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G150" s="23" t="inlineStr">
+      <c r="G154" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H150" s="25" t="inlineStr"/>
-    </row>
-    <row r="151" ht="34" customHeight="1">
-      <c r="A151" s="38" t="inlineStr">
+      <c r="H154" s="25" t="inlineStr"/>
+    </row>
+    <row r="155" ht="34" customHeight="1">
+      <c r="A155" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B151" s="24" t="inlineStr">
+      <c r="B155" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C151" s="25" t="inlineStr">
+      <c r="C155" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D151" s="25" t="inlineStr">
+      <c r="D155" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E151" s="23" t="inlineStr">
+      <c r="E155" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F151" s="23" t="inlineStr">
+      <c r="F155" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G151" s="23" t="inlineStr">
+      <c r="G155" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H151" s="25" t="inlineStr"/>
-    </row>
-    <row r="152" ht="34" customHeight="1">
-      <c r="A152" s="38" t="inlineStr">
+      <c r="H155" s="25" t="inlineStr"/>
+    </row>
+    <row r="156" ht="34" customHeight="1">
+      <c r="A156" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B152" s="24" t="inlineStr">
+      <c r="B156" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C152" s="25" t="inlineStr">
+      <c r="C156" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D152" s="25" t="inlineStr">
+      <c r="D156" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E152" s="23" t="inlineStr">
+      <c r="E156" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F152" s="23" t="inlineStr">
+      <c r="F156" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G152" s="23" t="inlineStr">
+      <c r="G156" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H152" s="25" t="inlineStr"/>
-    </row>
-    <row r="154" ht="20" customHeight="1">
-      <c r="A154" s="39" t="inlineStr">
+      <c r="H156" s="25" t="inlineStr"/>
+    </row>
+    <row r="158" ht="20" customHeight="1">
+      <c r="A158" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="155" ht="34" customHeight="1">
-      <c r="A155" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B155" s="41" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C155" s="42" t="inlineStr">
-        <is>
-          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
-        </is>
-      </c>
-      <c r="D155" s="42" t="inlineStr">
-        <is>
-          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
-        </is>
-      </c>
-      <c r="E155" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F155" s="40" t="inlineStr">
-        <is>
-          <t>doc35§7-3(1)</t>
-        </is>
-      </c>
-      <c r="G155" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H155" s="42" t="inlineStr"/>
-    </row>
-    <row r="156" ht="34" customHeight="1">
-      <c r="A156" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B156" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C156" s="42" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D156" s="42" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E156" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F156" s="40" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G156" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H156" s="42" t="inlineStr"/>
-    </row>
-    <row r="157" ht="34" customHeight="1">
-      <c r="A157" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B157" s="41" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C157" s="42" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D157" s="42" t="inlineStr">
-        <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
-        </is>
-      </c>
-      <c r="E157" s="40" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F157" s="40" t="inlineStr">
-        <is>
-          <t>doc28§4</t>
-        </is>
-      </c>
-      <c r="G157" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H157" s="42" t="inlineStr"/>
-    </row>
-    <row r="158" ht="34" customHeight="1">
-      <c r="A158" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B158" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C158" s="42" t="inlineStr">
-        <is>
-          <t>所得段階別の第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D158" s="42" t="inlineStr">
-        <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
-        </is>
-      </c>
-      <c r="E158" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F158" s="40" t="inlineStr">
-        <is>
-          <t>doc28§2</t>
-        </is>
-      </c>
-      <c r="G158" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H158" s="42" t="inlineStr"/>
     </row>
     <row r="159" ht="34" customHeight="1">
       <c r="A159" s="40" t="inlineStr">
@@ -12996,27 +12996,27 @@
       </c>
       <c r="B159" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C159" s="42" t="inlineStr">
         <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
+          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
         </is>
       </c>
       <c r="D159" s="42" t="inlineStr">
         <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
+          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
         </is>
       </c>
       <c r="E159" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F159" s="40" t="inlineStr">
         <is>
-          <t>doc28§1</t>
+          <t>doc35§7-3(1)</t>
         </is>
       </c>
       <c r="G159" s="40" t="inlineStr">
@@ -13034,32 +13034,32 @@
       </c>
       <c r="B160" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C160" s="42" t="inlineStr">
         <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D160" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E160" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F160" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-1</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G160" s="40" t="inlineStr">
         <is>
-          <t>解決済（一部再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H160" s="42" t="inlineStr"/>
@@ -13072,27 +13072,27 @@
       </c>
       <c r="B161" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C161" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D161" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E161" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F161" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G161" s="40" t="inlineStr">
@@ -13110,32 +13110,32 @@
       </c>
       <c r="B162" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C162" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D162" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E162" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F162" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G162" s="40" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H162" s="42" t="inlineStr"/>
@@ -13148,27 +13148,27 @@
       </c>
       <c r="B163" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C163" s="42" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D163" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E163" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F163" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G163" s="40" t="inlineStr">
@@ -13191,27 +13191,27 @@
       </c>
       <c r="C164" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D164" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E164" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F164" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G164" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H164" s="42" t="inlineStr"/>
@@ -13229,22 +13229,22 @@
       </c>
       <c r="C165" s="42" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D165" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E165" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F165" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G165" s="40" t="inlineStr">
@@ -13262,32 +13262,32 @@
       </c>
       <c r="B166" s="41" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C166" s="42" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D166" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E166" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F166" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G166" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H166" s="42" t="inlineStr"/>
@@ -13300,27 +13300,27 @@
       </c>
       <c r="B167" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C167" s="42" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D167" s="42" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E167" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F167" s="40" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G167" s="40" t="inlineStr">
@@ -13338,27 +13338,27 @@
       </c>
       <c r="B168" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C168" s="42" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D168" s="42" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E168" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F168" s="40" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G168" s="40" t="inlineStr">
@@ -13376,27 +13376,27 @@
       </c>
       <c r="B169" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C169" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D169" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E169" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F169" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G169" s="40" t="inlineStr">
@@ -13414,27 +13414,27 @@
       </c>
       <c r="B170" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C170" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D170" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E170" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F170" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G170" s="40" t="inlineStr">
@@ -13457,22 +13457,22 @@
       </c>
       <c r="C171" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D171" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E171" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F171" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G171" s="40" t="inlineStr">
@@ -13495,43 +13495,195 @@
       </c>
       <c r="C172" s="42" t="inlineStr">
         <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D172" s="42" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E172" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F172" s="40" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G172" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H172" s="42" t="inlineStr"/>
+    </row>
+    <row r="173" ht="34" customHeight="1">
+      <c r="A173" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B173" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C173" s="42" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D173" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E173" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F173" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G173" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H173" s="42" t="inlineStr"/>
+    </row>
+    <row r="174" ht="34" customHeight="1">
+      <c r="A174" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B174" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C174" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D174" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E174" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F174" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G174" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H174" s="42" t="inlineStr"/>
+    </row>
+    <row r="175" ht="34" customHeight="1">
+      <c r="A175" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B175" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C175" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D175" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E175" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F175" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G175" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H175" s="42" t="inlineStr"/>
+    </row>
+    <row r="176" ht="34" customHeight="1">
+      <c r="A176" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B176" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C176" s="42" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D172" s="42" t="inlineStr">
+      <c r="D176" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E172" s="40" t="inlineStr">
+      <c r="E176" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F172" s="40" t="inlineStr">
+      <c r="F176" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G172" s="40" t="inlineStr">
+      <c r="G176" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H172" s="42" t="inlineStr"/>
+      <c r="H176" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H152"/>
+  <autoFilter ref="A4:H156"/>
   <mergeCells count="3">
-    <mergeCell ref="A154:H154"/>
+    <mergeCell ref="A158:H158"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$159</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P65" s="13" t="inlineStr">
         <is>
-          <t>★9/8：doc30として推計の枠組みを確定。「見える化」システムのデータ定義（受給者数＝年度延べ、D45系の分母＝要介護度別認定者数）を検算のうえ確定し、estimate_services.py により区分別・サービス種類別の見込量を算定。全28サービスのうち令和7年度に実績のある16サービスについて受給者数・利用量・給付費の暫定値を doc18 第5章5-4に投入。施設・居住系の種類別人数は見える化に系列がなく給付費比の按分値のため、村の月報（第2表・第3表）で置き換えが必要。介護給付と予防給付の分離も同じく月報待ち。★9/12：他案件（川崎町・金ケ崎町・大雪）の到達水準と対照し（doc33）、基準年度を令和7年度と確定。見える化の系列別の月数を実測で確認し（D1はR7が11か月、D2/D3/D4は12か月相当）doc30の÷12が正しいことを裏付けて素案5-4に明記。令和9年4月新設4区分の枠と、国の推計ツールのワーニング判定式（閾値＝Q1−2Q〜Q3+2Q）による自己点検の手順を追加。国の推計ツールの出力は未受領で、依頼書18-2として最優先で追加した。★9/15：他案件（大雪・川崎・金ケ崎）の算定の進め方を確認し、本村に適用して第1次概算を実施（doc35）。(1)見込量は需要で置く／地域密着型と総合事業のみ村の供給力が上限、という原則を素案5-4に明記。(2)令和9年4月新設4区分を「―」「要協議」から0に立て直した。(3)夜間対応型訪問介護の令和9年3月末廃止を反映。(4)単価の趨勢を連鎖ラスパイレス指数で実測（R元→R7の年率+1.30%）。3か年平均で固定していることは給付費の5.32%過小＝保険料月額314円に当たる。(5)サービス別の受給者数の年率が▲13.12〜+54.88%と68ポイント開いていることを実測し、伸びをどこまで反映すべきかをバックテストで検証（backtest_growth.py）。φ=0.5・c=5%が最小（WMAPE19.11%）だが一律19.68%に対し改善は2.9%にとどまるため一律を採用すると決定。(6)一律の方法で3年先を予測したときの誤差は絶対値平均11.9%＝保険料月額約700円で、基金取崩24,000千円の効き（702円）と同規模。素案5-4(9)として新設。(7)在宅介護実態調査の施設入所申込みの反映シナリオの枠を素案5-4(3)に新設（+1人／月＝月額75円）。残るのは国の推計ワークシートによる基準年度の置き直しの分解のみ。★9/15（第3次）：推計の系列を統一し、給付費を分離した（doc35§7-3）。(1)素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し5-1・5-2・5-3を全面改訂。5-1に①第1号被保険者数→②認定者数→③受給者数→④利用量→⑤給付費→⑥標準給付費→⑦保険料の連なりを表で明示した。(2)決算（D48-b）の介護サービス等諸費／介護予防サービス等諸費と要介護度別受給者数を突き合わせ、予防給付19,002円・介護給付175,230円の1人あたり給付月額を復元（令和3〜5年度で±1.6%以内の安定）。第10期3か年で介護給付費755,119千円・予防給付費34,344千円に分離し、5-6の空欄を埋めた。(3)見込量の自己点検を実施（check_warning.py）。年度間の変化率は3区分とも4%以内。令和7年度実績→令和9年度見込で±10%超は4件（居宅療養管理指導▲25.3%、短期入所生活介護▲20.8%、訪問入浴介護・地域密着型通所介護は新規計上）。いずれも3か年平均で置くことの副作用であり委員会にお諮りする。(4)地域支援事業費を新系列で置き直し3か年122,737千円（保険料月額+22円）。★9/16：認知症関連を反映（doc36§4）。5-4(7)の必要利用定員総数に認知症高齢者数との対比を追加（自立度Ⅱ以上1人あたりの定員は令和2年0.178人分→令和6年0.168人分。定員は平成28年度以降27人で固定、稼働率93%）。5-5(1)に認知症総合支援事業の6行（初期集中支援推進事業の対象者数・地域支援推進員・認知症カフェ・サポーター養成講座・養成者数・チームオレンジ）を新設。大半が実績未受領のため空欄。村内GHの待機者数と村外GH利用者数が未受領で、定員の増減を委員会に諮れない状態である（優先度A）。</t>
+          <t>★9/8：doc30として推計の枠組みを確定。「見える化」システムのデータ定義（受給者数＝年度延べ、D45系の分母＝要介護度別認定者数）を検算のうえ確定し、estimate_services.py により区分別・サービス種類別の見込量を算定。全28サービスのうち令和7年度に実績のある16サービスについて受給者数・利用量・給付費の暫定値を doc18 第5章5-4に投入。施設・居住系の種類別人数は見える化に系列がなく給付費比の按分値のため、村の月報（第2表・第3表）で置き換えが必要。介護給付と予防給付の分離も同じく月報待ち。★9/12：他案件（川崎町・金ケ崎町・大雪）の到達水準と対照し（doc33）、基準年度を令和7年度と確定。見える化の系列別の月数を実測で確認し（D1はR7が11か月、D2/D3/D4は12か月相当）doc30の÷12が正しいことを裏付けて素案5-4に明記。令和9年4月新設4区分の枠と、国の推計ツールのワーニング判定式（閾値＝Q1−2Q〜Q3+2Q）による自己点検の手順を追加。国の推計ツールの出力は未受領で、依頼書18-2として最優先で追加した。★9/15：他案件（大雪・川崎・金ケ崎）の算定の進め方を確認し、本村に適用して第1次概算を実施（doc35）。(1)見込量は需要で置く／地域密着型と総合事業のみ村の供給力が上限、という原則を素案5-4に明記。(2)令和9年4月新設4区分を「―」「要協議」から0に立て直した。(3)夜間対応型訪問介護の令和9年3月末廃止を反映。(4)単価の趨勢を連鎖ラスパイレス指数で実測（R元→R7の年率+1.30%）。3か年平均で固定していることは給付費の5.32%過小＝保険料月額314円に当たる。(5)サービス別の受給者数の年率が▲13.12〜+54.88%と68ポイント開いていることを実測し、伸びをどこまで反映すべきかをバックテストで検証（backtest_growth.py）。φ=0.5・c=5%が最小（WMAPE19.11%）だが一律19.68%に対し改善は2.9%にとどまるため一律を採用すると決定。(6)一律の方法で3年先を予測したときの誤差は絶対値平均11.9%＝保険料月額約700円で、基金取崩24,000千円の効き（702円）と同規模。素案5-4(9)として新設。(7)在宅介護実態調査の施設入所申込みの反映シナリオの枠を素案5-4(3)に新設（+1人／月＝月額75円）。残るのは国の推計ワークシートによる基準年度の置き直しの分解のみ。★9/15（第3次）：推計の系列を統一し、給付費を分離した（doc35§7-3）。(1)素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し5-1・5-2・5-3を全面改訂。5-1に①第1号被保険者数→②認定者数→③受給者数→④利用量→⑤給付費→⑥標準給付費→⑦保険料の連なりを表で明示した。(2)決算（D48-b）の介護サービス等諸費／介護予防サービス等諸費と要介護度別受給者数を突き合わせ、予防給付19,002円・介護給付175,230円の1人あたり給付月額を復元（令和3〜5年度で±1.6%以内の安定）。第10期3か年で介護給付費755,119千円・予防給付費34,344千円に分離し、5-6の空欄を埋めた。(3)見込量の自己点検を実施（check_warning.py）。年度間の変化率は3区分とも4%以内。令和7年度実績→令和9年度見込で±10%超は4件（居宅療養管理指導▲25.3%、短期入所生活介護▲20.8%、訪問入浴介護・地域密着型通所介護は新規計上）。いずれも3か年平均で置くことの副作用であり委員会にお諮りする。(4)地域支援事業費を新系列で置き直し3か年122,737千円（保険料月額+22円）。★9/16：認知症関連を反映（doc36§4）。5-4(7)の必要利用定員総数に認知症高齢者数との対比を追加（自立度Ⅱ以上1人あたりの定員は令和2年0.178人分→令和6年0.168人分。定員は平成28年度以降27人で固定、稼働率93%）。5-5(1)に認知症総合支援事業の6行（初期集中支援推進事業の対象者数・地域支援推進員・認知症カフェ・サポーター養成講座・養成者数・チームオレンジ）を新設。大半が実績未受領のため空欄。村内GHの待機者数と村外GH利用者数が未受領で、定員の増減を委員会に諮れない状態である（優先度A）。★9/24：他案件（大雪・川崎）のブランチを確認し、大雪の点検から5点を採った（doc37）。(1)利用率の分母を実データで検算（verify_bunbo.py）。見える化のサービス利用率の分母は要介護度別認定者数であり本村の算定と整合、直すところはなかった。ただし国の将来推計が在宅の分母を「認定者数−施設・居住系」とする場合要介護1で58.8%→86.1%、要介護2で107.7%（100%超）に変わるため、ワークシート受領時に確認を要する。要介護2の3区分合計が101.5%で、年度途中の在宅→施設の移行による重複1.5%が判明。(2)単価の趨勢と介護報酬改定率の二重計上を防ぐ断りを5-4(10)①に追加。趨勢は改定を含む実測値のため両者は択一。(3)供給の制約（村内定員の到達率）を算定（estimate_supply.py）。GH令和11年度90.7%・通所介護83.6%で超過なし。年報は施設の所在地を問わないため到達率は上限ではないことを明記。5-4(5)として新設。</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="P68" s="13" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：第9期で県内平均を上回ったため急激な負担増を抑えたい意向。基金取崩も視野。令和9年度の介護報酬改定を見据え現行単価で一旦試算し単価確定後に補正。doc18 第5章5-7に様式と所得段階13段階の枠を作成済。★9/8：サービス諸費の推計（doc30）が出たため、残る停止要因は基金残高と令和6・7年度決算の2件に絞られた。★9/12：保険料算定の5式（金ケ崎町で第9期公表値と一致を確認した構造）と調整交付金見込交付割合の式（α+0.05）−α×F×Gを導入し、本村の第9期を0.32%で再現。限界率23.79%・F×G=1.034を復元。感応度9項目（給付費1%＝月額59円、第1号負担割合1pt＝294円、基金24,000千円＝▲702円）と12パターン（5,936〜7,341円・幅1,406円）を算定し素案5-7に投入（scripts/estimate_premium.py）。保険料の幅のうち702円は基金取崩の判断で決まるため、給付費推計の精緻化より基金方針の決定が先。★9/15：中長期（令和17年度・令和22年度）の保険料をαの2案で算定し素案5-11の【要確認】を解消（据え置き23%なら令和22年度6,883円、3年ごと1pt上昇なら8,379円。scripts/estimate_longterm.py）。素案5-6の標準給付費の様式を埋め3か年854,014千円を確定。5-7の感応度に3行（地域支援事業費+22円／単価の趨勢+314円／推計誤差±約700円）を追加した。残るのはα政令・基金残高・令和6-7年度決算の受領。</t>
+          <t>★議事録で方針決着：第9期で県内平均を上回ったため急激な負担増を抑えたい意向。基金取崩も視野。令和9年度の介護報酬改定を見据え現行単価で一旦試算し単価確定後に補正。doc18 第5章5-7に様式と所得段階13段階の枠を作成済。★9/8：サービス諸費の推計（doc30）が出たため、残る停止要因は基金残高と令和6・7年度決算の2件に絞られた。★9/12：保険料算定の5式（金ケ崎町で第9期公表値と一致を確認した構造）と調整交付金見込交付割合の式（α+0.05）−α×F×Gを導入し、本村の第9期を0.32%で再現。限界率23.79%・F×G=1.034を復元。感応度9項目（給付費1%＝月額59円、第1号負担割合1pt＝294円、基金24,000千円＝▲702円）と12パターン（5,936〜7,341円・幅1,406円）を算定し素案5-7に投入（scripts/estimate_premium.py）。保険料の幅のうち702円は基金取崩の判断で決まるため、給付費推計の精緻化より基金方針の決定が先。★9/15：中長期（令和17年度・令和22年度）の保険料をαの2案で算定し素案5-11の【要確認】を解消（据え置き23%なら令和22年度6,883円、3年ごと1pt上昇なら8,379円。scripts/estimate_longterm.py）。素案5-6の標準給付費の様式を埋め3か年854,014千円を確定。5-7の感応度に3行（地域支援事業費+22円／単価の趨勢+314円／推計誤差±約700円）を追加した。残るのはα政令・基金残高・令和6-7年度決算の受領。★9/24：年度別の保険料収納必要額を算定し素案5-7に新設（doc37§6）。令和9年度6,704円→令和11年度6,799円で95円上がる。給付費が横ばいで第1号被保険者数が1.7%減るため。3か年平均6,756円との差は令和9年度+596千円（余り）・令和10年度▲109千円・令和11年度▲486千円。第10期末の基金残高を見込むには期首残高が必要（未受領）。年度別の過不足は給付費が1%振れるだけで逆転する程度（年間約680千円）であり、基金の役割は年度間の均衡よりも推計の誤差（絶対値平均11.9%）の吸収にある。</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。★9/15：見込量算定の第1次概算を反映（doc35）。あわせて素案の記述を令和8年度の交付金評価指標で検算し、複数の訂正を行った。(1)中長期の保険料を算定し5-11の【要確認】を解消（αを23%据え置くと令和22年度6,883円、3年ごとに1ポイント上がると8,379円）。(2)標準給付費の様式を埋め5-6を確定（3か年854,014千円）。5-7と完全に一致。(3)交付金の評価指標を令和8年度で検算したところ、素案の記述の多くが令和6年度または令和4年度の評価に基づいており実態と食い違っていた。通いの場への参加率は0→8点満点（最上位の段階は全国で約10%）、参加促進のアウトリーチは9点満点、地域リハビリテーションの推進は0→7点満点、計画の進捗管理（目標Ⅰの3項目）は0→48点満点。一方、要介護3〜5の状態の変化は2指標とも0点（35点減）、認知症サポーター数は12点中0点、難聴は20点中0点。施策1-1を「通いの場の再構築と参加率の向上」から「通いの場の開催頻度の向上と地区差の是正」に改称し、課題3の見出しも改めた。(4)6-3の成果目標・活動指標に令和8年度の得点と全国平均を併記し、維持6指標・引上げ5指標に整理。(5)認知症基本法13条1項・成年後見促進法14条1項を確認し1-2の【要確認】を解消。素案は2,197行→2,341行。★9/15：3次にわたり修正。(1)見込量算定の第1次概算を反映（doc35）。(2)令和8年度の交付金評価指標で全記述を検算し、施策1-1の名称と課題3の見出しを改めた。(3)推計の系列を統一し、介護給付費と予防給付費を分離、見込量の自己点検を実施。5-12（据え置き項目31件）を新設。素案は約115頁→2,449行（段落約4,400・表約125・図20）。残る空欄は交付金の交付見込額、高齢者福祉サービスの量の目標の一部、委員名簿・パブコメなど確定後に記入するもの。★9/16：交付金の目標別に全国平均と対比したところ、素案2-8の「認知症総合支援が全国平均を下回る唯一の目標」が誤りと判明（上回るのは3目標、下回るのは5目標。認知症総合支援は差が最大の▲19.1点）。2-8に目標別の対比表を新設し関係箇所を訂正した。あわせて薄い節を埋めた（1-5日常生活圏域・4-2〜4-4基本目標の導入・5-10低所得者）。6-4に乖離の検証の見直しの目安（±5%以内／±5〜12%／±12%超）を、6-5に計画期間中に確定する5項目を新設。±12%は推計の誤差の絶対値の平均11.9%（保険料月額約700円）によるもので、この幅を超える乖離は基金の取崩しでは吸収できない。素案は2,449行→2,509行。★9/16：認知症施策推進計画としての検討（doc36）。本計画は認知症基本法第13条第1項の市町村計画を兼ねるが、認知症施策は施策4-4の1本のみで基本法の基本的施策との対応が示されていなかった。第4章に4-7「認知症施策推進計画としての位置づけ」を新設し、3つの基本的な考え方（新しい認知症観・本人および家族等の参画・共生社会）、基本法第14〜23条の10項目と本計画の施策との対応表、本村の状況、本人・家族の参画の方法、指標8件を掲載した。2-3に認知症高齢者の状況（自立度Ⅱ以上161人・2年間で22.0%増・認定者に占める割合63.6%）を新設。あわせて第4章の施策番号に「施策」を冠し、基本目標の節番号との衝突（4-4が基本目標4と施策4-4の両方を指す状態）を解消した。素案は2,509行→2,633行。★9/16（第2次）：認知症基本法の条文（令和5年法律第65号）と厚生労働省の概要資料を受領し、素案4-7を検算した。3件の誤りを訂正——(1)市町村が計画に位置づけるのは第14〜23条の10項目ではなく第14〜21条の8項目（第22条以降は主語が「国は」）、(2)意見聴取の根拠は第13条第3項ではなく「第13条第3項において準用する第12条第3項」、(3)第15条バリアフリー化の対応施策は住まい・除雪ではなく移動・見守り（条文の例示による）。あわせて条文から新たに4件を素案に追加——第13条第3項が準用する第12条第4〜7項（計画の公表・実施状況の評価と公表・5年ごとの検討・評価結果の取りまとめ時の意見聴取）、第9条（認知症の日9月21日・認知症月間9月）、第7条（公共交通・金融機関・小売業者等の合理的配慮）、第16条第2項（若年性認知症の雇用継続）。4-7を全面改訂し8つの見出しに再構成した。素案は2,633行→2,677行。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。★9/15：見込量算定の第1次概算を反映（doc35）。あわせて素案の記述を令和8年度の交付金評価指標で検算し、複数の訂正を行った。(1)中長期の保険料を算定し5-11の【要確認】を解消（αを23%据え置くと令和22年度6,883円、3年ごとに1ポイント上がると8,379円）。(2)標準給付費の様式を埋め5-6を確定（3か年854,014千円）。5-7と完全に一致。(3)交付金の評価指標を令和8年度で検算したところ、素案の記述の多くが令和6年度または令和4年度の評価に基づいており実態と食い違っていた。通いの場への参加率は0→8点満点（最上位の段階は全国で約10%）、参加促進のアウトリーチは9点満点、地域リハビリテーションの推進は0→7点満点、計画の進捗管理（目標Ⅰの3項目）は0→48点満点。一方、要介護3〜5の状態の変化は2指標とも0点（35点減）、認知症サポーター数は12点中0点、難聴は20点中0点。施策1-1を「通いの場の再構築と参加率の向上」から「通いの場の開催頻度の向上と地区差の是正」に改称し、課題3の見出しも改めた。(4)6-3の成果目標・活動指標に令和8年度の得点と全国平均を併記し、維持6指標・引上げ5指標に整理。(5)認知症基本法13条1項・成年後見促進法14条1項を確認し1-2の【要確認】を解消。素案は2,197行→2,341行。★9/15：3次にわたり修正。(1)見込量算定の第1次概算を反映（doc35）。(2)令和8年度の交付金評価指標で全記述を検算し、施策1-1の名称と課題3の見出しを改めた。(3)推計の系列を統一し、介護給付費と予防給付費を分離、見込量の自己点検を実施。5-12（据え置き項目31件）を新設。素案は約115頁→2,449行（段落約4,400・表約125・図20）。残る空欄は交付金の交付見込額、高齢者福祉サービスの量の目標の一部、委員名簿・パブコメなど確定後に記入するもの。★9/16：交付金の目標別に全国平均と対比したところ、素案2-8の「認知症総合支援が全国平均を下回る唯一の目標」が誤りと判明（上回るのは3目標、下回るのは5目標。認知症総合支援は差が最大の▲19.1点）。2-8に目標別の対比表を新設し関係箇所を訂正した。あわせて薄い節を埋めた（1-5日常生活圏域・4-2〜4-4基本目標の導入・5-10低所得者）。6-4に乖離の検証の見直しの目安（±5%以内／±5〜12%／±12%超）を、6-5に計画期間中に確定する5項目を新設。±12%は推計の誤差の絶対値の平均11.9%（保険料月額約700円）によるもので、この幅を超える乖離は基金の取崩しでは吸収できない。素案は2,449行→2,509行。★9/16：認知症施策推進計画としての検討（doc36）。本計画は認知症基本法第13条第1項の市町村計画を兼ねるが、認知症施策は施策4-4の1本のみで基本法の基本的施策との対応が示されていなかった。第4章に4-7「認知症施策推進計画としての位置づけ」を新設し、3つの基本的な考え方（新しい認知症観・本人および家族等の参画・共生社会）、基本法第14〜23条の10項目と本計画の施策との対応表、本村の状況、本人・家族の参画の方法、指標8件を掲載した。2-3に認知症高齢者の状況（自立度Ⅱ以上161人・2年間で22.0%増・認定者に占める割合63.6%）を新設。あわせて第4章の施策番号に「施策」を冠し、基本目標の節番号との衝突（4-4が基本目標4と施策4-4の両方を指す状態）を解消した。素案は2,509行→2,633行。★9/16（第2次）：認知症基本法の条文（令和5年法律第65号）と厚生労働省の概要資料を受領し、素案4-7を検算した。3件の誤りを訂正——(1)市町村が計画に位置づけるのは第14〜23条の10項目ではなく第14〜21条の8項目（第22条以降は主語が「国は」）、(2)意見聴取の根拠は第13条第3項ではなく「第13条第3項において準用する第12条第3項」、(3)第15条バリアフリー化の対応施策は住まい・除雪ではなく移動・見守り（条文の例示による）。あわせて条文から新たに4件を素案に追加——第13条第3項が準用する第12条第4〜7項（計画の公表・実施状況の評価と公表・5年ごとの検討・評価結果の取りまとめ時の意見聴取）、第9条（認知症の日9月21日・認知症月間9月）、第7条（公共交通・金融機関・小売業者等の合理的配慮）、第16条第2項（若年性認知症の雇用継続）。4-7を全面改訂し8つの見出しに再構成した。素案は2,633行→2,677行。★9/24：素案の自己点検16件を新設（verify_soan.py）。全件適合で終了コード0、不適合なら1。素案の数値は算定スクリプトの出力を手書きで書き写しているため、算定を改めたときの乖離を検出する。大雪は素案の生成が算定をrunpyで直接読む形に改めたが、本村は構造を変える工数が大きいため点検で代替する。点検項目は人口・認定者数・区分別受給者数・標準給付費の内部整合・給付費の分離・地域支援事業費・年度別保険料・中長期保険料・定員到達率・利用率の分母・二重計上の注記・乖離の目安・認知症基本法の条項・節番号の重複・据え置き一覧の16件。素案は2,715行→2,758行。</t>
         </is>
       </c>
     </row>
@@ -7136,7 +7136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8738,22 +8738,22 @@
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護（村内27人分）の待機者数と、村外のグループホームを利用している方の人数</t>
+          <t>国の推計ワークシートが求める在宅サービス利用率の分母</t>
         </is>
       </c>
       <c r="D45" s="34" t="inlineStr">
         <is>
-          <t>★施策3-2・5-4(7)の必要利用定員総数の判断に必須。認知症高齢者（自立度Ⅱ以上）は2年間で132人→161人と22.0%増えた一方、定員は平成28年度以降27人のまま。稼働率93%。増床の要否は待機と村外利用の実態がなければ判断できない。</t>
+          <t>★★他案件（大雪）の点検で「見込量の利用率の分母は認定者数であって第1号被保険者数ではない」ことが指摘された。本村の見える化のサービス利用率の分母は要介護度別認定者数であることを実データで確認済み（51件中21件が±0.6pt以内で一致、第1号被保険者数では0件）。ただし国の将来推計が在宅の分母を「認定者数−施設・居住系利用者数」とする場合、本村の率は要介護1で58.8%→86.1%、要介護4で26.8%→70.1%に変わり、要介護2では107.7%と100%を超える。分母の取り違えは見込量を数割動かす。</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 5-4(7)</t>
+          <t>doc37§3,doc18 5-4</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
@@ -8776,22 +8776,22 @@
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>認知症関連事業の実績（認知症カフェの箇所数、認知症初期集中支援推進事業の対象者数、認知症地域支援推進員の活動実績）</t>
+          <t>認知症対応型共同生活介護（村内27人分）の待機者数と、村外のグループホームを利用している方の人数</t>
         </is>
       </c>
       <c r="D46" s="34" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の地域支援事業の量に認知症総合支援事業の行を新設したが、いずれも実績が未受領。国の様式では認知症総合支援事業の量を定めることが求められる。</t>
+          <t>★施策3-2・5-4(7)の必要利用定員総数の判断に必須。認知症高齢者（自立度Ⅱ以上）は2年間で132人→161人と22.0%増えた一方、定員は平成28年度以降27人のまま。稼働率93%。増床の要否は待機と村外利用の実態がなければ判断できない。</t>
         </is>
       </c>
       <c r="E46" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-68</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F46" s="35" t="inlineStr">
         <is>
-          <t>doc36§4,doc18 5-5(1)</t>
+          <t>doc36§3,doc18 5-4(7)</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -8814,22 +8814,22 @@
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
+          <t>認知症関連事業の実績（認知症カフェの箇所数、認知症初期集中支援推進事業の対象者数、認知症地域支援推進員の活動実績）</t>
         </is>
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
+          <t>★素案5-5(1)の地域支援事業の量に認知症総合支援事業の行を新設したが、いずれも実績が未受領。国の様式では認知症総合支援事業の量を定めることが求められる。</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅱ-53,Ⅱ-68</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc36§4,doc18 5-5(1)</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -8852,22 +8852,22 @@
       </c>
       <c r="C48" s="34" t="inlineStr">
         <is>
-          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
+          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
         </is>
       </c>
       <c r="D48" s="34" t="inlineStr">
         <is>
-          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
+          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
         </is>
       </c>
       <c r="E48" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F48" s="35" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -8885,27 +8885,27 @@
       </c>
       <c r="B49" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -8928,22 +8928,22 @@
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F50" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -8966,22 +8966,22 @@
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="C52" s="34" t="inlineStr">
         <is>
-          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D52" s="34" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E52" s="35" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="F52" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-89</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -9042,22 +9042,22 @@
       </c>
       <c r="C53" s="34" t="inlineStr">
         <is>
-          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D53" s="34" t="inlineStr">
         <is>
-          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-97</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -9075,27 +9075,27 @@
       </c>
       <c r="B54" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C54" s="34" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
         </is>
       </c>
       <c r="D54" s="34" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
         </is>
       </c>
       <c r="E54" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-50</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F54" s="35" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc26§10 K-97</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -9118,22 +9118,22 @@
       </c>
       <c r="C55" s="34" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D55" s="34" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅰ-50</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -9156,22 +9156,22 @@
       </c>
       <c r="C56" s="34" t="inlineStr">
         <is>
-          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D56" s="34" t="inlineStr">
         <is>
-          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E56" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-46</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F56" s="35" t="inlineStr">
         <is>
-          <t>doc25§4-2 K-91</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -9189,27 +9189,27 @@
       </c>
       <c r="B57" s="33" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C57" s="34" t="inlineStr">
         <is>
-          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
+          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
         </is>
       </c>
       <c r="D57" s="34" t="inlineStr">
         <is>
-          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
+          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-70,Ⅱ-71</t>
+          <t>Ⅰ-46</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc25§4-2 K-91</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C58" s="34" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
         </is>
       </c>
       <c r="D58" s="34" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
         </is>
       </c>
       <c r="E58" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅱ-70,Ⅱ-71</t>
         </is>
       </c>
       <c r="F58" s="35" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -9265,27 +9265,27 @@
       </c>
       <c r="B59" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C59" s="34" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D59" s="34" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G59" s="35" t="inlineStr">
@@ -9308,22 +9308,22 @@
       </c>
       <c r="C60" s="34" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D60" s="34" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E60" s="35" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F60" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G60" s="35" t="inlineStr">
@@ -9341,27 +9341,27 @@
       </c>
       <c r="B61" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C61" s="34" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の対象が118人（想定150人）であることへの集計設計の対応</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D61" s="34" t="inlineStr">
         <is>
-          <t>★回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかの判断が要る。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Ⅲ-72,Ⅲ-73</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>doc34§5-2</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -9384,22 +9384,22 @@
       </c>
       <c r="C62" s="34" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
+          <t>在宅介護実態調査の対象が118人（想定150人）であることへの集計設計の対応</t>
         </is>
       </c>
       <c r="D62" s="34" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
+          <t>★回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかの判断が要る。</t>
         </is>
       </c>
       <c r="E62" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅲ-72,Ⅲ-73</t>
         </is>
       </c>
       <c r="F62" s="35" t="inlineStr">
         <is>
-          <t>doc33§3-5</t>
+          <t>doc34§5-2</t>
         </is>
       </c>
       <c r="G62" s="35" t="inlineStr">
@@ -9422,22 +9422,22 @@
       </c>
       <c r="C63" s="34" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
         </is>
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc33§3-5</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -9460,22 +9460,22 @@
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D64" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E64" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F64" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G64" s="35" t="inlineStr">
@@ -9498,22 +9498,22 @@
       </c>
       <c r="C65" s="34" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D65" s="34" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
@@ -9536,22 +9536,22 @@
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D66" s="34" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E66" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F66" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-99</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -9574,22 +9574,22 @@
       </c>
       <c r="C67" s="34" t="inlineStr">
         <is>
-          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D67" s="34" t="inlineStr">
         <is>
-          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>doc28§1-2 K-107</t>
+          <t>doc26§10 K-99</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
@@ -9612,22 +9612,22 @@
       </c>
       <c r="C68" s="34" t="inlineStr">
         <is>
-          <t>認知症施策の実施状況の評価と公表の運用</t>
+          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
+          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
         </is>
       </c>
       <c r="E68" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-71</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F68" s="35" t="inlineStr">
         <is>
-          <t>doc36§10-1,doc18 4-7(6)</t>
+          <t>doc28§1-2 K-107</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="C69" s="34" t="inlineStr">
         <is>
-          <t>認知症の人およびご家族から意見を聴く方法</t>
+          <t>認知症施策の実施状況の評価と公表の運用</t>
         </is>
       </c>
       <c r="D69" s="34" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
+          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>doc36§5,doc18 4-7(4)</t>
+          <t>doc36§10-1,doc18 4-7(6)</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
@@ -9688,22 +9688,22 @@
       </c>
       <c r="C70" s="34" t="inlineStr">
         <is>
-          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
+          <t>認知症の人およびご家族から意見を聴く方法</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
         <is>
-          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
+          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
         </is>
       </c>
       <c r="E70" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F70" s="35" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§5,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G70" s="35" t="inlineStr">
@@ -9721,27 +9721,27 @@
       </c>
       <c r="B71" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C71" s="34" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
         </is>
       </c>
       <c r="D71" s="34" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G71" s="35" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="C72" s="34" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D72" s="34" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E72" s="35" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="F72" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="C73" s="34" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D73" s="34" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G73" s="35" t="inlineStr">
@@ -9835,32 +9835,32 @@
       </c>
       <c r="B74" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C74" s="34" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D74" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E74" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F74" s="35" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G74" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H74" s="34" t="inlineStr"/>
@@ -9878,27 +9878,27 @@
       </c>
       <c r="C75" s="34" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
       <c r="D75" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
       <c r="E75" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H75" s="34" t="inlineStr"/>
@@ -9916,12 +9916,12 @@
       </c>
       <c r="C76" s="34" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
         </is>
       </c>
       <c r="D76" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
         </is>
       </c>
       <c r="E76" s="35" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="F76" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc27§3-3</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -9954,22 +9954,22 @@
       </c>
       <c r="C77" s="34" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
         </is>
       </c>
       <c r="D77" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-09,Ⅰ-10</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc27§5-2</t>
         </is>
       </c>
       <c r="G77" s="35" t="inlineStr">
@@ -9992,68 +9992,68 @@
       </c>
       <c r="C78" s="34" t="inlineStr">
         <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D78" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E78" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F78" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G78" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr"/>
+    </row>
+    <row r="79" ht="34" customHeight="1">
+      <c r="A79" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B79" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C79" s="34" t="inlineStr">
+        <is>
           <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
-      <c r="D78" s="34" t="inlineStr">
+      <c r="D79" s="34" t="inlineStr">
         <is>
           <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
-      <c r="E78" s="35" t="inlineStr">
+      <c r="E79" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="F78" s="35" t="inlineStr">
+      <c r="F79" s="35" t="inlineStr">
         <is>
           <t>doc27§6</t>
         </is>
       </c>
-      <c r="G78" s="35" t="inlineStr">
+      <c r="G79" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H78" s="34" t="inlineStr"/>
-    </row>
-    <row r="79" ht="34" customHeight="1">
-      <c r="A79" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B79" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C79" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D79" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E79" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F79" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H79" s="25" t="inlineStr"/>
+      <c r="H79" s="34" t="inlineStr"/>
     </row>
     <row r="80" ht="34" customHeight="1">
       <c r="A80" s="37" t="inlineStr">
@@ -10068,22 +10068,22 @@
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-1,doc30§2-4</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
@@ -10106,27 +10106,27 @@
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>doc02§16,§22</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H81" s="25" t="inlineStr"/>
@@ -10144,27 +10144,27 @@
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H82" s="25" t="inlineStr"/>
@@ -10182,22 +10182,22 @@
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10220,22 +10220,22 @@
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10296,17 +10296,17 @@
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
@@ -10372,22 +10372,22 @@
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -10410,22 +10410,22 @@
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10448,22 +10448,22 @@
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -10486,22 +10486,22 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -10524,22 +10524,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -10562,22 +10562,22 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -10638,22 +10638,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -10676,17 +10676,17 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
@@ -10714,17 +10714,17 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -10790,22 +10790,22 @@
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -10828,22 +10828,22 @@
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -10904,22 +10904,22 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -10942,22 +10942,22 @@
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -10980,22 +10980,22 @@
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-4,doc18 4-7(3)</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -11056,22 +11056,22 @@
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
+          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
+          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(2),doc18 5-6</t>
+          <t>doc36§10-4,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -11089,27 +11089,27 @@
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc35§7-3(2),doc18 5-6</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -11132,22 +11132,22 @@
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -11170,22 +11170,22 @@
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -11203,27 +11203,27 @@
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -11241,27 +11241,27 @@
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -11284,22 +11284,22 @@
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -11322,22 +11322,22 @@
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -11355,27 +11355,27 @@
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -11398,22 +11398,22 @@
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -11436,22 +11436,22 @@
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -11474,22 +11474,22 @@
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -11512,22 +11512,22 @@
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -11626,22 +11626,22 @@
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -11664,22 +11664,22 @@
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -11702,22 +11702,22 @@
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -11740,22 +11740,22 @@
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -11778,22 +11778,22 @@
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -11816,22 +11816,22 @@
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -11854,22 +11854,22 @@
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-2,doc18 4-7(4)</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -11892,22 +11892,22 @@
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
+          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
+          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-3,doc18 4-7(3)</t>
+          <t>doc37§4,doc18 5-4(10)</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -11930,22 +11930,22 @@
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護を再開するかどうか</t>
+          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
+          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 施策3-2</t>
+          <t>doc36§10-2,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
+          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
+          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 4-7(2)</t>
+          <t>doc36§10-3,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -12006,22 +12006,22 @@
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
+          <t>認知症対応型通所介護を再開するかどうか</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
+          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§3,doc18 施策3-2</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12044,22 +12044,22 @@
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc36§3,doc18 4-7(2)</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -12082,12 +12082,12 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -12115,27 +12115,27 @@
       </c>
       <c r="B134" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -12153,27 +12153,27 @@
       </c>
       <c r="B135" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -12196,22 +12196,22 @@
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -12234,22 +12234,22 @@
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -12272,22 +12272,22 @@
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
@@ -12310,22 +12310,22 @@
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>doc36§2,doc18 2-3</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
@@ -12343,27 +12343,27 @@
       </c>
       <c r="B140" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
@@ -12381,27 +12381,27 @@
       </c>
       <c r="B141" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
         </is>
       </c>
       <c r="E141" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc37§3-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
@@ -12419,27 +12419,27 @@
       </c>
       <c r="B142" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
         </is>
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc36§2,doc18 2-3</t>
         </is>
       </c>
       <c r="G142" s="23" t="inlineStr">
@@ -12462,12 +12462,12 @@
       </c>
       <c r="C143" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E143" s="23" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G143" s="23" t="inlineStr">
@@ -12500,22 +12500,22 @@
       </c>
       <c r="C144" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F144" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G144" s="23" t="inlineStr">
@@ -12538,22 +12538,22 @@
       </c>
       <c r="C145" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E145" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F145" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G145" s="23" t="inlineStr">
@@ -12571,27 +12571,27 @@
       </c>
       <c r="B146" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C146" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E146" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F146" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G146" s="23" t="inlineStr">
@@ -12609,27 +12609,27 @@
       </c>
       <c r="B147" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C147" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E147" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F147" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G147" s="23" t="inlineStr">
@@ -12647,27 +12647,27 @@
       </c>
       <c r="B148" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C148" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F148" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G148" s="23" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="C149" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E149" s="23" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="F149" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G149" s="23" t="inlineStr">
@@ -12723,27 +12723,27 @@
       </c>
       <c r="B150" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C150" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D150" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F150" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G150" s="23" t="inlineStr">
@@ -12761,27 +12761,27 @@
       </c>
       <c r="B151" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C151" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E151" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F151" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G151" s="23" t="inlineStr">
@@ -12799,27 +12799,27 @@
       </c>
       <c r="B152" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C152" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D152" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E152" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F152" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G152" s="23" t="inlineStr">
@@ -12842,22 +12842,22 @@
       </c>
       <c r="C153" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
         </is>
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
         </is>
       </c>
       <c r="E153" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-31</t>
         </is>
       </c>
       <c r="F153" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc19 追-6</t>
         </is>
       </c>
       <c r="G153" s="23" t="inlineStr">
@@ -12880,227 +12880,227 @@
       </c>
       <c r="C154" s="25" t="inlineStr">
         <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D154" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E154" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F154" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G154" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H154" s="25" t="inlineStr"/>
+    </row>
+    <row r="155" ht="34" customHeight="1">
+      <c r="A155" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B155" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C155" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D155" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E155" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F155" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G155" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H155" s="25" t="inlineStr"/>
+    </row>
+    <row r="156" ht="34" customHeight="1">
+      <c r="A156" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B156" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C156" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D156" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E156" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F156" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G156" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H156" s="25" t="inlineStr"/>
+    </row>
+    <row r="157" ht="34" customHeight="1">
+      <c r="A157" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B157" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C157" s="25" t="inlineStr">
+        <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D154" s="25" t="inlineStr">
+      <c r="D157" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E154" s="23" t="inlineStr">
+      <c r="E157" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F154" s="23" t="inlineStr">
+      <c r="F157" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G154" s="23" t="inlineStr">
+      <c r="G157" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H154" s="25" t="inlineStr"/>
-    </row>
-    <row r="155" ht="34" customHeight="1">
-      <c r="A155" s="38" t="inlineStr">
+      <c r="H157" s="25" t="inlineStr"/>
+    </row>
+    <row r="158" ht="34" customHeight="1">
+      <c r="A158" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B155" s="24" t="inlineStr">
+      <c r="B158" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C155" s="25" t="inlineStr">
+      <c r="C158" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D155" s="25" t="inlineStr">
+      <c r="D158" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E155" s="23" t="inlineStr">
+      <c r="E158" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F155" s="23" t="inlineStr">
+      <c r="F158" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G155" s="23" t="inlineStr">
+      <c r="G158" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H155" s="25" t="inlineStr"/>
-    </row>
-    <row r="156" ht="34" customHeight="1">
-      <c r="A156" s="38" t="inlineStr">
+      <c r="H158" s="25" t="inlineStr"/>
+    </row>
+    <row r="159" ht="34" customHeight="1">
+      <c r="A159" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B156" s="24" t="inlineStr">
+      <c r="B159" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C156" s="25" t="inlineStr">
+      <c r="C159" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D156" s="25" t="inlineStr">
+      <c r="D159" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E156" s="23" t="inlineStr">
+      <c r="E159" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F156" s="23" t="inlineStr">
+      <c r="F159" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G156" s="23" t="inlineStr">
+      <c r="G159" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H156" s="25" t="inlineStr"/>
-    </row>
-    <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="39" t="inlineStr">
+      <c r="H159" s="25" t="inlineStr"/>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="159" ht="34" customHeight="1">
-      <c r="A159" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B159" s="41" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C159" s="42" t="inlineStr">
-        <is>
-          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
-        </is>
-      </c>
-      <c r="D159" s="42" t="inlineStr">
-        <is>
-          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
-        </is>
-      </c>
-      <c r="E159" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F159" s="40" t="inlineStr">
-        <is>
-          <t>doc35§7-3(1)</t>
-        </is>
-      </c>
-      <c r="G159" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H159" s="42" t="inlineStr"/>
-    </row>
-    <row r="160" ht="34" customHeight="1">
-      <c r="A160" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B160" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C160" s="42" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D160" s="42" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E160" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F160" s="40" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G160" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H160" s="42" t="inlineStr"/>
-    </row>
-    <row r="161" ht="34" customHeight="1">
-      <c r="A161" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B161" s="41" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C161" s="42" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D161" s="42" t="inlineStr">
-        <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
-        </is>
-      </c>
-      <c r="E161" s="40" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F161" s="40" t="inlineStr">
-        <is>
-          <t>doc28§4</t>
-        </is>
-      </c>
-      <c r="G161" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H161" s="42" t="inlineStr"/>
     </row>
     <row r="162" ht="34" customHeight="1">
       <c r="A162" s="40" t="inlineStr">
@@ -13110,27 +13110,27 @@
       </c>
       <c r="B162" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C162" s="42" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数</t>
+          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
         </is>
       </c>
       <c r="D162" s="42" t="inlineStr">
         <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
+          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
         </is>
       </c>
       <c r="E162" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F162" s="40" t="inlineStr">
         <is>
-          <t>doc28§2</t>
+          <t>doc35§7-3(1)</t>
         </is>
       </c>
       <c r="G162" s="40" t="inlineStr">
@@ -13153,22 +13153,22 @@
       </c>
       <c r="C163" s="42" t="inlineStr">
         <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D163" s="42" t="inlineStr">
         <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E163" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F163" s="40" t="inlineStr">
         <is>
-          <t>doc28§1</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G163" s="40" t="inlineStr">
@@ -13186,32 +13186,32 @@
       </c>
       <c r="B164" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C164" s="42" t="inlineStr">
         <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D164" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E164" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F164" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-1</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G164" s="40" t="inlineStr">
         <is>
-          <t>解決済（一部再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H164" s="42" t="inlineStr"/>
@@ -13224,27 +13224,27 @@
       </c>
       <c r="B165" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C165" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D165" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E165" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F165" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G165" s="40" t="inlineStr">
@@ -13262,32 +13262,32 @@
       </c>
       <c r="B166" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C166" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D166" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E166" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F166" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G166" s="40" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H166" s="42" t="inlineStr"/>
@@ -13305,27 +13305,27 @@
       </c>
       <c r="C167" s="42" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D167" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E167" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F167" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G167" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H167" s="42" t="inlineStr"/>
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C168" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D168" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E168" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F168" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G168" s="40" t="inlineStr">
@@ -13381,27 +13381,27 @@
       </c>
       <c r="C169" s="42" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D169" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E169" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F169" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G169" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H169" s="42" t="inlineStr"/>
@@ -13414,22 +13414,22 @@
       </c>
       <c r="B170" s="41" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C170" s="42" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D170" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E170" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F170" s="40" t="inlineStr">
@@ -13452,27 +13452,27 @@
       </c>
       <c r="B171" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C171" s="42" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D171" s="42" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E171" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F171" s="40" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G171" s="40" t="inlineStr">
@@ -13490,27 +13490,27 @@
       </c>
       <c r="B172" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C172" s="42" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D172" s="42" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E172" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F172" s="40" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G172" s="40" t="inlineStr">
@@ -13528,27 +13528,27 @@
       </c>
       <c r="B173" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C173" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D173" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E173" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F173" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G173" s="40" t="inlineStr">
@@ -13571,22 +13571,22 @@
       </c>
       <c r="C174" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D174" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E174" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F174" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G174" s="40" t="inlineStr">
@@ -13609,22 +13609,22 @@
       </c>
       <c r="C175" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>交付要綱の配点表（満点）</t>
         </is>
       </c>
       <c r="D175" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
         </is>
       </c>
       <c r="E175" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F175" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc20§2</t>
         </is>
       </c>
       <c r="G175" s="40" t="inlineStr">
@@ -13647,43 +13647,157 @@
       </c>
       <c r="C176" s="42" t="inlineStr">
         <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D176" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E176" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F176" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G176" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H176" s="42" t="inlineStr"/>
+    </row>
+    <row r="177" ht="34" customHeight="1">
+      <c r="A177" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B177" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C177" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D177" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E177" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F177" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G177" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H177" s="42" t="inlineStr"/>
+    </row>
+    <row r="178" ht="34" customHeight="1">
+      <c r="A178" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B178" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C178" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D178" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E178" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F178" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G178" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H178" s="42" t="inlineStr"/>
+    </row>
+    <row r="179" ht="34" customHeight="1">
+      <c r="A179" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B179" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C179" s="42" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D176" s="42" t="inlineStr">
+      <c r="D179" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E176" s="40" t="inlineStr">
+      <c r="E179" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F176" s="40" t="inlineStr">
+      <c r="F179" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G176" s="40" t="inlineStr">
+      <c r="G179" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H176" s="42" t="inlineStr"/>
+      <c r="H179" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H156"/>
+  <autoFilter ref="A4:H159"/>
   <mergeCells count="3">
-    <mergeCell ref="A158:H158"/>
+    <mergeCell ref="A161:H161"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A159" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G159" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$163</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="P59" s="13" t="inlineStr">
         <is>
-          <t>D系給付費・K系施設数・D47/D48特別会計決算まで整理済（doc02）。令和6年度決算が未入手。</t>
+          <t>D系給付費・K系施設数・D47/D48特別会計決算まで整理済（doc02）。令和6年度決算が未入手。★9/24：介護サービス自給率（δ2・δ2-a〜e）が取得済みでありながら未使用であったため素案2-5に投入した（doc38§A-1）。村外利用の割合を測る最も直接的な指標であり、短期入所系0%は村内に事業所がないことの裏づけになる。</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。★9/15：見込量算定の第1次概算を反映（doc35）。あわせて素案の記述を令和8年度の交付金評価指標で検算し、複数の訂正を行った。(1)中長期の保険料を算定し5-11の【要確認】を解消（αを23%据え置くと令和22年度6,883円、3年ごとに1ポイント上がると8,379円）。(2)標準給付費の様式を埋め5-6を確定（3か年854,014千円）。5-7と完全に一致。(3)交付金の評価指標を令和8年度で検算したところ、素案の記述の多くが令和6年度または令和4年度の評価に基づいており実態と食い違っていた。通いの場への参加率は0→8点満点（最上位の段階は全国で約10%）、参加促進のアウトリーチは9点満点、地域リハビリテーションの推進は0→7点満点、計画の進捗管理（目標Ⅰの3項目）は0→48点満点。一方、要介護3〜5の状態の変化は2指標とも0点（35点減）、認知症サポーター数は12点中0点、難聴は20点中0点。施策1-1を「通いの場の再構築と参加率の向上」から「通いの場の開催頻度の向上と地区差の是正」に改称し、課題3の見出しも改めた。(4)6-3の成果目標・活動指標に令和8年度の得点と全国平均を併記し、維持6指標・引上げ5指標に整理。(5)認知症基本法13条1項・成年後見促進法14条1項を確認し1-2の【要確認】を解消。素案は2,197行→2,341行。★9/15：3次にわたり修正。(1)見込量算定の第1次概算を反映（doc35）。(2)令和8年度の交付金評価指標で全記述を検算し、施策1-1の名称と課題3の見出しを改めた。(3)推計の系列を統一し、介護給付費と予防給付費を分離、見込量の自己点検を実施。5-12（据え置き項目31件）を新設。素案は約115頁→2,449行（段落約4,400・表約125・図20）。残る空欄は交付金の交付見込額、高齢者福祉サービスの量の目標の一部、委員名簿・パブコメなど確定後に記入するもの。★9/16：交付金の目標別に全国平均と対比したところ、素案2-8の「認知症総合支援が全国平均を下回る唯一の目標」が誤りと判明（上回るのは3目標、下回るのは5目標。認知症総合支援は差が最大の▲19.1点）。2-8に目標別の対比表を新設し関係箇所を訂正した。あわせて薄い節を埋めた（1-5日常生活圏域・4-2〜4-4基本目標の導入・5-10低所得者）。6-4に乖離の検証の見直しの目安（±5%以内／±5〜12%／±12%超）を、6-5に計画期間中に確定する5項目を新設。±12%は推計の誤差の絶対値の平均11.9%（保険料月額約700円）によるもので、この幅を超える乖離は基金の取崩しでは吸収できない。素案は2,449行→2,509行。★9/16：認知症施策推進計画としての検討（doc36）。本計画は認知症基本法第13条第1項の市町村計画を兼ねるが、認知症施策は施策4-4の1本のみで基本法の基本的施策との対応が示されていなかった。第4章に4-7「認知症施策推進計画としての位置づけ」を新設し、3つの基本的な考え方（新しい認知症観・本人および家族等の参画・共生社会）、基本法第14〜23条の10項目と本計画の施策との対応表、本村の状況、本人・家族の参画の方法、指標8件を掲載した。2-3に認知症高齢者の状況（自立度Ⅱ以上161人・2年間で22.0%増・認定者に占める割合63.6%）を新設。あわせて第4章の施策番号に「施策」を冠し、基本目標の節番号との衝突（4-4が基本目標4と施策4-4の両方を指す状態）を解消した。素案は2,509行→2,633行。★9/16（第2次）：認知症基本法の条文（令和5年法律第65号）と厚生労働省の概要資料を受領し、素案4-7を検算した。3件の誤りを訂正——(1)市町村が計画に位置づけるのは第14〜23条の10項目ではなく第14〜21条の8項目（第22条以降は主語が「国は」）、(2)意見聴取の根拠は第13条第3項ではなく「第13条第3項において準用する第12条第3項」、(3)第15条バリアフリー化の対応施策は住まい・除雪ではなく移動・見守り（条文の例示による）。あわせて条文から新たに4件を素案に追加——第13条第3項が準用する第12条第4〜7項（計画の公表・実施状況の評価と公表・5年ごとの検討・評価結果の取りまとめ時の意見聴取）、第9条（認知症の日9月21日・認知症月間9月）、第7条（公共交通・金融機関・小売業者等の合理的配慮）、第16条第2項（若年性認知症の雇用継続）。4-7を全面改訂し8つの見出しに再構成した。素案は2,633行→2,677行。★9/24：素案の自己点検16件を新設（verify_soan.py）。全件適合で終了コード0、不適合なら1。素案の数値は算定スクリプトの出力を手書きで書き写しているため、算定を改めたときの乖離を検出する。大雪は素案の生成が算定をrunpyで直接読む形に改めたが、本村は構造を変える工数が大きいため点検で代替する。点検項目は人口・認定者数・区分別受給者数・標準給付費の内部整合・給付費の分離・地域支援事業費・年度別保険料・中長期保険料・定員到達率・利用率の分母・二重計上の注記・乖離の目安・認知症基本法の条項・節番号の重複・据え置き一覧の16件。素案は2,715行→2,758行。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。★9/15：見込量算定の第1次概算を反映（doc35）。あわせて素案の記述を令和8年度の交付金評価指標で検算し、複数の訂正を行った。(1)中長期の保険料を算定し5-11の【要確認】を解消（αを23%据え置くと令和22年度6,883円、3年ごとに1ポイント上がると8,379円）。(2)標準給付費の様式を埋め5-6を確定（3か年854,014千円）。5-7と完全に一致。(3)交付金の評価指標を令和8年度で検算したところ、素案の記述の多くが令和6年度または令和4年度の評価に基づいており実態と食い違っていた。通いの場への参加率は0→8点満点（最上位の段階は全国で約10%）、参加促進のアウトリーチは9点満点、地域リハビリテーションの推進は0→7点満点、計画の進捗管理（目標Ⅰの3項目）は0→48点満点。一方、要介護3〜5の状態の変化は2指標とも0点（35点減）、認知症サポーター数は12点中0点、難聴は20点中0点。施策1-1を「通いの場の再構築と参加率の向上」から「通いの場の開催頻度の向上と地区差の是正」に改称し、課題3の見出しも改めた。(4)6-3の成果目標・活動指標に令和8年度の得点と全国平均を併記し、維持6指標・引上げ5指標に整理。(5)認知症基本法13条1項・成年後見促進法14条1項を確認し1-2の【要確認】を解消。素案は2,197行→2,341行。★9/15：3次にわたり修正。(1)見込量算定の第1次概算を反映（doc35）。(2)令和8年度の交付金評価指標で全記述を検算し、施策1-1の名称と課題3の見出しを改めた。(3)推計の系列を統一し、介護給付費と予防給付費を分離、見込量の自己点検を実施。5-12（据え置き項目31件）を新設。素案は約115頁→2,449行（段落約4,400・表約125・図20）。残る空欄は交付金の交付見込額、高齢者福祉サービスの量の目標の一部、委員名簿・パブコメなど確定後に記入するもの。★9/16：交付金の目標別に全国平均と対比したところ、素案2-8の「認知症総合支援が全国平均を下回る唯一の目標」が誤りと判明（上回るのは3目標、下回るのは5目標。認知症総合支援は差が最大の▲19.1点）。2-8に目標別の対比表を新設し関係箇所を訂正した。あわせて薄い節を埋めた（1-5日常生活圏域・4-2〜4-4基本目標の導入・5-10低所得者）。6-4に乖離の検証の見直しの目安（±5%以内／±5〜12%／±12%超）を、6-5に計画期間中に確定する5項目を新設。±12%は推計の誤差の絶対値の平均11.9%（保険料月額約700円）によるもので、この幅を超える乖離は基金の取崩しでは吸収できない。素案は2,449行→2,509行。★9/16：認知症施策推進計画としての検討（doc36）。本計画は認知症基本法第13条第1項の市町村計画を兼ねるが、認知症施策は施策4-4の1本のみで基本法の基本的施策との対応が示されていなかった。第4章に4-7「認知症施策推進計画としての位置づけ」を新設し、3つの基本的な考え方（新しい認知症観・本人および家族等の参画・共生社会）、基本法第14〜23条の10項目と本計画の施策との対応表、本村の状況、本人・家族の参画の方法、指標8件を掲載した。2-3に認知症高齢者の状況（自立度Ⅱ以上161人・2年間で22.0%増・認定者に占める割合63.6%）を新設。あわせて第4章の施策番号に「施策」を冠し、基本目標の節番号との衝突（4-4が基本目標4と施策4-4の両方を指す状態）を解消した。素案は2,509行→2,633行。★9/16（第2次）：認知症基本法の条文（令和5年法律第65号）と厚生労働省の概要資料を受領し、素案4-7を検算した。3件の誤りを訂正——(1)市町村が計画に位置づけるのは第14〜23条の10項目ではなく第14〜21条の8項目（第22条以降は主語が「国は」）、(2)意見聴取の根拠は第13条第3項ではなく「第13条第3項において準用する第12条第3項」、(3)第15条バリアフリー化の対応施策は住まい・除雪ではなく移動・見守り（条文の例示による）。あわせて条文から新たに4件を素案に追加——第13条第3項が準用する第12条第4〜7項（計画の公表・実施状況の評価と公表・5年ごとの検討・評価結果の取りまとめ時の意見聴取）、第9条（認知症の日9月21日・認知症月間9月）、第7条（公共交通・金融機関・小売業者等の合理的配慮）、第16条第2項（若年性認知症の雇用継続）。4-7を全面改訂し8つの見出しに再構成した。素案は2,633行→2,677行。★9/24：素案の自己点検16件を新設（verify_soan.py）。全件適合で終了コード0、不適合なら1。素案の数値は算定スクリプトの出力を手書きで書き写しているため、算定を改めたときの乖離を検出する。大雪は素案の生成が算定をrunpyで直接読む形に改めたが、本村は構造を変える工数が大きいため点検で代替する。点検項目は人口・認定者数・区分別受給者数・標準給付費の内部整合・給付費の分離・地域支援事業費・年度別保険料・中長期保険料・定員到達率・利用率の分母・二重計上の注記・乖離の目安・認知症基本法の条項・節番号の重複・据え置き一覧の16件。素案は2,715行→2,758行。★9/24（第2次）：未解決の確認事項46件を見える化での確認可否により4分類し（doc38）、取得済みでありながら素案で使っていなかった2件を投入した。(1)介護サービス自給率（δ2系）を2-5に新設。全体46.5%・訪問系41.1%・通所系79.3%・短期入所系0%・施設居住系41.3%（令和7年度）。訪問系は令和3年度62.7%から21.6pt低下しており村内の供給力の低下が疑われる。施設居住系は給付の58.7%が村外。(2)居宅介護支援・介護予防支援の受給者数を5-4(9)に投入。見える化の2系列から逆算し（D13-r×B1÷D17-l）、令和3〜7年度の値が在宅サービス受給者数と0.1人以内で一致することを確認した。従前は全て空欄であった。素案は2,758行→2,787行。</t>
         </is>
       </c>
     </row>
@@ -7136,7 +7136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8738,22 +8738,22 @@
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>国の推計ワークシートが求める在宅サービス利用率の分母</t>
+          <t>養護老人ホーム措置・軽費老人ホーム・老人クラブの実績は見える化に系列が一切ない</t>
         </is>
       </c>
       <c r="D45" s="34" t="inlineStr">
         <is>
-          <t>★★他案件（大雪）の点検で「見込量の利用率の分母は認定者数であって第1号被保険者数ではない」ことが指摘された。本村の見える化のサービス利用率の分母は要介護度別認定者数であることを実データで確認済み（51件中21件が±0.6pt以内で一致、第1号被保険者数では0件）。ただし国の将来推計が在宅の分母を「認定者数−施設・居住系利用者数」とする場合、本村の率は要介護1で58.8%→86.1%、要介護4で26.8%→70.1%に変わり、要介護2では107.7%と100%を超える。分母の取り違えは見込量を数割動かす。</t>
+          <t>★老人福祉法第20条の8第2項が計画への記載を義務づける「老人福祉事業の量の目標」（素案4-6）の基礎。見える化に該当する系列がないため、村資料の受領が必須。代替手段はない。</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>doc37§3,doc18 5-4</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G45" s="35" t="inlineStr">
@@ -8776,22 +8776,22 @@
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護（村内27人分）の待機者数と、村外のグループホームを利用している方の人数</t>
+          <t>国の推計ワークシートが求める在宅サービス利用率の分母</t>
         </is>
       </c>
       <c r="D46" s="34" t="inlineStr">
         <is>
-          <t>★施策3-2・5-4(7)の必要利用定員総数の判断に必須。認知症高齢者（自立度Ⅱ以上）は2年間で132人→161人と22.0%増えた一方、定員は平成28年度以降27人のまま。稼働率93%。増床の要否は待機と村外利用の実態がなければ判断できない。</t>
+          <t>★★他案件（大雪）の点検で「見込量の利用率の分母は認定者数であって第1号被保険者数ではない」ことが指摘された。本村の見える化のサービス利用率の分母は要介護度別認定者数であることを実データで確認済み（51件中21件が±0.6pt以内で一致、第1号被保険者数では0件）。ただし国の将来推計が在宅の分母を「認定者数−施設・居住系利用者数」とする場合、本村の率は要介護1で58.8%→86.1%、要介護4で26.8%→70.1%に変わり、要介護2では107.7%と100%を超える。分母の取り違えは見込量を数割動かす。</t>
         </is>
       </c>
       <c r="E46" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F46" s="35" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 5-4(7)</t>
+          <t>doc37§3,doc18 5-4</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -8814,22 +8814,22 @@
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>認知症関連事業の実績（認知症カフェの箇所数、認知症初期集中支援推進事業の対象者数、認知症地域支援推進員の活動実績）</t>
+          <t>認知症対応型共同生活介護（村内27人分）の待機者数と、村外のグループホームを利用している方の人数</t>
         </is>
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の地域支援事業の量に認知症総合支援事業の行を新設したが、いずれも実績が未受領。国の様式では認知症総合支援事業の量を定めることが求められる。</t>
+          <t>★施策3-2・5-4(7)の必要利用定員総数の判断に必須。認知症高齢者（自立度Ⅱ以上）は2年間で132人→161人と22.0%増えた一方、定員は平成28年度以降27人のまま。稼働率93%。増床の要否は待機と村外利用の実態がなければ判断できない。</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-68</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>doc36§4,doc18 5-5(1)</t>
+          <t>doc36§3,doc18 5-4(7)</t>
         </is>
       </c>
       <c r="G47" s="35" t="inlineStr">
@@ -8852,22 +8852,22 @@
       </c>
       <c r="C48" s="34" t="inlineStr">
         <is>
-          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
+          <t>認知症関連事業の実績（認知症カフェの箇所数、認知症初期集中支援推進事業の対象者数、認知症地域支援推進員の活動実績）</t>
         </is>
       </c>
       <c r="D48" s="34" t="inlineStr">
         <is>
-          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
+          <t>★素案5-5(1)の地域支援事業の量に認知症総合支援事業の行を新設したが、いずれも実績が未受領。国の様式では認知症総合支援事業の量を定めることが求められる。</t>
         </is>
       </c>
       <c r="E48" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅱ-53,Ⅱ-68</t>
         </is>
       </c>
       <c r="F48" s="35" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc36§4,doc18 5-5(1)</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -8890,22 +8890,22 @@
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
+          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
+          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G49" s="35" t="inlineStr">
@@ -8923,27 +8923,27 @@
       </c>
       <c r="B50" s="33" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F50" s="35" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -8966,22 +8966,22 @@
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G51" s="35" t="inlineStr">
@@ -9004,22 +9004,22 @@
       </c>
       <c r="C52" s="34" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D52" s="34" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E52" s="35" t="inlineStr">
         <is>
-          <t>Ⅴ-96</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F52" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -9042,12 +9042,12 @@
       </c>
       <c r="C53" s="34" t="inlineStr">
         <is>
-          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D53" s="34" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-89</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G53" s="35" t="inlineStr">
@@ -9080,22 +9080,22 @@
       </c>
       <c r="C54" s="34" t="inlineStr">
         <is>
-          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D54" s="34" t="inlineStr">
         <is>
-          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
         </is>
       </c>
       <c r="E54" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅴ-96</t>
         </is>
       </c>
       <c r="F54" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-97</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -9113,27 +9113,27 @@
       </c>
       <c r="B55" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C55" s="34" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
         </is>
       </c>
       <c r="D55" s="34" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-50</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc26§10 K-97</t>
         </is>
       </c>
       <c r="G55" s="35" t="inlineStr">
@@ -9151,32 +9151,32 @@
       </c>
       <c r="B56" s="33" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C56" s="34" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>★見える化の「将来推計」メニューで在宅サービス利用率の分母を確認する</t>
         </is>
       </c>
       <c r="D56" s="34" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>★★見込量が数割変わる論点（要介護1で58.8%→86.1%、要介護2で107.7%と100%超）。村への依頼ではなく、当方が見える化にログインして推計方法の設定画面を開けば確かめられる見込み。他案件（大雪）は「画面の設定順からの推定［要確認］」としている。最優先で確認する。</t>
         </is>
       </c>
       <c r="E56" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F56" s="35" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc38§C-1</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>社内対応</t>
         </is>
       </c>
       <c r="H56" s="34" t="inlineStr"/>
@@ -9194,22 +9194,22 @@
       </c>
       <c r="C57" s="34" t="inlineStr">
         <is>
-          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D57" s="34" t="inlineStr">
         <is>
-          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-46</t>
+          <t>Ⅰ-50</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>doc25§4-2 K-91</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G57" s="35" t="inlineStr">
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C58" s="34" t="inlineStr">
         <is>
-          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D58" s="34" t="inlineStr">
         <is>
-          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E58" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-70,Ⅱ-71</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F58" s="35" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G58" s="35" t="inlineStr">
@@ -9265,27 +9265,27 @@
       </c>
       <c r="B59" s="33" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C59" s="34" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
         </is>
       </c>
       <c r="D59" s="34" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅰ-46</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc25§4-2 K-91</t>
         </is>
       </c>
       <c r="G59" s="35" t="inlineStr">
@@ -9303,27 +9303,27 @@
       </c>
       <c r="B60" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C60" s="34" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
         </is>
       </c>
       <c r="D60" s="34" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
         </is>
       </c>
       <c r="E60" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅱ-70,Ⅱ-71</t>
         </is>
       </c>
       <c r="F60" s="35" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G60" s="35" t="inlineStr">
@@ -9341,27 +9341,27 @@
       </c>
       <c r="B61" s="33" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C61" s="34" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D61" s="34" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
@@ -9379,27 +9379,27 @@
       </c>
       <c r="B62" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C62" s="34" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の対象が118人（想定150人）であることへの集計設計の対応</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D62" s="34" t="inlineStr">
         <is>
-          <t>★回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかの判断が要る。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E62" s="35" t="inlineStr">
         <is>
-          <t>Ⅲ-72,Ⅲ-73</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F62" s="35" t="inlineStr">
         <is>
-          <t>doc34§5-2</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G62" s="35" t="inlineStr">
@@ -9417,27 +9417,27 @@
       </c>
       <c r="B63" s="33" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C63" s="34" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>doc33§3-5</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
@@ -9460,22 +9460,22 @@
       </c>
       <c r="C64" s="34" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>在宅介護実態調査の対象が118人（想定150人）であることへの集計設計の対応</t>
         </is>
       </c>
       <c r="D64" s="34" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかの判断が要る。</t>
         </is>
       </c>
       <c r="E64" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅲ-72,Ⅲ-73</t>
         </is>
       </c>
       <c r="F64" s="35" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc34§5-2</t>
         </is>
       </c>
       <c r="G64" s="35" t="inlineStr">
@@ -9498,22 +9498,22 @@
       </c>
       <c r="C65" s="34" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
         </is>
       </c>
       <c r="D65" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc33§3-5</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
@@ -9536,22 +9536,22 @@
       </c>
       <c r="C66" s="34" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D66" s="34" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E66" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F66" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
@@ -9574,22 +9574,22 @@
       </c>
       <c r="C67" s="34" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D67" s="34" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>doc26§10 K-99</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G67" s="35" t="inlineStr">
@@ -9612,22 +9612,22 @@
       </c>
       <c r="C68" s="34" t="inlineStr">
         <is>
-          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
         <is>
-          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E68" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F68" s="35" t="inlineStr">
         <is>
-          <t>doc28§1-2 K-107</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
@@ -9650,22 +9650,22 @@
       </c>
       <c r="C69" s="34" t="inlineStr">
         <is>
-          <t>認知症施策の実施状況の評価と公表の運用</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D69" s="34" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-71</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>doc36§10-1,doc18 4-7(6)</t>
+          <t>doc26§10 K-99</t>
         </is>
       </c>
       <c r="G69" s="35" t="inlineStr">
@@ -9688,22 +9688,22 @@
       </c>
       <c r="C70" s="34" t="inlineStr">
         <is>
-          <t>認知症の人およびご家族から意見を聴く方法</t>
+          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
+          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
         </is>
       </c>
       <c r="E70" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-71</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F70" s="35" t="inlineStr">
         <is>
-          <t>doc36§5,doc18 4-7(4)</t>
+          <t>doc28§1-2 K-107</t>
         </is>
       </c>
       <c r="G70" s="35" t="inlineStr">
@@ -9726,22 +9726,22 @@
       </c>
       <c r="C71" s="34" t="inlineStr">
         <is>
-          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
+          <t>認知症施策の実施状況の評価と公表の運用</t>
         </is>
       </c>
       <c r="D71" s="34" t="inlineStr">
         <is>
-          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
+          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§10-1,doc18 4-7(6)</t>
         </is>
       </c>
       <c r="G71" s="35" t="inlineStr">
@@ -9759,27 +9759,27 @@
       </c>
       <c r="B72" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C72" s="34" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>認知症の人およびご家族から意見を聴く方法</t>
         </is>
       </c>
       <c r="D72" s="34" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
         </is>
       </c>
       <c r="E72" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F72" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc36§5,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G72" s="35" t="inlineStr">
@@ -9797,27 +9797,27 @@
       </c>
       <c r="B73" s="33" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C73" s="34" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
         </is>
       </c>
       <c r="D73" s="34" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G73" s="35" t="inlineStr">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="C74" s="34" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D74" s="34" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E74" s="35" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="F74" s="35" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G74" s="35" t="inlineStr">
@@ -9873,32 +9873,32 @@
       </c>
       <c r="B75" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C75" s="34" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D75" s="34" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E75" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G75" s="35" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H75" s="34" t="inlineStr"/>
@@ -9911,27 +9911,27 @@
       </c>
       <c r="B76" s="33" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C76" s="34" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D76" s="34" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E76" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F76" s="35" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G76" s="35" t="inlineStr">
@@ -9954,27 +9954,27 @@
       </c>
       <c r="C77" s="34" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
       <c r="D77" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G77" s="35" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H77" s="34" t="inlineStr"/>
@@ -9992,22 +9992,22 @@
       </c>
       <c r="C78" s="34" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
         </is>
       </c>
       <c r="D78" s="34" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
         </is>
       </c>
       <c r="E78" s="35" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-09,Ⅰ-10</t>
         </is>
       </c>
       <c r="F78" s="35" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc27§3-3</t>
         </is>
       </c>
       <c r="G78" s="35" t="inlineStr">
@@ -10030,106 +10030,106 @@
       </c>
       <c r="C79" s="34" t="inlineStr">
         <is>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+        </is>
+      </c>
+      <c r="D79" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+        </is>
+      </c>
+      <c r="E79" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F79" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-2</t>
+        </is>
+      </c>
+      <c r="G79" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr"/>
+    </row>
+    <row r="80" ht="34" customHeight="1">
+      <c r="A80" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B80" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C80" s="34" t="inlineStr">
+        <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D80" s="34" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E80" s="35" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F80" s="35" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G80" s="35" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr"/>
+    </row>
+    <row r="81" ht="34" customHeight="1">
+      <c r="A81" s="36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B81" s="33" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C81" s="34" t="inlineStr">
+        <is>
           <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
-      <c r="D79" s="34" t="inlineStr">
+      <c r="D81" s="34" t="inlineStr">
         <is>
           <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
-      <c r="E79" s="35" t="inlineStr">
+      <c r="E81" s="35" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="F79" s="35" t="inlineStr">
+      <c r="F81" s="35" t="inlineStr">
         <is>
           <t>doc27§6</t>
         </is>
       </c>
-      <c r="G79" s="35" t="inlineStr">
+      <c r="G81" s="35" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H79" s="34" t="inlineStr"/>
-    </row>
-    <row r="80" ht="34" customHeight="1">
-      <c r="A80" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B80" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C80" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D80" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E80" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F80" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G80" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H80" s="25" t="inlineStr"/>
-    </row>
-    <row r="81" ht="34" customHeight="1">
-      <c r="A81" s="37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B81" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C81" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D81" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
-        </is>
-      </c>
-      <c r="E81" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F81" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1,doc30§2-4</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H81" s="25" t="inlineStr"/>
+      <c r="H81" s="34" t="inlineStr"/>
     </row>
     <row r="82" ht="34" customHeight="1">
       <c r="A82" s="37" t="inlineStr">
@@ -10144,27 +10144,27 @@
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F82" s="23" t="inlineStr">
         <is>
-          <t>doc02§16,§22</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G82" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H82" s="25" t="inlineStr"/>
@@ -10182,22 +10182,22 @@
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -10220,27 +10220,27 @@
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H84" s="25" t="inlineStr"/>
@@ -10258,22 +10258,22 @@
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -10334,22 +10334,22 @@
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -10372,17 +10372,17 @@
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（令和5〜7年度）</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>見える化は両者を合算した給付費のみ。人数は在宅サービス受給者数（112.6人／月）に近い水準とみられるが実数が要る。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
@@ -10410,22 +10410,22 @@
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -10448,27 +10448,27 @@
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc38§A-2,doc18 5-4(9)</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H90" s="25" t="inlineStr"/>
@@ -10486,22 +10486,22 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -10524,22 +10524,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -10562,22 +10562,22 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
@@ -10638,22 +10638,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -10676,22 +10676,22 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -10714,22 +10714,22 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
@@ -10790,22 +10790,22 @@
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -10828,22 +10828,22 @@
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -10866,22 +10866,22 @@
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -10904,22 +10904,22 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -10942,22 +10942,22 @@
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -10980,22 +10980,22 @@
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-4,doc18 4-7(3)</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -11094,22 +11094,22 @@
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(2),doc18 5-6</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -11127,27 +11127,27 @@
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅴ-95</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -11165,27 +11165,27 @@
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc36§10-4,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -11203,27 +11203,27 @@
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc35§7-3(2),doc18 5-6</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -11241,27 +11241,27 @@
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅴ-95</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -11279,27 +11279,27 @@
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -11317,27 +11317,27 @@
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-108</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -11355,27 +11355,27 @@
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -11393,27 +11393,27 @@
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -11431,27 +11431,27 @@
       </c>
       <c r="B116" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-108</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -11469,27 +11469,27 @@
       </c>
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc24§12 K-88</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -11512,22 +11512,22 @@
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -11626,22 +11626,22 @@
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -11664,22 +11664,22 @@
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -11702,22 +11702,22 @@
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -11740,22 +11740,22 @@
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -11778,22 +11778,22 @@
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -11816,22 +11816,22 @@
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -11854,22 +11854,22 @@
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -11892,22 +11892,22 @@
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc37§4,doc18 5-4(10)</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -11930,22 +11930,22 @@
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-2,doc18 4-7(4)</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -11968,22 +11968,22 @@
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-105</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-3,doc18 4-7(3)</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -12006,22 +12006,22 @@
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護を再開するかどうか</t>
+          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
+          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 施策3-2</t>
+          <t>doc37§4,doc18 5-4(10)</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12044,22 +12044,22 @@
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
+          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
+          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 4-7(2)</t>
+          <t>doc36§10-2,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -12082,22 +12082,22 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
+          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
+          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§10-3,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -12120,22 +12120,22 @@
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>認知症対応型通所介護を再開するかどうか</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc36§3,doc18 施策3-2</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -12158,22 +12158,22 @@
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc36§3,doc18 4-7(2)</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -12191,27 +12191,27 @@
       </c>
       <c r="B136" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -12229,27 +12229,27 @@
       </c>
       <c r="B137" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -12267,27 +12267,27 @@
       </c>
       <c r="B138" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
@@ -12310,22 +12310,22 @@
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
@@ -12348,22 +12348,22 @@
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E141" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>doc37§3-2,doc18 5-4</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
@@ -12424,22 +12424,22 @@
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
-          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>doc36§2,doc18 2-3</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G142" s="23" t="inlineStr">
@@ -12457,27 +12457,27 @@
       </c>
       <c r="B143" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C143" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E143" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G143" s="23" t="inlineStr">
@@ -12495,32 +12495,32 @@
       </c>
       <c r="B144" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C144" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
         </is>
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F144" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc38§B-2</t>
         </is>
       </c>
       <c r="G144" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>社内対応</t>
         </is>
       </c>
       <c r="H144" s="25" t="inlineStr"/>
@@ -12533,27 +12533,27 @@
       </c>
       <c r="B145" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C145" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
         </is>
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
         </is>
       </c>
       <c r="E145" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F145" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc37§3-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G145" s="23" t="inlineStr">
@@ -12571,27 +12571,27 @@
       </c>
       <c r="B146" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C146" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
         </is>
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
         </is>
       </c>
       <c r="E146" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F146" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc36§2,doc18 2-3</t>
         </is>
       </c>
       <c r="G146" s="23" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="C147" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E147" s="23" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="F147" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G147" s="23" t="inlineStr">
@@ -12652,22 +12652,22 @@
       </c>
       <c r="C148" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F148" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G148" s="23" t="inlineStr">
@@ -12685,27 +12685,27 @@
       </c>
       <c r="B149" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C149" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E149" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F149" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G149" s="23" t="inlineStr">
@@ -12723,27 +12723,27 @@
       </c>
       <c r="B150" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C150" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D150" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F150" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G150" s="23" t="inlineStr">
@@ -12761,27 +12761,27 @@
       </c>
       <c r="B151" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C151" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E151" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F151" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G151" s="23" t="inlineStr">
@@ -12799,27 +12799,27 @@
       </c>
       <c r="B152" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C152" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D152" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E152" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F152" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G152" s="23" t="inlineStr">
@@ -12837,27 +12837,27 @@
       </c>
       <c r="B153" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C153" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E153" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F153" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G153" s="23" t="inlineStr">
@@ -12875,27 +12875,27 @@
       </c>
       <c r="B154" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C154" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D154" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E154" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F154" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G154" s="23" t="inlineStr">
@@ -12913,27 +12913,27 @@
       </c>
       <c r="B155" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C155" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D155" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E155" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F155" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G155" s="23" t="inlineStr">
@@ -12951,27 +12951,27 @@
       </c>
       <c r="B156" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C156" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D156" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E156" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F156" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G156" s="23" t="inlineStr">
@@ -12994,265 +12994,265 @@
       </c>
       <c r="C157" s="25" t="inlineStr">
         <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D157" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E157" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F157" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G157" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H157" s="25" t="inlineStr"/>
+    </row>
+    <row r="158" ht="34" customHeight="1">
+      <c r="A158" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B158" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C158" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D158" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E158" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F158" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G158" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H158" s="25" t="inlineStr"/>
+    </row>
+    <row r="159" ht="34" customHeight="1">
+      <c r="A159" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B159" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C159" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D159" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E159" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F159" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G159" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H159" s="25" t="inlineStr"/>
+    </row>
+    <row r="160" ht="34" customHeight="1">
+      <c r="A160" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B160" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C160" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D160" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E160" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F160" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G160" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H160" s="25" t="inlineStr"/>
+    </row>
+    <row r="161" ht="34" customHeight="1">
+      <c r="A161" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B161" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C161" s="25" t="inlineStr">
+        <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D157" s="25" t="inlineStr">
+      <c r="D161" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E157" s="23" t="inlineStr">
+      <c r="E161" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F157" s="23" t="inlineStr">
+      <c r="F161" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G157" s="23" t="inlineStr">
+      <c r="G161" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H157" s="25" t="inlineStr"/>
-    </row>
-    <row r="158" ht="34" customHeight="1">
-      <c r="A158" s="38" t="inlineStr">
+      <c r="H161" s="25" t="inlineStr"/>
+    </row>
+    <row r="162" ht="34" customHeight="1">
+      <c r="A162" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B158" s="24" t="inlineStr">
+      <c r="B162" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C158" s="25" t="inlineStr">
+      <c r="C162" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D158" s="25" t="inlineStr">
+      <c r="D162" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E158" s="23" t="inlineStr">
+      <c r="E162" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-89</t>
         </is>
       </c>
-      <c r="F158" s="23" t="inlineStr">
+      <c r="F162" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G158" s="23" t="inlineStr">
+      <c r="G162" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H158" s="25" t="inlineStr"/>
-    </row>
-    <row r="159" ht="34" customHeight="1">
-      <c r="A159" s="38" t="inlineStr">
+      <c r="H162" s="25" t="inlineStr"/>
+    </row>
+    <row r="163" ht="34" customHeight="1">
+      <c r="A163" s="38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B159" s="24" t="inlineStr">
+      <c r="B163" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C159" s="25" t="inlineStr">
+      <c r="C163" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D159" s="25" t="inlineStr">
+      <c r="D163" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E159" s="23" t="inlineStr">
+      <c r="E163" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F159" s="23" t="inlineStr">
+      <c r="F163" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G159" s="23" t="inlineStr">
+      <c r="G163" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H159" s="25" t="inlineStr"/>
-    </row>
-    <row r="161" ht="20" customHeight="1">
-      <c r="A161" s="39" t="inlineStr">
+      <c r="H163" s="25" t="inlineStr"/>
+    </row>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="39" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="162" ht="34" customHeight="1">
-      <c r="A162" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B162" s="41" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C162" s="42" t="inlineStr">
-        <is>
-          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
-        </is>
-      </c>
-      <c r="D162" s="42" t="inlineStr">
-        <is>
-          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
-        </is>
-      </c>
-      <c r="E162" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F162" s="40" t="inlineStr">
-        <is>
-          <t>doc35§7-3(1)</t>
-        </is>
-      </c>
-      <c r="G162" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H162" s="42" t="inlineStr"/>
-    </row>
-    <row r="163" ht="34" customHeight="1">
-      <c r="A163" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B163" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C163" s="42" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D163" s="42" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E163" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F163" s="40" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G163" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H163" s="42" t="inlineStr"/>
-    </row>
-    <row r="164" ht="34" customHeight="1">
-      <c r="A164" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B164" s="41" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C164" s="42" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D164" s="42" t="inlineStr">
-        <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
-        </is>
-      </c>
-      <c r="E164" s="40" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F164" s="40" t="inlineStr">
-        <is>
-          <t>doc28§4</t>
-        </is>
-      </c>
-      <c r="G164" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H164" s="42" t="inlineStr"/>
-    </row>
-    <row r="165" ht="34" customHeight="1">
-      <c r="A165" s="40" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B165" s="41" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C165" s="42" t="inlineStr">
-        <is>
-          <t>所得段階別の第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D165" s="42" t="inlineStr">
-        <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
-        </is>
-      </c>
-      <c r="E165" s="40" t="inlineStr">
-        <is>
-          <t>Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F165" s="40" t="inlineStr">
-        <is>
-          <t>doc28§2</t>
-        </is>
-      </c>
-      <c r="G165" s="40" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H165" s="42" t="inlineStr"/>
     </row>
     <row r="166" ht="34" customHeight="1">
       <c r="A166" s="40" t="inlineStr">
@@ -13262,27 +13262,27 @@
       </c>
       <c r="B166" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C166" s="42" t="inlineStr">
         <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
+          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
         </is>
       </c>
       <c r="D166" s="42" t="inlineStr">
         <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
+          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
         </is>
       </c>
       <c r="E166" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F166" s="40" t="inlineStr">
         <is>
-          <t>doc28§1</t>
+          <t>doc35§7-3(1)</t>
         </is>
       </c>
       <c r="G166" s="40" t="inlineStr">
@@ -13300,32 +13300,32 @@
       </c>
       <c r="B167" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C167" s="42" t="inlineStr">
         <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D167" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E167" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F167" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-1</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G167" s="40" t="inlineStr">
         <is>
-          <t>解決済（一部再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H167" s="42" t="inlineStr"/>
@@ -13338,27 +13338,27 @@
       </c>
       <c r="B168" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C168" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D168" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E168" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F168" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G168" s="40" t="inlineStr">
@@ -13376,32 +13376,32 @@
       </c>
       <c r="B169" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C169" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D169" s="42" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E169" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F169" s="40" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G169" s="40" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H169" s="42" t="inlineStr"/>
@@ -13414,27 +13414,27 @@
       </c>
       <c r="B170" s="41" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C170" s="42" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D170" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E170" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F170" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G170" s="40" t="inlineStr">
@@ -13457,27 +13457,27 @@
       </c>
       <c r="C171" s="42" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D171" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E171" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F171" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G171" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H171" s="42" t="inlineStr"/>
@@ -13495,22 +13495,22 @@
       </c>
       <c r="C172" s="42" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D172" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E172" s="40" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F172" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G172" s="40" t="inlineStr">
@@ -13528,32 +13528,32 @@
       </c>
       <c r="B173" s="41" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C173" s="42" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D173" s="42" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E173" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F173" s="40" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G173" s="40" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H173" s="42" t="inlineStr"/>
@@ -13566,27 +13566,27 @@
       </c>
       <c r="B174" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C174" s="42" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D174" s="42" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E174" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F174" s="40" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G174" s="40" t="inlineStr">
@@ -13604,27 +13604,27 @@
       </c>
       <c r="B175" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C175" s="42" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D175" s="42" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E175" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F175" s="40" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G175" s="40" t="inlineStr">
@@ -13642,27 +13642,27 @@
       </c>
       <c r="B176" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C176" s="42" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D176" s="42" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E176" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F176" s="40" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G176" s="40" t="inlineStr">
@@ -13680,27 +13680,27 @@
       </c>
       <c r="B177" s="41" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C177" s="42" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D177" s="42" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E177" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F177" s="40" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G177" s="40" t="inlineStr">
@@ -13723,22 +13723,22 @@
       </c>
       <c r="C178" s="42" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D178" s="42" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E178" s="40" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F178" s="40" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G178" s="40" t="inlineStr">
@@ -13761,43 +13761,195 @@
       </c>
       <c r="C179" s="42" t="inlineStr">
         <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D179" s="42" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E179" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F179" s="40" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G179" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H179" s="42" t="inlineStr"/>
+    </row>
+    <row r="180" ht="34" customHeight="1">
+      <c r="A180" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B180" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C180" s="42" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D180" s="42" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E180" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F180" s="40" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G180" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H180" s="42" t="inlineStr"/>
+    </row>
+    <row r="181" ht="34" customHeight="1">
+      <c r="A181" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B181" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C181" s="42" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D181" s="42" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E181" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F181" s="40" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G181" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H181" s="42" t="inlineStr"/>
+    </row>
+    <row r="182" ht="34" customHeight="1">
+      <c r="A182" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B182" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C182" s="42" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D182" s="42" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E182" s="40" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F182" s="40" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G182" s="40" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H182" s="42" t="inlineStr"/>
+    </row>
+    <row r="183" ht="34" customHeight="1">
+      <c r="A183" s="40" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B183" s="41" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C183" s="42" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D179" s="42" t="inlineStr">
+      <c r="D183" s="42" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E179" s="40" t="inlineStr">
+      <c r="E183" s="40" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F179" s="40" t="inlineStr">
+      <c r="F183" s="40" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G179" s="40" t="inlineStr">
+      <c r="G183" s="40" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H179" s="42" t="inlineStr"/>
+      <c r="H183" s="42" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H159"/>
+  <autoFilter ref="A4:H163"/>
   <mergeCells count="3">
-    <mergeCell ref="A161:H161"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A165:H165"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A159" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G159" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$162</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'仕様書対照'!$A$4:$H$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="P27" s="13" t="inlineStr">
         <is>
-          <t>★対象者リストによりニーズ882人・在宅118人と判明。仕様書の「約850人／約150人」に対し在宅が32人少ない。予備を含めた部数と、在宅の少なさを集計設計でどう扱うかが未決。</t>
+          <t>★対象者リストによりニーズ882人・在宅118人と判明。★9/24：村の回答により在宅118人で決着（仕様書の「約150人」との差異は解消）。残るのは予備を含めた部数の確定と、回収70〜80件を前提とした集計設計（要介護度3区分を2区分に束ねるか）の判断。</t>
         </is>
       </c>
     </row>
@@ -2457,60 +2457,66 @@
       <c r="P29" s="25" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-23</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-2 印刷・発送準備</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>返信用封筒の印刷</t>
         </is>
       </c>
-      <c r="E30" s="18" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(3)</t>
         </is>
       </c>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G30" s="20" t="inlineStr">
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>返信用封筒</t>
         </is>
       </c>
-      <c r="H30" s="20" t="inlineStr"/>
-      <c r="I30" s="18" t="inlineStr">
+      <c r="H30" s="13" t="inlineStr"/>
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>R8.9中</t>
         </is>
       </c>
-      <c r="J30" s="21" t="n"/>
-      <c r="K30" s="21" t="n"/>
-      <c r="L30" s="21" t="n"/>
-      <c r="M30" s="21" t="n"/>
-      <c r="N30" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P30" s="20" t="inlineStr"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
+      <c r="L30" s="14" t="n">
+        <v>46274</v>
+      </c>
+      <c r="M30" s="14" t="n"/>
+      <c r="N30" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O30" s="16" t="inlineStr">
+        <is>
+          <t>確認中</t>
+        </is>
+      </c>
+      <c r="P30" s="13" t="inlineStr">
+        <is>
+          <t>★版下を受領済（doc34）。★9/24：配布用封筒は村が用意し費用は村側で請求処理することが決着したため、受託者が印刷するのは返信用（回収用）のみで確定（仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消）。差出有効期間が回収期限と同日（2026年10月16日）である点は未決で、期限翌日以降に投函された回答が届かない。</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -2676,17 +2682,23 @@
       </c>
       <c r="J33" s="14" t="n"/>
       <c r="K33" s="14" t="n"/>
-      <c r="L33" s="14" t="n"/>
+      <c r="L33" s="14" t="n">
+        <v>46266</v>
+      </c>
       <c r="M33" s="14" t="n"/>
       <c r="N33" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="11" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P33" s="13" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="O33" s="16" t="inlineStr">
+        <is>
+          <t>確認中</t>
+        </is>
+      </c>
+      <c r="P33" s="13" t="inlineStr">
+        <is>
+          <t>★キックオフ会議で村が用意すると決着。★9/24：費用は村側で請求処理することを確認。提供期限は9/14（9/11への前倒しを要請中）。</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="18" t="inlineStr">
@@ -4168,67 +4180,77 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="P57" s="25" t="inlineStr"/>
+      <c r="P57" s="25" t="inlineStr">
+        <is>
+          <t>★1頁あたり2設問から、選択肢の少ない設問は3設問に詰める（100頁に収めるため）。図が小さくなるためモノクロ印刷での可読性に注意を要する。計画書と同じく明度差・線種・ハッチングで識別し、凡例を図の近くに置く。集計結果の確定待ち。</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>Ⅰ-48</t>
         </is>
       </c>
-      <c r="B58" s="19" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C58" s="19" t="inlineStr">
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>Ⅰ-6 報告書</t>
         </is>
       </c>
-      <c r="D58" s="20" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>調査結果報告書の執筆・レイアウト</t>
         </is>
       </c>
-      <c r="E58" s="18" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(7)</t>
         </is>
       </c>
-      <c r="F58" s="18" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G58" s="20" t="inlineStr">
+      <c r="G58" s="13" t="inlineStr">
         <is>
           <t>報告書案</t>
         </is>
       </c>
-      <c r="H58" s="20" t="inlineStr">
+      <c r="H58" s="13" t="inlineStr">
         <is>
           <t>A4両面約100頁</t>
         </is>
       </c>
-      <c r="I58" s="18" t="inlineStr">
+      <c r="I58" s="11" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="J58" s="21" t="n"/>
-      <c r="K58" s="21" t="n"/>
-      <c r="L58" s="21" t="n"/>
-      <c r="M58" s="21" t="n"/>
-      <c r="N58" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="18" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P58" s="20" t="inlineStr"/>
+      <c r="J58" s="14" t="n"/>
+      <c r="K58" s="14" t="n"/>
+      <c r="L58" s="14" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M58" s="14" t="n"/>
+      <c r="N58" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O58" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P58" s="13" t="inlineStr">
+        <is>
+          <t>★doc24として骨子案を作成（2部構成・第Ⅰ部 単純集計編／第Ⅱ部 ICF分析編）。★9/24：村の指示により仕様書どおり約100頁に統一することが決着し、当初案118頁から18頁を圧縮する構成に改訂（doc24§1-1）。第Ⅱ部25頁は計画の施策の根拠のため維持し、第3章40→33頁・第4章20→14頁・資料編25→22頁・第1,2章8→6頁で削る。設問数は削らない（仕様書4Ⅰ(7)が設問ごとのグラフを求めるため）。本文の執筆は調査の回収・集計待ち。</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="23" t="inlineStr">
@@ -7536,7 +7558,11 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="P110" s="20" t="inlineStr"/>
+      <c r="P110" s="20" t="inlineStr">
+        <is>
+          <t>★9/24：仕様書どおりA4判両面約100頁・モノクロ・ホチキス製本・10部で確定。両面100頁＝紙50枚でホチキス製本の上限に近く、当初案の118頁（59枚）は製本の面でも無理があった。</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="23" t="inlineStr">
@@ -8058,7 +8084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10116,22 +10142,22 @@
       </c>
       <c r="C57" s="33" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>在宅介護実態調査の集計設計（要介護度3区分×介護者勤務形態3区分のセル数）</t>
         </is>
       </c>
       <c r="D57" s="33" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>★対象が118人（仕様書の想定150人）であることは村の了解を得て決着。残るのは集計設計の判断で、回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかを当方で決める。</t>
         </is>
       </c>
       <c r="E57" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-95</t>
+          <t>Ⅰ-45</t>
         </is>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc34§5-2</t>
         </is>
       </c>
       <c r="G57" s="34" t="inlineStr">
@@ -10154,22 +10180,22 @@
       </c>
       <c r="C58" s="33" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D58" s="33" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E58" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅰ-95</t>
         </is>
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G58" s="34" t="inlineStr">
@@ -10192,22 +10218,22 @@
       </c>
       <c r="C59" s="33" t="inlineStr">
         <is>
-          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D59" s="33" t="inlineStr">
         <is>
-          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E59" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-46</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
-          <t>doc25§4-2 K-91</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G59" s="34" t="inlineStr">
@@ -10225,27 +10251,27 @@
       </c>
       <c r="B60" s="32" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C60" s="33" t="inlineStr">
         <is>
-          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
+          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
         </is>
       </c>
       <c r="D60" s="33" t="inlineStr">
         <is>
-          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
+          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
         </is>
       </c>
       <c r="E60" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-70,Ⅱ-71</t>
+          <t>Ⅰ-46</t>
         </is>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc25§4-2 K-91</t>
         </is>
       </c>
       <c r="G60" s="34" t="inlineStr">
@@ -10263,27 +10289,27 @@
       </c>
       <c r="B61" s="32" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C61" s="33" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
         </is>
       </c>
       <c r="D61" s="33" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
         </is>
       </c>
       <c r="E61" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅱ-70,Ⅱ-71</t>
         </is>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G61" s="34" t="inlineStr">
@@ -10301,27 +10327,27 @@
       </c>
       <c r="B62" s="32" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C62" s="33" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D62" s="33" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E62" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G62" s="34" t="inlineStr">
@@ -10344,22 +10370,22 @@
       </c>
       <c r="C63" s="33" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D63" s="33" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E63" s="34" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G63" s="34" t="inlineStr">
@@ -10377,27 +10403,27 @@
       </c>
       <c r="B64" s="32" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C64" s="33" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の対象が118人（想定150人）であることへの集計設計の対応</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D64" s="33" t="inlineStr">
         <is>
-          <t>★回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかの判断が要る。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E64" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-45</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>doc34§5-2</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G64" s="34" t="inlineStr">
@@ -12391,27 +12417,27 @@
       </c>
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量と製本仕様（頁数・部数）</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>約118頁（第Ⅰ部 単純集計編60頁＋第Ⅱ部 分析編25頁＋資料編25頁ほか）を想定。仕様書はホチキス製本としか定めておらず頁数・部数の明示がない。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-88</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -12434,22 +12460,22 @@
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -12472,22 +12498,22 @@
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -12510,22 +12536,22 @@
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -12548,22 +12574,22 @@
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -12586,22 +12612,22 @@
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -12624,22 +12650,22 @@
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -12662,22 +12688,22 @@
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-105,Ⅱ-67</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -12700,22 +12726,22 @@
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -12738,22 +12764,22 @@
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -12776,22 +12802,22 @@
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -12814,22 +12840,22 @@
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -12852,22 +12878,22 @@
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -12890,22 +12916,22 @@
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc37§4,doc18 5-4(10)</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -12928,22 +12954,22 @@
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
+          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
+          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc37§4,doc18 5-4(10)</t>
+          <t>doc36§10-2,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12966,22 +12992,22 @@
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
+          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
+          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-2,doc18 4-7(4)</t>
+          <t>doc36§10-3,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -13004,22 +13030,22 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
+          <t>認知症対応型通所介護を再開するかどうか</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
+          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-3,doc18 4-7(3)</t>
+          <t>doc36§3,doc18 施策3-2</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -13042,22 +13068,22 @@
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護を再開するかどうか</t>
+          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
+          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 施策3-2</t>
+          <t>doc36§3,doc18 4-7(2)</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -13080,22 +13106,22 @@
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 4-7(2)</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -13118,22 +13144,22 @@
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -13156,22 +13182,22 @@
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -13189,27 +13215,27 @@
       </c>
       <c r="B138" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
@@ -13232,12 +13258,12 @@
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
@@ -13247,7 +13273,7 @@
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
@@ -13270,22 +13296,22 @@
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
@@ -13308,22 +13334,22 @@
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E141" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
@@ -13346,22 +13372,22 @@
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G142" s="23" t="inlineStr">
@@ -13384,12 +13410,12 @@
       </c>
       <c r="C143" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
         </is>
       </c>
       <c r="E143" s="23" t="inlineStr">
@@ -13399,12 +13425,12 @@
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc38§B-2</t>
         </is>
       </c>
       <c r="G143" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>社内対応</t>
         </is>
       </c>
       <c r="H143" s="25" t="inlineStr"/>
@@ -13422,27 +13448,27 @@
       </c>
       <c r="C144" s="25" t="inlineStr">
         <is>
-          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
+          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
         </is>
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
+          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F144" s="23" t="inlineStr">
         <is>
-          <t>doc38§B-2</t>
+          <t>doc37§3-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G144" s="23" t="inlineStr">
         <is>
-          <t>社内対応</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H144" s="25" t="inlineStr"/>
@@ -13460,22 +13486,22 @@
       </c>
       <c r="C145" s="25" t="inlineStr">
         <is>
-          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
+          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
         </is>
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
+          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
         </is>
       </c>
       <c r="E145" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F145" s="23" t="inlineStr">
         <is>
-          <t>doc37§3-2,doc18 5-4</t>
+          <t>doc36§2,doc18 2-3</t>
         </is>
       </c>
       <c r="G145" s="23" t="inlineStr">
@@ -13493,27 +13519,27 @@
       </c>
       <c r="B146" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C146" s="25" t="inlineStr">
         <is>
-          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E146" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F146" s="23" t="inlineStr">
         <is>
-          <t>doc36§2,doc18 2-3</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G146" s="23" t="inlineStr">
@@ -13536,22 +13562,22 @@
       </c>
       <c r="C147" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E147" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F147" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G147" s="23" t="inlineStr">
@@ -13574,12 +13600,12 @@
       </c>
       <c r="C148" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
@@ -13589,7 +13615,7 @@
       </c>
       <c r="F148" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G148" s="23" t="inlineStr">
@@ -13612,22 +13638,22 @@
       </c>
       <c r="C149" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E149" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F149" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G149" s="23" t="inlineStr">
@@ -13650,12 +13676,12 @@
       </c>
       <c r="C150" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D150" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
@@ -13665,7 +13691,7 @@
       </c>
       <c r="F150" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G150" s="23" t="inlineStr">
@@ -13688,22 +13714,22 @@
       </c>
       <c r="C151" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E151" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F151" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G151" s="23" t="inlineStr">
@@ -13721,27 +13747,27 @@
       </c>
       <c r="B152" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C152" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D152" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E152" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F152" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G152" s="23" t="inlineStr">
@@ -13764,22 +13790,22 @@
       </c>
       <c r="C153" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E153" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F153" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G153" s="23" t="inlineStr">
@@ -13802,22 +13828,22 @@
       </c>
       <c r="C154" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D154" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E154" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F154" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G154" s="23" t="inlineStr">
@@ -13840,22 +13866,22 @@
       </c>
       <c r="C155" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D155" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E155" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F155" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G155" s="23" t="inlineStr">
@@ -13873,27 +13899,27 @@
       </c>
       <c r="B156" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C156" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
         </is>
       </c>
       <c r="D156" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
         </is>
       </c>
       <c r="E156" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-31</t>
         </is>
       </c>
       <c r="F156" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc19 追-6</t>
         </is>
       </c>
       <c r="G156" s="23" t="inlineStr">
@@ -13916,22 +13942,22 @@
       </c>
       <c r="C157" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
         </is>
       </c>
       <c r="D157" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
         </is>
       </c>
       <c r="E157" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅰ-40,Ⅰ-42</t>
         </is>
       </c>
       <c r="F157" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc19 追-7</t>
         </is>
       </c>
       <c r="G157" s="23" t="inlineStr">
@@ -13954,22 +13980,22 @@
       </c>
       <c r="C158" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
         </is>
       </c>
       <c r="D158" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
         </is>
       </c>
       <c r="E158" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F158" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc23§1-3</t>
         </is>
       </c>
       <c r="G158" s="23" t="inlineStr">
@@ -13992,22 +14018,22 @@
       </c>
       <c r="C159" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>送付状の個人情報に関する説明の補強</t>
         </is>
       </c>
       <c r="D159" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
         </is>
       </c>
       <c r="E159" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F159" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc27§5-1</t>
         </is>
       </c>
       <c r="G159" s="23" t="inlineStr">
@@ -14030,22 +14056,22 @@
       </c>
       <c r="C160" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
       <c r="D160" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
       <c r="E160" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F160" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc27§4</t>
         </is>
       </c>
       <c r="G160" s="23" t="inlineStr">
@@ -14056,34 +14082,34 @@
       <c r="H160" s="25" t="inlineStr"/>
     </row>
     <row r="161" ht="34" customHeight="1">
-      <c r="A161" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A161" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B161" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C161" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
+          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
       <c r="D161" s="25" t="inlineStr">
         <is>
-          <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
+          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
       <c r="E161" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
       <c r="F161" s="23" t="inlineStr">
         <is>
-          <t>doc27§4</t>
+          <t>doc01-10</t>
         </is>
       </c>
       <c r="G161" s="23" t="inlineStr">
@@ -14106,22 +14132,22 @@
       </c>
       <c r="C162" s="25" t="inlineStr">
         <is>
-          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
+          <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
       <c r="D162" s="25" t="inlineStr">
         <is>
-          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
+          <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
       <c r="E162" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅳ-89</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F162" s="23" t="inlineStr">
         <is>
-          <t>doc01-10</t>
+          <t>doc01-10,doc08</t>
         </is>
       </c>
       <c r="G162" s="23" t="inlineStr">
@@ -14131,50 +14157,50 @@
       </c>
       <c r="H162" s="25" t="inlineStr"/>
     </row>
-    <row r="163" ht="34" customHeight="1">
-      <c r="A163" s="37" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B163" s="24" t="inlineStr">
-        <is>
-          <t>成果品</t>
-        </is>
-      </c>
-      <c r="C163" s="25" t="inlineStr">
-        <is>
-          <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
-        </is>
-      </c>
-      <c r="D163" s="25" t="inlineStr">
-        <is>
-          <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
-        </is>
-      </c>
-      <c r="E163" s="23" t="inlineStr">
-        <is>
-          <t>Ⅳ-92</t>
-        </is>
-      </c>
-      <c r="F163" s="23" t="inlineStr">
-        <is>
-          <t>doc01-10,doc08</t>
-        </is>
-      </c>
-      <c r="G163" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H163" s="25" t="inlineStr"/>
-    </row>
-    <row r="165" ht="20" customHeight="1">
-      <c r="A165" s="38" t="inlineStr">
+    <row r="164" ht="20" customHeight="1">
+      <c r="A164" s="38" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
+    </row>
+    <row r="165" ht="34" customHeight="1">
+      <c r="A165" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B165" s="40" t="inlineStr">
+        <is>
+          <t>疑義</t>
+        </is>
+      </c>
+      <c r="C165" s="41" t="inlineStr">
+        <is>
+          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
+        </is>
+      </c>
+      <c r="D165" s="41" t="inlineStr">
+        <is>
+          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
+        </is>
+      </c>
+      <c r="E165" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-64</t>
+        </is>
+      </c>
+      <c r="F165" s="39" t="inlineStr">
+        <is>
+          <t>doc35§7-3(1)</t>
+        </is>
+      </c>
+      <c r="G165" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H165" s="41" t="inlineStr"/>
     </row>
     <row r="166" ht="34" customHeight="1">
       <c r="A166" s="39" t="inlineStr">
@@ -14184,27 +14210,27 @@
       </c>
       <c r="B166" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C166" s="41" t="inlineStr">
         <is>
-          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D166" s="41" t="inlineStr">
         <is>
-          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E166" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F166" s="39" t="inlineStr">
         <is>
-          <t>doc35§7-3(1)</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G166" s="39" t="inlineStr">
@@ -14222,27 +14248,27 @@
       </c>
       <c r="B167" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C167" s="41" t="inlineStr">
         <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D167" s="41" t="inlineStr">
         <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E167" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F167" s="39" t="inlineStr">
         <is>
-          <t>doc28§3</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G167" s="39" t="inlineStr">
@@ -14260,27 +14286,27 @@
       </c>
       <c r="B168" s="40" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C168" s="41" t="inlineStr">
         <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D168" s="41" t="inlineStr">
         <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E168" s="39" t="inlineStr">
         <is>
-          <t>０-04</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F168" s="39" t="inlineStr">
         <is>
-          <t>doc28§4</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G168" s="39" t="inlineStr">
@@ -14303,22 +14329,22 @@
       </c>
       <c r="C169" s="41" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D169" s="41" t="inlineStr">
         <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E169" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F169" s="39" t="inlineStr">
         <is>
-          <t>doc28§2</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G169" s="39" t="inlineStr">
@@ -14336,32 +14362,32 @@
       </c>
       <c r="B170" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C170" s="41" t="inlineStr">
         <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D170" s="41" t="inlineStr">
         <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E170" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F170" s="39" t="inlineStr">
         <is>
-          <t>doc28§1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G170" s="39" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H170" s="41" t="inlineStr"/>
@@ -14379,27 +14405,27 @@
       </c>
       <c r="C171" s="41" t="inlineStr">
         <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D171" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E171" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F171" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G171" s="39" t="inlineStr">
         <is>
-          <t>解決済（一部再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H171" s="41" t="inlineStr"/>
@@ -14417,12 +14443,12 @@
       </c>
       <c r="C172" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D172" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E172" s="39" t="inlineStr">
@@ -14437,7 +14463,7 @@
       </c>
       <c r="G172" s="39" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H172" s="41" t="inlineStr"/>
@@ -14455,27 +14481,27 @@
       </c>
       <c r="C173" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D173" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E173" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F173" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G173" s="39" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H173" s="41" t="inlineStr"/>
@@ -14493,12 +14519,12 @@
       </c>
       <c r="C174" s="41" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D174" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E174" s="39" t="inlineStr">
@@ -14531,17 +14557,17 @@
       </c>
       <c r="C175" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D175" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E175" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F175" s="39" t="inlineStr">
@@ -14564,27 +14590,27 @@
       </c>
       <c r="B176" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C176" s="41" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>配布用封筒の用意の主体（仕様書4Ⅰ(3)は受託者の印刷対象としている）</t>
         </is>
       </c>
       <c r="D176" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>★2026/09/24 村の回答で決着：配布用封筒は村が用意し、費用は村側で請求処理する。受託者が印刷するのは返信用（回収用）のみ。仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消した。</t>
         </is>
       </c>
       <c r="E176" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-23,Ⅰ-26,Ⅰ-103</t>
         </is>
       </c>
       <c r="F176" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G176" s="39" t="inlineStr">
@@ -14602,27 +14628,27 @@
       </c>
       <c r="B177" s="40" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C177" s="41" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>在宅介護実態調査の対象者数（仕様書の約150人に対し118人）</t>
         </is>
       </c>
       <c r="D177" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>★2026/09/24 村の回答で決着：118人で問題なし。仕様書4Ⅰ(1)の「約150人」との差異は解消した。集計設計上のセル数の扱いは当方の判断事項として継続。</t>
         </is>
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-08,Ⅰ-24,Ⅰ-103</t>
         </is>
       </c>
       <c r="F177" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G177" s="39" t="inlineStr">
@@ -14640,27 +14666,27 @@
       </c>
       <c r="B178" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C178" s="41" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>アンケート調査報告書の分量（仕様書の約100頁に対し想定118頁）</t>
         </is>
       </c>
       <c r="D178" s="41" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>★2026/09/24 村の回答で決着：仕様書どおり約100頁に統一する。第Ⅱ部（分析編25頁）は計画の根拠のため維持し、第Ⅰ部（単純集計編）と資料編で18頁を圧縮する（doc24§1改訂）。部数は仕様書のとおり10部。</t>
         </is>
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F178" s="39" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G178" s="39" t="inlineStr">
@@ -14678,27 +14704,27 @@
       </c>
       <c r="B179" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C179" s="41" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D179" s="41" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F179" s="39" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G179" s="39" t="inlineStr">
@@ -14721,12 +14747,12 @@
       </c>
       <c r="C180" s="41" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D180" s="41" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E180" s="39" t="inlineStr">
@@ -14736,7 +14762,7 @@
       </c>
       <c r="F180" s="39" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G180" s="39" t="inlineStr">
@@ -14759,22 +14785,22 @@
       </c>
       <c r="C181" s="41" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>交付要綱の配点表（満点）</t>
         </is>
       </c>
       <c r="D181" s="41" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
         </is>
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F181" s="39" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc20§2</t>
         </is>
       </c>
       <c r="G181" s="39" t="inlineStr">
@@ -14797,22 +14823,22 @@
       </c>
       <c r="C182" s="41" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
         </is>
       </c>
       <c r="D182" s="41" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
         </is>
       </c>
       <c r="E182" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F182" s="39" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc20§3-1</t>
         </is>
       </c>
       <c r="G182" s="39" t="inlineStr">
@@ -14835,43 +14861,119 @@
       </c>
       <c r="C183" s="41" t="inlineStr">
         <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D183" s="41" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E183" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F183" s="39" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G183" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H183" s="41" t="inlineStr"/>
+    </row>
+    <row r="184" ht="34" customHeight="1">
+      <c r="A184" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B184" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C184" s="41" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D184" s="41" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E184" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F184" s="39" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G184" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H184" s="41" t="inlineStr"/>
+    </row>
+    <row r="185" ht="34" customHeight="1">
+      <c r="A185" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B185" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C185" s="41" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D183" s="41" t="inlineStr">
+      <c r="D185" s="41" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E183" s="39" t="inlineStr">
+      <c r="E185" s="39" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F183" s="39" t="inlineStr">
+      <c r="F185" s="39" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G183" s="39" t="inlineStr">
+      <c r="G185" s="39" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H183" s="41" t="inlineStr"/>
+      <c r="H185" s="41" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H163"/>
+  <autoFilter ref="A4:H162"/>
   <mergeCells count="3">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A165:H165"/>
+    <mergeCell ref="A164:H164"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15480,7 +15582,7 @@
       </c>
       <c r="H17" s="25" t="inlineStr">
         <is>
-          <t>実際の抽出は118人。32人の差の集計設計上の扱いを要確認</t>
+          <t>実際の抽出は118人。2026/09/24 村の了解により決着（集計設計上の扱いは当方の判断事項）</t>
         </is>
       </c>
     </row>
@@ -15897,48 +15999,48 @@
       <c r="H27" s="25" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="32" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>4Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="B28" s="34" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(3)-c</t>
         </is>
       </c>
-      <c r="C28" s="33" t="inlineStr">
+      <c r="C28" s="25" t="inlineStr">
         <is>
           <t>封筒（配布用・回収用）を各必要部数用意する</t>
         </is>
       </c>
-      <c r="D28" s="34" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>双方</t>
         </is>
       </c>
-      <c r="E28" s="33" t="inlineStr">
+      <c r="E28" s="25" t="inlineStr">
         <is>
           <t>Ⅰ-23
 Ⅰ-26
 Ⅰ-103</t>
         </is>
       </c>
-      <c r="F28" s="33" t="inlineStr">
+      <c r="F28" s="25" t="inlineStr">
         <is>
           <t>返信用封筒の印刷
 配布用封筒の提供
 印刷部数の確定（予備を含む）</t>
         </is>
       </c>
-      <c r="G28" s="34" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="H28" s="33" t="inlineStr">
-        <is>
-          <t>★仕様書は配布用も印刷対象とするが、キックオフ議事録で配布用は村提供と確定した（仕様書との差異）</t>
+      <c r="H28" s="25" t="inlineStr">
+        <is>
+          <t>2026/09/24 決着：配布用封筒は村が用意し費用は村側で請求処理。受託者の印刷は返信用（回収用）のみ</t>
         </is>
       </c>
     </row>
@@ -18564,7 +18666,7 @@
       </c>
       <c r="H94" s="25" t="inlineStr">
         <is>
-          <t>想定約118頁。頁数・部数の明示がなく要確認</t>
+          <t>2026/09/24 決着：仕様書どおり約100頁に統一。第Ⅱ部（分析編25頁）は維持し第Ⅰ部・資料編で18頁を圧縮（doc24§1-1）</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$164</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'仕様書対照'!$A$4:$H$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
   </definedNames>
@@ -8084,7 +8084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10408,22 +10408,22 @@
       </c>
       <c r="C64" s="33" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>★アンケート調査報告書に調査票の再掲を載せるか（第9期報告書の巻末の確認を含む）</t>
         </is>
       </c>
       <c r="D64" s="33" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★100頁の枠で最も効く判断。資料編22頁の大半は調査票の再掲（ニーズ12頁＋在宅8頁）で、これを電子媒体に回すと集計編を47頁→63頁に戻せ、第9期の1設問1頁に近い密度（1頁1.7設問）を保てる。載せる場合は集計編が1頁2.3設問となり第9期の2.5倍の密度になる。doc01§5-5に記録した第9期の構成には資料編がないが、目次の見出しのみの記録のため巻末に調査票があるかを実物でご確認いただきたい。</t>
         </is>
       </c>
       <c r="E64" s="34" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅳ-90,Ⅰ-48,Ⅳ-114</t>
         </is>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc40§2-3</t>
         </is>
       </c>
       <c r="G64" s="34" t="inlineStr">
@@ -10441,27 +10441,27 @@
       </c>
       <c r="B65" s="32" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C65" s="33" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D65" s="33" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E65" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>doc33§3-5</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G65" s="34" t="inlineStr">
@@ -10484,22 +10484,22 @@
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
         </is>
       </c>
       <c r="D66" s="33" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
         </is>
       </c>
       <c r="E66" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc33§3-5</t>
         </is>
       </c>
       <c r="G66" s="34" t="inlineStr">
@@ -10522,22 +10522,22 @@
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D67" s="33" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E67" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G67" s="34" t="inlineStr">
@@ -10560,22 +10560,22 @@
       </c>
       <c r="C68" s="33" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D68" s="33" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E68" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G68" s="34" t="inlineStr">
@@ -10598,22 +10598,22 @@
       </c>
       <c r="C69" s="33" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D69" s="33" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-99</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G69" s="34" t="inlineStr">
@@ -10636,22 +10636,22 @@
       </c>
       <c r="C70" s="33" t="inlineStr">
         <is>
-          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D70" s="33" t="inlineStr">
         <is>
-          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
         </is>
       </c>
       <c r="E70" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>doc28§1-2 K-107</t>
+          <t>doc26§10 K-99</t>
         </is>
       </c>
       <c r="G70" s="34" t="inlineStr">
@@ -10674,22 +10674,22 @@
       </c>
       <c r="C71" s="33" t="inlineStr">
         <is>
-          <t>認知症施策の実施状況の評価と公表の運用</t>
+          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
         </is>
       </c>
       <c r="D71" s="33" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
+          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
         </is>
       </c>
       <c r="E71" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-71</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
-          <t>doc36§10-1,doc18 4-7(6)</t>
+          <t>doc28§1-2 K-107</t>
         </is>
       </c>
       <c r="G71" s="34" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="C72" s="33" t="inlineStr">
         <is>
-          <t>認知症の人およびご家族から意見を聴く方法</t>
+          <t>認知症施策の実施状況の評価と公表の運用</t>
         </is>
       </c>
       <c r="D72" s="33" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
+          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
         </is>
       </c>
       <c r="E72" s="34" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>doc36§5,doc18 4-7(4)</t>
+          <t>doc36§10-1,doc18 4-7(6)</t>
         </is>
       </c>
       <c r="G72" s="34" t="inlineStr">
@@ -10750,22 +10750,22 @@
       </c>
       <c r="C73" s="33" t="inlineStr">
         <is>
-          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
+          <t>認知症の人およびご家族から意見を聴く方法</t>
         </is>
       </c>
       <c r="D73" s="33" t="inlineStr">
         <is>
-          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
+          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
         </is>
       </c>
       <c r="E73" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§5,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G73" s="34" t="inlineStr">
@@ -10783,27 +10783,27 @@
       </c>
       <c r="B74" s="32" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
         </is>
       </c>
       <c r="D74" s="33" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
         </is>
       </c>
       <c r="E74" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G74" s="34" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D75" s="33" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E75" s="34" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G75" s="34" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D76" s="33" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E76" s="34" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G76" s="34" t="inlineStr">
@@ -10897,32 +10897,32 @@
       </c>
       <c r="B77" s="32" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E77" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G77" s="34" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H77" s="33" t="inlineStr"/>
@@ -10940,27 +10940,27 @@
       </c>
       <c r="C78" s="33" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
       <c r="D78" s="33" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
       <c r="E78" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G78" s="34" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H78" s="33" t="inlineStr"/>
@@ -10978,12 +10978,12 @@
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
         </is>
       </c>
       <c r="D79" s="33" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
         </is>
       </c>
       <c r="E79" s="34" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc27§3-3</t>
         </is>
       </c>
       <c r="G79" s="34" t="inlineStr">
@@ -11016,22 +11016,22 @@
       </c>
       <c r="C80" s="33" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
         </is>
       </c>
       <c r="D80" s="33" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
         </is>
       </c>
       <c r="E80" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-09,Ⅰ-10</t>
         </is>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc27§5-2</t>
         </is>
       </c>
       <c r="G80" s="34" t="inlineStr">
@@ -11054,68 +11054,68 @@
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D81" s="33" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E81" s="34" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F81" s="34" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G81" s="34" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H81" s="33" t="inlineStr"/>
+    </row>
+    <row r="82" ht="34" customHeight="1">
+      <c r="A82" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C82" s="33" t="inlineStr">
+        <is>
           <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
-      <c r="D81" s="33" t="inlineStr">
+      <c r="D82" s="33" t="inlineStr">
         <is>
           <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
-      <c r="E81" s="34" t="inlineStr">
+      <c r="E82" s="34" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="F81" s="34" t="inlineStr">
+      <c r="F82" s="34" t="inlineStr">
         <is>
           <t>doc27§6</t>
         </is>
       </c>
-      <c r="G81" s="34" t="inlineStr">
+      <c r="G82" s="34" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H81" s="33" t="inlineStr"/>
-    </row>
-    <row r="82" ht="34" customHeight="1">
-      <c r="A82" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B82" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C82" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D82" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E82" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F82" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G82" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H82" s="25" t="inlineStr"/>
+      <c r="H82" s="33" t="inlineStr"/>
     </row>
     <row r="83" ht="34" customHeight="1">
       <c r="A83" s="36" t="inlineStr">
@@ -11130,22 +11130,22 @@
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-1,doc30§2-4</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -11168,27 +11168,27 @@
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc02§16,§22</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H84" s="25" t="inlineStr"/>
@@ -11206,27 +11206,27 @@
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H85" s="25" t="inlineStr"/>
@@ -11244,22 +11244,22 @@
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -11282,22 +11282,22 @@
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -11358,17 +11358,17 @@
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc38§A-2,doc18 5-4(9)</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H90" s="25" t="inlineStr"/>
@@ -11434,27 +11434,27 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc38§A-2,doc18 5-4(9)</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H91" s="25" t="inlineStr"/>
@@ -11472,22 +11472,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -11510,22 +11510,22 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -11548,22 +11548,22 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -11586,22 +11586,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -11624,22 +11624,22 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -11700,22 +11700,22 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -11738,17 +11738,17 @@
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
@@ -11776,17 +11776,17 @@
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
@@ -11814,12 +11814,12 @@
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -11852,22 +11852,22 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -11890,22 +11890,22 @@
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -11928,12 +11928,12 @@
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11966,22 +11966,22 @@
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -12004,22 +12004,22 @@
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -12042,22 +12042,22 @@
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-107</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -12080,22 +12080,22 @@
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-107</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc38§D</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -12118,22 +12118,22 @@
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
+          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
+          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-4,doc18 4-7(3)</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -12156,22 +12156,22 @@
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
+          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
+          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(2),doc18 5-6</t>
+          <t>doc36§10-4,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -12189,27 +12189,27 @@
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc35§7-3(2),doc18 5-6</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -12232,22 +12232,22 @@
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -12270,22 +12270,22 @@
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -12303,27 +12303,27 @@
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -12341,27 +12341,27 @@
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -12384,22 +12384,22 @@
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>計画書・報告書の頁数の実測（当方では docx→PDF 変換ができず目視確認ができない）</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>★当方の推定では計画書は本文88頁＋前付4頁＝92頁で、仕様書の約100頁に8頁の余裕がある（レイアウト値からの積算・doc40§0）。字詰め・禁則・表の折り返しの実挙動で前後するため、村側で実際に開いて頁数をご確認いただきたい。余裕が確認できれば第3章の施策体系図（第9期にあり第10期素案にない）とSDGsの対応表を追加したい。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-93</t>
+          <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc40§1-4</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -12417,27 +12417,27 @@
       </c>
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -12455,27 +12455,27 @@
       </c>
       <c r="B118" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-93</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -12498,22 +12498,22 @@
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -12536,22 +12536,22 @@
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -12574,22 +12574,22 @@
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -12612,22 +12612,22 @@
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -12650,22 +12650,22 @@
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -12688,22 +12688,22 @@
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -12726,22 +12726,22 @@
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -12764,22 +12764,22 @@
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-105,Ⅱ-67</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -12802,22 +12802,22 @@
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -12840,22 +12840,22 @@
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -12878,22 +12878,22 @@
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -12916,22 +12916,22 @@
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc37§4,doc18 5-4(10)</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -12954,22 +12954,22 @@
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-2,doc18 4-7(4)</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12992,22 +12992,22 @@
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
+          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
+          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-3,doc18 4-7(3)</t>
+          <t>doc37§4,doc18 5-4(10)</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -13030,22 +13030,22 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護を再開するかどうか</t>
+          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
+          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 施策3-2</t>
+          <t>doc36§10-2,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -13068,12 +13068,12 @@
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
+          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
+          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 4-7(2)</t>
+          <t>doc36§10-3,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -13106,22 +13106,22 @@
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
+          <t>認知症対応型通所介護を再開するかどうか</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
+          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§3,doc18 施策3-2</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -13144,22 +13144,22 @@
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc36§3,doc18 4-7(2)</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -13182,12 +13182,12 @@
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -13215,27 +13215,27 @@
       </c>
       <c r="B138" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
@@ -13253,27 +13253,27 @@
       </c>
       <c r="B139" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
@@ -13296,22 +13296,22 @@
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
@@ -13334,22 +13334,22 @@
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E141" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
@@ -13372,22 +13372,22 @@
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G142" s="23" t="inlineStr">
@@ -13410,27 +13410,27 @@
       </c>
       <c r="C143" s="25" t="inlineStr">
         <is>
-          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E143" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>doc38§B-2</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G143" s="23" t="inlineStr">
         <is>
-          <t>社内対応</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H143" s="25" t="inlineStr"/>
@@ -13448,22 +13448,22 @@
       </c>
       <c r="C144" s="25" t="inlineStr">
         <is>
-          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F144" s="23" t="inlineStr">
         <is>
-          <t>doc37§3-2,doc18 5-4</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G144" s="23" t="inlineStr">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="C145" s="25" t="inlineStr">
         <is>
-          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
+          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
         </is>
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
+          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
         </is>
       </c>
       <c r="E145" s="23" t="inlineStr">
@@ -13501,12 +13501,12 @@
       </c>
       <c r="F145" s="23" t="inlineStr">
         <is>
-          <t>doc36§2,doc18 2-3</t>
+          <t>doc38§B-2</t>
         </is>
       </c>
       <c r="G145" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>社内対応</t>
         </is>
       </c>
       <c r="H145" s="25" t="inlineStr"/>
@@ -13519,27 +13519,27 @@
       </c>
       <c r="B146" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C146" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
         </is>
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
         </is>
       </c>
       <c r="E146" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F146" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc37§3-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G146" s="23" t="inlineStr">
@@ -13557,27 +13557,27 @@
       </c>
       <c r="B147" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C147" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
         </is>
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
         </is>
       </c>
       <c r="E147" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F147" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc36§2,doc18 2-3</t>
         </is>
       </c>
       <c r="G147" s="23" t="inlineStr">
@@ -13600,22 +13600,22 @@
       </c>
       <c r="C148" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F148" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G148" s="23" t="inlineStr">
@@ -13638,22 +13638,22 @@
       </c>
       <c r="C149" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E149" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F149" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G149" s="23" t="inlineStr">
@@ -13676,22 +13676,22 @@
       </c>
       <c r="C150" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D150" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F150" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G150" s="23" t="inlineStr">
@@ -13714,22 +13714,22 @@
       </c>
       <c r="C151" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E151" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F151" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G151" s="23" t="inlineStr">
@@ -13747,27 +13747,27 @@
       </c>
       <c r="B152" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C152" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D152" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E152" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F152" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G152" s="23" t="inlineStr">
@@ -13785,27 +13785,27 @@
       </c>
       <c r="B153" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C153" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E153" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F153" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G153" s="23" t="inlineStr">
@@ -13828,22 +13828,22 @@
       </c>
       <c r="C154" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D154" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E154" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F154" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G154" s="23" t="inlineStr">
@@ -13866,22 +13866,22 @@
       </c>
       <c r="C155" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D155" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E155" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F155" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G155" s="23" t="inlineStr">
@@ -13899,27 +13899,27 @@
       </c>
       <c r="B156" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C156" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D156" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E156" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F156" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G156" s="23" t="inlineStr">
@@ -13937,27 +13937,27 @@
       </c>
       <c r="B157" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C157" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D157" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E157" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F157" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G157" s="23" t="inlineStr">
@@ -13980,22 +13980,22 @@
       </c>
       <c r="C158" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
         </is>
       </c>
       <c r="D158" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
         </is>
       </c>
       <c r="E158" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-31</t>
         </is>
       </c>
       <c r="F158" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc19 追-6</t>
         </is>
       </c>
       <c r="G158" s="23" t="inlineStr">
@@ -14018,22 +14018,22 @@
       </c>
       <c r="C159" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
         </is>
       </c>
       <c r="D159" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
         </is>
       </c>
       <c r="E159" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-40,Ⅰ-42</t>
         </is>
       </c>
       <c r="F159" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc19 追-7</t>
         </is>
       </c>
       <c r="G159" s="23" t="inlineStr">
@@ -14056,189 +14056,189 @@
       </c>
       <c r="C160" s="25" t="inlineStr">
         <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D160" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E160" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F160" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G160" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H160" s="25" t="inlineStr"/>
+    </row>
+    <row r="161" ht="34" customHeight="1">
+      <c r="A161" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B161" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C161" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D161" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E161" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F161" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G161" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H161" s="25" t="inlineStr"/>
+    </row>
+    <row r="162" ht="34" customHeight="1">
+      <c r="A162" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B162" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C162" s="25" t="inlineStr">
+        <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D160" s="25" t="inlineStr">
+      <c r="D162" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E160" s="23" t="inlineStr">
+      <c r="E162" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F160" s="23" t="inlineStr">
+      <c r="F162" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G160" s="23" t="inlineStr">
+      <c r="G162" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H160" s="25" t="inlineStr"/>
-    </row>
-    <row r="161" ht="34" customHeight="1">
-      <c r="A161" s="37" t="inlineStr">
+      <c r="H162" s="25" t="inlineStr"/>
+    </row>
+    <row r="163" ht="34" customHeight="1">
+      <c r="A163" s="37" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B161" s="24" t="inlineStr">
+      <c r="B163" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C161" s="25" t="inlineStr">
+      <c r="C163" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D161" s="25" t="inlineStr">
+      <c r="D163" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E161" s="23" t="inlineStr">
+      <c r="E163" s="23" t="inlineStr">
         <is>
           <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
-      <c r="F161" s="23" t="inlineStr">
+      <c r="F163" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G161" s="23" t="inlineStr">
+      <c r="G163" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H161" s="25" t="inlineStr"/>
-    </row>
-    <row r="162" ht="34" customHeight="1">
-      <c r="A162" s="37" t="inlineStr">
+      <c r="H163" s="25" t="inlineStr"/>
+    </row>
+    <row r="164" ht="34" customHeight="1">
+      <c r="A164" s="37" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B162" s="24" t="inlineStr">
+      <c r="B164" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C162" s="25" t="inlineStr">
+      <c r="C164" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D162" s="25" t="inlineStr">
+      <c r="D164" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E162" s="23" t="inlineStr">
+      <c r="E164" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F162" s="23" t="inlineStr">
+      <c r="F164" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G162" s="23" t="inlineStr">
+      <c r="G164" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H162" s="25" t="inlineStr"/>
-    </row>
-    <row r="164" ht="20" customHeight="1">
-      <c r="A164" s="38" t="inlineStr">
+      <c r="H164" s="25" t="inlineStr"/>
+    </row>
+    <row r="166" ht="20" customHeight="1">
+      <c r="A166" s="38" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="165" ht="34" customHeight="1">
-      <c r="A165" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B165" s="40" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C165" s="41" t="inlineStr">
-        <is>
-          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
-        </is>
-      </c>
-      <c r="D165" s="41" t="inlineStr">
-        <is>
-          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
-        </is>
-      </c>
-      <c r="E165" s="39" t="inlineStr">
-        <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F165" s="39" t="inlineStr">
-        <is>
-          <t>doc35§7-3(1)</t>
-        </is>
-      </c>
-      <c r="G165" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H165" s="41" t="inlineStr"/>
-    </row>
-    <row r="166" ht="34" customHeight="1">
-      <c r="A166" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B166" s="40" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C166" s="41" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D166" s="41" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E166" s="39" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F166" s="39" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G166" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H166" s="41" t="inlineStr"/>
     </row>
     <row r="167" ht="34" customHeight="1">
       <c r="A167" s="39" t="inlineStr">
@@ -14248,27 +14248,27 @@
       </c>
       <c r="B167" s="40" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C167" s="41" t="inlineStr">
         <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
         </is>
       </c>
       <c r="D167" s="41" t="inlineStr">
         <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
+          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
         </is>
       </c>
       <c r="E167" s="39" t="inlineStr">
         <is>
-          <t>０-04</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F167" s="39" t="inlineStr">
         <is>
-          <t>doc28§4</t>
+          <t>doc35§7-3(1)</t>
         </is>
       </c>
       <c r="G167" s="39" t="inlineStr">
@@ -14291,22 +14291,22 @@
       </c>
       <c r="C168" s="41" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D168" s="41" t="inlineStr">
         <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E168" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F168" s="39" t="inlineStr">
         <is>
-          <t>doc28§2</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G168" s="39" t="inlineStr">
@@ -14324,27 +14324,27 @@
       </c>
       <c r="B169" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C169" s="41" t="inlineStr">
         <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D169" s="41" t="inlineStr">
         <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E169" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F169" s="39" t="inlineStr">
         <is>
-          <t>doc28§1</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G169" s="39" t="inlineStr">
@@ -14362,32 +14362,32 @@
       </c>
       <c r="B170" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C170" s="41" t="inlineStr">
         <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D170" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E170" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F170" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-1</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G170" s="39" t="inlineStr">
         <is>
-          <t>解決済（一部再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H170" s="41" t="inlineStr"/>
@@ -14400,27 +14400,27 @@
       </c>
       <c r="B171" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C171" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D171" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E171" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F171" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G171" s="39" t="inlineStr">
@@ -14443,27 +14443,27 @@
       </c>
       <c r="C172" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D172" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E172" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F172" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G172" s="39" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H172" s="41" t="inlineStr"/>
@@ -14481,22 +14481,22 @@
       </c>
       <c r="C173" s="41" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D173" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E173" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F173" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G173" s="39" t="inlineStr">
@@ -14519,27 +14519,27 @@
       </c>
       <c r="C174" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D174" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E174" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F174" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G174" s="39" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H174" s="41" t="inlineStr"/>
@@ -14557,17 +14557,17 @@
       </c>
       <c r="C175" s="41" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D175" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E175" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F175" s="39" t="inlineStr">
@@ -14590,27 +14590,27 @@
       </c>
       <c r="B176" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C176" s="41" t="inlineStr">
         <is>
-          <t>配布用封筒の用意の主体（仕様書4Ⅰ(3)は受託者の印刷対象としている）</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D176" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：配布用封筒は村が用意し、費用は村側で請求処理する。受託者が印刷するのは返信用（回収用）のみ。仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消した。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E176" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-23,Ⅰ-26,Ⅰ-103</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F176" s="39" t="inlineStr">
         <is>
-          <t>doc39§5</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G176" s="39" t="inlineStr">
@@ -14628,27 +14628,27 @@
       </c>
       <c r="B177" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C177" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の対象者数（仕様書の約150人に対し118人）</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D177" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：118人で問題なし。仕様書4Ⅰ(1)の「約150人」との差異は解消した。集計設計上のセル数の扱いは当方の判断事項として継続。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24,Ⅰ-103</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F177" s="39" t="inlineStr">
         <is>
-          <t>doc39§5</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G177" s="39" t="inlineStr">
@@ -14666,22 +14666,22 @@
       </c>
       <c r="B178" s="40" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C178" s="41" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量（仕様書の約100頁に対し想定118頁）</t>
+          <t>配布用封筒の用意の主体（仕様書4Ⅰ(3)は受託者の印刷対象としている）</t>
         </is>
       </c>
       <c r="D178" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：仕様書どおり約100頁に統一する。第Ⅱ部（分析編25頁）は計画の根拠のため維持し、第Ⅰ部（単純集計編）と資料編で18頁を圧縮する（doc24§1改訂）。部数は仕様書のとおり10部。</t>
+          <t>★2026/09/24 村の回答で決着：配布用封筒は村が用意し、費用は村側で請求処理する。受託者が印刷するのは返信用（回収用）のみ。仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消した。</t>
         </is>
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅰ-23,Ⅰ-26,Ⅰ-103</t>
         </is>
       </c>
       <c r="F178" s="39" t="inlineStr">
@@ -14704,27 +14704,27 @@
       </c>
       <c r="B179" s="40" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C179" s="41" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>在宅介護実態調査の対象者数（仕様書の約150人に対し118人）</t>
         </is>
       </c>
       <c r="D179" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>★2026/09/24 村の回答で決着：118人で問題なし。仕様書4Ⅰ(1)の「約150人」との差異は解消した。集計設計上のセル数の扱いは当方の判断事項として継続。</t>
         </is>
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-08,Ⅰ-24,Ⅰ-103</t>
         </is>
       </c>
       <c r="F179" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G179" s="39" t="inlineStr">
@@ -14742,27 +14742,27 @@
       </c>
       <c r="B180" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C180" s="41" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>アンケート調査報告書の分量（仕様書の約100頁に対し想定118頁）</t>
         </is>
       </c>
       <c r="D180" s="41" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>★2026/09/24 村の回答で決着：仕様書どおり約100頁に統一する。第Ⅱ部（分析編25頁）は計画の根拠のため維持し、第Ⅰ部（単純集計編）と資料編で18頁を圧縮する（doc24§1改訂）。部数は仕様書のとおり10部。</t>
         </is>
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F180" s="39" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G180" s="39" t="inlineStr">
@@ -14780,27 +14780,27 @@
       </c>
       <c r="B181" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C181" s="41" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D181" s="41" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F181" s="39" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G181" s="39" t="inlineStr">
@@ -14823,12 +14823,12 @@
       </c>
       <c r="C182" s="41" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D182" s="41" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E182" s="39" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="F182" s="39" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G182" s="39" t="inlineStr">
@@ -14861,22 +14861,22 @@
       </c>
       <c r="C183" s="41" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>交付要綱の配点表（満点）</t>
         </is>
       </c>
       <c r="D183" s="41" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
         </is>
       </c>
       <c r="E183" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F183" s="39" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc20§2</t>
         </is>
       </c>
       <c r="G183" s="39" t="inlineStr">
@@ -14899,22 +14899,22 @@
       </c>
       <c r="C184" s="41" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
         </is>
       </c>
       <c r="D184" s="41" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
         </is>
       </c>
       <c r="E184" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F184" s="39" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc20§3-1</t>
         </is>
       </c>
       <c r="G184" s="39" t="inlineStr">
@@ -14937,43 +14937,119 @@
       </c>
       <c r="C185" s="41" t="inlineStr">
         <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D185" s="41" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E185" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F185" s="39" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G185" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H185" s="41" t="inlineStr"/>
+    </row>
+    <row r="186" ht="34" customHeight="1">
+      <c r="A186" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B186" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C186" s="41" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D186" s="41" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E186" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F186" s="39" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G186" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H186" s="41" t="inlineStr"/>
+    </row>
+    <row r="187" ht="34" customHeight="1">
+      <c r="A187" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B187" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C187" s="41" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D185" s="41" t="inlineStr">
+      <c r="D187" s="41" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E185" s="39" t="inlineStr">
+      <c r="E187" s="39" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F185" s="39" t="inlineStr">
+      <c r="F187" s="39" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G185" s="39" t="inlineStr">
+      <c r="G187" s="39" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H185" s="41" t="inlineStr"/>
+      <c r="H187" s="41" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H162"/>
+  <autoFilter ref="A4:H164"/>
   <mergeCells count="3">
+    <mergeCell ref="A166:H166"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A164:H164"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A164" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G164" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -762,7 +762,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>委託第27号／業務期間：契約締結の日〜令和9年3月31日／計画期間：令和9〜11年度　｜　出典：仕様書（8北保福第483号 別紙）を作業レベルに分解（対応は「仕様書対照」シート）　｜　進捗基準日：令和8年9月24日</t>
+          <t>委託第27号／業務期間：契約締結の日〜令和9年3月31日／計画期間：令和9〜11年度　｜　出典：仕様書（8北保福第483号 別紙）を作業レベルに分解（対応は「仕様書対照」シート）　｜　進捗基準日：令和8年9月25日</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="P57" s="25" t="inlineStr">
         <is>
-          <t>★1頁あたり2設問から、選択肢の少ない設問は3設問に詰める（100頁に収めるため）。図が小さくなるためモノクロ印刷での可読性に注意を要する。計画書と同じく明度差・線種・ハッチングで識別し、凡例を図の近くに置く。集計結果の確定待ち。</t>
+          <t>★9/25：案Bの採用により1頁2設問を維持できることとなった（案Aでは1頁3設問に詰める必要があった）。ただし第9期は1頁0.9設問＝実質1設問1頁であり約1.9倍の密度になる。計画書と同じく明度差・線種・ハッチングで識別し、凡例を図の近くに置く。集計結果の確定待ち。</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="P58" s="13" t="inlineStr">
         <is>
-          <t>★doc24として骨子案を作成（2部構成・第Ⅰ部 単純集計編／第Ⅱ部 ICF分析編）。★9/24：村の指示により仕様書どおり約100頁に統一することが決着し、当初案118頁から18頁を圧縮する構成に改訂（doc24§1-1）。第Ⅱ部25頁は計画の施策の根拠のため維持し、第3章40→33頁・第4章20→14頁・資料編25→22頁・第1,2章8→6頁で削る。設問数は削らない（仕様書4Ⅰ(7)が設問ごとのグラフを求めるため）。本文の執筆は調査の回収・集計待ち。</t>
+          <t>★doc24として骨子案を作成（2部構成・第Ⅰ部 単純集計編／第Ⅱ部 ICF分析編）。★9/24：村の指示により仕様書どおり約100頁に統一することが決着（当初案118頁）。★9/25：圧縮の当て方を案Bで確定。調査票2種・単純集計表・自由記述の全文を電子媒体に移し資料編を25→6頁とし、浮いた頁を集計編に戻して第3章42頁・第4章21頁（計63頁）とした。1頁1.7設問で当初案118頁と同じ密度を100頁の枠内に収めた。第Ⅱ部25頁は計画の施策の根拠のため維持。設問数は削らない（仕様書4Ⅰ(7)が設問ごとのグラフを求めるため）。第9期は1頁0.9設問＝実質1設問1頁であり、採用案でも密度は約1.9倍になるためモノクロ印刷での可読性に注意を要する。本文の執筆は調査の回収・集計待ち。</t>
         </is>
       </c>
     </row>
@@ -7565,64 +7565,70 @@
       </c>
     </row>
     <row r="111" ht="30" customHeight="1">
-      <c r="A111" s="23" t="inlineStr">
+      <c r="A111" s="11" t="inlineStr">
         <is>
           <t>Ⅳ-91</t>
         </is>
       </c>
-      <c r="B111" s="24" t="inlineStr">
+      <c r="B111" s="12" t="inlineStr">
         <is>
           <t>Ⅳ 成果品・納品</t>
         </is>
       </c>
-      <c r="C111" s="24" t="inlineStr">
+      <c r="C111" s="12" t="inlineStr">
         <is>
           <t>Ⅳ-1 成果品</t>
         </is>
       </c>
-      <c r="D111" s="25" t="inlineStr">
+      <c r="D111" s="13" t="inlineStr">
         <is>
           <t>電子媒体の作成（Word/Excel/PowerPoint/PDF）</t>
         </is>
       </c>
-      <c r="E111" s="23" t="inlineStr">
+      <c r="E111" s="11" t="inlineStr">
         <is>
           <t>仕様書5③</t>
         </is>
       </c>
-      <c r="F111" s="23" t="inlineStr">
+      <c r="F111" s="11" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G111" s="25" t="inlineStr">
+      <c r="G111" s="13" t="inlineStr">
         <is>
           <t>CD-R等一式</t>
         </is>
       </c>
-      <c r="H111" s="25" t="inlineStr">
+      <c r="H111" s="13" t="inlineStr">
         <is>
           <t>関連データを含む</t>
         </is>
       </c>
-      <c r="I111" s="23" t="inlineStr">
+      <c r="I111" s="11" t="inlineStr">
         <is>
           <t>R9.3</t>
         </is>
       </c>
-      <c r="J111" s="26" t="n"/>
-      <c r="K111" s="26" t="n"/>
-      <c r="L111" s="26" t="n"/>
-      <c r="M111" s="26" t="n"/>
-      <c r="N111" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" s="23" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P111" s="25" t="inlineStr"/>
+      <c r="J111" s="14" t="n"/>
+      <c r="K111" s="14" t="n"/>
+      <c r="L111" s="14" t="n">
+        <v>46290</v>
+      </c>
+      <c r="M111" s="14" t="n"/>
+      <c r="N111" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O111" s="16" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="P111" s="13" t="inlineStr">
+        <is>
+          <t>★案Bの採用により、報告書の紙から外した調査票2種（PDF）・単純集計表（Excel）・自由記述の全文（匿名化済み・Excel）・見える化システム登録用データ（Excel）を収録することが確定した（doc24§9-2）。仕様書5③の「関連データ」の主要部分がこれで埋まる。収録一覧は報告書の資料3として紙にも載せる。回答原票と管理番号対応表を含めるかは未決。</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="18" t="inlineStr">
@@ -7684,7 +7690,7 @@
       </c>
       <c r="P112" s="20" t="inlineStr">
         <is>
-          <t>仕様書5③の「関連データ」に回答原票・管理番号対応表を含めるかは村の指示による。含めない場合は集計後データのみを収録し、原票は仕様書6(1)に従い消去する。</t>
+          <t>★9/25：案Bの採用により収録対象が確定した部分がある。調査票2種（PDF・発送した現物の版）・単純集計表（全設問・Excel）・自由記述の全文（匿名化済みのみ）・見える化システム登録用データを収録する（doc24§9-2）。報告書の紙の資料編はリスク判定の判定方法2頁・自由記述の分類と主要意見3頁・電子媒体の収録一覧1頁の6頁とした。未決は回答原票と管理番号対応表を含めるかで、含めない場合は原票は仕様書6(1)に従い消去する。</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8100,7 +8106,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>北塩原村への確認事項　一覧（基準日：令和8年9月24日）</t>
+          <t>北塩原村への確認事項　一覧（基準日：令和8年9月25日）</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10039,7 @@
       </c>
       <c r="D54" s="33" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。★9/25：案Bの採用により自由記述の全文を電子媒体に収録することとなったため、匿名化の対象は紙の「分類と主要意見」（資料2）と電子媒体の全文の双方に及ぶ。電子媒体に回しても匿名化は免除されない。</t>
         </is>
       </c>
       <c r="E54" s="34" t="inlineStr">
@@ -10408,22 +10414,22 @@
       </c>
       <c r="C64" s="33" t="inlineStr">
         <is>
-          <t>★アンケート調査報告書に調査票の再掲を載せるか（第9期報告書の巻末の確認を含む）</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D64" s="33" t="inlineStr">
         <is>
-          <t>★100頁の枠で最も効く判断。資料編22頁の大半は調査票の再掲（ニーズ12頁＋在宅8頁）で、これを電子媒体に回すと集計編を47頁→63頁に戻せ、第9期の1設問1頁に近い密度（1頁1.7設問）を保てる。載せる場合は集計編が1頁2.3設問となり第9期の2.5倍の密度になる。doc01§5-5に記録した第9期の構成には資料編がないが、目次の見出しのみの記録のため巻末に調査票があるかを実物でご確認いただきたい。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E64" s="34" t="inlineStr">
         <is>
-          <t>Ⅳ-90,Ⅰ-48,Ⅳ-114</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>doc40§2-3</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G64" s="34" t="inlineStr">
@@ -10441,27 +10447,27 @@
       </c>
       <c r="B65" s="32" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C65" s="33" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
         </is>
       </c>
       <c r="D65" s="33" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
         </is>
       </c>
       <c r="E65" s="34" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc33§3-5</t>
         </is>
       </c>
       <c r="G65" s="34" t="inlineStr">
@@ -10484,22 +10490,22 @@
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D66" s="33" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E66" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>doc33§3-5</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G66" s="34" t="inlineStr">
@@ -10522,22 +10528,22 @@
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D67" s="33" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E67" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G67" s="34" t="inlineStr">
@@ -10560,22 +10566,22 @@
       </c>
       <c r="C68" s="33" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D68" s="33" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E68" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G68" s="34" t="inlineStr">
@@ -10598,22 +10604,22 @@
       </c>
       <c r="C69" s="33" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D69" s="33" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
         </is>
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc26§10 K-99</t>
         </is>
       </c>
       <c r="G69" s="34" t="inlineStr">
@@ -10636,22 +10642,22 @@
       </c>
       <c r="C70" s="33" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
         </is>
       </c>
       <c r="D70" s="33" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
         </is>
       </c>
       <c r="E70" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-99</t>
+          <t>doc28§1-2 K-107</t>
         </is>
       </c>
       <c r="G70" s="34" t="inlineStr">
@@ -10674,22 +10680,22 @@
       </c>
       <c r="C71" s="33" t="inlineStr">
         <is>
-          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
+          <t>認知症施策の実施状況の評価と公表の運用</t>
         </is>
       </c>
       <c r="D71" s="33" t="inlineStr">
         <is>
-          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
+          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
         </is>
       </c>
       <c r="E71" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
-          <t>doc28§1-2 K-107</t>
+          <t>doc36§10-1,doc18 4-7(6)</t>
         </is>
       </c>
       <c r="G71" s="34" t="inlineStr">
@@ -10712,12 +10718,12 @@
       </c>
       <c r="C72" s="33" t="inlineStr">
         <is>
-          <t>認知症施策の実施状況の評価と公表の運用</t>
+          <t>認知症の人およびご家族から意見を聴く方法</t>
         </is>
       </c>
       <c r="D72" s="33" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
+          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
         </is>
       </c>
       <c r="E72" s="34" t="inlineStr">
@@ -10727,7 +10733,7 @@
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>doc36§10-1,doc18 4-7(6)</t>
+          <t>doc36§5,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G72" s="34" t="inlineStr">
@@ -10750,22 +10756,22 @@
       </c>
       <c r="C73" s="33" t="inlineStr">
         <is>
-          <t>認知症の人およびご家族から意見を聴く方法</t>
+          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
         </is>
       </c>
       <c r="D73" s="33" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
+          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
         </is>
       </c>
       <c r="E73" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-71</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>doc36§5,doc18 4-7(4)</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G73" s="34" t="inlineStr">
@@ -10783,27 +10789,27 @@
       </c>
       <c r="B74" s="32" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
-          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D74" s="33" t="inlineStr">
         <is>
-          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E74" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G74" s="34" t="inlineStr">
@@ -10826,12 +10832,12 @@
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D75" s="33" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E75" s="34" t="inlineStr">
@@ -10841,7 +10847,7 @@
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G75" s="34" t="inlineStr">
@@ -10864,12 +10870,12 @@
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D76" s="33" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E76" s="34" t="inlineStr">
@@ -10879,7 +10885,7 @@
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G76" s="34" t="inlineStr">
@@ -10897,32 +10903,32 @@
       </c>
       <c r="B77" s="32" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
       <c r="E77" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G77" s="34" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H77" s="33" t="inlineStr"/>
@@ -10940,27 +10946,27 @@
       </c>
       <c r="C78" s="33" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
         </is>
       </c>
       <c r="D78" s="33" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
         </is>
       </c>
       <c r="E78" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅰ-09,Ⅰ-10</t>
         </is>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§3-3</t>
         </is>
       </c>
       <c r="G78" s="34" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H78" s="33" t="inlineStr"/>
@@ -10978,12 +10984,12 @@
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
         </is>
       </c>
       <c r="D79" s="33" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
         </is>
       </c>
       <c r="E79" s="34" t="inlineStr">
@@ -10993,7 +10999,7 @@
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc27§5-2</t>
         </is>
       </c>
       <c r="G79" s="34" t="inlineStr">
@@ -11016,22 +11022,22 @@
       </c>
       <c r="C80" s="33" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
         </is>
       </c>
       <c r="D80" s="33" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
         </is>
       </c>
       <c r="E80" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc27§5-3</t>
         </is>
       </c>
       <c r="G80" s="34" t="inlineStr">
@@ -11054,22 +11060,22 @@
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
       <c r="D81" s="33" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
       <c r="E81" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-20</t>
         </is>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc27§6</t>
         </is>
       </c>
       <c r="G81" s="34" t="inlineStr">
@@ -11080,42 +11086,42 @@
       <c r="H81" s="33" t="inlineStr"/>
     </row>
     <row r="82" ht="34" customHeight="1">
-      <c r="A82" s="35" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C82" s="33" t="inlineStr">
-        <is>
-          <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
-        </is>
-      </c>
-      <c r="D82" s="33" t="inlineStr">
-        <is>
-          <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
-        </is>
-      </c>
-      <c r="E82" s="34" t="inlineStr">
-        <is>
-          <t>Ⅰ-20</t>
-        </is>
-      </c>
-      <c r="F82" s="34" t="inlineStr">
-        <is>
-          <t>doc27§6</t>
-        </is>
-      </c>
-      <c r="G82" s="34" t="inlineStr">
+      <c r="A82" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C82" s="25" t="inlineStr">
+        <is>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
+        </is>
+      </c>
+      <c r="D82" s="25" t="inlineStr">
+        <is>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
+        </is>
+      </c>
+      <c r="E82" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-63,Ⅱ-64</t>
+        </is>
+      </c>
+      <c r="F82" s="23" t="inlineStr">
+        <is>
+          <t>doc02§22,doc08§8</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H82" s="33" t="inlineStr"/>
+      <c r="H82" s="25" t="inlineStr"/>
     </row>
     <row r="83" ht="34" customHeight="1">
       <c r="A83" s="36" t="inlineStr">
@@ -11130,22 +11136,22 @@
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>doc02§22,doc08§8</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G83" s="23" t="inlineStr">
@@ -11168,27 +11174,27 @@
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F84" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-1,doc30§2-4</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H84" s="25" t="inlineStr"/>
@@ -11206,27 +11212,27 @@
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F85" s="23" t="inlineStr">
         <is>
-          <t>doc02§16,§22</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H85" s="25" t="inlineStr"/>
@@ -11244,22 +11250,22 @@
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -11282,22 +11288,22 @@
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -11320,12 +11326,12 @@
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
@@ -11335,7 +11341,7 @@
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -11358,17 +11364,17 @@
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
@@ -11396,12 +11402,12 @@
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
@@ -11411,12 +11417,12 @@
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc38§A-2,doc18 5-4(9)</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H90" s="25" t="inlineStr"/>
@@ -11434,27 +11440,27 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc38§A-2,doc18 5-4(9)</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H91" s="25" t="inlineStr"/>
@@ -11472,22 +11478,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -11510,22 +11516,22 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -11548,22 +11554,22 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -11586,22 +11592,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -11624,22 +11630,22 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -11662,12 +11668,12 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
@@ -11677,7 +11683,7 @@
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -11700,22 +11706,22 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -11738,17 +11744,17 @@
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
@@ -11776,17 +11782,17 @@
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
@@ -11814,12 +11820,12 @@
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
@@ -11829,7 +11835,7 @@
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -11852,22 +11858,22 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -11890,22 +11896,22 @@
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -11928,12 +11934,12 @@
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
@@ -11943,7 +11949,7 @@
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11966,22 +11972,22 @@
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -12004,22 +12010,22 @@
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -12042,22 +12048,22 @@
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-107</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -12080,22 +12086,22 @@
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-107</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -12118,22 +12124,22 @@
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
+          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
+          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc38§D</t>
+          <t>doc36§10-4,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -12156,22 +12162,22 @@
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
+          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
+          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-4,doc18 4-7(3)</t>
+          <t>doc35§7-3(2),doc18 5-6</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -12189,27 +12195,27 @@
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(2),doc18 5-6</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -12232,22 +12238,22 @@
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -12270,22 +12276,22 @@
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -12303,27 +12309,27 @@
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -12341,27 +12347,27 @@
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
+          <t>報告書に調査票を再掲しないことの村への事前説明（第9期の巻末の確認を含む）</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
+          <t>★案Bを採用し、調査票の全文・単純集計表・自由記述の全文は紙の資料編から外して電子媒体に収録する（doc24§9）。doc01§5-5に記録した第9期報告書の構成に調査票の再掲はないが、目次の見出しのみの記録のため巻末に載っていた可能性がある。載っていた場合は前回からの変更にあたるため、納品時の齟齬を避けるため事前に説明しておきたい。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅳ-90,Ⅳ-114</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc24§1-3</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -14780,27 +14786,27 @@
       </c>
       <c r="B181" s="40" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C181" s="41" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>100頁への圧縮の当て方（集計編を圧縮するか、調査票を電子媒体に移すか）</t>
         </is>
       </c>
       <c r="D181" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>★2026/09/25 案Bを採用：調査票2種・単純集計表・自由記述の全文を電子媒体に収録し、資料編を25頁→6頁とする。浮いた頁を集計編に戻し第3章42頁・第4章21頁（計63頁・1頁1.7設問）とした。当初案118頁と同じ密度を100頁の枠内で保てる。案A（集計編を47頁に圧縮）は1頁2.3設問で第9期の2.5倍の密度となり、選択肢の多い設問が物理的に入らないため採らなかった。</t>
         </is>
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅳ-90,Ⅰ-48,Ⅳ-91,Ⅳ-114</t>
         </is>
       </c>
       <c r="F181" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc24§1-1,doc40§2</t>
         </is>
       </c>
       <c r="G181" s="39" t="inlineStr">
@@ -14818,27 +14824,27 @@
       </c>
       <c r="B182" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C182" s="41" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D182" s="41" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E182" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F182" s="39" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G182" s="39" t="inlineStr">
@@ -14861,12 +14867,12 @@
       </c>
       <c r="C183" s="41" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D183" s="41" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E183" s="39" t="inlineStr">
@@ -14876,7 +14882,7 @@
       </c>
       <c r="F183" s="39" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G183" s="39" t="inlineStr">
@@ -14899,12 +14905,12 @@
       </c>
       <c r="C184" s="41" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>交付要綱の配点表（満点）</t>
         </is>
       </c>
       <c r="D184" s="41" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
         </is>
       </c>
       <c r="E184" s="39" t="inlineStr">
@@ -14914,7 +14920,7 @@
       </c>
       <c r="F184" s="39" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc20§2</t>
         </is>
       </c>
       <c r="G184" s="39" t="inlineStr">
@@ -14937,22 +14943,22 @@
       </c>
       <c r="C185" s="41" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
         </is>
       </c>
       <c r="D185" s="41" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
         </is>
       </c>
       <c r="E185" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F185" s="39" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc20§3-1</t>
         </is>
       </c>
       <c r="G185" s="39" t="inlineStr">
@@ -14975,22 +14981,22 @@
       </c>
       <c r="C186" s="41" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
         </is>
       </c>
       <c r="D186" s="41" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
         </is>
       </c>
       <c r="E186" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-56,Ⅱ-58</t>
         </is>
       </c>
       <c r="F186" s="39" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc09</t>
         </is>
       </c>
       <c r="G186" s="39" t="inlineStr">
@@ -15013,30 +15019,68 @@
       </c>
       <c r="C187" s="41" t="inlineStr">
         <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D187" s="41" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E187" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F187" s="39" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G187" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H187" s="41" t="inlineStr"/>
+    </row>
+    <row r="188" ht="34" customHeight="1">
+      <c r="A188" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B188" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C188" s="41" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D187" s="41" t="inlineStr">
+      <c r="D188" s="41" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E187" s="39" t="inlineStr">
+      <c r="E188" s="39" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F187" s="39" t="inlineStr">
+      <c r="F188" s="39" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G187" s="39" t="inlineStr">
+      <c r="G188" s="39" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H187" s="41" t="inlineStr"/>
+      <c r="H188" s="41" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:H164"/>
@@ -19704,7 +19748,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>受領資料・データ管理（基準日：令和8年9月24日）</t>
+          <t>受領資料・データ管理（基準日：令和8年9月25日）</t>
         </is>
       </c>
     </row>
@@ -21801,7 +21845,7 @@
     <row r="59">
       <c r="B59" s="45" t="inlineStr">
         <is>
-          <t>※ 進捗基準日は令和8年9月24日です。備考欄の doc番号は docs/北塩原村_第10期/ 配下の分析資料に対応します。</t>
+          <t>※ 進捗基準日は令和8年9月25日です。備考欄の doc番号は docs/北塩原村_第10期/ 配下の分析資料に対応します。</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$166</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'仕様書対照'!$A$4:$H$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'受領資料・データ管理'!$A$4:$F$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'受領資料・データ管理'!$A$4:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8090,7 +8090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11250,22 +11250,22 @@
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>介護人材の確保に関する福島県の事業（介護人材確保対策・修学資金貸付）の内容と本村からの利用実績</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>★令和8年度の交付金（都道府県分）により、介護人材の確保・サービス提供基盤の整備は福島県が全国平均を13.1点下回る県全体の課題であることが判明した（本村は▲4.8点）。本村単独では動かしにくいため、施策4-6は県の事業と定住自立圏（喜多方市・西会津町）の研修費用助成を活用する形に組み立てたい。県の事業の内容と本村からの利用実績をご教示いただきたい。</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-67,Ⅱ-54</t>
         </is>
       </c>
       <c r="F86" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc41§3</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
@@ -11288,22 +11288,22 @@
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -11364,17 +11364,17 @@
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F89" s="23" t="inlineStr">
@@ -11402,12 +11402,12 @@
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
@@ -11417,12 +11417,12 @@
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc38§A-2,doc18 5-4(9)</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H90" s="25" t="inlineStr"/>
@@ -11440,27 +11440,27 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc38§A-2,doc18 5-4(9)</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H91" s="25" t="inlineStr"/>
@@ -11478,22 +11478,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -11516,22 +11516,22 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -11554,22 +11554,22 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -11592,22 +11592,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -11630,22 +11630,22 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -11668,12 +11668,12 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -11706,22 +11706,22 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -11744,17 +11744,17 @@
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
@@ -11782,17 +11782,17 @@
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
@@ -11835,7 +11835,7 @@
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -11896,22 +11896,22 @@
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -12010,22 +12010,22 @@
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -12048,22 +12048,22 @@
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-107</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -12086,22 +12086,22 @@
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-107</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc38§D</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -12124,22 +12124,22 @@
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
+          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
+          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-4,doc18 4-7(3)</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -12162,22 +12162,22 @@
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
+          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
+          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(2),doc18 5-6</t>
+          <t>doc36§10-4,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -12195,27 +12195,27 @@
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc35§7-3(2),doc18 5-6</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -12238,22 +12238,22 @@
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -12276,22 +12276,22 @@
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -12309,27 +12309,27 @@
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -12347,27 +12347,27 @@
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>報告書に調査票を再掲しないことの村への事前説明（第9期の巻末の確認を含む）</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>★案Bを採用し、調査票の全文・単純集計表・自由記述の全文は紙の資料編から外して電子媒体に収録する（doc24§9）。doc01§5-5に記録した第9期報告書の構成に調査票の再掲はないが、目次の見出しのみの記録のため巻末に載っていた可能性がある。載っていた場合は前回からの変更にあたるため、納品時の齟齬を避けるため事前に説明しておきたい。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90,Ⅳ-114</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc24§1-3</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -12390,22 +12390,22 @@
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>計画書・報告書の頁数の実測（当方では docx→PDF 変換ができず目視確認ができない）</t>
+          <t>報告書に調査票を再掲しないことの村への事前説明（第9期の巻末の確認を含む）</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>★当方の推定では計画書は本文88頁＋前付4頁＝92頁で、仕様書の約100頁に8頁の余裕がある（レイアウト値からの積算・doc40§0）。字詰め・禁則・表の折り返しの実挙動で前後するため、村側で実際に開いて頁数をご確認いただきたい。余裕が確認できれば第3章の施策体系図（第9期にあり第10期素案にない）とSDGsの対応表を追加したい。</t>
+          <t>★案Bを採用し、調査票の全文・単純集計表・自由記述の全文は紙の資料編から外して電子媒体に収録する（doc24§9）。doc01§5-5に記録した第9期報告書の構成に調査票の再掲はないが、目次の見出しのみの記録のため巻末に載っていた可能性がある。載っていた場合は前回からの変更にあたるため、納品時の齟齬を避けるため事前に説明しておきたい。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅳ-89</t>
+          <t>Ⅳ-90,Ⅳ-114</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc40§1-4</t>
+          <t>doc24§1-3</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -12428,22 +12428,22 @@
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>施策体系図（基本理念→基本目標5→施策28の階層図）を計画書3-5に載せるか</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>★第9期は第3章8頁に施策体系とSDGsの対応を掲げていた。第10期は3-5に対応表（28施策×根拠・交付金の目標・SDGs）を新設したが階層図がない。図は第2回策定委員会 資料4に用意しており、当方の推定では計画書は94頁で仕様書の約100頁に6頁の余裕がある。頁数の実測で余裕が確認できれば追加したい。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-113,Ⅱ-71</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc41§6</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -12466,22 +12466,22 @@
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>計画書・報告書の頁数の実測（当方では docx→PDF 変換ができず目視確認ができない）</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>★当方の推定では計画書は本文88頁＋前付4頁＝92頁で、仕様書の約100頁に8頁の余裕がある（レイアウト値からの積算・doc40§0）。字詰め・禁則・表の折り返しの実挙動で前後するため、村側で実際に開いて頁数をご確認いただきたい。余裕が確認できれば第3章の施策体系図（第9期にあり第10期素案にない）とSDGsの対応表を追加したい。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-93</t>
+          <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc40§1-4</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -12499,27 +12499,27 @@
       </c>
       <c r="B119" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -12537,27 +12537,27 @@
       </c>
       <c r="B120" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-93</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -12580,22 +12580,22 @@
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -12618,22 +12618,22 @@
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -12656,22 +12656,22 @@
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -12694,22 +12694,22 @@
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -12732,22 +12732,22 @@
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -12808,22 +12808,22 @@
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -12846,22 +12846,22 @@
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-105,Ⅱ-67</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -12884,22 +12884,22 @@
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -12922,22 +12922,22 @@
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -12960,22 +12960,22 @@
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12998,22 +12998,22 @@
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc37§4,doc18 5-4(10)</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -13036,22 +13036,22 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-2,doc18 4-7(4)</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -13074,22 +13074,22 @@
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
+          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
+          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-3,doc18 4-7(3)</t>
+          <t>doc37§4,doc18 5-4(10)</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -13112,22 +13112,22 @@
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護を再開するかどうか</t>
+          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
+          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 施策3-2</t>
+          <t>doc36§10-2,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -13150,12 +13150,12 @@
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
+          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
+          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 4-7(2)</t>
+          <t>doc36§10-3,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -13188,22 +13188,22 @@
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
+          <t>認知症対応型通所介護を再開するかどうか</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
+          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§3,doc18 施策3-2</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -13226,22 +13226,22 @@
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc36§3,doc18 4-7(2)</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
@@ -13297,27 +13297,27 @@
       </c>
       <c r="B140" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
@@ -13335,27 +13335,27 @@
       </c>
       <c r="B141" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E141" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
@@ -13378,22 +13378,22 @@
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G142" s="23" t="inlineStr">
@@ -13416,22 +13416,22 @@
       </c>
       <c r="C143" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E143" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G143" s="23" t="inlineStr">
@@ -13454,22 +13454,22 @@
       </c>
       <c r="C144" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F144" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G144" s="23" t="inlineStr">
@@ -13492,27 +13492,27 @@
       </c>
       <c r="C145" s="25" t="inlineStr">
         <is>
-          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E145" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F145" s="23" t="inlineStr">
         <is>
-          <t>doc38§B-2</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G145" s="23" t="inlineStr">
         <is>
-          <t>社内対応</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H145" s="25" t="inlineStr"/>
@@ -13530,22 +13530,22 @@
       </c>
       <c r="C146" s="25" t="inlineStr">
         <is>
-          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E146" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F146" s="23" t="inlineStr">
         <is>
-          <t>doc37§3-2,doc18 5-4</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G146" s="23" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="C147" s="25" t="inlineStr">
         <is>
-          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
+          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
         </is>
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
+          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
         </is>
       </c>
       <c r="E147" s="23" t="inlineStr">
@@ -13583,12 +13583,12 @@
       </c>
       <c r="F147" s="23" t="inlineStr">
         <is>
-          <t>doc36§2,doc18 2-3</t>
+          <t>doc38§B-2</t>
         </is>
       </c>
       <c r="G147" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>社内対応</t>
         </is>
       </c>
       <c r="H147" s="25" t="inlineStr"/>
@@ -13601,27 +13601,27 @@
       </c>
       <c r="B148" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C148" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
         </is>
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F148" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc37§3-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G148" s="23" t="inlineStr">
@@ -13639,27 +13639,27 @@
       </c>
       <c r="B149" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C149" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
         </is>
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
         </is>
       </c>
       <c r="E149" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F149" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc36§2,doc18 2-3</t>
         </is>
       </c>
       <c r="G149" s="23" t="inlineStr">
@@ -13682,22 +13682,22 @@
       </c>
       <c r="C150" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D150" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F150" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G150" s="23" t="inlineStr">
@@ -13720,22 +13720,22 @@
       </c>
       <c r="C151" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E151" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F151" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G151" s="23" t="inlineStr">
@@ -13758,22 +13758,22 @@
       </c>
       <c r="C152" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D152" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E152" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F152" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G152" s="23" t="inlineStr">
@@ -13796,22 +13796,22 @@
       </c>
       <c r="C153" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E153" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F153" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G153" s="23" t="inlineStr">
@@ -13829,27 +13829,27 @@
       </c>
       <c r="B154" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C154" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D154" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E154" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F154" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G154" s="23" t="inlineStr">
@@ -13867,27 +13867,27 @@
       </c>
       <c r="B155" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C155" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D155" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E155" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F155" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G155" s="23" t="inlineStr">
@@ -13910,22 +13910,22 @@
       </c>
       <c r="C156" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D156" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E156" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F156" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G156" s="23" t="inlineStr">
@@ -13948,22 +13948,22 @@
       </c>
       <c r="C157" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D157" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E157" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F157" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G157" s="23" t="inlineStr">
@@ -13981,27 +13981,27 @@
       </c>
       <c r="B158" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C158" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D158" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E158" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F158" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G158" s="23" t="inlineStr">
@@ -14019,27 +14019,27 @@
       </c>
       <c r="B159" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C159" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D159" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E159" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F159" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G159" s="23" t="inlineStr">
@@ -14062,22 +14062,22 @@
       </c>
       <c r="C160" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
         </is>
       </c>
       <c r="D160" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
         </is>
       </c>
       <c r="E160" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-31</t>
         </is>
       </c>
       <c r="F160" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc19 追-6</t>
         </is>
       </c>
       <c r="G160" s="23" t="inlineStr">
@@ -14100,22 +14100,22 @@
       </c>
       <c r="C161" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
         </is>
       </c>
       <c r="D161" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
         </is>
       </c>
       <c r="E161" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-40,Ⅰ-42</t>
         </is>
       </c>
       <c r="F161" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc19 追-7</t>
         </is>
       </c>
       <c r="G161" s="23" t="inlineStr">
@@ -14138,189 +14138,189 @@
       </c>
       <c r="C162" s="25" t="inlineStr">
         <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D162" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E162" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F162" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G162" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H162" s="25" t="inlineStr"/>
+    </row>
+    <row r="163" ht="34" customHeight="1">
+      <c r="A163" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B163" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C163" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D163" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E163" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F163" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G163" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H163" s="25" t="inlineStr"/>
+    </row>
+    <row r="164" ht="34" customHeight="1">
+      <c r="A164" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B164" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C164" s="25" t="inlineStr">
+        <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D162" s="25" t="inlineStr">
+      <c r="D164" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E162" s="23" t="inlineStr">
+      <c r="E164" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F162" s="23" t="inlineStr">
+      <c r="F164" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G162" s="23" t="inlineStr">
+      <c r="G164" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H162" s="25" t="inlineStr"/>
-    </row>
-    <row r="163" ht="34" customHeight="1">
-      <c r="A163" s="37" t="inlineStr">
+      <c r="H164" s="25" t="inlineStr"/>
+    </row>
+    <row r="165" ht="34" customHeight="1">
+      <c r="A165" s="37" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B163" s="24" t="inlineStr">
+      <c r="B165" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C163" s="25" t="inlineStr">
+      <c r="C165" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D163" s="25" t="inlineStr">
+      <c r="D165" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E163" s="23" t="inlineStr">
+      <c r="E165" s="23" t="inlineStr">
         <is>
           <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
-      <c r="F163" s="23" t="inlineStr">
+      <c r="F165" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G163" s="23" t="inlineStr">
+      <c r="G165" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H163" s="25" t="inlineStr"/>
-    </row>
-    <row r="164" ht="34" customHeight="1">
-      <c r="A164" s="37" t="inlineStr">
+      <c r="H165" s="25" t="inlineStr"/>
+    </row>
+    <row r="166" ht="34" customHeight="1">
+      <c r="A166" s="37" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B164" s="24" t="inlineStr">
+      <c r="B166" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C164" s="25" t="inlineStr">
+      <c r="C166" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D164" s="25" t="inlineStr">
+      <c r="D166" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E164" s="23" t="inlineStr">
+      <c r="E166" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F164" s="23" t="inlineStr">
+      <c r="F166" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G164" s="23" t="inlineStr">
+      <c r="G166" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H164" s="25" t="inlineStr"/>
-    </row>
-    <row r="166" ht="20" customHeight="1">
-      <c r="A166" s="38" t="inlineStr">
+      <c r="H166" s="25" t="inlineStr"/>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="38" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="167" ht="34" customHeight="1">
-      <c r="A167" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B167" s="40" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C167" s="41" t="inlineStr">
-        <is>
-          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
-        </is>
-      </c>
-      <c r="D167" s="41" t="inlineStr">
-        <is>
-          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
-        </is>
-      </c>
-      <c r="E167" s="39" t="inlineStr">
-        <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F167" s="39" t="inlineStr">
-        <is>
-          <t>doc35§7-3(1)</t>
-        </is>
-      </c>
-      <c r="G167" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H167" s="41" t="inlineStr"/>
-    </row>
-    <row r="168" ht="34" customHeight="1">
-      <c r="A168" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B168" s="40" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C168" s="41" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D168" s="41" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E168" s="39" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F168" s="39" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G168" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H168" s="41" t="inlineStr"/>
     </row>
     <row r="169" ht="34" customHeight="1">
       <c r="A169" s="39" t="inlineStr">
@@ -14330,27 +14330,27 @@
       </c>
       <c r="B169" s="40" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C169" s="41" t="inlineStr">
         <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
         </is>
       </c>
       <c r="D169" s="41" t="inlineStr">
         <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
+          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
         </is>
       </c>
       <c r="E169" s="39" t="inlineStr">
         <is>
-          <t>０-04</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F169" s="39" t="inlineStr">
         <is>
-          <t>doc28§4</t>
+          <t>doc35§7-3(1)</t>
         </is>
       </c>
       <c r="G169" s="39" t="inlineStr">
@@ -14373,22 +14373,22 @@
       </c>
       <c r="C170" s="41" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D170" s="41" t="inlineStr">
         <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E170" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F170" s="39" t="inlineStr">
         <is>
-          <t>doc28§2</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G170" s="39" t="inlineStr">
@@ -14406,27 +14406,27 @@
       </c>
       <c r="B171" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C171" s="41" t="inlineStr">
         <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D171" s="41" t="inlineStr">
         <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E171" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F171" s="39" t="inlineStr">
         <is>
-          <t>doc28§1</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G171" s="39" t="inlineStr">
@@ -14444,32 +14444,32 @@
       </c>
       <c r="B172" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C172" s="41" t="inlineStr">
         <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D172" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E172" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F172" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-1</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G172" s="39" t="inlineStr">
         <is>
-          <t>解決済（一部再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H172" s="41" t="inlineStr"/>
@@ -14482,27 +14482,27 @@
       </c>
       <c r="B173" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C173" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D173" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E173" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F173" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G173" s="39" t="inlineStr">
@@ -14525,27 +14525,27 @@
       </c>
       <c r="C174" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D174" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E174" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F174" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G174" s="39" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H174" s="41" t="inlineStr"/>
@@ -14563,22 +14563,22 @@
       </c>
       <c r="C175" s="41" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D175" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E175" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F175" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G175" s="39" t="inlineStr">
@@ -14601,27 +14601,27 @@
       </c>
       <c r="C176" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D176" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E176" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F176" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G176" s="39" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H176" s="41" t="inlineStr"/>
@@ -14639,17 +14639,17 @@
       </c>
       <c r="C177" s="41" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D177" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F177" s="39" t="inlineStr">
@@ -14672,27 +14672,27 @@
       </c>
       <c r="B178" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C178" s="41" t="inlineStr">
         <is>
-          <t>配布用封筒の用意の主体（仕様書4Ⅰ(3)は受託者の印刷対象としている）</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D178" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：配布用封筒は村が用意し、費用は村側で請求処理する。受託者が印刷するのは返信用（回収用）のみ。仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消した。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-23,Ⅰ-26,Ⅰ-103</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F178" s="39" t="inlineStr">
         <is>
-          <t>doc39§5</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G178" s="39" t="inlineStr">
@@ -14710,27 +14710,27 @@
       </c>
       <c r="B179" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C179" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の対象者数（仕様書の約150人に対し118人）</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D179" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：118人で問題なし。仕様書4Ⅰ(1)の「約150人」との差異は解消した。集計設計上のセル数の扱いは当方の判断事項として継続。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24,Ⅰ-103</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F179" s="39" t="inlineStr">
         <is>
-          <t>doc39§5</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G179" s="39" t="inlineStr">
@@ -14748,22 +14748,22 @@
       </c>
       <c r="B180" s="40" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C180" s="41" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量（仕様書の約100頁に対し想定118頁）</t>
+          <t>配布用封筒の用意の主体（仕様書4Ⅰ(3)は受託者の印刷対象としている）</t>
         </is>
       </c>
       <c r="D180" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：仕様書どおり約100頁に統一する。第Ⅱ部（分析編25頁）は計画の根拠のため維持し、第Ⅰ部（単純集計編）と資料編で18頁を圧縮する（doc24§1改訂）。部数は仕様書のとおり10部。</t>
+          <t>★2026/09/24 村の回答で決着：配布用封筒は村が用意し、費用は村側で請求処理する。受託者が印刷するのは返信用（回収用）のみ。仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消した。</t>
         </is>
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅰ-23,Ⅰ-26,Ⅰ-103</t>
         </is>
       </c>
       <c r="F180" s="39" t="inlineStr">
@@ -14786,27 +14786,27 @@
       </c>
       <c r="B181" s="40" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C181" s="41" t="inlineStr">
         <is>
-          <t>100頁への圧縮の当て方（集計編を圧縮するか、調査票を電子媒体に移すか）</t>
+          <t>在宅介護実態調査の対象者数（仕様書の約150人に対し118人）</t>
         </is>
       </c>
       <c r="D181" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/25 案Bを採用：調査票2種・単純集計表・自由記述の全文を電子媒体に収録し、資料編を25頁→6頁とする。浮いた頁を集計編に戻し第3章42頁・第4章21頁（計63頁・1頁1.7設問）とした。当初案118頁と同じ密度を100頁の枠内で保てる。案A（集計編を47頁に圧縮）は1頁2.3設問で第9期の2.5倍の密度となり、選択肢の多い設問が物理的に入らないため採らなかった。</t>
+          <t>★2026/09/24 村の回答で決着：118人で問題なし。仕様書4Ⅰ(1)の「約150人」との差異は解消した。集計設計上のセル数の扱いは当方の判断事項として継続。</t>
         </is>
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>Ⅳ-90,Ⅰ-48,Ⅳ-91,Ⅳ-114</t>
+          <t>Ⅰ-08,Ⅰ-24,Ⅰ-103</t>
         </is>
       </c>
       <c r="F181" s="39" t="inlineStr">
         <is>
-          <t>doc24§1-1,doc40§2</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G181" s="39" t="inlineStr">
@@ -14824,27 +14824,27 @@
       </c>
       <c r="B182" s="40" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C182" s="41" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>アンケート調査報告書の分量（仕様書の約100頁に対し想定118頁）</t>
         </is>
       </c>
       <c r="D182" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>★2026/09/24 村の回答で決着：仕様書どおり約100頁に統一する。第Ⅱ部（分析編25頁）は計画の根拠のため維持し、第Ⅰ部（単純集計編）と資料編で18頁を圧縮する（doc24§1改訂）。部数は仕様書のとおり10部。</t>
         </is>
       </c>
       <c r="E182" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F182" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G182" s="39" t="inlineStr">
@@ -14862,27 +14862,27 @@
       </c>
       <c r="B183" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C183" s="41" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>100頁への圧縮の当て方（集計編を圧縮するか、調査票を電子媒体に移すか）</t>
         </is>
       </c>
       <c r="D183" s="41" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>★2026/09/25 案Bを採用：調査票2種・単純集計表・自由記述の全文を電子媒体に収録し、資料編を25頁→6頁とする。浮いた頁を集計編に戻し第3章42頁・第4章21頁（計63頁・1頁1.7設問）とした。当初案118頁と同じ密度を100頁の枠内で保てる。案A（集計編を47頁に圧縮）は1頁2.3設問で第9期の2.5倍の密度となり、選択肢の多い設問が物理的に入らないため採らなかった。</t>
         </is>
       </c>
       <c r="E183" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅳ-90,Ⅰ-48,Ⅳ-91,Ⅳ-114</t>
         </is>
       </c>
       <c r="F183" s="39" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc24§1-1,doc40§2</t>
         </is>
       </c>
       <c r="G183" s="39" t="inlineStr">
@@ -14900,27 +14900,27 @@
       </c>
       <c r="B184" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C184" s="41" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D184" s="41" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E184" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F184" s="39" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G184" s="39" t="inlineStr">
@@ -14943,12 +14943,12 @@
       </c>
       <c r="C185" s="41" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D185" s="41" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E185" s="39" t="inlineStr">
@@ -14958,7 +14958,7 @@
       </c>
       <c r="F185" s="39" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G185" s="39" t="inlineStr">
@@ -14981,22 +14981,22 @@
       </c>
       <c r="C186" s="41" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>交付要綱の配点表（満点）</t>
         </is>
       </c>
       <c r="D186" s="41" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
         </is>
       </c>
       <c r="E186" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F186" s="39" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc20§2</t>
         </is>
       </c>
       <c r="G186" s="39" t="inlineStr">
@@ -15019,22 +15019,22 @@
       </c>
       <c r="C187" s="41" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
         </is>
       </c>
       <c r="D187" s="41" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
         </is>
       </c>
       <c r="E187" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F187" s="39" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc20§3-1</t>
         </is>
       </c>
       <c r="G187" s="39" t="inlineStr">
@@ -15057,43 +15057,119 @@
       </c>
       <c r="C188" s="41" t="inlineStr">
         <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D188" s="41" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E188" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F188" s="39" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G188" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H188" s="41" t="inlineStr"/>
+    </row>
+    <row r="189" ht="34" customHeight="1">
+      <c r="A189" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B189" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C189" s="41" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D189" s="41" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E189" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F189" s="39" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G189" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H189" s="41" t="inlineStr"/>
+    </row>
+    <row r="190" ht="34" customHeight="1">
+      <c r="A190" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B190" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C190" s="41" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D188" s="41" t="inlineStr">
+      <c r="D190" s="41" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E188" s="39" t="inlineStr">
+      <c r="E190" s="39" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F188" s="39" t="inlineStr">
+      <c r="F190" s="39" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G188" s="39" t="inlineStr">
+      <c r="G190" s="39" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H188" s="41" t="inlineStr"/>
+      <c r="H190" s="41" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H164"/>
+  <autoFilter ref="A4:H166"/>
   <mergeCells count="3">
-    <mergeCell ref="A166:H166"/>
+    <mergeCell ref="A168:H168"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A164" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G164" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19734,7 +19810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -20884,39 +20960,99 @@
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="34" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>国資料</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>令和8年度 評価指標に係る該当状況調査票集計表（都道府県分）</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>47都道府県・752列。福島県530点・全国26位（前年度468点・42位）</t>
+        </is>
+      </c>
+      <c r="D41" s="46" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/41_交付金_都道府県分の確認.md</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>国資料</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>令和8年度 評価指標（都道府県分）全38頁</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>管内市町村平均得点・著しく得点の低い市町村の判定基準を確認</t>
+        </is>
+      </c>
+      <c r="D42" s="46" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/41_交付金_都道府県分の確認.md</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="34" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B41" s="33" t="inlineStr">
+      <c r="B43" s="33" t="inlineStr">
         <is>
           <t>★要介護認定データ（調査票との関連付け用）</t>
         </is>
       </c>
-      <c r="C41" s="33" t="inlineStr">
+      <c r="C43" s="33" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(5)。調査回収後に必要</t>
         </is>
       </c>
-      <c r="D41" s="34" t="inlineStr">
+      <c r="D43" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E41" s="33" t="inlineStr">
+      <c r="E43" s="33" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F41" s="34" t="inlineStr">
+      <c r="F43" s="34" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F41"/>
+  <autoFilter ref="A4:F43"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$172</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'仕様書対照'!$A$4:$H$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'受領資料・データ管理'!$A$4:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'受領資料・データ管理'!$A$4:$F$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8090,7 +8090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9312,22 +9312,22 @@
       </c>
       <c r="C35" s="33" t="inlineStr">
         <is>
-          <t>国の介護保険事業計画作成支援ツール（将来推計総括表）の出力一式</t>
+          <t>★介護給付適正化の主要3事業のうち「要介護認定の適正化」の実施状況（令和8年度に0点となった原因）</t>
         </is>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
-          <t>★★最優先。他案件（川崎町・金ケ崎町・大雪）はいずれも保険者が操作したツールの出力を受領し検証する立場にあるが、本村は見える化から独自算定しており国の様式との検算ができていない。他案件では令和8年度が実績でなく推計値、主要項目が未入力のまま保険料だけ数値が入る等の事例が実際に見つかっている。</t>
+          <t>★主要3事業の全実施を問う指標（6点・全国96.9%が取得・県内55位／59）が0点である。適正化方策の策定は4項目すべて満点、ケアプラン点検と医療情報との突合は活動指標も満点であることから、残る「要介護認定の適正化」が実施されていない可能性が高い。取組が後退したのか、国への該当状況調査票の記載によるものかをご教示いただきたい。</t>
         </is>
       </c>
       <c r="E35" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-109</t>
         </is>
       </c>
       <c r="F35" s="34" t="inlineStr">
         <is>
-          <t>doc33§5-1</t>
+          <t>doc42§3</t>
         </is>
       </c>
       <c r="G35" s="34" t="inlineStr">
@@ -9350,22 +9350,22 @@
       </c>
       <c r="C36" s="33" t="inlineStr">
         <is>
-          <t>第9期計画の本文（サービス別見込量の表を含む全体）</t>
+          <t>国の介護保険事業計画作成支援ツール（将来推計総括表）の出力一式</t>
         </is>
       </c>
       <c r="D36" s="33" t="inlineStr">
         <is>
-          <t>★★用途が2つある。①対計画比（サービス別の計画値と実績の対比）。他案件では総額が計画どおりでも内訳が11.5〜967.4％まで開くことが確認されており、本村は受給率を3か年平均で固定しているため偏りを持ち越す。②老人福祉事業の量の目標の記載位置の確認（doc32§4-1）。保有しているのは概要版のみでサービス別見込量がない。</t>
+          <t>★★最優先。他案件（川崎町・金ケ崎町・大雪）はいずれも保険者が操作したツールの出力を受領し検証する立場にあるが、本村は見える化から独自算定しており国の様式との検算ができていない。他案件では令和8年度が実績でなく推計値、主要項目が未入力のまま保険料だけ数値が入る等の事例が実際に見つかっている。</t>
         </is>
       </c>
       <c r="E36" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>doc33§5-2</t>
+          <t>doc33§5-1</t>
         </is>
       </c>
       <c r="G36" s="34" t="inlineStr">
@@ -9388,22 +9388,22 @@
       </c>
       <c r="C37" s="33" t="inlineStr">
         <is>
-          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
+          <t>第9期計画の本文（サービス別見込量の表を含む全体）</t>
         </is>
       </c>
       <c r="D37" s="33" t="inlineStr">
         <is>
-          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
+          <t>★★用途が2つある。①対計画比（サービス別の計画値と実績の対比）。他案件では総額が計画どおりでも内訳が11.5〜967.4％まで開くことが確認されており、本村は受給率を3か年平均で固定しているため偏りを持ち越す。②老人福祉事業の量の目標の記載位置の確認（doc32§4-1）。保有しているのは概要版のみでサービス別見込量がない。</t>
         </is>
       </c>
       <c r="E37" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-53,Ⅱ-55</t>
         </is>
       </c>
       <c r="F37" s="34" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61</t>
+          <t>doc33§5-2</t>
         </is>
       </c>
       <c r="G37" s="34" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="C38" s="33" t="inlineStr">
         <is>
-          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
+          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D38" s="33" t="inlineStr">
         <is>
-          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
+          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
         </is>
       </c>
       <c r="E38" s="34" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61b</t>
+          <t>doc20§8-2 K-61</t>
         </is>
       </c>
       <c r="G38" s="34" t="inlineStr">
@@ -9464,22 +9464,22 @@
       </c>
       <c r="C39" s="33" t="inlineStr">
         <is>
-          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
+          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D39" s="33" t="inlineStr">
         <is>
-          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
+          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
         </is>
       </c>
       <c r="E39" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-62</t>
+          <t>doc20§8-2 K-61b</t>
         </is>
       </c>
       <c r="G39" s="34" t="inlineStr">
@@ -9502,12 +9502,12 @@
       </c>
       <c r="C40" s="33" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
+          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
         </is>
       </c>
       <c r="D40" s="33" t="inlineStr">
         <is>
-          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
+          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
         </is>
       </c>
       <c r="E40" s="34" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-63</t>
+          <t>doc20§6-2 K-62</t>
         </is>
       </c>
       <c r="G40" s="34" t="inlineStr">
@@ -9540,22 +9540,22 @@
       </c>
       <c r="C41" s="33" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
+          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
         </is>
       </c>
       <c r="D41" s="33" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
+          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
         </is>
       </c>
       <c r="E41" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-64</t>
+          <t>doc20§6-2 K-63</t>
         </is>
       </c>
       <c r="G41" s="34" t="inlineStr">
@@ -9578,22 +9578,22 @@
       </c>
       <c r="C42" s="33" t="inlineStr">
         <is>
-          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
+          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
         </is>
       </c>
       <c r="D42" s="33" t="inlineStr">
         <is>
-          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
+          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
         </is>
       </c>
       <c r="E42" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-75</t>
+          <t>doc20§6-2 K-64</t>
         </is>
       </c>
       <c r="G42" s="34" t="inlineStr">
@@ -9616,22 +9616,22 @@
       </c>
       <c r="C43" s="33" t="inlineStr">
         <is>
-          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
+          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
         </is>
       </c>
       <c r="D43" s="33" t="inlineStr">
         <is>
-          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
+          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
         </is>
       </c>
       <c r="E43" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-37</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F43" s="34" t="inlineStr">
         <is>
-          <t>doc24§12 K-87</t>
+          <t>doc22 K-75</t>
         </is>
       </c>
       <c r="G43" s="34" t="inlineStr">
@@ -9654,22 +9654,22 @@
       </c>
       <c r="C44" s="33" t="inlineStr">
         <is>
-          <t>★会津権利擁護・成年後見センターへの相談が1年で件数−43%・時間−55%と減少した要因</t>
+          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
         </is>
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
+          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
         </is>
       </c>
       <c r="E44" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-37</t>
         </is>
       </c>
       <c r="F44" s="34" t="inlineStr">
         <is>
-          <t>doc28§3-3 K-108</t>
+          <t>doc24§12 K-87</t>
         </is>
       </c>
       <c r="G44" s="34" t="inlineStr">
@@ -9692,22 +9692,22 @@
       </c>
       <c r="C45" s="33" t="inlineStr">
         <is>
-          <t>養護老人ホーム措置・軽費老人ホーム・老人クラブの実績は見える化に系列が一切ない</t>
+          <t>★会津権利擁護・成年後見センターへの相談が1年で件数−43%・時間−55%と減少した要因</t>
         </is>
       </c>
       <c r="D45" s="33" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が計画への記載を義務づける「老人福祉事業の量の目標」（素案4-6）の基礎。見える化に該当する系列がないため、村資料の受領が必須。代替手段はない。</t>
+          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
         </is>
       </c>
       <c r="E45" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F45" s="34" t="inlineStr">
         <is>
-          <t>doc38§D</t>
+          <t>doc28§3-3 K-108</t>
         </is>
       </c>
       <c r="G45" s="34" t="inlineStr">
@@ -9730,22 +9730,22 @@
       </c>
       <c r="C46" s="33" t="inlineStr">
         <is>
-          <t>国の推計ワークシートが求める在宅サービス利用率の分母</t>
+          <t>養護老人ホーム措置・軽費老人ホーム・老人クラブの実績は見える化に系列が一切ない</t>
         </is>
       </c>
       <c r="D46" s="33" t="inlineStr">
         <is>
-          <t>★★他案件（大雪）の点検で「見込量の利用率の分母は認定者数であって第1号被保険者数ではない」ことが指摘された。本村の見える化のサービス利用率の分母は要介護度別認定者数であることを実データで確認済み（51件中21件が±0.6pt以内で一致、第1号被保険者数では0件）。ただし国の将来推計が在宅の分母を「認定者数−施設・居住系利用者数」とする場合、本村の率は要介護1で58.8%→86.1%、要介護4で26.8%→70.1%に変わり、要介護2では107.7%と100%を超える。分母の取り違えは見込量を数割動かす。</t>
+          <t>★老人福祉法第20条の8第2項が計画への記載を義務づける「老人福祉事業の量の目標」（素案4-6）の基礎。見える化に該当する系列がないため、村資料の受領が必須。代替手段はない。</t>
         </is>
       </c>
       <c r="E46" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>doc37§3,doc18 5-4</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G46" s="34" t="inlineStr">
@@ -9768,22 +9768,22 @@
       </c>
       <c r="C47" s="33" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護（村内27人分）の待機者数と、村外のグループホームを利用している方の人数</t>
+          <t>国の推計ワークシートが求める在宅サービス利用率の分母</t>
         </is>
       </c>
       <c r="D47" s="33" t="inlineStr">
         <is>
-          <t>★施策3-2・5-4(7)の必要利用定員総数の判断に必須。認知症高齢者（自立度Ⅱ以上）は2年間で132人→161人と22.0%増えた一方、定員は平成28年度以降27人のまま。稼働率93%。増床の要否は待機と村外利用の実態がなければ判断できない。</t>
+          <t>★★他案件（大雪）の点検で「見込量の利用率の分母は認定者数であって第1号被保険者数ではない」ことが指摘された。本村の見える化のサービス利用率の分母は要介護度別認定者数であることを実データで確認済み（51件中21件が±0.6pt以内で一致、第1号被保険者数では0件）。ただし国の将来推計が在宅の分母を「認定者数−施設・居住系利用者数」とする場合、本村の率は要介護1で58.8%→86.1%、要介護4で26.8%→70.1%に変わり、要介護2では107.7%と100%を超える。分母の取り違えは見込量を数割動かす。</t>
         </is>
       </c>
       <c r="E47" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F47" s="34" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 5-4(7)</t>
+          <t>doc37§3,doc18 5-4</t>
         </is>
       </c>
       <c r="G47" s="34" t="inlineStr">
@@ -9806,22 +9806,22 @@
       </c>
       <c r="C48" s="33" t="inlineStr">
         <is>
-          <t>認知症関連事業の実績（認知症カフェの箇所数、認知症初期集中支援推進事業の対象者数、認知症地域支援推進員の活動実績）</t>
+          <t>認知症対応型共同生活介護（村内27人分）の待機者数と、村外のグループホームを利用している方の人数</t>
         </is>
       </c>
       <c r="D48" s="33" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の地域支援事業の量に認知症総合支援事業の行を新設したが、いずれも実績が未受領。国の様式では認知症総合支援事業の量を定めることが求められる。</t>
+          <t>★施策3-2・5-4(7)の必要利用定員総数の判断に必須。認知症高齢者（自立度Ⅱ以上）は2年間で132人→161人と22.0%増えた一方、定員は平成28年度以降27人のまま。稼働率93%。増床の要否は待機と村外利用の実態がなければ判断できない。</t>
         </is>
       </c>
       <c r="E48" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-68</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>doc36§4,doc18 5-5(1)</t>
+          <t>doc36§3,doc18 5-4(7)</t>
         </is>
       </c>
       <c r="G48" s="34" t="inlineStr">
@@ -9844,22 +9844,22 @@
       </c>
       <c r="C49" s="33" t="inlineStr">
         <is>
-          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
+          <t>認知症関連事業の実績（認知症カフェの箇所数、認知症初期集中支援推進事業の対象者数、認知症地域支援推進員の活動実績）</t>
         </is>
       </c>
       <c r="D49" s="33" t="inlineStr">
         <is>
-          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
+          <t>★素案5-5(1)の地域支援事業の量に認知症総合支援事業の行を新設したが、いずれも実績が未受領。国の様式では認知症総合支援事業の量を定めることが求められる。</t>
         </is>
       </c>
       <c r="E49" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅱ-53,Ⅱ-68</t>
         </is>
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc36§4,doc18 5-5(1)</t>
         </is>
       </c>
       <c r="G49" s="34" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="C50" s="33" t="inlineStr">
         <is>
-          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
+          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
         </is>
       </c>
       <c r="D50" s="33" t="inlineStr">
         <is>
-          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
+          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
         </is>
       </c>
       <c r="E50" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G50" s="34" t="inlineStr">
@@ -9915,27 +9915,27 @@
       </c>
       <c r="B51" s="32" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C51" s="33" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
         </is>
       </c>
       <c r="D51" s="33" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
         </is>
       </c>
       <c r="E51" s="34" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G51" s="34" t="inlineStr">
@@ -9958,22 +9958,22 @@
       </c>
       <c r="C52" s="33" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D52" s="33" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E52" s="34" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G52" s="34" t="inlineStr">
@@ -9996,22 +9996,22 @@
       </c>
       <c r="C53" s="33" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D53" s="33" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E53" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-94</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G53" s="34" t="inlineStr">
@@ -10034,22 +10034,22 @@
       </c>
       <c r="C54" s="33" t="inlineStr">
         <is>
-          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D54" s="33" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。★9/25：案Bの採用により自由記述の全文を電子媒体に収録することとなったため、匿名化の対象は紙の「分類と主要意見」（資料2）と電子媒体の全文の双方に及ぶ。電子媒体に回しても匿名化は免除されない。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E54" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-44</t>
+          <t>Ⅰ-94</t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>doc24§12 K-89</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G54" s="34" t="inlineStr">
@@ -10072,22 +10072,22 @@
       </c>
       <c r="C55" s="33" t="inlineStr">
         <is>
-          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D55" s="33" t="inlineStr">
         <is>
-          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。★9/25：案Bの採用により自由記述の全文を電子媒体に収録することとなったため、匿名化の対象は紙の「分類と主要意見」（資料2）と電子媒体の全文の双方に及ぶ。電子媒体に回しても匿名化は免除されない。</t>
         </is>
       </c>
       <c r="E55" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅰ-44</t>
         </is>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-97</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G55" s="34" t="inlineStr">
@@ -10110,27 +10110,27 @@
       </c>
       <c r="C56" s="33" t="inlineStr">
         <is>
-          <t>★見える化の「将来推計」メニューで在宅サービス利用率の分母を確認する</t>
+          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
         </is>
       </c>
       <c r="D56" s="33" t="inlineStr">
         <is>
-          <t>★★見込量が数割変わる論点（要介護1で58.8%→86.1%、要介護2で107.7%と100%超）。村への依頼ではなく、当方が見える化にログインして推計方法の設定画面を開けば確かめられる見込み。他案件（大雪）は「画面の設定順からの推定［要確認］」としている。最優先で確認する。</t>
+          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
         </is>
       </c>
       <c r="E56" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>doc38§C-1</t>
+          <t>doc26§10 K-97</t>
         </is>
       </c>
       <c r="G56" s="34" t="inlineStr">
         <is>
-          <t>社内対応</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H56" s="33" t="inlineStr"/>
@@ -10143,32 +10143,32 @@
       </c>
       <c r="B57" s="32" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C57" s="33" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の集計設計（要介護度3区分×介護者勤務形態3区分のセル数）</t>
+          <t>★見える化の「将来推計」メニューで在宅サービス利用率の分母を確認する</t>
         </is>
       </c>
       <c r="D57" s="33" t="inlineStr">
         <is>
-          <t>★対象が118人（仕様書の想定150人）であることは村の了解を得て決着。残るのは集計設計の判断で、回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかを当方で決める。</t>
+          <t>★★見込量が数割変わる論点（要介護1で58.8%→86.1%、要介護2で107.7%と100%超）。村への依頼ではなく、当方が見える化にログインして推計方法の設定画面を開けば確かめられる見込み。他案件（大雪）は「画面の設定順からの推定［要確認］」としている。最優先で確認する。</t>
         </is>
       </c>
       <c r="E57" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-45</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>doc34§5-2</t>
+          <t>doc38§C-1</t>
         </is>
       </c>
       <c r="G57" s="34" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>社内対応</t>
         </is>
       </c>
       <c r="H57" s="33" t="inlineStr"/>
@@ -10186,22 +10186,22 @@
       </c>
       <c r="C58" s="33" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>在宅介護実態調査の集計設計（要介護度3区分×介護者勤務形態3区分のセル数）</t>
         </is>
       </c>
       <c r="D58" s="33" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>★対象が118人（仕様書の想定150人）であることは村の了解を得て決着。残るのは集計設計の判断で、回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかを当方で決める。</t>
         </is>
       </c>
       <c r="E58" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-95</t>
+          <t>Ⅰ-45</t>
         </is>
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc34§5-2</t>
         </is>
       </c>
       <c r="G58" s="34" t="inlineStr">
@@ -10224,22 +10224,22 @@
       </c>
       <c r="C59" s="33" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D59" s="33" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E59" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅰ-95</t>
         </is>
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G59" s="34" t="inlineStr">
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C60" s="33" t="inlineStr">
         <is>
-          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D60" s="33" t="inlineStr">
         <is>
-          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E60" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-46</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>doc25§4-2 K-91</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G60" s="34" t="inlineStr">
@@ -10295,27 +10295,27 @@
       </c>
       <c r="B61" s="32" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C61" s="33" t="inlineStr">
         <is>
-          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
+          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
         </is>
       </c>
       <c r="D61" s="33" t="inlineStr">
         <is>
-          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
+          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
         </is>
       </c>
       <c r="E61" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-70,Ⅱ-71</t>
+          <t>Ⅰ-46</t>
         </is>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc25§4-2 K-91</t>
         </is>
       </c>
       <c r="G61" s="34" t="inlineStr">
@@ -10333,27 +10333,27 @@
       </c>
       <c r="B62" s="32" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C62" s="33" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>難聴高齢者の早期発見・早期介入の取組の実施可否（普及啓発・早期発見）</t>
         </is>
       </c>
       <c r="D62" s="33" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★合わせて10点（全国68.9%・48.8%、県内48位・46位）。普及啓発は広報・健診案内での周知、早期発見は健診時の聴力確認等が想定される。施策4-4に位置づけ、施策1-6（高齢者の保健事業と介護予防の一体的実施）と連動させたい。現在の取組状況をご教示いただきたい。</t>
         </is>
       </c>
       <c r="E62" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅱ-67,Ⅱ-65</t>
         </is>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc42§3</t>
         </is>
       </c>
       <c r="G62" s="34" t="inlineStr">
@@ -10371,27 +10371,27 @@
       </c>
       <c r="B63" s="32" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C63" s="33" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>成年後見制度利用支援事業の要綱の対象範囲（市町村長申立・生活保護受給者への限定を外す改正の可否）</t>
         </is>
       </c>
       <c r="D63" s="33" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★4点（全国78.1%・県内46位）。申立費用助成・報酬助成はいずれも整備済（doc28§3）であり、対象の限定を外す要綱改正のみで取得できる。新たな予算を要しない。施策4-7に位置づけたい。</t>
         </is>
       </c>
       <c r="E63" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅱ-69,Ⅱ-67</t>
         </is>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc42§3-3</t>
         </is>
       </c>
       <c r="G63" s="34" t="inlineStr">
@@ -10409,27 +10409,27 @@
       </c>
       <c r="B64" s="32" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C64" s="33" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
         </is>
       </c>
       <c r="D64" s="33" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
         </is>
       </c>
       <c r="E64" s="34" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-70,Ⅱ-71</t>
         </is>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G64" s="34" t="inlineStr">
@@ -10447,27 +10447,27 @@
       </c>
       <c r="B65" s="32" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C65" s="33" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D65" s="33" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E65" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>doc33§3-5</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G65" s="34" t="inlineStr">
@@ -10485,27 +10485,27 @@
       </c>
       <c r="B66" s="32" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D66" s="33" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E66" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G66" s="34" t="inlineStr">
@@ -10523,27 +10523,27 @@
       </c>
       <c r="B67" s="32" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D67" s="33" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E67" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G67" s="34" t="inlineStr">
@@ -10566,22 +10566,22 @@
       </c>
       <c r="C68" s="33" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>★交付金で61点が取れる未得点項目11件の取組可否（計画への記載・要綱改正・手順の明文化のみで取得できるもの）</t>
         </is>
       </c>
       <c r="D68" s="33" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>★令和8年度の市町村分 全国一覧表と評価指標42頁を突合し、新たな予算や施設を要さず取得できる項目を61点分特定した（doc42§3）。447点→508点で全国1,005位→525位、県内34位→18位になる。内訳は認知症施策推進計画の策定着手5点／成年後見の要綱改正4点／難聴の普及啓発・早期発見10点／在宅医療連携の4場面の設定と対応策10点／相談内容の取りまとめ2点／給付適正化の福祉用具・住宅改修16点／ケアプラン点検の村外施設分8点／主要3事業の全実施6点。素案への反映には村の意向確認を要する。</t>
         </is>
       </c>
       <c r="E68" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅱ-65,Ⅱ-67,Ⅱ-109</t>
         </is>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc42§3</t>
         </is>
       </c>
       <c r="G68" s="34" t="inlineStr">
@@ -10604,22 +10604,22 @@
       </c>
       <c r="C69" s="33" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>ケアプラン点検に村外の有料老人ホーム・サービス付き高齢者向け住宅の入居者分を含める体制の構築可否</t>
         </is>
       </c>
       <c r="D69" s="33" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+          <t>★評価指標の留意点により、管内に該当施設がない市町村でも、被保険者が他市町村の施設に入居して介護サービスを適正に利用しているかの実態を把握し、必要に応じ県・他市町村と連携して対応できる体制があれば8点の対象となる。素案5-8で「村内に該当施設がないため対象外」としていたのは誤りで訂正した。本村は給付費の58.7%が村外であり、利用実態の把握は得点にとどまらず計画上の課題である。</t>
         </is>
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-109,Ⅱ-61</t>
         </is>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-99</t>
+          <t>doc42§3-1</t>
         </is>
       </c>
       <c r="G69" s="34" t="inlineStr">
@@ -10642,22 +10642,22 @@
       </c>
       <c r="C70" s="33" t="inlineStr">
         <is>
-          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
+          <t>福祉用具・住宅改修へのリハビリテーション専門職等の関与の仕組み（広域連携による整備の可否）</t>
         </is>
       </c>
       <c r="D70" s="33" t="inlineStr">
         <is>
-          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
+          <t>★合わせて16点。評価指標の留意点により、関係団体や県・近隣市町村による広域団体と連携した仕組みでも対象となり、住宅改修費については建築専門職・福祉住環境コーディネーター検定試験2級以上も「リハビリテーション専門職等」に含まれる。購入費・改修費のいずれかで足りる。令和6・7年度は実施していたものが令和8年度に0点となっており、後退の原因もご教示いただきたい。</t>
         </is>
       </c>
       <c r="E70" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-109</t>
         </is>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>doc28§1-2 K-107</t>
+          <t>doc42§3-1</t>
         </is>
       </c>
       <c r="G70" s="34" t="inlineStr">
@@ -10680,22 +10680,22 @@
       </c>
       <c r="C71" s="33" t="inlineStr">
         <is>
-          <t>認知症施策の実施状況の評価と公表の運用</t>
+          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
         </is>
       </c>
       <c r="D71" s="33" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
+          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
         </is>
       </c>
       <c r="E71" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-71</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
-          <t>doc36§10-1,doc18 4-7(6)</t>
+          <t>doc33§3-5</t>
         </is>
       </c>
       <c r="G71" s="34" t="inlineStr">
@@ -10718,22 +10718,22 @@
       </c>
       <c r="C72" s="33" t="inlineStr">
         <is>
-          <t>認知症の人およびご家族から意見を聴く方法</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D72" s="33" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E72" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-71</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>doc36§5,doc18 4-7(4)</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G72" s="34" t="inlineStr">
@@ -10756,22 +10756,22 @@
       </c>
       <c r="C73" s="33" t="inlineStr">
         <is>
-          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D73" s="33" t="inlineStr">
         <is>
-          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E73" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G73" s="34" t="inlineStr">
@@ -10789,27 +10789,27 @@
       </c>
       <c r="B74" s="32" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D74" s="33" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E74" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G74" s="34" t="inlineStr">
@@ -10827,27 +10827,27 @@
       </c>
       <c r="B75" s="32" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D75" s="33" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
         </is>
       </c>
       <c r="E75" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc26§10 K-99</t>
         </is>
       </c>
       <c r="G75" s="34" t="inlineStr">
@@ -10865,27 +10865,27 @@
       </c>
       <c r="B76" s="32" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
         </is>
       </c>
       <c r="D76" s="33" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
         </is>
       </c>
       <c r="E76" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc28§1-2 K-107</t>
         </is>
       </c>
       <c r="G76" s="34" t="inlineStr">
@@ -10903,32 +10903,32 @@
       </c>
       <c r="B77" s="32" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>認知症施策の実施状況の評価と公表の運用</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
         </is>
       </c>
       <c r="E77" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc36§10-1,doc18 4-7(6)</t>
         </is>
       </c>
       <c r="G77" s="34" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H77" s="33" t="inlineStr"/>
@@ -10941,27 +10941,27 @@
       </c>
       <c r="B78" s="32" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C78" s="33" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>認知症の人およびご家族から意見を聴く方法</t>
         </is>
       </c>
       <c r="D78" s="33" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
         </is>
       </c>
       <c r="E78" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc36§5,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G78" s="34" t="inlineStr">
@@ -10979,27 +10979,27 @@
       </c>
       <c r="B79" s="32" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
         </is>
       </c>
       <c r="D79" s="33" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
         </is>
       </c>
       <c r="E79" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G79" s="34" t="inlineStr">
@@ -11017,27 +11017,27 @@
       </c>
       <c r="B80" s="32" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C80" s="33" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D80" s="33" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E80" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G80" s="34" t="inlineStr">
@@ -11055,263 +11055,263 @@
       </c>
       <c r="B81" s="32" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C81" s="33" t="inlineStr">
+        <is>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+        </is>
+      </c>
+      <c r="D81" s="33" t="inlineStr">
+        <is>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+        </is>
+      </c>
+      <c r="E81" s="34" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F81" s="34" t="inlineStr">
+        <is>
+          <t>doc21§5 K-70</t>
+        </is>
+      </c>
+      <c r="G81" s="34" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H81" s="33" t="inlineStr"/>
+    </row>
+    <row r="82" ht="34" customHeight="1">
+      <c r="A82" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C82" s="33" t="inlineStr">
+        <is>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+        </is>
+      </c>
+      <c r="D82" s="33" t="inlineStr">
+        <is>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+        </is>
+      </c>
+      <c r="E82" s="34" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F82" s="34" t="inlineStr">
+        <is>
+          <t>doc28§3-4 K-111</t>
+        </is>
+      </c>
+      <c r="G82" s="34" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H82" s="33" t="inlineStr"/>
+    </row>
+    <row r="83" ht="34" customHeight="1">
+      <c r="A83" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B83" s="32" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C81" s="33" t="inlineStr">
+      <c r="C83" s="33" t="inlineStr">
+        <is>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+        </is>
+      </c>
+      <c r="D83" s="33" t="inlineStr">
+        <is>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+        </is>
+      </c>
+      <c r="E83" s="34" t="inlineStr">
+        <is>
+          <t>Ⅰ-19,Ⅰ-25</t>
+        </is>
+      </c>
+      <c r="F83" s="34" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G83" s="34" t="inlineStr">
+        <is>
+          <t>一部回答</t>
+        </is>
+      </c>
+      <c r="H83" s="33" t="inlineStr"/>
+    </row>
+    <row r="84" ht="34" customHeight="1">
+      <c r="A84" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B84" s="32" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C84" s="33" t="inlineStr">
+        <is>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+        </is>
+      </c>
+      <c r="D84" s="33" t="inlineStr">
+        <is>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+        </is>
+      </c>
+      <c r="E84" s="34" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F84" s="34" t="inlineStr">
+        <is>
+          <t>doc27§3-3</t>
+        </is>
+      </c>
+      <c r="G84" s="34" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H84" s="33" t="inlineStr"/>
+    </row>
+    <row r="85" ht="34" customHeight="1">
+      <c r="A85" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B85" s="32" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C85" s="33" t="inlineStr">
+        <is>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+        </is>
+      </c>
+      <c r="D85" s="33" t="inlineStr">
+        <is>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+        </is>
+      </c>
+      <c r="E85" s="34" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F85" s="34" t="inlineStr">
+        <is>
+          <t>doc27§5-2</t>
+        </is>
+      </c>
+      <c r="G85" s="34" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H85" s="33" t="inlineStr"/>
+    </row>
+    <row r="86" ht="34" customHeight="1">
+      <c r="A86" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B86" s="32" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C86" s="33" t="inlineStr">
+        <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D86" s="33" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E86" s="34" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F86" s="34" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G86" s="34" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H86" s="33" t="inlineStr"/>
+    </row>
+    <row r="87" ht="34" customHeight="1">
+      <c r="A87" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B87" s="32" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C87" s="33" t="inlineStr">
         <is>
           <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
-      <c r="D81" s="33" t="inlineStr">
+      <c r="D87" s="33" t="inlineStr">
         <is>
           <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
-      <c r="E81" s="34" t="inlineStr">
+      <c r="E87" s="34" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="F81" s="34" t="inlineStr">
+      <c r="F87" s="34" t="inlineStr">
         <is>
           <t>doc27§6</t>
         </is>
       </c>
-      <c r="G81" s="34" t="inlineStr">
+      <c r="G87" s="34" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H81" s="33" t="inlineStr"/>
-    </row>
-    <row r="82" ht="34" customHeight="1">
-      <c r="A82" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B82" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C82" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D82" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E82" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F82" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G82" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H82" s="25" t="inlineStr"/>
-    </row>
-    <row r="83" ht="34" customHeight="1">
-      <c r="A83" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B83" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C83" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D83" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
-        </is>
-      </c>
-      <c r="E83" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F83" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1,doc30§2-4</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H83" s="25" t="inlineStr"/>
-    </row>
-    <row r="84" ht="34" customHeight="1">
-      <c r="A84" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B84" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C84" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D84" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
-        </is>
-      </c>
-      <c r="E84" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F84" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G84" s="23" t="inlineStr">
-        <is>
-          <t>一部回答</t>
-        </is>
-      </c>
-      <c r="H84" s="25" t="inlineStr"/>
-    </row>
-    <row r="85" ht="34" customHeight="1">
-      <c r="A85" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B85" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C85" s="25" t="inlineStr">
-        <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
-        </is>
-      </c>
-      <c r="D85" s="25" t="inlineStr">
-        <is>
-          <t>現行計画の評価に必要。</t>
-        </is>
-      </c>
-      <c r="E85" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F85" s="23" t="inlineStr">
-        <is>
-          <t>doc01-11</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H85" s="25" t="inlineStr"/>
-    </row>
-    <row r="86" ht="34" customHeight="1">
-      <c r="A86" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B86" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C86" s="25" t="inlineStr">
-        <is>
-          <t>介護人材の確保に関する福島県の事業（介護人材確保対策・修学資金貸付）の内容と本村からの利用実績</t>
-        </is>
-      </c>
-      <c r="D86" s="25" t="inlineStr">
-        <is>
-          <t>★令和8年度の交付金（都道府県分）により、介護人材の確保・サービス提供基盤の整備は福島県が全国平均を13.1点下回る県全体の課題であることが判明した（本村は▲4.8点）。本村単独では動かしにくいため、施策4-6は県の事業と定住自立圏（喜多方市・西会津町）の研修費用助成を活用する形に組み立てたい。県の事業の内容と本村からの利用実績をご教示いただきたい。</t>
-        </is>
-      </c>
-      <c r="E86" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-67,Ⅱ-54</t>
-        </is>
-      </c>
-      <c r="F86" s="23" t="inlineStr">
-        <is>
-          <t>doc41§3</t>
-        </is>
-      </c>
-      <c r="G86" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H86" s="25" t="inlineStr"/>
-    </row>
-    <row r="87" ht="34" customHeight="1">
-      <c r="A87" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B87" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C87" s="25" t="inlineStr">
-        <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
-        </is>
-      </c>
-      <c r="D87" s="25" t="inlineStr">
-        <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
-        </is>
-      </c>
-      <c r="E87" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
-        </is>
-      </c>
-      <c r="F87" s="23" t="inlineStr">
-        <is>
-          <t>doc19 追-9</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H87" s="25" t="inlineStr"/>
+      <c r="H87" s="33" t="inlineStr"/>
     </row>
     <row r="88" ht="34" customHeight="1">
       <c r="A88" s="36" t="inlineStr">
@@ -11326,22 +11326,22 @@
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F88" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F89" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
@@ -11402,27 +11402,27 @@
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H90" s="25" t="inlineStr"/>
@@ -11440,27 +11440,27 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc38§A-2,doc18 5-4(9)</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H91" s="25" t="inlineStr"/>
@@ -11478,22 +11478,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>介護人材の確保に関する福島県の事業（介護人材確保対策・修学資金貸付）の内容と本村からの利用実績</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>★令和8年度の交付金（都道府県分）により、介護人材の確保・サービス提供基盤の整備は福島県が全国平均を13.1点下回る県全体の課題であることが判明した（本村は▲4.8点）。本村単独では動かしにくいため、施策4-6は県の事業と定住自立圏（喜多方市・西会津町）の研修費用助成を活用する形に組み立てたい。県の事業の内容と本村からの利用実績をご教示いただきたい。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-67,Ⅱ-54</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc41§3</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -11516,22 +11516,22 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -11554,22 +11554,22 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -11592,22 +11592,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -11630,22 +11630,22 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -11668,27 +11668,27 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc38§A-2,doc18 5-4(9)</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H97" s="25" t="inlineStr"/>
@@ -11706,12 +11706,12 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -11744,22 +11744,22 @@
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -11820,22 +11820,22 @@
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -11858,12 +11858,12 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -11896,22 +11896,22 @@
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -12010,22 +12010,22 @@
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -12048,22 +12048,22 @@
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -12086,22 +12086,22 @@
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-107</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -12124,22 +12124,22 @@
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc38§D</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -12162,22 +12162,22 @@
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-4,doc18 4-7(3)</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -12200,22 +12200,22 @@
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(2),doc18 5-6</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -12233,27 +12233,27 @@
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -12271,27 +12271,27 @@
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -12309,27 +12309,27 @@
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅱ-107</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -12347,27 +12347,27 @@
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
+          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
+          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -12385,27 +12385,27 @@
       </c>
       <c r="B116" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>報告書に調査票を再掲しないことの村への事前説明（第9期の巻末の確認を含む）</t>
+          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>★案Bを採用し、調査票の全文・単純集計表・自由記述の全文は紙の資料編から外して電子媒体に収録する（doc24§9）。doc01§5-5に記録した第9期報告書の構成に調査票の再掲はないが、目次の見出しのみの記録のため巻末に載っていた可能性がある。載っていた場合は前回からの変更にあたるため、納品時の齟齬を避けるため事前に説明しておきたい。</t>
+          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90,Ⅳ-114</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc24§1-3</t>
+          <t>doc36§10-4,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -12423,27 +12423,27 @@
       </c>
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>施策体系図（基本理念→基本目標5→施策28の階層図）を計画書3-5に載せるか</t>
+          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>★第9期は第3章8頁に施策体系とSDGsの対応を掲げていた。第10期は3-5に対応表（28施策×根拠・交付金の目標・SDGs）を新設したが階層図がない。図は第2回策定委員会 資料4に用意しており、当方の推定では計画書は94頁で仕様書の約100頁に6頁の余裕がある。頁数の実測で余裕が確認できれば追加したい。</t>
+          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅱ-71</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc41§6</t>
+          <t>doc35§7-3(2),doc18 5-6</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -12461,27 +12461,27 @@
       </c>
       <c r="B118" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>計画書・報告書の頁数の実測（当方では docx→PDF 変換ができず目視確認ができない）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>★当方の推定では計画書は本文88頁＋前付4頁＝92頁で、仕様書の約100頁に8頁の余裕がある（レイアウト値からの積算・doc40§0）。字詰め・禁則・表の折り返しの実挙動で前後するため、村側で実際に開いて頁数をご確認いただきたい。余裕が確認できれば第3章の施策体系図（第9期にあり第10期素案にない）とSDGsの対応表を追加したい。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅳ-89</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc40§1-4</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -12499,27 +12499,27 @@
       </c>
       <c r="B119" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -12537,27 +12537,27 @@
       </c>
       <c r="B120" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-93</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -12575,27 +12575,27 @@
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -12613,27 +12613,27 @@
       </c>
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>報告書に調査票を再掲しないことの村への事前説明（第9期の巻末の確認を含む）</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>★案Bを採用し、調査票の全文・単純集計表・自由記述の全文は紙の資料編から外して電子媒体に収録する（doc24§9）。doc01§5-5に記録した第9期報告書の構成に調査票の再掲はないが、目次の見出しのみの記録のため巻末に載っていた可能性がある。載っていた場合は前回からの変更にあたるため、納品時の齟齬を避けるため事前に説明しておきたい。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅳ-90,Ⅳ-114</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc24§1-3</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -12651,27 +12651,27 @@
       </c>
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>施策体系図（基本理念→基本目標5→施策28の階層図）を計画書3-5に載せるか</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>★第9期は第3章8頁に施策体系とSDGsの対応を掲げていた。第10期は3-5に対応表（28施策×根拠・交付金の目標・SDGs）を新設したが階層図がない。図は第2回策定委員会 資料4に用意しており、当方の推定では計画書は94頁で仕様書の約100頁に6頁の余裕がある。頁数の実測で余裕が確認できれば追加したい。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-113,Ⅱ-71</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc41§6</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -12689,27 +12689,27 @@
       </c>
       <c r="B124" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>計画書・報告書の頁数の実測（当方では docx→PDF 変換ができず目視確認ができない）</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>★当方の推定では計画書は本文88頁＋前付4頁＝92頁で、仕様書の約100頁に8頁の余裕がある（レイアウト値からの積算・doc40§0）。字詰め・禁則・表の折り返しの実挙動で前後するため、村側で実際に開いて頁数をご確認いただきたい。余裕が確認できれば第3章の施策体系図（第9期にあり第10期素案にない）とSDGsの対応表を追加したい。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc40§1-4</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -12727,27 +12727,27 @@
       </c>
       <c r="B125" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -12765,27 +12765,27 @@
       </c>
       <c r="B126" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-93</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -12808,22 +12808,22 @@
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -12846,22 +12846,22 @@
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105,Ⅱ-67</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -12884,22 +12884,22 @@
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -12922,22 +12922,22 @@
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -12960,22 +12960,22 @@
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12998,22 +12998,22 @@
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -13036,22 +13036,22 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -13074,22 +13074,22 @@
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-105,Ⅱ-67</t>
         </is>
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc37§4,doc18 5-4(10)</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -13112,22 +13112,22 @@
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-2,doc18 4-7(4)</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -13150,22 +13150,22 @@
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-3,doc18 4-7(3)</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -13188,22 +13188,22 @@
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護を再開するかどうか</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 施策3-2</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -13226,22 +13226,22 @@
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 4-7(2)</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
@@ -13264,22 +13264,22 @@
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
@@ -13302,22 +13302,22 @@
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc37§4,doc18 5-4(10)</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
@@ -13340,22 +13340,22 @@
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
         </is>
       </c>
       <c r="E141" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc36§10-2,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
@@ -13373,27 +13373,27 @@
       </c>
       <c r="B142" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
         </is>
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc36§10-3,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G142" s="23" t="inlineStr">
@@ -13411,27 +13411,27 @@
       </c>
       <c r="B143" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C143" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>認知症対応型通所介護を再開するかどうか</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
         </is>
       </c>
       <c r="E143" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc36§3,doc18 施策3-2</t>
         </is>
       </c>
       <c r="G143" s="23" t="inlineStr">
@@ -13449,27 +13449,27 @@
       </c>
       <c r="B144" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C144" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
         </is>
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F144" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc36§3,doc18 4-7(2)</t>
         </is>
       </c>
       <c r="G144" s="23" t="inlineStr">
@@ -13487,27 +13487,27 @@
       </c>
       <c r="B145" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C145" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E145" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F145" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G145" s="23" t="inlineStr">
@@ -13525,27 +13525,27 @@
       </c>
       <c r="B146" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C146" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E146" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F146" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G146" s="23" t="inlineStr">
@@ -13563,32 +13563,32 @@
       </c>
       <c r="B147" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C147" s="25" t="inlineStr">
         <is>
-          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E147" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F147" s="23" t="inlineStr">
         <is>
-          <t>doc38§B-2</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G147" s="23" t="inlineStr">
         <is>
-          <t>社内対応</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H147" s="25" t="inlineStr"/>
@@ -13606,22 +13606,22 @@
       </c>
       <c r="C148" s="25" t="inlineStr">
         <is>
-          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F148" s="23" t="inlineStr">
         <is>
-          <t>doc37§3-2,doc18 5-4</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G148" s="23" t="inlineStr">
@@ -13644,22 +13644,22 @@
       </c>
       <c r="C149" s="25" t="inlineStr">
         <is>
-          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E149" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F149" s="23" t="inlineStr">
         <is>
-          <t>doc36§2,doc18 2-3</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G149" s="23" t="inlineStr">
@@ -13677,27 +13677,27 @@
       </c>
       <c r="B150" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C150" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D150" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F150" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G150" s="23" t="inlineStr">
@@ -13715,27 +13715,27 @@
       </c>
       <c r="B151" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C151" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E151" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F151" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G151" s="23" t="inlineStr">
@@ -13753,27 +13753,27 @@
       </c>
       <c r="B152" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C152" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D152" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E152" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F152" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G152" s="23" t="inlineStr">
@@ -13791,32 +13791,32 @@
       </c>
       <c r="B153" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C153" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
         </is>
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
         </is>
       </c>
       <c r="E153" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F153" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc38§B-2</t>
         </is>
       </c>
       <c r="G153" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>社内対応</t>
         </is>
       </c>
       <c r="H153" s="25" t="inlineStr"/>
@@ -13829,27 +13829,27 @@
       </c>
       <c r="B154" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C154" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
         </is>
       </c>
       <c r="D154" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
         </is>
       </c>
       <c r="E154" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F154" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc37§3-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G154" s="23" t="inlineStr">
@@ -13867,27 +13867,27 @@
       </c>
       <c r="B155" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C155" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
         </is>
       </c>
       <c r="D155" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
         </is>
       </c>
       <c r="E155" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F155" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc36§2,doc18 2-3</t>
         </is>
       </c>
       <c r="G155" s="23" t="inlineStr">
@@ -13905,27 +13905,27 @@
       </c>
       <c r="B156" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C156" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D156" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E156" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F156" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G156" s="23" t="inlineStr">
@@ -13943,27 +13943,27 @@
       </c>
       <c r="B157" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C157" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D157" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E157" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F157" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G157" s="23" t="inlineStr">
@@ -13981,27 +13981,27 @@
       </c>
       <c r="B158" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C158" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D158" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E158" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F158" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G158" s="23" t="inlineStr">
@@ -14019,27 +14019,27 @@
       </c>
       <c r="B159" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C159" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D159" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E159" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F159" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G159" s="23" t="inlineStr">
@@ -14057,27 +14057,27 @@
       </c>
       <c r="B160" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C160" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D160" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E160" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F160" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G160" s="23" t="inlineStr">
@@ -14095,27 +14095,27 @@
       </c>
       <c r="B161" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C161" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D161" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E161" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F161" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G161" s="23" t="inlineStr">
@@ -14133,27 +14133,27 @@
       </c>
       <c r="B162" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C162" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D162" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E162" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F162" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G162" s="23" t="inlineStr">
@@ -14171,27 +14171,27 @@
       </c>
       <c r="B163" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C163" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D163" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E163" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F163" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G163" s="23" t="inlineStr">
@@ -14209,346 +14209,346 @@
       </c>
       <c r="B164" s="24" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C164" s="25" t="inlineStr">
+        <is>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+        </is>
+      </c>
+      <c r="D164" s="25" t="inlineStr">
+        <is>
+          <t>施策の書きぶりに影響。</t>
+        </is>
+      </c>
+      <c r="E164" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-71,Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F164" s="23" t="inlineStr">
+        <is>
+          <t>doc01-12</t>
+        </is>
+      </c>
+      <c r="G164" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H164" s="25" t="inlineStr"/>
+    </row>
+    <row r="165" ht="34" customHeight="1">
+      <c r="A165" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B165" s="24" t="inlineStr">
+        <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C165" s="25" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+        </is>
+      </c>
+      <c r="D165" s="25" t="inlineStr">
+        <is>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+        </is>
+      </c>
+      <c r="E165" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F165" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-13</t>
+        </is>
+      </c>
+      <c r="G165" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H165" s="25" t="inlineStr"/>
+    </row>
+    <row r="166" ht="34" customHeight="1">
+      <c r="A166" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B166" s="24" t="inlineStr">
+        <is>
           <t>調査設計</t>
         </is>
       </c>
-      <c r="C164" s="25" t="inlineStr">
+      <c r="C166" s="25" t="inlineStr">
+        <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D166" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E166" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F166" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G166" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H166" s="25" t="inlineStr"/>
+    </row>
+    <row r="167" ht="34" customHeight="1">
+      <c r="A167" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B167" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C167" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D167" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E167" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F167" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G167" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H167" s="25" t="inlineStr"/>
+    </row>
+    <row r="168" ht="34" customHeight="1">
+      <c r="A168" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B168" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C168" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D168" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E168" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F168" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G168" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H168" s="25" t="inlineStr"/>
+    </row>
+    <row r="169" ht="34" customHeight="1">
+      <c r="A169" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B169" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C169" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D169" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E169" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F169" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G169" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H169" s="25" t="inlineStr"/>
+    </row>
+    <row r="170" ht="34" customHeight="1">
+      <c r="A170" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B170" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C170" s="25" t="inlineStr">
         <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D164" s="25" t="inlineStr">
+      <c r="D170" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E164" s="23" t="inlineStr">
+      <c r="E170" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F164" s="23" t="inlineStr">
+      <c r="F170" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G164" s="23" t="inlineStr">
+      <c r="G170" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H164" s="25" t="inlineStr"/>
-    </row>
-    <row r="165" ht="34" customHeight="1">
-      <c r="A165" s="37" t="inlineStr">
+      <c r="H170" s="25" t="inlineStr"/>
+    </row>
+    <row r="171" ht="34" customHeight="1">
+      <c r="A171" s="37" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B165" s="24" t="inlineStr">
+      <c r="B171" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C165" s="25" t="inlineStr">
+      <c r="C171" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D165" s="25" t="inlineStr">
+      <c r="D171" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E165" s="23" t="inlineStr">
+      <c r="E171" s="23" t="inlineStr">
         <is>
           <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
-      <c r="F165" s="23" t="inlineStr">
+      <c r="F171" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G165" s="23" t="inlineStr">
+      <c r="G171" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H165" s="25" t="inlineStr"/>
-    </row>
-    <row r="166" ht="34" customHeight="1">
-      <c r="A166" s="37" t="inlineStr">
+      <c r="H171" s="25" t="inlineStr"/>
+    </row>
+    <row r="172" ht="34" customHeight="1">
+      <c r="A172" s="37" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B166" s="24" t="inlineStr">
+      <c r="B172" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C166" s="25" t="inlineStr">
+      <c r="C172" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D166" s="25" t="inlineStr">
+      <c r="D172" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E166" s="23" t="inlineStr">
+      <c r="E172" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F166" s="23" t="inlineStr">
+      <c r="F172" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G166" s="23" t="inlineStr">
+      <c r="G172" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H166" s="25" t="inlineStr"/>
-    </row>
-    <row r="168" ht="20" customHeight="1">
-      <c r="A168" s="38" t="inlineStr">
+      <c r="H172" s="25" t="inlineStr"/>
+    </row>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="38" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="169" ht="34" customHeight="1">
-      <c r="A169" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B169" s="40" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C169" s="41" t="inlineStr">
-        <is>
-          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
-        </is>
-      </c>
-      <c r="D169" s="41" t="inlineStr">
-        <is>
-          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
-        </is>
-      </c>
-      <c r="E169" s="39" t="inlineStr">
-        <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F169" s="39" t="inlineStr">
-        <is>
-          <t>doc35§7-3(1)</t>
-        </is>
-      </c>
-      <c r="G169" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H169" s="41" t="inlineStr"/>
-    </row>
-    <row r="170" ht="34" customHeight="1">
-      <c r="A170" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B170" s="40" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C170" s="41" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D170" s="41" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E170" s="39" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F170" s="39" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G170" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H170" s="41" t="inlineStr"/>
-    </row>
-    <row r="171" ht="34" customHeight="1">
-      <c r="A171" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B171" s="40" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C171" s="41" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D171" s="41" t="inlineStr">
-        <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
-        </is>
-      </c>
-      <c r="E171" s="39" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F171" s="39" t="inlineStr">
-        <is>
-          <t>doc28§4</t>
-        </is>
-      </c>
-      <c r="G171" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H171" s="41" t="inlineStr"/>
-    </row>
-    <row r="172" ht="34" customHeight="1">
-      <c r="A172" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B172" s="40" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C172" s="41" t="inlineStr">
-        <is>
-          <t>所得段階別の第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D172" s="41" t="inlineStr">
-        <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
-        </is>
-      </c>
-      <c r="E172" s="39" t="inlineStr">
-        <is>
-          <t>Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F172" s="39" t="inlineStr">
-        <is>
-          <t>doc28§2</t>
-        </is>
-      </c>
-      <c r="G172" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H172" s="41" t="inlineStr"/>
-    </row>
-    <row r="173" ht="34" customHeight="1">
-      <c r="A173" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B173" s="40" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C173" s="41" t="inlineStr">
-        <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
-        </is>
-      </c>
-      <c r="D173" s="41" t="inlineStr">
-        <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
-        </is>
-      </c>
-      <c r="E173" s="39" t="inlineStr">
-        <is>
-          <t>Ⅱ-59</t>
-        </is>
-      </c>
-      <c r="F173" s="39" t="inlineStr">
-        <is>
-          <t>doc28§1</t>
-        </is>
-      </c>
-      <c r="G173" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H173" s="41" t="inlineStr"/>
-    </row>
-    <row r="174" ht="34" customHeight="1">
-      <c r="A174" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B174" s="40" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C174" s="41" t="inlineStr">
-        <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
-        </is>
-      </c>
-      <c r="D174" s="41" t="inlineStr">
-        <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
-        </is>
-      </c>
-      <c r="E174" s="39" t="inlineStr">
-        <is>
-          <t>Ⅰ-09</t>
-        </is>
-      </c>
-      <c r="F174" s="39" t="inlineStr">
-        <is>
-          <t>doc27§1-1</t>
-        </is>
-      </c>
-      <c r="G174" s="39" t="inlineStr">
-        <is>
-          <t>解決済（一部再掲）</t>
-        </is>
-      </c>
-      <c r="H174" s="41" t="inlineStr"/>
     </row>
     <row r="175" ht="34" customHeight="1">
       <c r="A175" s="39" t="inlineStr">
@@ -14558,27 +14558,27 @@
       </c>
       <c r="B175" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C175" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
         </is>
       </c>
       <c r="D175" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
         </is>
       </c>
       <c r="E175" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F175" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc35§7-3(1)</t>
         </is>
       </c>
       <c r="G175" s="39" t="inlineStr">
@@ -14596,32 +14596,32 @@
       </c>
       <c r="B176" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C176" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D176" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E176" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F176" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G176" s="39" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H176" s="41" t="inlineStr"/>
@@ -14634,27 +14634,27 @@
       </c>
       <c r="B177" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C177" s="41" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D177" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F177" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G177" s="39" t="inlineStr">
@@ -14672,27 +14672,27 @@
       </c>
       <c r="B178" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C178" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D178" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F178" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G178" s="39" t="inlineStr">
@@ -14710,27 +14710,27 @@
       </c>
       <c r="B179" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C179" s="41" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D179" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F179" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G179" s="39" t="inlineStr">
@@ -14748,32 +14748,32 @@
       </c>
       <c r="B180" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C180" s="41" t="inlineStr">
         <is>
-          <t>配布用封筒の用意の主体（仕様書4Ⅰ(3)は受託者の印刷対象としている）</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D180" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：配布用封筒は村が用意し、費用は村側で請求処理する。受託者が印刷するのは返信用（回収用）のみ。仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消した。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-23,Ⅰ-26,Ⅰ-103</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F180" s="39" t="inlineStr">
         <is>
-          <t>doc39§5</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G180" s="39" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H180" s="41" t="inlineStr"/>
@@ -14786,27 +14786,27 @@
       </c>
       <c r="B181" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C181" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の対象者数（仕様書の約150人に対し118人）</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D181" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：118人で問題なし。仕様書4Ⅰ(1)の「約150人」との差異は解消した。集計設計上のセル数の扱いは当方の判断事項として継続。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24,Ⅰ-103</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F181" s="39" t="inlineStr">
         <is>
-          <t>doc39§5</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G181" s="39" t="inlineStr">
@@ -14824,32 +14824,32 @@
       </c>
       <c r="B182" s="40" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C182" s="41" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量（仕様書の約100頁に対し想定118頁）</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D182" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：仕様書どおり約100頁に統一する。第Ⅱ部（分析編25頁）は計画の根拠のため維持し、第Ⅰ部（単純集計編）と資料編で18頁を圧縮する（doc24§1改訂）。部数は仕様書のとおり10部。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E182" s="39" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F182" s="39" t="inlineStr">
         <is>
-          <t>doc39§5</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G182" s="39" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H182" s="41" t="inlineStr"/>
@@ -14862,27 +14862,27 @@
       </c>
       <c r="B183" s="40" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C183" s="41" t="inlineStr">
         <is>
-          <t>100頁への圧縮の当て方（集計編を圧縮するか、調査票を電子媒体に移すか）</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D183" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/25 案Bを採用：調査票2種・単純集計表・自由記述の全文を電子媒体に収録し、資料編を25頁→6頁とする。浮いた頁を集計編に戻し第3章42頁・第4章21頁（計63頁・1頁1.7設問）とした。当初案118頁と同じ密度を100頁の枠内で保てる。案A（集計編を47頁に圧縮）は1頁2.3設問で第9期の2.5倍の密度となり、選択肢の多い設問が物理的に入らないため採らなかった。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E183" s="39" t="inlineStr">
         <is>
-          <t>Ⅳ-90,Ⅰ-48,Ⅳ-91,Ⅳ-114</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F183" s="39" t="inlineStr">
         <is>
-          <t>doc24§1-1,doc40§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G183" s="39" t="inlineStr">
@@ -14900,22 +14900,22 @@
       </c>
       <c r="B184" s="40" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C184" s="41" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D184" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E184" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F184" s="39" t="inlineStr">
@@ -14938,27 +14938,27 @@
       </c>
       <c r="B185" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C185" s="41" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D185" s="41" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E185" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F185" s="39" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G185" s="39" t="inlineStr">
@@ -14976,27 +14976,27 @@
       </c>
       <c r="B186" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C186" s="41" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>配布用封筒の用意の主体（仕様書4Ⅰ(3)は受託者の印刷対象としている）</t>
         </is>
       </c>
       <c r="D186" s="41" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>★2026/09/24 村の回答で決着：配布用封筒は村が用意し、費用は村側で請求処理する。受託者が印刷するのは返信用（回収用）のみ。仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消した。</t>
         </is>
       </c>
       <c r="E186" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-23,Ⅰ-26,Ⅰ-103</t>
         </is>
       </c>
       <c r="F186" s="39" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G186" s="39" t="inlineStr">
@@ -15014,27 +15014,27 @@
       </c>
       <c r="B187" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C187" s="41" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>在宅介護実態調査の対象者数（仕様書の約150人に対し118人）</t>
         </is>
       </c>
       <c r="D187" s="41" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>★2026/09/24 村の回答で決着：118人で問題なし。仕様書4Ⅰ(1)の「約150人」との差異は解消した。集計設計上のセル数の扱いは当方の判断事項として継続。</t>
         </is>
       </c>
       <c r="E187" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24,Ⅰ-103</t>
         </is>
       </c>
       <c r="F187" s="39" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G187" s="39" t="inlineStr">
@@ -15052,27 +15052,27 @@
       </c>
       <c r="B188" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C188" s="41" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>アンケート調査報告書の分量（仕様書の約100頁に対し想定118頁）</t>
         </is>
       </c>
       <c r="D188" s="41" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>★2026/09/24 村の回答で決着：仕様書どおり約100頁に統一する。第Ⅱ部（分析編25頁）は計画の根拠のため維持し、第Ⅰ部（単純集計編）と資料編で18頁を圧縮する（doc24§1改訂）。部数は仕様書のとおり10部。</t>
         </is>
       </c>
       <c r="E188" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F188" s="39" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G188" s="39" t="inlineStr">
@@ -15090,27 +15090,27 @@
       </c>
       <c r="B189" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C189" s="41" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>100頁への圧縮の当て方（集計編を圧縮するか、調査票を電子媒体に移すか）</t>
         </is>
       </c>
       <c r="D189" s="41" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>★2026/09/25 案Bを採用：調査票2種・単純集計表・自由記述の全文を電子媒体に収録し、資料編を25頁→6頁とする。浮いた頁を集計編に戻し第3章42頁・第4章21頁（計63頁・1頁1.7設問）とした。当初案118頁と同じ密度を100頁の枠内で保てる。案A（集計編を47頁に圧縮）は1頁2.3設問で第9期の2.5倍の密度となり、選択肢の多い設問が物理的に入らないため採らなかった。</t>
         </is>
       </c>
       <c r="E189" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅳ-90,Ⅰ-48,Ⅳ-91,Ⅳ-114</t>
         </is>
       </c>
       <c r="F189" s="39" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc24§1-1,doc40§2</t>
         </is>
       </c>
       <c r="G189" s="39" t="inlineStr">
@@ -15128,48 +15128,276 @@
       </c>
       <c r="B190" s="40" t="inlineStr">
         <is>
+          <t>計画構成</t>
+        </is>
+      </c>
+      <c r="C190" s="41" t="inlineStr">
+        <is>
+          <t>整合を図る関連計画の範囲</t>
+        </is>
+      </c>
+      <c r="D190" s="41" t="inlineStr">
+        <is>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+        </is>
+      </c>
+      <c r="E190" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F190" s="39" t="inlineStr">
+        <is>
+          <t>doc22 §1</t>
+        </is>
+      </c>
+      <c r="G190" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H190" s="41" t="inlineStr"/>
+    </row>
+    <row r="191" ht="34" customHeight="1">
+      <c r="A191" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B191" s="40" t="inlineStr">
+        <is>
           <t>データ</t>
         </is>
       </c>
-      <c r="C190" s="41" t="inlineStr">
+      <c r="C191" s="41" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+        </is>
+      </c>
+      <c r="D191" s="41" t="inlineStr">
+        <is>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+        </is>
+      </c>
+      <c r="E191" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F191" s="39" t="inlineStr">
+        <is>
+          <t>doc20§3,§4</t>
+        </is>
+      </c>
+      <c r="G191" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H191" s="41" t="inlineStr"/>
+    </row>
+    <row r="192" ht="34" customHeight="1">
+      <c r="A192" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B192" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C192" s="41" t="inlineStr">
+        <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D192" s="41" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E192" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F192" s="39" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G192" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H192" s="41" t="inlineStr"/>
+    </row>
+    <row r="193" ht="34" customHeight="1">
+      <c r="A193" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B193" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C193" s="41" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D193" s="41" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E193" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F193" s="39" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G193" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H193" s="41" t="inlineStr"/>
+    </row>
+    <row r="194" ht="34" customHeight="1">
+      <c r="A194" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B194" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C194" s="41" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D194" s="41" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E194" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F194" s="39" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G194" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H194" s="41" t="inlineStr"/>
+    </row>
+    <row r="195" ht="34" customHeight="1">
+      <c r="A195" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B195" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C195" s="41" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D195" s="41" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E195" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F195" s="39" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G195" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H195" s="41" t="inlineStr"/>
+    </row>
+    <row r="196" ht="34" customHeight="1">
+      <c r="A196" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B196" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C196" s="41" t="inlineStr">
         <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D190" s="41" t="inlineStr">
+      <c r="D196" s="41" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E190" s="39" t="inlineStr">
+      <c r="E196" s="39" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F190" s="39" t="inlineStr">
+      <c r="F196" s="39" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G190" s="39" t="inlineStr">
+      <c r="G196" s="39" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H190" s="41" t="inlineStr"/>
+      <c r="H196" s="41" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H166"/>
+  <autoFilter ref="A4:H172"/>
   <mergeCells count="3">
-    <mergeCell ref="A168:H168"/>
+    <mergeCell ref="A174:H174"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A172" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G166" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G172" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19810,7 +20038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -21020,39 +21248,99 @@
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="34" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>国資料</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>令和8年度 該当状況調査票集計表（市町村分・全国一覧表）</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>1,779行×1,563列。本村は通し番号380。既収録の9項目すべてと一致</t>
+        </is>
+      </c>
+      <c r="D43" s="46" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/42_交付金_市町村分の確認.md</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>国資料</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>令和8年度 評価指標（市町村分）全42頁</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>留意点を突合し、未得点のうち61点が計画への記載等で取得できることを特定</t>
+        </is>
+      </c>
+      <c r="D44" s="46" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/42_交付金_市町村分の確認.md</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="34" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B43" s="33" t="inlineStr">
+      <c r="B45" s="33" t="inlineStr">
         <is>
           <t>★要介護認定データ（調査票との関連付け用）</t>
         </is>
       </c>
-      <c r="C43" s="33" t="inlineStr">
+      <c r="C45" s="33" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(5)。調査回収後に必要</t>
         </is>
       </c>
-      <c r="D43" s="34" t="inlineStr">
+      <c r="D45" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E43" s="33" t="inlineStr">
+      <c r="E45" s="33" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F43" s="34" t="inlineStr">
+      <c r="F45" s="34" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F43"/>
+  <autoFilter ref="A4:F45"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$174</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'仕様書対照'!$A$4:$H$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'受領資料・データ管理'!$A$4:$F$45</definedName>
   </definedNames>
@@ -8090,7 +8090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H196"/>
+  <dimension ref="A1:H198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="D62" s="33" t="inlineStr">
         <is>
-          <t>★合わせて10点（全国68.9%・48.8%、県内48位・46位）。普及啓発は広報・健診案内での周知、早期発見は健診時の聴力確認等が想定される。施策4-4に位置づけ、施策1-6（高齢者の保健事業と介護予防の一体的実施）と連動させたい。現在の取組状況をご教示いただきたい。</t>
+          <t>★合わせて10点（全国68.9%・48.8%、県内48位・46位）。★9/25：素案の施策4-4に3つの取組（広報・健診案内・通いの場での周知／健診と通いの場での聞こえの確認／耳鼻咽喉科への受診勧奨と受診状況の把握）として反映し、指標表を普及啓発5点・早期発見5点・受診状況10点に分けた。実施の可否と現在の取組状況をご教示いただきたい。受診状況の把握と受診率50%以上は全国でも14.6%・4.8%と取得が少ないため第10期中の検討事項としている。</t>
         </is>
       </c>
       <c r="E62" s="34" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="D63" s="33" t="inlineStr">
         <is>
-          <t>★4点（全国78.1%・県内46位）。申立費用助成・報酬助成はいずれも整備済（doc28§3）であり、対象の限定を外す要綱改正のみで取得できる。新たな予算を要しない。施策4-7に位置づけたい。</t>
+          <t>★4点（全国78.1%・県内46位）。申立費用助成・報酬助成はいずれも整備済（doc28§3）であり、対象の限定を外す要綱改正のみで取得できる。新たな予算を要しない。★9/25：素案の施策4-7に取組として反映し、指標表に1行を追加した。現在の要綱が対象を市町村長申立てや生活保護受給者に限定しているかをご確認いただき、改正の可否をご判断いただきたい。</t>
         </is>
       </c>
       <c r="E63" s="34" t="inlineStr">
@@ -11478,22 +11478,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>介護人材の確保に関する福島県の事業（介護人材確保対策・修学資金貸付）の内容と本村からの利用実績</t>
+          <t>訪問診療・訪問看護の提供実績（村内外の事業所別・令和6〜7年度）</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>★令和8年度の交付金（都道府県分）により、介護人材の確保・サービス提供基盤の整備は福島県が全国平均を13.1点下回る県全体の課題であることが判明した（本村は▲4.8点）。本村単独では動かしにくいため、施策4-6は県の事業と定住自立圏（喜多方市・西会津町）の研修費用助成を活用する形に組み立てたい。県の事業の内容と本村からの利用実績をご教示いただきたい。</t>
+          <t>★素案の施策4-3に在宅医療・介護連携の4場面ごとの目指すべき姿を新設し、①日常の療養支援の現状を【要確認】としている。村内は南東北裏磐梯診療所・桧原診療所の2か所で訪問看護事業所は村内にない。訪問診療の実施状況と村外からの訪問看護の提供量が分からないと、日常の療養支援の余力を示せない。県への提供依頼で把握できる範囲もあわせてご相談したい。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-54</t>
+          <t>Ⅱ-67,Ⅱ-61</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc41§3</t>
+          <t>doc42§4,doc18 施策4-3</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -11516,22 +11516,22 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>急変時に本人の意思と医療情報を関係者間で共有する仕組みの有無（救急医療情報キット等）</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>★素案の施策4-3の4場面のうち③急変時の対応の現状を【要確認】としている。救急搬送先は村外の病院であり、本人の意思・服薬・既往の情報が救急隊と搬送先へ伝わる仕組みがあるかで、第10期の対応策（仕組みの導入を検討するか運用の改善にとどめるか）が変わる。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-67</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc42§4,doc18 施策4-3</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
@@ -11554,22 +11554,22 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>介護人材の確保に関する福島県の事業（介護人材確保対策・修学資金貸付）の内容と本村からの利用実績</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>★令和8年度の交付金（都道府県分）により、介護人材の確保・サービス提供基盤の整備は福島県が全国平均を13.1点下回る県全体の課題であることが判明した（本村は▲4.8点）。本村単独では動かしにくいため、施策4-6は県の事業と定住自立圏（喜多方市・西会津町）の研修費用助成を活用する形に組み立てたい。県の事業の内容と本村からの利用実績をご教示いただきたい。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-67,Ⅱ-54</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc41§3</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -11592,22 +11592,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -11630,22 +11630,22 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -11668,27 +11668,27 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc38§A-2,doc18 5-4(9)</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H97" s="25" t="inlineStr"/>
@@ -11706,22 +11706,22 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -11744,27 +11744,27 @@
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc38§A-2,doc18 5-4(9)</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H99" s="25" t="inlineStr"/>
@@ -11782,22 +11782,22 @@
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -11820,22 +11820,22 @@
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
@@ -11934,22 +11934,22 @@
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -12010,22 +12010,22 @@
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
@@ -12086,22 +12086,22 @@
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -12124,22 +12124,22 @@
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -12162,22 +12162,22 @@
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -12200,22 +12200,22 @@
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -12238,22 +12238,22 @@
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -12276,22 +12276,22 @@
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -12314,22 +12314,22 @@
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-107</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -12352,22 +12352,22 @@
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc38§D</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -12390,22 +12390,22 @@
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-107</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-4,doc18 4-7(3)</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -12428,22 +12428,22 @@
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
+          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
+          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(2),doc18 5-6</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -12461,27 +12461,27 @@
       </c>
       <c r="B118" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc36§10-4,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -12499,27 +12499,27 @@
       </c>
       <c r="B119" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc35§7-3(2),doc18 5-6</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -12542,22 +12542,22 @@
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -12575,27 +12575,27 @@
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -12613,27 +12613,27 @@
       </c>
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>報告書に調査票を再掲しないことの村への事前説明（第9期の巻末の確認を含む）</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>★案Bを採用し、調査票の全文・単純集計表・自由記述の全文は紙の資料編から外して電子媒体に収録する（doc24§9）。doc01§5-5に記録した第9期報告書の構成に調査票の再掲はないが、目次の見出しのみの記録のため巻末に載っていた可能性がある。載っていた場合は前回からの変更にあたるため、納品時の齟齬を避けるため事前に説明しておきたい。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90,Ⅳ-114</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc24§1-3</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -12651,27 +12651,27 @@
       </c>
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>施策体系図（基本理念→基本目標5→施策28の階層図）を計画書3-5に載せるか</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>★第9期は第3章8頁に施策体系とSDGsの対応を掲げていた。第10期は3-5に対応表（28施策×根拠・交付金の目標・SDGs）を新設したが階層図がない。図は第2回策定委員会 資料4に用意しており、当方の推定では計画書は94頁で仕様書の約100頁に6頁の余裕がある。頁数の実測で余裕が確認できれば追加したい。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅱ-71</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc41§6</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -12694,22 +12694,22 @@
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>計画書・報告書の頁数の実測（当方では docx→PDF 変換ができず目視確認ができない）</t>
+          <t>報告書に調査票を再掲しないことの村への事前説明（第9期の巻末の確認を含む）</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>★当方の推定では計画書は本文88頁＋前付4頁＝92頁で、仕様書の約100頁に8頁の余裕がある（レイアウト値からの積算・doc40§0）。字詰め・禁則・表の折り返しの実挙動で前後するため、村側で実際に開いて頁数をご確認いただきたい。余裕が確認できれば第3章の施策体系図（第9期にあり第10期素案にない）とSDGsの対応表を追加したい。</t>
+          <t>★案Bを採用し、調査票の全文・単純集計表・自由記述の全文は紙の資料編から外して電子媒体に収録する（doc24§9）。doc01§5-5に記録した第9期報告書の構成に調査票の再掲はないが、目次の見出しのみの記録のため巻末に載っていた可能性がある。載っていた場合は前回からの変更にあたるため、納品時の齟齬を避けるため事前に説明しておきたい。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅳ-89</t>
+          <t>Ⅳ-90,Ⅳ-114</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc40§1-4</t>
+          <t>doc24§1-3</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -12732,22 +12732,22 @@
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>施策体系図（基本理念→基本目標5→施策28の階層図）を計画書3-5に載せるか</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>★第9期は第3章8頁に施策体系とSDGsの対応を掲げていた。第10期は3-5に対応表（28施策×根拠・交付金の目標・SDGs）を新設したが階層図がない。図は第2回策定委員会 資料4に用意しており、当方の推定では計画書は94頁で仕様書の約100頁に6頁の余裕がある。頁数の実測で余裕が確認できれば追加したい。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-113,Ⅱ-71</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc41§6</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>計画書・報告書の頁数の実測（当方では docx→PDF 変換ができず目視確認ができない）</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>★当方の推定では計画書は本文88頁＋前付4頁＝92頁で、仕様書の約100頁に8頁の余裕がある（レイアウト値からの積算・doc40§0）。字詰め・禁則・表の折り返しの実挙動で前後するため、村側で実際に開いて頁数をご確認いただきたい。余裕が確認できれば第3章の施策体系図（第9期にあり第10期素案にない）とSDGsの対応表を追加したい。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-93</t>
+          <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc40§1-4</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -12803,27 +12803,27 @@
       </c>
       <c r="B127" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -12841,27 +12841,27 @@
       </c>
       <c r="B128" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-93</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -12884,22 +12884,22 @@
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -12922,22 +12922,22 @@
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -12960,22 +12960,22 @@
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12998,22 +12998,22 @@
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -13036,22 +13036,22 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -13074,22 +13074,22 @@
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -13112,22 +13112,22 @@
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -13150,22 +13150,22 @@
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-105,Ⅱ-67</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -13188,22 +13188,22 @@
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -13226,22 +13226,22 @@
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
@@ -13264,22 +13264,22 @@
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
@@ -13302,22 +13302,22 @@
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>doc37§4,doc18 5-4(10)</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
@@ -13340,22 +13340,22 @@
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E141" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-2,doc18 4-7(4)</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
@@ -13378,22 +13378,22 @@
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
-          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
+          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
         </is>
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
+          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-3,doc18 4-7(3)</t>
+          <t>doc37§4,doc18 5-4(10)</t>
         </is>
       </c>
       <c r="G142" s="23" t="inlineStr">
@@ -13416,22 +13416,22 @@
       </c>
       <c r="C143" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護を再開するかどうか</t>
+          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
+          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
         </is>
       </c>
       <c r="E143" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 施策3-2</t>
+          <t>doc36§10-2,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G143" s="23" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="C144" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
+          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
         </is>
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
+          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="F144" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 4-7(2)</t>
+          <t>doc36§10-3,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G144" s="23" t="inlineStr">
@@ -13492,22 +13492,22 @@
       </c>
       <c r="C145" s="25" t="inlineStr">
         <is>
-          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
+          <t>認知症対応型通所介護を再開するかどうか</t>
         </is>
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
+          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
         </is>
       </c>
       <c r="E145" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F145" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§3,doc18 施策3-2</t>
         </is>
       </c>
       <c r="G145" s="23" t="inlineStr">
@@ -13530,22 +13530,22 @@
       </c>
       <c r="C146" s="25" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
         </is>
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
         </is>
       </c>
       <c r="E146" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F146" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc36§3,doc18 4-7(2)</t>
         </is>
       </c>
       <c r="G146" s="23" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="C147" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E147" s="23" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="F147" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G147" s="23" t="inlineStr">
@@ -13601,27 +13601,27 @@
       </c>
       <c r="B148" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C148" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F148" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G148" s="23" t="inlineStr">
@@ -13639,27 +13639,27 @@
       </c>
       <c r="B149" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C149" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E149" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F149" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G149" s="23" t="inlineStr">
@@ -13682,22 +13682,22 @@
       </c>
       <c r="C150" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D150" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F150" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G150" s="23" t="inlineStr">
@@ -13720,22 +13720,22 @@
       </c>
       <c r="C151" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E151" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F151" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G151" s="23" t="inlineStr">
@@ -13758,22 +13758,22 @@
       </c>
       <c r="C152" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D152" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E152" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F152" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G152" s="23" t="inlineStr">
@@ -13796,27 +13796,27 @@
       </c>
       <c r="C153" s="25" t="inlineStr">
         <is>
-          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E153" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F153" s="23" t="inlineStr">
         <is>
-          <t>doc38§B-2</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G153" s="23" t="inlineStr">
         <is>
-          <t>社内対応</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H153" s="25" t="inlineStr"/>
@@ -13834,22 +13834,22 @@
       </c>
       <c r="C154" s="25" t="inlineStr">
         <is>
-          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D154" s="25" t="inlineStr">
         <is>
-          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E154" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F154" s="23" t="inlineStr">
         <is>
-          <t>doc37§3-2,doc18 5-4</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G154" s="23" t="inlineStr">
@@ -13872,12 +13872,12 @@
       </c>
       <c r="C155" s="25" t="inlineStr">
         <is>
-          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
+          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
         </is>
       </c>
       <c r="D155" s="25" t="inlineStr">
         <is>
-          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
+          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
         </is>
       </c>
       <c r="E155" s="23" t="inlineStr">
@@ -13887,12 +13887,12 @@
       </c>
       <c r="F155" s="23" t="inlineStr">
         <is>
-          <t>doc36§2,doc18 2-3</t>
+          <t>doc38§B-2</t>
         </is>
       </c>
       <c r="G155" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>社内対応</t>
         </is>
       </c>
       <c r="H155" s="25" t="inlineStr"/>
@@ -13905,27 +13905,27 @@
       </c>
       <c r="B156" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C156" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
         </is>
       </c>
       <c r="D156" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
         </is>
       </c>
       <c r="E156" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F156" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc37§3-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G156" s="23" t="inlineStr">
@@ -13943,27 +13943,27 @@
       </c>
       <c r="B157" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C157" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
         </is>
       </c>
       <c r="D157" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
         </is>
       </c>
       <c r="E157" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F157" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc36§2,doc18 2-3</t>
         </is>
       </c>
       <c r="G157" s="23" t="inlineStr">
@@ -13986,22 +13986,22 @@
       </c>
       <c r="C158" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D158" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E158" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F158" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G158" s="23" t="inlineStr">
@@ -14024,22 +14024,22 @@
       </c>
       <c r="C159" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D159" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E159" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F159" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G159" s="23" t="inlineStr">
@@ -14062,22 +14062,22 @@
       </c>
       <c r="C160" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D160" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E160" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F160" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G160" s="23" t="inlineStr">
@@ -14100,22 +14100,22 @@
       </c>
       <c r="C161" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D161" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E161" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F161" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G161" s="23" t="inlineStr">
@@ -14133,27 +14133,27 @@
       </c>
       <c r="B162" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C162" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D162" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E162" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F162" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G162" s="23" t="inlineStr">
@@ -14171,27 +14171,27 @@
       </c>
       <c r="B163" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C163" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D163" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E163" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F163" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G163" s="23" t="inlineStr">
@@ -14214,22 +14214,22 @@
       </c>
       <c r="C164" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D164" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E164" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F164" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G164" s="23" t="inlineStr">
@@ -14252,22 +14252,22 @@
       </c>
       <c r="C165" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D165" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E165" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F165" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G165" s="23" t="inlineStr">
@@ -14285,27 +14285,27 @@
       </c>
       <c r="B166" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C166" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D166" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E166" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F166" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G166" s="23" t="inlineStr">
@@ -14323,27 +14323,27 @@
       </c>
       <c r="B167" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C167" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D167" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E167" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F167" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G167" s="23" t="inlineStr">
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C168" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
         </is>
       </c>
       <c r="D168" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
         </is>
       </c>
       <c r="E168" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-31</t>
         </is>
       </c>
       <c r="F168" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc19 追-6</t>
         </is>
       </c>
       <c r="G168" s="23" t="inlineStr">
@@ -14404,22 +14404,22 @@
       </c>
       <c r="C169" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
         </is>
       </c>
       <c r="D169" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
         </is>
       </c>
       <c r="E169" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-40,Ⅰ-42</t>
         </is>
       </c>
       <c r="F169" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc19 追-7</t>
         </is>
       </c>
       <c r="G169" s="23" t="inlineStr">
@@ -14442,189 +14442,189 @@
       </c>
       <c r="C170" s="25" t="inlineStr">
         <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D170" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E170" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F170" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G170" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H170" s="25" t="inlineStr"/>
+    </row>
+    <row r="171" ht="34" customHeight="1">
+      <c r="A171" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B171" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C171" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D171" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E171" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F171" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G171" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H171" s="25" t="inlineStr"/>
+    </row>
+    <row r="172" ht="34" customHeight="1">
+      <c r="A172" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B172" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C172" s="25" t="inlineStr">
+        <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D170" s="25" t="inlineStr">
+      <c r="D172" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E170" s="23" t="inlineStr">
+      <c r="E172" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F170" s="23" t="inlineStr">
+      <c r="F172" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G170" s="23" t="inlineStr">
+      <c r="G172" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H170" s="25" t="inlineStr"/>
-    </row>
-    <row r="171" ht="34" customHeight="1">
-      <c r="A171" s="37" t="inlineStr">
+      <c r="H172" s="25" t="inlineStr"/>
+    </row>
+    <row r="173" ht="34" customHeight="1">
+      <c r="A173" s="37" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B171" s="24" t="inlineStr">
+      <c r="B173" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C171" s="25" t="inlineStr">
+      <c r="C173" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D171" s="25" t="inlineStr">
+      <c r="D173" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E171" s="23" t="inlineStr">
+      <c r="E173" s="23" t="inlineStr">
         <is>
           <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
-      <c r="F171" s="23" t="inlineStr">
+      <c r="F173" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G171" s="23" t="inlineStr">
+      <c r="G173" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H171" s="25" t="inlineStr"/>
-    </row>
-    <row r="172" ht="34" customHeight="1">
-      <c r="A172" s="37" t="inlineStr">
+      <c r="H173" s="25" t="inlineStr"/>
+    </row>
+    <row r="174" ht="34" customHeight="1">
+      <c r="A174" s="37" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B172" s="24" t="inlineStr">
+      <c r="B174" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C172" s="25" t="inlineStr">
+      <c r="C174" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D172" s="25" t="inlineStr">
+      <c r="D174" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E172" s="23" t="inlineStr">
+      <c r="E174" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F172" s="23" t="inlineStr">
+      <c r="F174" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G172" s="23" t="inlineStr">
+      <c r="G174" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H172" s="25" t="inlineStr"/>
-    </row>
-    <row r="174" ht="20" customHeight="1">
-      <c r="A174" s="38" t="inlineStr">
+      <c r="H174" s="25" t="inlineStr"/>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="38" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="175" ht="34" customHeight="1">
-      <c r="A175" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B175" s="40" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C175" s="41" t="inlineStr">
-        <is>
-          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
-        </is>
-      </c>
-      <c r="D175" s="41" t="inlineStr">
-        <is>
-          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
-        </is>
-      </c>
-      <c r="E175" s="39" t="inlineStr">
-        <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F175" s="39" t="inlineStr">
-        <is>
-          <t>doc35§7-3(1)</t>
-        </is>
-      </c>
-      <c r="G175" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H175" s="41" t="inlineStr"/>
-    </row>
-    <row r="176" ht="34" customHeight="1">
-      <c r="A176" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B176" s="40" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C176" s="41" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D176" s="41" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E176" s="39" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F176" s="39" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G176" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H176" s="41" t="inlineStr"/>
     </row>
     <row r="177" ht="34" customHeight="1">
       <c r="A177" s="39" t="inlineStr">
@@ -14634,27 +14634,27 @@
       </c>
       <c r="B177" s="40" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C177" s="41" t="inlineStr">
         <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
         </is>
       </c>
       <c r="D177" s="41" t="inlineStr">
         <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
+          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
         </is>
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>０-04</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F177" s="39" t="inlineStr">
         <is>
-          <t>doc28§4</t>
+          <t>doc35§7-3(1)</t>
         </is>
       </c>
       <c r="G177" s="39" t="inlineStr">
@@ -14677,22 +14677,22 @@
       </c>
       <c r="C178" s="41" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D178" s="41" t="inlineStr">
         <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F178" s="39" t="inlineStr">
         <is>
-          <t>doc28§2</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G178" s="39" t="inlineStr">
@@ -14710,27 +14710,27 @@
       </c>
       <c r="B179" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C179" s="41" t="inlineStr">
         <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D179" s="41" t="inlineStr">
         <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F179" s="39" t="inlineStr">
         <is>
-          <t>doc28§1</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G179" s="39" t="inlineStr">
@@ -14748,32 +14748,32 @@
       </c>
       <c r="B180" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C180" s="41" t="inlineStr">
         <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D180" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F180" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-1</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G180" s="39" t="inlineStr">
         <is>
-          <t>解決済（一部再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H180" s="41" t="inlineStr"/>
@@ -14786,27 +14786,27 @@
       </c>
       <c r="B181" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C181" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D181" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F181" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G181" s="39" t="inlineStr">
@@ -14829,27 +14829,27 @@
       </c>
       <c r="C182" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D182" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E182" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F182" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G182" s="39" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H182" s="41" t="inlineStr"/>
@@ -14867,22 +14867,22 @@
       </c>
       <c r="C183" s="41" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D183" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E183" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F183" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G183" s="39" t="inlineStr">
@@ -14905,27 +14905,27 @@
       </c>
       <c r="C184" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D184" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E184" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F184" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G184" s="39" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H184" s="41" t="inlineStr"/>
@@ -14943,17 +14943,17 @@
       </c>
       <c r="C185" s="41" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D185" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E185" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F185" s="39" t="inlineStr">
@@ -14976,27 +14976,27 @@
       </c>
       <c r="B186" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C186" s="41" t="inlineStr">
         <is>
-          <t>配布用封筒の用意の主体（仕様書4Ⅰ(3)は受託者の印刷対象としている）</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D186" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：配布用封筒は村が用意し、費用は村側で請求処理する。受託者が印刷するのは返信用（回収用）のみ。仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消した。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E186" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-23,Ⅰ-26,Ⅰ-103</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F186" s="39" t="inlineStr">
         <is>
-          <t>doc39§5</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G186" s="39" t="inlineStr">
@@ -15014,27 +15014,27 @@
       </c>
       <c r="B187" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C187" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の対象者数（仕様書の約150人に対し118人）</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D187" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：118人で問題なし。仕様書4Ⅰ(1)の「約150人」との差異は解消した。集計設計上のセル数の扱いは当方の判断事項として継続。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E187" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24,Ⅰ-103</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F187" s="39" t="inlineStr">
         <is>
-          <t>doc39§5</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G187" s="39" t="inlineStr">
@@ -15052,22 +15052,22 @@
       </c>
       <c r="B188" s="40" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C188" s="41" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量（仕様書の約100頁に対し想定118頁）</t>
+          <t>配布用封筒の用意の主体（仕様書4Ⅰ(3)は受託者の印刷対象としている）</t>
         </is>
       </c>
       <c r="D188" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：仕様書どおり約100頁に統一する。第Ⅱ部（分析編25頁）は計画の根拠のため維持し、第Ⅰ部（単純集計編）と資料編で18頁を圧縮する（doc24§1改訂）。部数は仕様書のとおり10部。</t>
+          <t>★2026/09/24 村の回答で決着：配布用封筒は村が用意し、費用は村側で請求処理する。受託者が印刷するのは返信用（回収用）のみ。仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消した。</t>
         </is>
       </c>
       <c r="E188" s="39" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅰ-23,Ⅰ-26,Ⅰ-103</t>
         </is>
       </c>
       <c r="F188" s="39" t="inlineStr">
@@ -15090,27 +15090,27 @@
       </c>
       <c r="B189" s="40" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C189" s="41" t="inlineStr">
         <is>
-          <t>100頁への圧縮の当て方（集計編を圧縮するか、調査票を電子媒体に移すか）</t>
+          <t>在宅介護実態調査の対象者数（仕様書の約150人に対し118人）</t>
         </is>
       </c>
       <c r="D189" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/25 案Bを採用：調査票2種・単純集計表・自由記述の全文を電子媒体に収録し、資料編を25頁→6頁とする。浮いた頁を集計編に戻し第3章42頁・第4章21頁（計63頁・1頁1.7設問）とした。当初案118頁と同じ密度を100頁の枠内で保てる。案A（集計編を47頁に圧縮）は1頁2.3設問で第9期の2.5倍の密度となり、選択肢の多い設問が物理的に入らないため採らなかった。</t>
+          <t>★2026/09/24 村の回答で決着：118人で問題なし。仕様書4Ⅰ(1)の「約150人」との差異は解消した。集計設計上のセル数の扱いは当方の判断事項として継続。</t>
         </is>
       </c>
       <c r="E189" s="39" t="inlineStr">
         <is>
-          <t>Ⅳ-90,Ⅰ-48,Ⅳ-91,Ⅳ-114</t>
+          <t>Ⅰ-08,Ⅰ-24,Ⅰ-103</t>
         </is>
       </c>
       <c r="F189" s="39" t="inlineStr">
         <is>
-          <t>doc24§1-1,doc40§2</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G189" s="39" t="inlineStr">
@@ -15128,27 +15128,27 @@
       </c>
       <c r="B190" s="40" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C190" s="41" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>アンケート調査報告書の分量（仕様書の約100頁に対し想定118頁）</t>
         </is>
       </c>
       <c r="D190" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>★2026/09/24 村の回答で決着：仕様書どおり約100頁に統一する。第Ⅱ部（分析編25頁）は計画の根拠のため維持し、第Ⅰ部（単純集計編）と資料編で18頁を圧縮する（doc24§1改訂）。部数は仕様書のとおり10部。</t>
         </is>
       </c>
       <c r="E190" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F190" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G190" s="39" t="inlineStr">
@@ -15166,27 +15166,27 @@
       </c>
       <c r="B191" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C191" s="41" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>100頁への圧縮の当て方（集計編を圧縮するか、調査票を電子媒体に移すか）</t>
         </is>
       </c>
       <c r="D191" s="41" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>★2026/09/25 案Bを採用：調査票2種・単純集計表・自由記述の全文を電子媒体に収録し、資料編を25頁→6頁とする。浮いた頁を集計編に戻し第3章42頁・第4章21頁（計63頁・1頁1.7設問）とした。当初案118頁と同じ密度を100頁の枠内で保てる。案A（集計編を47頁に圧縮）は1頁2.3設問で第9期の2.5倍の密度となり、選択肢の多い設問が物理的に入らないため採らなかった。</t>
         </is>
       </c>
       <c r="E191" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅳ-90,Ⅰ-48,Ⅳ-91,Ⅳ-114</t>
         </is>
       </c>
       <c r="F191" s="39" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc24§1-1,doc40§2</t>
         </is>
       </c>
       <c r="G191" s="39" t="inlineStr">
@@ -15204,27 +15204,27 @@
       </c>
       <c r="B192" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C192" s="41" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D192" s="41" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E192" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F192" s="39" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G192" s="39" t="inlineStr">
@@ -15247,12 +15247,12 @@
       </c>
       <c r="C193" s="41" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D193" s="41" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E193" s="39" t="inlineStr">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="F193" s="39" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G193" s="39" t="inlineStr">
@@ -15285,22 +15285,22 @@
       </c>
       <c r="C194" s="41" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>交付要綱の配点表（満点）</t>
         </is>
       </c>
       <c r="D194" s="41" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
         </is>
       </c>
       <c r="E194" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F194" s="39" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc20§2</t>
         </is>
       </c>
       <c r="G194" s="39" t="inlineStr">
@@ -15323,22 +15323,22 @@
       </c>
       <c r="C195" s="41" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
         </is>
       </c>
       <c r="D195" s="41" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
         </is>
       </c>
       <c r="E195" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F195" s="39" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc20§3-1</t>
         </is>
       </c>
       <c r="G195" s="39" t="inlineStr">
@@ -15361,43 +15361,119 @@
       </c>
       <c r="C196" s="41" t="inlineStr">
         <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D196" s="41" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E196" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F196" s="39" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G196" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H196" s="41" t="inlineStr"/>
+    </row>
+    <row r="197" ht="34" customHeight="1">
+      <c r="A197" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B197" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C197" s="41" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D197" s="41" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E197" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F197" s="39" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G197" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H197" s="41" t="inlineStr"/>
+    </row>
+    <row r="198" ht="34" customHeight="1">
+      <c r="A198" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B198" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C198" s="41" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D196" s="41" t="inlineStr">
+      <c r="D198" s="41" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E196" s="39" t="inlineStr">
+      <c r="E198" s="39" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F196" s="39" t="inlineStr">
+      <c r="F198" s="39" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G196" s="39" t="inlineStr">
+      <c r="G198" s="39" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H196" s="41" t="inlineStr"/>
+      <c r="H198" s="41" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H172"/>
+  <autoFilter ref="A4:H174"/>
   <mergeCells count="3">
-    <mergeCell ref="A174:H174"/>
+    <mergeCell ref="A176:H176"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A172" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A174" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G172" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G174" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$173</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'仕様書対照'!$A$4:$H$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'受領資料・データ管理'!$A$4:$F$45</definedName>
   </definedNames>
@@ -12732,22 +12732,22 @@
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>施策体系図（基本理念→基本目標5→施策28の階層図）を計画書3-5に載せるか</t>
+          <t>計画書・報告書の頁数の実測（当方では docx→PDF 変換ができず目視確認ができない）</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>★第9期は第3章8頁に施策体系とSDGsの対応を掲げていた。第10期は3-5に対応表（28施策×根拠・交付金の目標・SDGs）を新設したが階層図がない。図は第2回策定委員会 資料4に用意しており、当方の推定では計画書は94頁で仕様書の約100頁に6頁の余裕がある。頁数の実測で余裕が確認できれば追加したい。</t>
+          <t>★当方の推定では計画書は本文88頁＋前付4頁＝92頁で、仕様書の約100頁に8頁の余裕がある（レイアウト値からの積算・doc40§0）。字詰め・禁則・表の折り返しの実挙動で前後するため、村側で実際に開いて頁数をご確認いただきたい。余裕が確認できれば第3章の施策体系図（第9期にあり第10期素案にない）とSDGsの対応表を追加したい。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅱ-71</t>
+          <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc41§6</t>
+          <t>doc40§1-4</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>計画書・報告書の頁数の実測（当方では docx→PDF 変換ができず目視確認ができない）</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>★当方の推定では計画書は本文88頁＋前付4頁＝92頁で、仕様書の約100頁に8頁の余裕がある（レイアウト値からの積算・doc40§0）。字詰め・禁則・表の折り返しの実挙動で前後するため、村側で実際に開いて頁数をご確認いただきたい。余裕が確認できれば第3章の施策体系図（第9期にあり第10期素案にない）とSDGsの対応表を追加したい。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅳ-89</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc40§1-4</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -12808,22 +12808,22 @@
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-93</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -12841,27 +12841,27 @@
       </c>
       <c r="B128" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-93</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -12884,22 +12884,22 @@
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -12922,22 +12922,22 @@
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -12960,22 +12960,22 @@
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12998,22 +12998,22 @@
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -13036,22 +13036,22 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -13074,22 +13074,22 @@
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -13112,22 +13112,22 @@
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-105,Ⅱ-67</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -13150,22 +13150,22 @@
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -13188,22 +13188,22 @@
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -13226,22 +13226,22 @@
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
@@ -13264,22 +13264,22 @@
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
@@ -13302,22 +13302,22 @@
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
@@ -13340,22 +13340,22 @@
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
         </is>
       </c>
       <c r="E141" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc37§4,doc18 5-4(10)</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
@@ -13378,22 +13378,22 @@
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
-          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
+          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
         </is>
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
+          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>doc37§4,doc18 5-4(10)</t>
+          <t>doc36§10-2,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G142" s="23" t="inlineStr">
@@ -13416,22 +13416,22 @@
       </c>
       <c r="C143" s="25" t="inlineStr">
         <is>
-          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
+          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
+          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
         </is>
       </c>
       <c r="E143" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-2,doc18 4-7(4)</t>
+          <t>doc36§10-3,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G143" s="23" t="inlineStr">
@@ -13454,22 +13454,22 @@
       </c>
       <c r="C144" s="25" t="inlineStr">
         <is>
-          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
+          <t>認知症対応型通所介護を再開するかどうか</t>
         </is>
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
+          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F144" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-3,doc18 4-7(3)</t>
+          <t>doc36§3,doc18 施策3-2</t>
         </is>
       </c>
       <c r="G144" s="23" t="inlineStr">
@@ -13492,22 +13492,22 @@
       </c>
       <c r="C145" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護を再開するかどうか</t>
+          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
         </is>
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
+          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
         </is>
       </c>
       <c r="E145" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F145" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 施策3-2</t>
+          <t>doc36§3,doc18 4-7(2)</t>
         </is>
       </c>
       <c r="G145" s="23" t="inlineStr">
@@ -13530,22 +13530,22 @@
       </c>
       <c r="C146" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E146" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F146" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 4-7(2)</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G146" s="23" t="inlineStr">
@@ -13568,22 +13568,22 @@
       </c>
       <c r="C147" s="25" t="inlineStr">
         <is>
-          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E147" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F147" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G147" s="23" t="inlineStr">
@@ -13606,22 +13606,22 @@
       </c>
       <c r="C148" s="25" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F148" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G148" s="23" t="inlineStr">
@@ -13639,27 +13639,27 @@
       </c>
       <c r="B149" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C149" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E149" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F149" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G149" s="23" t="inlineStr">
@@ -13682,12 +13682,12 @@
       </c>
       <c r="C150" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D150" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="F150" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G150" s="23" t="inlineStr">
@@ -13720,22 +13720,22 @@
       </c>
       <c r="C151" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E151" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F151" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G151" s="23" t="inlineStr">
@@ -13758,22 +13758,22 @@
       </c>
       <c r="C152" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D152" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E152" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F152" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G152" s="23" t="inlineStr">
@@ -13796,22 +13796,22 @@
       </c>
       <c r="C153" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E153" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F153" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G153" s="23" t="inlineStr">
@@ -13834,12 +13834,12 @@
       </c>
       <c r="C154" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
         </is>
       </c>
       <c r="D154" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
         </is>
       </c>
       <c r="E154" s="23" t="inlineStr">
@@ -13849,12 +13849,12 @@
       </c>
       <c r="F154" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc38§B-2</t>
         </is>
       </c>
       <c r="G154" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>社内対応</t>
         </is>
       </c>
       <c r="H154" s="25" t="inlineStr"/>
@@ -13872,27 +13872,27 @@
       </c>
       <c r="C155" s="25" t="inlineStr">
         <is>
-          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
+          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
         </is>
       </c>
       <c r="D155" s="25" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
+          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
         </is>
       </c>
       <c r="E155" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F155" s="23" t="inlineStr">
         <is>
-          <t>doc38§B-2</t>
+          <t>doc37§3-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G155" s="23" t="inlineStr">
         <is>
-          <t>社内対応</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H155" s="25" t="inlineStr"/>
@@ -13910,22 +13910,22 @@
       </c>
       <c r="C156" s="25" t="inlineStr">
         <is>
-          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
+          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
         </is>
       </c>
       <c r="D156" s="25" t="inlineStr">
         <is>
-          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
+          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
         </is>
       </c>
       <c r="E156" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F156" s="23" t="inlineStr">
         <is>
-          <t>doc37§3-2,doc18 5-4</t>
+          <t>doc36§2,doc18 2-3</t>
         </is>
       </c>
       <c r="G156" s="23" t="inlineStr">
@@ -13943,27 +13943,27 @@
       </c>
       <c r="B157" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C157" s="25" t="inlineStr">
         <is>
-          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D157" s="25" t="inlineStr">
         <is>
-          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E157" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F157" s="23" t="inlineStr">
         <is>
-          <t>doc36§2,doc18 2-3</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G157" s="23" t="inlineStr">
@@ -13986,22 +13986,22 @@
       </c>
       <c r="C158" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D158" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E158" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F158" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G158" s="23" t="inlineStr">
@@ -14024,12 +14024,12 @@
       </c>
       <c r="C159" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D159" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E159" s="23" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="F159" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G159" s="23" t="inlineStr">
@@ -14062,22 +14062,22 @@
       </c>
       <c r="C160" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D160" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E160" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F160" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G160" s="23" t="inlineStr">
@@ -14100,12 +14100,12 @@
       </c>
       <c r="C161" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D161" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E161" s="23" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="F161" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G161" s="23" t="inlineStr">
@@ -14138,22 +14138,22 @@
       </c>
       <c r="C162" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D162" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E162" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F162" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G162" s="23" t="inlineStr">
@@ -14171,27 +14171,27 @@
       </c>
       <c r="B163" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C163" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D163" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E163" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F163" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G163" s="23" t="inlineStr">
@@ -14214,22 +14214,22 @@
       </c>
       <c r="C164" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D164" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E164" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F164" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G164" s="23" t="inlineStr">
@@ -14252,22 +14252,22 @@
       </c>
       <c r="C165" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D165" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E165" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F165" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G165" s="23" t="inlineStr">
@@ -14290,22 +14290,22 @@
       </c>
       <c r="C166" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D166" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E166" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F166" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G166" s="23" t="inlineStr">
@@ -14323,27 +14323,27 @@
       </c>
       <c r="B167" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C167" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
         </is>
       </c>
       <c r="D167" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
         </is>
       </c>
       <c r="E167" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-31</t>
         </is>
       </c>
       <c r="F167" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc19 追-6</t>
         </is>
       </c>
       <c r="G167" s="23" t="inlineStr">
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C168" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
         </is>
       </c>
       <c r="D168" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
         </is>
       </c>
       <c r="E168" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅰ-40,Ⅰ-42</t>
         </is>
       </c>
       <c r="F168" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc19 追-7</t>
         </is>
       </c>
       <c r="G168" s="23" t="inlineStr">
@@ -14404,22 +14404,22 @@
       </c>
       <c r="C169" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
         </is>
       </c>
       <c r="D169" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
         </is>
       </c>
       <c r="E169" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F169" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc23§1-3</t>
         </is>
       </c>
       <c r="G169" s="23" t="inlineStr">
@@ -14442,22 +14442,22 @@
       </c>
       <c r="C170" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>送付状の個人情報に関する説明の補強</t>
         </is>
       </c>
       <c r="D170" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
         </is>
       </c>
       <c r="E170" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F170" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc27§5-1</t>
         </is>
       </c>
       <c r="G170" s="23" t="inlineStr">
@@ -14480,22 +14480,22 @@
       </c>
       <c r="C171" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
       <c r="D171" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
       <c r="E171" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F171" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc27§4</t>
         </is>
       </c>
       <c r="G171" s="23" t="inlineStr">
@@ -14506,34 +14506,34 @@
       <c r="H171" s="25" t="inlineStr"/>
     </row>
     <row r="172" ht="34" customHeight="1">
-      <c r="A172" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A172" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B172" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C172" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
+          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
       <c r="D172" s="25" t="inlineStr">
         <is>
-          <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
+          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
       <c r="E172" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
       <c r="F172" s="23" t="inlineStr">
         <is>
-          <t>doc27§4</t>
+          <t>doc01-10</t>
         </is>
       </c>
       <c r="G172" s="23" t="inlineStr">
@@ -14556,22 +14556,22 @@
       </c>
       <c r="C173" s="25" t="inlineStr">
         <is>
-          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
+          <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
       <c r="D173" s="25" t="inlineStr">
         <is>
-          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
+          <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
       <c r="E173" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅳ-89</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F173" s="23" t="inlineStr">
         <is>
-          <t>doc01-10</t>
+          <t>doc01-10,doc08</t>
         </is>
       </c>
       <c r="G173" s="23" t="inlineStr">
@@ -14581,50 +14581,50 @@
       </c>
       <c r="H173" s="25" t="inlineStr"/>
     </row>
-    <row r="174" ht="34" customHeight="1">
-      <c r="A174" s="37" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B174" s="24" t="inlineStr">
-        <is>
-          <t>成果品</t>
-        </is>
-      </c>
-      <c r="C174" s="25" t="inlineStr">
-        <is>
-          <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
-        </is>
-      </c>
-      <c r="D174" s="25" t="inlineStr">
-        <is>
-          <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
-        </is>
-      </c>
-      <c r="E174" s="23" t="inlineStr">
-        <is>
-          <t>Ⅳ-92</t>
-        </is>
-      </c>
-      <c r="F174" s="23" t="inlineStr">
-        <is>
-          <t>doc01-10,doc08</t>
-        </is>
-      </c>
-      <c r="G174" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H174" s="25" t="inlineStr"/>
-    </row>
-    <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="38" t="inlineStr">
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="38" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
+    </row>
+    <row r="176" ht="34" customHeight="1">
+      <c r="A176" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B176" s="40" t="inlineStr">
+        <is>
+          <t>疑義</t>
+        </is>
+      </c>
+      <c r="C176" s="41" t="inlineStr">
+        <is>
+          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
+        </is>
+      </c>
+      <c r="D176" s="41" t="inlineStr">
+        <is>
+          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
+        </is>
+      </c>
+      <c r="E176" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-64</t>
+        </is>
+      </c>
+      <c r="F176" s="39" t="inlineStr">
+        <is>
+          <t>doc35§7-3(1)</t>
+        </is>
+      </c>
+      <c r="G176" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H176" s="41" t="inlineStr"/>
     </row>
     <row r="177" ht="34" customHeight="1">
       <c r="A177" s="39" t="inlineStr">
@@ -14634,27 +14634,27 @@
       </c>
       <c r="B177" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C177" s="41" t="inlineStr">
         <is>
-          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D177" s="41" t="inlineStr">
         <is>
-          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E177" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F177" s="39" t="inlineStr">
         <is>
-          <t>doc35§7-3(1)</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G177" s="39" t="inlineStr">
@@ -14672,27 +14672,27 @@
       </c>
       <c r="B178" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C178" s="41" t="inlineStr">
         <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D178" s="41" t="inlineStr">
         <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F178" s="39" t="inlineStr">
         <is>
-          <t>doc28§3</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G178" s="39" t="inlineStr">
@@ -14710,27 +14710,27 @@
       </c>
       <c r="B179" s="40" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C179" s="41" t="inlineStr">
         <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D179" s="41" t="inlineStr">
         <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>０-04</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F179" s="39" t="inlineStr">
         <is>
-          <t>doc28§4</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G179" s="39" t="inlineStr">
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C180" s="41" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D180" s="41" t="inlineStr">
         <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F180" s="39" t="inlineStr">
         <is>
-          <t>doc28§2</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G180" s="39" t="inlineStr">
@@ -14786,32 +14786,32 @@
       </c>
       <c r="B181" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C181" s="41" t="inlineStr">
         <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D181" s="41" t="inlineStr">
         <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F181" s="39" t="inlineStr">
         <is>
-          <t>doc28§1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G181" s="39" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H181" s="41" t="inlineStr"/>
@@ -14829,27 +14829,27 @@
       </c>
       <c r="C182" s="41" t="inlineStr">
         <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D182" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E182" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F182" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G182" s="39" t="inlineStr">
         <is>
-          <t>解決済（一部再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H182" s="41" t="inlineStr"/>
@@ -14867,12 +14867,12 @@
       </c>
       <c r="C183" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D183" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E183" s="39" t="inlineStr">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="G183" s="39" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H183" s="41" t="inlineStr"/>
@@ -14905,27 +14905,27 @@
       </c>
       <c r="C184" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D184" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E184" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F184" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G184" s="39" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H184" s="41" t="inlineStr"/>
@@ -14943,12 +14943,12 @@
       </c>
       <c r="C185" s="41" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D185" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E185" s="39" t="inlineStr">
@@ -14976,27 +14976,27 @@
       </c>
       <c r="B186" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C186" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>施策体系図（基本理念→基本目標5→施策28の階層図）の計画書への掲載</t>
         </is>
       </c>
       <c r="D186" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>★2026/09/25 作成して素案3-4と委員会資料4-4に掲載した。第9期が第3章に掲げていた施策体系とSDGsの対応を、体系図（3-4）と対応表（3-5）の2本立てに再構成したもの。3-4にあった同じ内容の平坦な表は図に置き換えて重複を解いた。計画書の推定は97頁で仕様書の約100頁に3頁の余裕がある。</t>
         </is>
       </c>
       <c r="E186" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-113,Ⅱ-71</t>
         </is>
       </c>
       <c r="F186" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc41§6</t>
         </is>
       </c>
       <c r="G186" s="39" t="inlineStr">
@@ -15463,17 +15463,17 @@
       <c r="H198" s="41" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H174"/>
+  <autoFilter ref="A4:H173"/>
   <mergeCells count="3">
-    <mergeCell ref="A176:H176"/>
+    <mergeCell ref="A175:H175"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A174" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G174" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -762,7 +762,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>委託第27号／業務期間：契約締結の日〜令和9年3月31日／計画期間：令和9〜11年度　｜　出典：仕様書（8北保福第483号 別紙）を作業レベルに分解（対応は「仕様書対照」シート）　｜　進捗基準日：令和8年9月25日</t>
+          <t>委託第27号／業務期間：契約締結の日〜令和9年3月31日／計画期間：令和9〜11年度　｜　出典：仕様書（8北保福第483号 別紙）を作業レベルに分解（対応は「仕様書対照」シート）　｜　進捗基準日：令和8年9月28日</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="P102" s="13" t="inlineStr">
         <is>
-          <t>★doc26で資料構成を確定（資料1〜8・約53頁＋素案別冊）。合意を得たい事項5点を先頭に置く構成。★9/3：output/08_第2回策定委員会資料.docx として資料2（本体完成）・資料5（骨格）・資料6（骨格）・資料7（本体完成）を作成。★9/4：資料4（第10期の基本理念・基本目標・施策体系）を追加し本体完成（全体で39表・A4約40頁）。基本理念は2案併記、基本目標5本、施策28本（新規10）。残るは資料3（調査結果速報）のみで、調査結果の確定後に作成。資料4に差し込む住民ニーズの数値も資料3から供給する。LibreOfficeが動作しないためレイアウトの目視確認は未実施。★9/16：資料5を骨格から本体に引き上げ（8頁→14頁）。5-3にサービス種類別の見込量と給付費の分離を、5-4に推計の幅（単価の趨勢+314円・伸びの偏りのバックテスト・推計誤差±約700円・自己点検の4件）を、5-5に令和9年4月の新設区分を新設した。資料6も本体に引き上げ（6頁→10頁）。6-3に算定の5式と感応度9項目、6-3bに12パターン（5,936〜7,341円）、6-5に中長期の保険料（αの2案）を投入。資料7に7-3bとして令和8年度の得点と全国平均の対比（維持6指標・引上げ5指標）を追加。算定の進展により委員の判断を要する論点が4つ増えたため、合意事項を5点→8点に改訂し、当日の進行案（2時間）を doc26§12 に作成した。資料は26表→43表・約65頁。残る律速は委員の改選・基金残高・調査の回収集計の3つ。</t>
+          <t>★doc26で資料構成を確定（資料1〜8・約53頁＋素案別冊）。合意を得たい事項5点を先頭に置く構成。★9/3：output/08_第2回策定委員会資料.docx として資料2（本体完成）・資料5（骨格）・資料6（骨格）・資料7（本体完成）を作成。★9/4：資料4（第10期の基本理念・基本目標・施策体系）を追加し本体完成（全体で39表・A4約40頁）。基本理念は2案併記、基本目標5本、施策28本（新規10）。残るは資料3（調査結果速報）のみで、調査結果の確定後に作成。資料4に差し込む住民ニーズの数値も資料3から供給する。LibreOfficeが動作しないためレイアウトの目視確認は未実施。★9/16：資料5を骨格から本体に引き上げ（8頁→14頁）。5-3にサービス種類別の見込量と給付費の分離を、5-4に推計の幅（単価の趨勢+314円・伸びの偏りのバックテスト・推計誤差±約700円・自己点検の4件）を、5-5に令和9年4月の新設区分を新設した。資料6も本体に引き上げ（6頁→10頁）。6-3に算定の5式と感応度9項目、6-3bに12パターン（5,936〜7,341円）、6-5に中長期の保険料（αの2案）を投入。資料7に7-3bとして令和8年度の得点と全国平均の対比（維持6指標・引上げ5指標）を追加。算定の進展により委員の判断を要する論点が4つ増えたため、合意事項を5点→8点に改訂し、当日の進行案（2時間）を doc26§12 に作成した。資料は26表→43表・約65頁。残る律速は委員の改選・基金残高・調査の回収集計の3つ。★9/25：交付金の分析を反映（doc41・doc42）。資料2-4の誤り（認知症総合支援を「下回る唯一の目標」とした記述）を訂正し、目標別の県平均・県内順位・全国順位と福島県（都道府県分）との切り分けの表を新設。資料4-4に施策体系図を追加。資料7-3cとして計画への記載で取得できる11項目・61点を新設。合意事項を8点→9点に改めた。資料の自己点検を新設（verify_shiryo.py・5件）。★9/28：資料3（アンケート調査結果 速報）の骨子を作成（10節・16表）。回収・集計前のため数値欄は【集計後】の枠。第9期の回収率を対比欄に置き、集計前でも読める形にした。骨子を組んだことで、ニーズ調査 問4(15)(16)の削除（優先度S・未回答）と要介護認定データの提供時期（優先度A）の2件が未決だと3-2〜3-4および核となる3-6が作成できないことが明確になった。自己点検を7件に拡充。資料は6資料・43節・73表・図1点。</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>北塩原村への確認事項　一覧（基準日：令和8年9月25日）</t>
+          <t>北塩原村への確認事項　一覧（基準日：令和8年9月28日）</t>
         </is>
       </c>
     </row>
@@ -20128,7 +20128,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>受領資料・データ管理（基準日：令和8年9月25日）</t>
+          <t>受領資料・データ管理（基準日：令和8年9月28日）</t>
         </is>
       </c>
     </row>
@@ -22345,7 +22345,7 @@
     <row r="59">
       <c r="B59" s="45" t="inlineStr">
         <is>
-          <t>※ 進捗基準日は令和8年9月25日です。備考欄の doc番号は docs/北塩原村_第10期/ 配下の分析資料に対応します。</t>
+          <t>※ 進捗基準日は令和8年9月28日です。備考欄の doc番号は docs/北塩原村_第10期/ 配下の分析資料に対応します。</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -7072,7 +7072,7 @@
       </c>
       <c r="P102" s="13" t="inlineStr">
         <is>
-          <t>★doc26で資料構成を確定（資料1〜8・約53頁＋素案別冊）。合意を得たい事項5点を先頭に置く構成。★9/3：output/08_第2回策定委員会資料.docx として資料2（本体完成）・資料5（骨格）・資料6（骨格）・資料7（本体完成）を作成。★9/4：資料4（第10期の基本理念・基本目標・施策体系）を追加し本体完成（全体で39表・A4約40頁）。基本理念は2案併記、基本目標5本、施策28本（新規10）。残るは資料3（調査結果速報）のみで、調査結果の確定後に作成。資料4に差し込む住民ニーズの数値も資料3から供給する。LibreOfficeが動作しないためレイアウトの目視確認は未実施。★9/16：資料5を骨格から本体に引き上げ（8頁→14頁）。5-3にサービス種類別の見込量と給付費の分離を、5-4に推計の幅（単価の趨勢+314円・伸びの偏りのバックテスト・推計誤差±約700円・自己点検の4件）を、5-5に令和9年4月の新設区分を新設した。資料6も本体に引き上げ（6頁→10頁）。6-3に算定の5式と感応度9項目、6-3bに12パターン（5,936〜7,341円）、6-5に中長期の保険料（αの2案）を投入。資料7に7-3bとして令和8年度の得点と全国平均の対比（維持6指標・引上げ5指標）を追加。算定の進展により委員の判断を要する論点が4つ増えたため、合意事項を5点→8点に改訂し、当日の進行案（2時間）を doc26§12 に作成した。資料は26表→43表・約65頁。残る律速は委員の改選・基金残高・調査の回収集計の3つ。★9/25：交付金の分析を反映（doc41・doc42）。資料2-4の誤り（認知症総合支援を「下回る唯一の目標」とした記述）を訂正し、目標別の県平均・県内順位・全国順位と福島県（都道府県分）との切り分けの表を新設。資料4-4に施策体系図を追加。資料7-3cとして計画への記載で取得できる11項目・61点を新設。合意事項を8点→9点に改めた。資料の自己点検を新設（verify_shiryo.py・5件）。★9/28：資料3（アンケート調査結果 速報）の骨子を作成（10節・16表）。回収・集計前のため数値欄は【集計後】の枠。第9期の回収率を対比欄に置き、集計前でも読める形にした。骨子を組んだことで、ニーズ調査 問4(15)(16)の削除（優先度S・未回答）と要介護認定データの提供時期（優先度A）の2件が未決だと3-2〜3-4および核となる3-6が作成できないことが明確になった。自己点検を7件に拡充。資料は6資料・43節・73表・図1点。</t>
+          <t>★doc26で資料構成を確定（資料1〜8・約53頁＋素案別冊）。合意を得たい事項5点を先頭に置く構成。★9/3：output/08_第2回策定委員会資料.docx として資料2（本体完成）・資料5（骨格）・資料6（骨格）・資料7（本体完成）を作成。★9/4：資料4（第10期の基本理念・基本目標・施策体系）を追加し本体完成（全体で39表・A4約40頁）。基本理念は2案併記、基本目標5本、施策28本（新規10）。残るは資料3（調査結果速報）のみで、調査結果の確定後に作成。資料4に差し込む住民ニーズの数値も資料3から供給する。LibreOfficeが動作しないためレイアウトの目視確認は未実施。★9/16：資料5を骨格から本体に引き上げ（8頁→14頁）。5-3にサービス種類別の見込量と給付費の分離を、5-4に推計の幅（単価の趨勢+314円・伸びの偏りのバックテスト・推計誤差±約700円・自己点検の4件）を、5-5に令和9年4月の新設区分を新設した。資料6も本体に引き上げ（6頁→10頁）。6-3に算定の5式と感応度9項目、6-3bに12パターン（5,936〜7,341円）、6-5に中長期の保険料（αの2案）を投入。資料7に7-3bとして令和8年度の得点と全国平均の対比（維持6指標・引上げ5指標）を追加。算定の進展により委員の判断を要する論点が4つ増えたため、合意事項を5点→8点に改訂し、当日の進行案（2時間）を doc26§12 に作成した。資料は26表→43表・約65頁。残る律速は委員の改選・基金残高・調査の回収集計の3つ。★9/25：交付金の分析を反映（doc41・doc42）。資料2-4の誤り（認知症総合支援を「下回る唯一の目標」とした記述）を訂正し、目標別の県平均・県内順位・全国順位と福島県（都道府県分）との切り分けの表を新設。資料4-4に施策体系図を追加。資料7-3cとして計画への記載で取得できる11項目・61点を新設。合意事項を8点→9点に改めた。資料の自己点検を新設（verify_shiryo.py・5件）。★9/28：資料3（アンケート調査結果 速報）の骨子を作成（10節・16表）。回収・集計前のため数値欄は【集計後】の枠。第9期の回収率を対比欄に置き、集計前でも読める形にした。骨子を組んだことで、ニーズ調査 問4(15)(16)の削除（優先度S・未回答）と要介護認定データの提供時期（優先度A）の2件が未決だと3-2〜3-4および核となる3-6が作成できないことが明確になった。自己点検を7件に拡充。★9/28（第2次）：資料8（今後のスケジュール）を作成し、資料1（次第・委員名簿）を除く全7資料が揃った。本日が計画の中身に意見を述べられる実質的に最後の機会であること（第3回はパブコメ結果の報告が中心）、本日決めるべき3点（パブコメの期間・第3回の開催日・概要版）、履行期限が動かないため遅れが積み上がる3か所（パブコメの終了・第3回・計画書の確定）を明示した。要介護認定データがないと資料3の3-3・3-4・3-6が作成できないことも委員会資料に明記した。自己点検を8件に拡充（資料8の日程・数値が仕様書と整合し、パブコメの主体を村としていることを照合）。資料は7資料・47節・77表・図1点。残る律速は委員の改選・調査の回収集計と認定データ・基金残高の3つ。</t>
         </is>
       </c>
     </row>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'仕様書対照'!$A$4:$H$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'受領資料・データ管理'!$A$4:$F$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'受領資料・データ管理'!$A$4:$F$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2519,64 +2519,72 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Ⅰ-24</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Ⅰ ニーズ調査</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Ⅰ-2 印刷・発送準備</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>調査対象者の抽出</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(1)</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>北塩原村</t>
         </is>
       </c>
-      <c r="G31" s="13" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>対象者リスト</t>
         </is>
       </c>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>ニーズ約850人／在宅約150人</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>R8.9中</t>
         </is>
       </c>
-      <c r="J31" s="14" t="n"/>
-      <c r="K31" s="14" t="n"/>
-      <c r="L31" s="14" t="n"/>
-      <c r="M31" s="14" t="n"/>
-      <c r="N31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="11" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P31" s="13" t="inlineStr"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
+      <c r="L31" s="8" t="n">
+        <v>46266</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>46293</v>
+      </c>
+      <c r="N31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="10" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>★村が抽出。2026/09/28に対象者名簿2件を受領した。ニーズ調査882人（リスト805＋引き抜き77）、在宅介護実態調査118人（リスト66＋引き抜き52）。個人情報を含むため原本はリポジトリに複製せず、属性の集計値のみを保存（doc16§5-2・§6に従い、年齢・性別・行政区・要介護度のみを読み、該当数10未満は伏せた）。</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
@@ -2626,17 +2634,23 @@
       </c>
       <c r="J32" s="14" t="n"/>
       <c r="K32" s="14" t="n"/>
-      <c r="L32" s="14" t="n"/>
+      <c r="L32" s="14" t="n">
+        <v>46279</v>
+      </c>
       <c r="M32" s="14" t="n"/>
       <c r="N32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="11" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P32" s="13" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="O32" s="16" t="inlineStr">
+        <is>
+          <t>確認中</t>
+        </is>
+      </c>
+      <c r="P32" s="13" t="inlineStr">
+        <is>
+          <t>★名簿の管理番号はニーズ調査が数字のみ、在宅介護実態調査が英字＋数字であることを確認した。調査票の印字見本はどちらも「1」で、形式が食い違っている（doc43§2-4）。回収後に名簿と回答を突き合わせられなくなるため、優先度Sの確認事項として起票した。</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
@@ -3412,17 +3426,23 @@
       </c>
       <c r="J45" s="14" t="n"/>
       <c r="K45" s="14" t="n"/>
-      <c r="L45" s="14" t="n"/>
+      <c r="L45" s="14" t="n">
+        <v>46293</v>
+      </c>
       <c r="M45" s="14" t="n"/>
       <c r="N45" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="11" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="P45" s="13" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="O45" s="16" t="inlineStr">
+        <is>
+          <t>確認中</t>
+        </is>
+      </c>
+      <c r="P45" s="13" t="inlineStr">
+        <is>
+          <t>★在宅介護実態調査の対象者118人分については、名簿に要介護度・受給申請日・初回認定日が含まれていた。要介護1が49人・要介護2が30人・要介護3が18人・要介護4が14人・要介護5が7人で、要支援の方は含まれていない。一方ニーズ調査の対象者882人分には要介護度の列がなく、資料3の3-3・3-4・3-6（認定状況と生活機能を重ねる分析）は作成できない。引き続き提供を要請する。</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="18" t="inlineStr">
@@ -8090,7 +8110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8585,27 +8605,27 @@
       </c>
       <c r="B16" s="32" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の手法（手法Ⅲか、手法Ⅳ〈新版 在宅生活改善調査〉を加えるか）</t>
+          <t>★★管理番号の形式の食い違い（名簿は英字＋数字、調査票の印字見本は数字のみ）</t>
         </is>
       </c>
       <c r="D16" s="33" t="inlineStr">
         <is>
-          <t>調査票の設計・印刷頁数・集計方法がすべて決まる。第10期の新設手法。</t>
+          <t>★2026/09/28に受領した対象者名簿により確定した。在宅介護実態調査の名簿（リスト66件・引き抜き52件）の管理番号は英字＋数字、ニーズ調査の名簿（805件・77件）は数字のみである。一方doc34§5-3のとおり調査票の印字見本はどちらも「1」であった。形式が食い違うと回収後に名簿と回答を突き合わせられず、認定データとの関連付けも成立しない。発送済みの場合は回収時の読み替えの規則を決める必要がある。</t>
         </is>
       </c>
       <c r="E16" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-07,Ⅰ-10</t>
+          <t>Ⅰ-18,Ⅰ-20,Ⅰ-38</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
         <is>
-          <t>doc03/doc05</t>
+          <t>doc43§2-4</t>
         </is>
       </c>
       <c r="G16" s="34" t="inlineStr">
@@ -8628,27 +8648,27 @@
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
-          <t>ニーズ調査 約850人の抽出基準（要支援認定者を含むか／第9期との対比）</t>
+          <t>在宅介護実態調査の手法（手法Ⅲか、手法Ⅳ〈新版 在宅生活改善調査〉を加えるか）</t>
         </is>
       </c>
       <c r="D17" s="33" t="inlineStr">
         <is>
-          <t>議事録で在宅150件は「要支援1・2および要介護1〜5の在宅生活者等」と決着。ニーズ約850件の抽出基準（要支援を含むか）は未決着のため残置。</t>
+          <t>調査票の設計・印刷頁数・集計方法がすべて決まる。第10期の新設手法。</t>
         </is>
       </c>
       <c r="E17" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-07,Ⅰ-10</t>
         </is>
       </c>
       <c r="F17" s="34" t="inlineStr">
         <is>
-          <t>doc01-2,3／doc22</t>
+          <t>doc03/doc05</t>
         </is>
       </c>
       <c r="G17" s="34" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H17" s="33" t="inlineStr"/>
@@ -8666,27 +8686,27 @@
       </c>
       <c r="C18" s="33" t="inlineStr">
         <is>
-          <t>オプション項目の採否（「問6 就労について」ほか）</t>
+          <t>ニーズ調査 約850人の抽出基準（要支援認定者を含むか／第9期との対比）</t>
         </is>
       </c>
       <c r="D18" s="33" t="inlineStr">
         <is>
-          <t>令和7年8月版で就労はオプションと確定。採否で頁数が変わる。</t>
+          <t>議事録で在宅150件は「要支援1・2および要介護1〜5の在宅生活者等」と決着。ニーズ約850件の抽出基準（要支援を含むか）は未決着のため残置。</t>
         </is>
       </c>
       <c r="E18" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-12</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F18" s="34" t="inlineStr">
         <is>
-          <t>doc05</t>
+          <t>doc01-2,3／doc22</t>
         </is>
       </c>
       <c r="G18" s="34" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H18" s="33" t="inlineStr"/>
@@ -8704,22 +8724,22 @@
       </c>
       <c r="C19" s="33" t="inlineStr">
         <is>
-          <t>村独自設問の採否（除雪・在宅医療・成年後見・歯科受診・服薬ほか）</t>
+          <t>オプション項目の採否（「問6 就労について」ほか）</t>
         </is>
       </c>
       <c r="D19" s="33" t="inlineStr">
         <is>
-          <t>第9期との時系列比較を優先するか、新規論点を入れるかの判断。</t>
+          <t>令和7年8月版で就労はオプションと確定。採否で頁数が変わる。</t>
         </is>
       </c>
       <c r="E19" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-13</t>
+          <t>Ⅰ-12</t>
         </is>
       </c>
       <c r="F19" s="34" t="inlineStr">
         <is>
-          <t>doc03</t>
+          <t>doc05</t>
         </is>
       </c>
       <c r="G19" s="34" t="inlineStr">
@@ -8742,22 +8762,22 @@
       </c>
       <c r="C20" s="33" t="inlineStr">
         <is>
-          <t>ウェブ回答フォームの仕様（回答期限・村HP掲載の有無・二次元コード印字位置）</t>
+          <t>村独自設問の採否（除雪・在宅医療・成年後見・歯科受診・服薬ほか）</t>
         </is>
       </c>
       <c r="D20" s="33" t="inlineStr">
         <is>
-          <t>入稿データ作成の前提。</t>
+          <t>第9期との時系列比較を優先するか、新規論点を入れるかの判断。</t>
         </is>
       </c>
       <c r="E20" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-16,Ⅰ-17</t>
+          <t>Ⅰ-13</t>
         </is>
       </c>
       <c r="F20" s="34" t="inlineStr">
         <is>
-          <t>doc01-8</t>
+          <t>doc03</t>
         </is>
       </c>
       <c r="G20" s="34" t="inlineStr">
@@ -8780,27 +8800,27 @@
       </c>
       <c r="C21" s="33" t="inlineStr">
         <is>
-          <t>★発送日の確定（9/17前倒し／9/18のまま／9/24後ろ倒し）と回収期限</t>
+          <t>ウェブ回答フォームの仕様（回答期限・村HP掲載の有無・二次元コード印字位置）</t>
         </is>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
-          <t>★議事録は「9月18日頃」とするのみで、5連休の論点に触れていない。9/17（木）への前倒し可否と回収期限を9/3の第1稿提出時に併せて提起する。</t>
+          <t>入稿データ作成の前提。</t>
         </is>
       </c>
       <c r="E21" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-29,Ⅰ-32</t>
+          <t>Ⅰ-16,Ⅰ-17</t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr">
         <is>
-          <t>doc19 指-1／doc22 A-4</t>
+          <t>doc01-8</t>
         </is>
       </c>
       <c r="G21" s="34" t="inlineStr">
         <is>
-          <t>再提起</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H21" s="33" t="inlineStr"/>
@@ -8818,27 +8838,27 @@
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
-          <t>★ウェブ回答フォームにGoogleフォームを用いることの可否</t>
+          <t>★発送日の確定（9/17前倒し／9/18のまま／9/24後ろ倒し）と回収期限</t>
         </is>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
-          <t>★通信の暗号化とデータの保存先は別の論点。回答データが村外サーバに保存される。個人情報保護条例上の取扱いと、重複排除の実装・エクスポート後の元データ削除・公開期間管理の確認が必要。</t>
+          <t>★議事録は「9月18日頃」とするのみで、5連休の論点に触れていない。9/17（木）への前倒し可否と回収期限を9/3の第1稿提出時に併せて提起する。</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-16,Ⅰ-18</t>
+          <t>Ⅰ-29,Ⅰ-32</t>
         </is>
       </c>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>doc19 追-3</t>
+          <t>doc19 指-1／doc22 A-4</t>
         </is>
       </c>
       <c r="G22" s="34" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>再提起</t>
         </is>
       </c>
       <c r="H22" s="33" t="inlineStr"/>
@@ -8856,22 +8876,22 @@
       </c>
       <c r="C23" s="33" t="inlineStr">
         <is>
-          <t>調査票の印刷頁数の調整方針（仕様書はニーズ約12頁／在宅約8頁）</t>
+          <t>★ウェブ回答フォームにGoogleフォームを用いることの可否</t>
         </is>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
-          <t>現在の調査票案は設問数が多く、レイアウト調整か設問の絞り込みが必要になる可能性。オプション項目の採否と一体。</t>
+          <t>★通信の暗号化とデータの保存先は別の論点。回答データが村外サーバに保存される。個人情報保護条例上の取扱いと、重複排除の実装・エクスポート後の元データ削除・公開期間管理の確認が必要。</t>
         </is>
       </c>
       <c r="E23" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-20,Ⅰ-21</t>
+          <t>Ⅰ-16,Ⅰ-18</t>
         </is>
       </c>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>doc19 S-5</t>
+          <t>doc19 追-3</t>
         </is>
       </c>
       <c r="G23" s="34" t="inlineStr">
@@ -8894,27 +8914,27 @@
       </c>
       <c r="C24" s="33" t="inlineStr">
         <is>
-          <t>依頼状の差出人名義（村名義／村長名）</t>
+          <t>調査票の印刷頁数の調整方針（仕様書はニーズ約12頁／在宅約8頁）</t>
         </is>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
-          <t>★第1稿は「北塩原村長　遠藤　和夫」と村長名で作成済み。名義の可否と、あわせて現職の村長名が正しいかの確認が必要（当方が保有する平成30年の資料では別の方が村長）。</t>
+          <t>現在の調査票案は設問数が多く、レイアウト調整か設問の絞り込みが必要になる可能性。オプション項目の採否と一体。</t>
         </is>
       </c>
       <c r="E24" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-20,Ⅰ-21</t>
         </is>
       </c>
       <c r="F24" s="34" t="inlineStr">
         <is>
-          <t>doc19 追-4／doc23§5</t>
+          <t>doc19 S-5</t>
         </is>
       </c>
       <c r="G24" s="34" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H24" s="33" t="inlineStr"/>
@@ -8932,27 +8952,27 @@
       </c>
       <c r="C25" s="33" t="inlineStr">
         <is>
-          <t>調査票の印刷部数（予備を何部見込むか）</t>
+          <t>依頼状の差出人名義（村名義／村長名）</t>
         </is>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
-          <t>約1,000部＋予備。発送後の追加印刷は工程上困難。</t>
+          <t>★第1稿は「北塩原村長　遠藤　和夫」と村長名で作成済み。名義の可否と、あわせて現職の村長名が正しいかの確認が必要（当方が保有する平成30年の資料では別の方が村長）。</t>
         </is>
       </c>
       <c r="E25" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-21,Ⅰ-22</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F25" s="34" t="inlineStr">
         <is>
-          <t>doc19 追-5</t>
+          <t>doc19 追-4／doc23§5</t>
         </is>
       </c>
       <c r="G25" s="34" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H25" s="33" t="inlineStr"/>
@@ -8970,22 +8990,22 @@
       </c>
       <c r="C26" s="33" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 問8・問9の基準月</t>
+          <t>調査票の印刷部数（予備を何部見込むか）</t>
         </is>
       </c>
       <c r="D26" s="33" t="inlineStr">
         <is>
-          <t>発送月の前月が通常。発送日の確定とセット。</t>
+          <t>約1,000部＋予備。発送後の追加印刷は工程上困難。</t>
         </is>
       </c>
       <c r="E26" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-21,Ⅰ-22</t>
         </is>
       </c>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>doc19 追-2</t>
+          <t>doc19 追-5</t>
         </is>
       </c>
       <c r="G26" s="34" t="inlineStr">
@@ -9008,22 +9028,22 @@
       </c>
       <c r="C27" s="33" t="inlineStr">
         <is>
-          <t>★ニーズ調査 問7(7)「この1か月間に会った友人・知人の人数」の採用可否</t>
+          <t>在宅介護実態調査 問8・問9の基準月</t>
         </is>
       </c>
       <c r="D27" s="33" t="inlineStr">
         <is>
-          <t>★第1稿では不採用のうえ以降の番号を繰り上げているため、見える化への入力時に設問の対応が崩れる。採用すれば番号ずれが解消し、かつICF分析の「参加」の量的指標としてそのまま使える。</t>
+          <t>発送月の前月が通常。発送日の確定とセット。</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>doc23§1-2</t>
+          <t>doc19 追-2</t>
         </is>
       </c>
       <c r="G27" s="34" t="inlineStr">
@@ -9046,22 +9066,22 @@
       </c>
       <c r="C28" s="33" t="inlineStr">
         <is>
-          <t>★ニーズ調査 村独自設問14問の採否と頁数（問3(10)の削除・問7(9)の簡素化）</t>
+          <t>★ニーズ調査 問7(7)「この1か月間に会った友人・知人の人数」の採用可否</t>
         </is>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
-          <t>★標準約66問＋村独自14問＝約79問。仕様書の目安A4約12頁を超える見込み。削除を提案するのは問3(10)「1日に何回食事をとりますか」の1問のみ（低栄養は問3(1)(7)(8)で把握可能）。他13問は施策・交付金の指標と結びついており残すべき。</t>
+          <t>★第1稿では不採用のうえ以降の番号を繰り上げているため、見える化への入力時に設問の対応が崩れる。採用すれば番号ずれが解消し、かつICF分析の「参加」の量的指標としてそのまま使える。</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-12,Ⅰ-13</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>doc23§4</t>
+          <t>doc23§1-2</t>
         </is>
       </c>
       <c r="G28" s="34" t="inlineStr">
@@ -9084,22 +9104,22 @@
       </c>
       <c r="C29" s="33" t="inlineStr">
         <is>
-          <t>★現職の村長名・所管課・役場の住所の確認</t>
+          <t>★ニーズ調査 村独自設問14問の採否と頁数（問3(10)の削除・問7(9)の簡素化）</t>
         </is>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
-          <t>★第1稿の依頼状に「北塩原村長 遠藤 和夫」「保健福祉課 福祉係」「大字北山字姥ヶ作3151番地」と記載。当方では現職の村長名を確認できない。所管課は住民課との別が未確認のまま（doc01 確認事項1）。</t>
+          <t>★標準約66問＋村独自14問＝約79問。仕様書の目安A4約12頁を超える見込み。削除を提案するのは問3(10)「1日に何回食事をとりますか」の1問のみ（低栄養は問3(1)(7)(8)で把握可能）。他13問は施策・交付金の指標と結びついており残すべき。</t>
         </is>
       </c>
       <c r="E29" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-12,Ⅰ-13</t>
         </is>
       </c>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>doc23§5</t>
+          <t>doc23§4</t>
         </is>
       </c>
       <c r="G29" s="34" t="inlineStr">
@@ -9122,22 +9142,22 @@
       </c>
       <c r="C30" s="33" t="inlineStr">
         <is>
-          <t>★【必須】在宅A票 訪問診療の設問を問13に直す（問12が重複し問13が欠番）</t>
+          <t>★現職の村長名・所管課・役場の住所の確認</t>
         </is>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
-          <t>★第2稿で訪問診療が復活したが番号が問12となり、今後必要と感じる支援（問12）と重複している。回答者が混乱し集計時に設問を特定できない。9/9の校了までに必ず修正。</t>
+          <t>★第1稿の依頼状に「北塩原村長 遠藤 和夫」「保健福祉課 福祉係」「大字北山字姥ヶ作3151番地」と記載。当方では現職の村長名を確認できない。所管課は住民課との別が未確認のまま（doc01 確認事項1）。</t>
         </is>
       </c>
       <c r="E30" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>doc27§3-1</t>
+          <t>doc23§5</t>
         </is>
       </c>
       <c r="G30" s="34" t="inlineStr">
@@ -9160,12 +9180,12 @@
       </c>
       <c r="C31" s="33" t="inlineStr">
         <is>
-          <t>★【必須】在宅A票 問9の基準月を「令和8年8月」に修正</t>
+          <t>★【必須】在宅A票 訪問診療の設問を問13に直す（問12が重複し問13が欠番）</t>
         </is>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
-          <t>★問8は修正されたが問9が「令和●年●月」のまま。</t>
+          <t>★第2稿で訪問診療が復活したが番号が問12となり、今後必要と感じる支援（問12）と重複している。回答者が混乱し集計時に設問を特定できない。9/9の校了までに必ず修正。</t>
         </is>
       </c>
       <c r="E31" s="34" t="inlineStr">
@@ -9175,7 +9195,7 @@
       </c>
       <c r="F31" s="34" t="inlineStr">
         <is>
-          <t>doc27§3-2</t>
+          <t>doc27§3-1</t>
         </is>
       </c>
       <c r="G31" s="34" t="inlineStr">
@@ -9198,60 +9218,60 @@
       </c>
       <c r="C32" s="33" t="inlineStr">
         <is>
+          <t>★【必須】在宅A票 問9の基準月を「令和8年8月」に修正</t>
+        </is>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>★問8は修正されたが問9が「令和●年●月」のまま。</t>
+        </is>
+      </c>
+      <c r="E32" s="34" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F32" s="34" t="inlineStr">
+        <is>
+          <t>doc27§3-2</t>
+        </is>
+      </c>
+      <c r="G32" s="34" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H32" s="33" t="inlineStr"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C33" s="33" t="inlineStr">
+        <is>
           <t>★【必須】ニーズ 問1(2)① 選択肢14・15を「14．その他／15．不明」に修正</t>
         </is>
       </c>
-      <c r="D32" s="33" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>★選択肢の順序の修正7か所のうち、この1か所のみ修正漏れ。標準は13．高齢による衰弱／14．その他（　）／15．不明。</t>
         </is>
       </c>
-      <c r="E32" s="34" t="inlineStr">
+      <c r="E33" s="34" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F32" s="34" t="inlineStr">
+      <c r="F33" s="34" t="inlineStr">
         <is>
           <t>doc27§2-1</t>
-        </is>
-      </c>
-      <c r="G32" s="34" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H32" s="33" t="inlineStr"/>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="35" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B33" s="32" t="inlineStr">
-        <is>
-          <t>スケジュール</t>
-        </is>
-      </c>
-      <c r="C33" s="33" t="inlineStr">
-        <is>
-          <t>★第2回策定委員会の開催日（11月のいつか）</t>
-        </is>
-      </c>
-      <c r="D33" s="33" t="inlineStr">
-        <is>
-          <t>★資料の事前送付の期限が決まる。素案約90頁を当日配付では読めないため事前送付が前提。</t>
-        </is>
-      </c>
-      <c r="E33" s="34" t="inlineStr">
-        <is>
-          <t>Ⅱ-83</t>
-        </is>
-      </c>
-      <c r="F33" s="34" t="inlineStr">
-        <is>
-          <t>doc26§10 K-95</t>
         </is>
       </c>
       <c r="G33" s="34" t="inlineStr">
@@ -9269,27 +9289,27 @@
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="C34" s="33" t="inlineStr">
         <is>
-          <t>通いの場の参加者281人は実人数か延べ人数か（基準値の置き方）</t>
+          <t>★第2回策定委員会の開催日（11月のいつか）</t>
         </is>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
-          <t>★9/15：参加率の分母を検算し、見える化F1・F4系の定義が「参加者実人数÷65歳以上人口」であることを確認した（H30は306÷961＝31.8%で公表値と一致）。令和6年度は281÷1,009＝27.8%（週1回以上は123÷1,009＝12.2%）となり、素案の12.2%・5.3%を訂正した。一方、第9期アンケートの自己申告による参加率11.2%とは16.6ポイント開く。281人が複数の通いの場への参加を重複計上しているのであれば実人数はこれより少ない。第10期の活動指標の基準値をどちらに置くかは把握方法の確認が前提。</t>
+          <t>★資料の事前送付の期限が決まる。素案約90頁を当日配付では読めないため事前送付が前提。</t>
         </is>
       </c>
       <c r="E34" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F34" s="34" t="inlineStr">
         <is>
-          <t>doc35§2</t>
+          <t>doc26§10 K-95</t>
         </is>
       </c>
       <c r="G34" s="34" t="inlineStr">
@@ -9312,22 +9332,22 @@
       </c>
       <c r="C35" s="33" t="inlineStr">
         <is>
-          <t>★介護給付適正化の主要3事業のうち「要介護認定の適正化」の実施状況（令和8年度に0点となった原因）</t>
+          <t>通いの場の参加者281人は実人数か延べ人数か（基準値の置き方）</t>
         </is>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
-          <t>★主要3事業の全実施を問う指標（6点・全国96.9%が取得・県内55位／59）が0点である。適正化方策の策定は4項目すべて満点、ケアプラン点検と医療情報との突合は活動指標も満点であることから、残る「要介護認定の適正化」が実施されていない可能性が高い。取組が後退したのか、国への該当状況調査票の記載によるものかをご教示いただきたい。</t>
+          <t>★9/15：参加率の分母を検算し、見える化F1・F4系の定義が「参加者実人数÷65歳以上人口」であることを確認した（H30は306÷961＝31.8%で公表値と一致）。令和6年度は281÷1,009＝27.8%（週1回以上は123÷1,009＝12.2%）となり、素案の12.2%・5.3%を訂正した。一方、第9期アンケートの自己申告による参加率11.2%とは16.6ポイント開く。281人が複数の通いの場への参加を重複計上しているのであれば実人数はこれより少ない。第10期の活動指標の基準値をどちらに置くかは把握方法の確認が前提。</t>
         </is>
       </c>
       <c r="E35" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-109</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F35" s="34" t="inlineStr">
         <is>
-          <t>doc42§3</t>
+          <t>doc35§2</t>
         </is>
       </c>
       <c r="G35" s="34" t="inlineStr">
@@ -9350,22 +9370,22 @@
       </c>
       <c r="C36" s="33" t="inlineStr">
         <is>
-          <t>国の介護保険事業計画作成支援ツール（将来推計総括表）の出力一式</t>
+          <t>★介護給付適正化の主要3事業のうち「要介護認定の適正化」の実施状況（令和8年度に0点となった原因）</t>
         </is>
       </c>
       <c r="D36" s="33" t="inlineStr">
         <is>
-          <t>★★最優先。他案件（川崎町・金ケ崎町・大雪）はいずれも保険者が操作したツールの出力を受領し検証する立場にあるが、本村は見える化から独自算定しており国の様式との検算ができていない。他案件では令和8年度が実績でなく推計値、主要項目が未入力のまま保険料だけ数値が入る等の事例が実際に見つかっている。</t>
+          <t>★主要3事業の全実施を問う指標（6点・全国96.9%が取得・県内55位／59）が0点である。適正化方策の策定は4項目すべて満点、ケアプラン点検と医療情報との突合は活動指標も満点であることから、残る「要介護認定の適正化」が実施されていない可能性が高い。取組が後退したのか、国への該当状況調査票の記載によるものかをご教示いただきたい。</t>
         </is>
       </c>
       <c r="E36" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-109</t>
         </is>
       </c>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>doc33§5-1</t>
+          <t>doc42§3</t>
         </is>
       </c>
       <c r="G36" s="34" t="inlineStr">
@@ -9388,22 +9408,22 @@
       </c>
       <c r="C37" s="33" t="inlineStr">
         <is>
-          <t>第9期計画の本文（サービス別見込量の表を含む全体）</t>
+          <t>国の介護保険事業計画作成支援ツール（将来推計総括表）の出力一式</t>
         </is>
       </c>
       <c r="D37" s="33" t="inlineStr">
         <is>
-          <t>★★用途が2つある。①対計画比（サービス別の計画値と実績の対比）。他案件では総額が計画どおりでも内訳が11.5〜967.4％まで開くことが確認されており、本村は受給率を3か年平均で固定しているため偏りを持ち越す。②老人福祉事業の量の目標の記載位置の確認（doc32§4-1）。保有しているのは概要版のみでサービス別見込量がない。</t>
+          <t>★★最優先。他案件（川崎町・金ケ崎町・大雪）はいずれも保険者が操作したツールの出力を受領し検証する立場にあるが、本村は見える化から独自算定しており国の様式との検算ができていない。他案件では令和8年度が実績でなく推計値、主要項目が未入力のまま保険料だけ数値が入る等の事例が実際に見つかっている。</t>
         </is>
       </c>
       <c r="E37" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F37" s="34" t="inlineStr">
         <is>
-          <t>doc33§5-2</t>
+          <t>doc33§5-1</t>
         </is>
       </c>
       <c r="G37" s="34" t="inlineStr">
@@ -9426,22 +9446,22 @@
       </c>
       <c r="C38" s="33" t="inlineStr">
         <is>
-          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
+          <t>第9期計画の本文（サービス別見込量の表を含む全体）</t>
         </is>
       </c>
       <c r="D38" s="33" t="inlineStr">
         <is>
-          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
+          <t>★★用途が2つある。①対計画比（サービス別の計画値と実績の対比）。他案件では総額が計画どおりでも内訳が11.5〜967.4％まで開くことが確認されており、本村は受給率を3か年平均で固定しているため偏りを持ち越す。②老人福祉事業の量の目標の記載位置の確認（doc32§4-1）。保有しているのは概要版のみでサービス別見込量がない。</t>
         </is>
       </c>
       <c r="E38" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-53,Ⅱ-55</t>
         </is>
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61</t>
+          <t>doc33§5-2</t>
         </is>
       </c>
       <c r="G38" s="34" t="inlineStr">
@@ -9464,12 +9484,12 @@
       </c>
       <c r="C39" s="33" t="inlineStr">
         <is>
-          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
+          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D39" s="33" t="inlineStr">
         <is>
-          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
+          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
         </is>
       </c>
       <c r="E39" s="34" t="inlineStr">
@@ -9479,7 +9499,7 @@
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61b</t>
+          <t>doc20§8-2 K-61</t>
         </is>
       </c>
       <c r="G39" s="34" t="inlineStr">
@@ -9502,22 +9522,22 @@
       </c>
       <c r="C40" s="33" t="inlineStr">
         <is>
-          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
+          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D40" s="33" t="inlineStr">
         <is>
-          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
+          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
         </is>
       </c>
       <c r="E40" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-62</t>
+          <t>doc20§8-2 K-61b</t>
         </is>
       </c>
       <c r="G40" s="34" t="inlineStr">
@@ -9540,12 +9560,12 @@
       </c>
       <c r="C41" s="33" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
+          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
         </is>
       </c>
       <c r="D41" s="33" t="inlineStr">
         <is>
-          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
+          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
         </is>
       </c>
       <c r="E41" s="34" t="inlineStr">
@@ -9555,7 +9575,7 @@
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-63</t>
+          <t>doc20§6-2 K-62</t>
         </is>
       </c>
       <c r="G41" s="34" t="inlineStr">
@@ -9578,22 +9598,22 @@
       </c>
       <c r="C42" s="33" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
+          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
         </is>
       </c>
       <c r="D42" s="33" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
+          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
         </is>
       </c>
       <c r="E42" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-64</t>
+          <t>doc20§6-2 K-63</t>
         </is>
       </c>
       <c r="G42" s="34" t="inlineStr">
@@ -9616,22 +9636,22 @@
       </c>
       <c r="C43" s="33" t="inlineStr">
         <is>
-          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
+          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
         </is>
       </c>
       <c r="D43" s="33" t="inlineStr">
         <is>
-          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
+          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
         </is>
       </c>
       <c r="E43" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F43" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-75</t>
+          <t>doc20§6-2 K-64</t>
         </is>
       </c>
       <c r="G43" s="34" t="inlineStr">
@@ -9654,22 +9674,22 @@
       </c>
       <c r="C44" s="33" t="inlineStr">
         <is>
-          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
+          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
         </is>
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
+          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
         </is>
       </c>
       <c r="E44" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-37</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F44" s="34" t="inlineStr">
         <is>
-          <t>doc24§12 K-87</t>
+          <t>doc22 K-75</t>
         </is>
       </c>
       <c r="G44" s="34" t="inlineStr">
@@ -9692,22 +9712,22 @@
       </c>
       <c r="C45" s="33" t="inlineStr">
         <is>
-          <t>★会津権利擁護・成年後見センターへの相談が1年で件数−43%・時間−55%と減少した要因</t>
+          <t>★ニーズ調査の対象者882人に対応する要介護認定データ（認定の有無・要介護度）</t>
         </is>
       </c>
       <c r="D45" s="33" t="inlineStr">
         <is>
-          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
+          <t>★2026/09/28に受領した名簿のうち、要介護度の列があるのは在宅介護実態調査の対象者118人分のみで、ニーズ調査の対象者882人分にはない。資料3の3-3（元気な軽度者）・3-4（生活機能からみた4つの層）・3-6（担い手の可能性）は、ニーズ調査の回答者一人ひとりの認定状況を必要とするため、このままでは作成できない。3-6は第10期に共助・互助の仕組みをどの規模で構想できるかを示す表であり、合意1・2の根拠でもある。</t>
         </is>
       </c>
       <c r="E45" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-37,Ⅰ-38</t>
         </is>
       </c>
       <c r="F45" s="34" t="inlineStr">
         <is>
-          <t>doc28§3-3 K-108</t>
+          <t>doc43§1</t>
         </is>
       </c>
       <c r="G45" s="34" t="inlineStr">
@@ -9730,22 +9750,22 @@
       </c>
       <c r="C46" s="33" t="inlineStr">
         <is>
-          <t>養護老人ホーム措置・軽費老人ホーム・老人クラブの実績は見える化に系列が一切ない</t>
+          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
         </is>
       </c>
       <c r="D46" s="33" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が計画への記載を義務づける「老人福祉事業の量の目標」（素案4-6）の基礎。見える化に該当する系列がないため、村資料の受領が必須。代替手段はない。</t>
+          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
         </is>
       </c>
       <c r="E46" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅰ-37</t>
         </is>
       </c>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>doc38§D</t>
+          <t>doc24§12 K-87</t>
         </is>
       </c>
       <c r="G46" s="34" t="inlineStr">
@@ -9768,22 +9788,22 @@
       </c>
       <c r="C47" s="33" t="inlineStr">
         <is>
-          <t>国の推計ワークシートが求める在宅サービス利用率の分母</t>
+          <t>★会津権利擁護・成年後見センターへの相談が1年で件数−43%・時間−55%と減少した要因</t>
         </is>
       </c>
       <c r="D47" s="33" t="inlineStr">
         <is>
-          <t>★★他案件（大雪）の点検で「見込量の利用率の分母は認定者数であって第1号被保険者数ではない」ことが指摘された。本村の見える化のサービス利用率の分母は要介護度別認定者数であることを実データで確認済み（51件中21件が±0.6pt以内で一致、第1号被保険者数では0件）。ただし国の将来推計が在宅の分母を「認定者数−施設・居住系利用者数」とする場合、本村の率は要介護1で58.8%→86.1%、要介護4で26.8%→70.1%に変わり、要介護2では107.7%と100%を超える。分母の取り違えは見込量を数割動かす。</t>
+          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
         </is>
       </c>
       <c r="E47" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F47" s="34" t="inlineStr">
         <is>
-          <t>doc37§3,doc18 5-4</t>
+          <t>doc28§3-3 K-108</t>
         </is>
       </c>
       <c r="G47" s="34" t="inlineStr">
@@ -9806,22 +9826,22 @@
       </c>
       <c r="C48" s="33" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護（村内27人分）の待機者数と、村外のグループホームを利用している方の人数</t>
+          <t>養護老人ホーム措置・軽費老人ホーム・老人クラブの実績は見える化に系列が一切ない</t>
         </is>
       </c>
       <c r="D48" s="33" t="inlineStr">
         <is>
-          <t>★施策3-2・5-4(7)の必要利用定員総数の判断に必須。認知症高齢者（自立度Ⅱ以上）は2年間で132人→161人と22.0%増えた一方、定員は平成28年度以降27人のまま。稼働率93%。増床の要否は待機と村外利用の実態がなければ判断できない。</t>
+          <t>★老人福祉法第20条の8第2項が計画への記載を義務づける「老人福祉事業の量の目標」（素案4-6）の基礎。見える化に該当する系列がないため、村資料の受領が必須。代替手段はない。</t>
         </is>
       </c>
       <c r="E48" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 5-4(7)</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G48" s="34" t="inlineStr">
@@ -9844,22 +9864,22 @@
       </c>
       <c r="C49" s="33" t="inlineStr">
         <is>
-          <t>認知症関連事業の実績（認知症カフェの箇所数、認知症初期集中支援推進事業の対象者数、認知症地域支援推進員の活動実績）</t>
+          <t>国の推計ワークシートが求める在宅サービス利用率の分母</t>
         </is>
       </c>
       <c r="D49" s="33" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の地域支援事業の量に認知症総合支援事業の行を新設したが、いずれも実績が未受領。国の様式では認知症総合支援事業の量を定めることが求められる。</t>
+          <t>★★他案件（大雪）の点検で「見込量の利用率の分母は認定者数であって第1号被保険者数ではない」ことが指摘された。本村の見える化のサービス利用率の分母は要介護度別認定者数であることを実データで確認済み（51件中21件が±0.6pt以内で一致、第1号被保険者数では0件）。ただし国の将来推計が在宅の分母を「認定者数−施設・居住系利用者数」とする場合、本村の率は要介護1で58.8%→86.1%、要介護4で26.8%→70.1%に変わり、要介護2では107.7%と100%を超える。分母の取り違えは見込量を数割動かす。</t>
         </is>
       </c>
       <c r="E49" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-68</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>doc36§4,doc18 5-5(1)</t>
+          <t>doc37§3,doc18 5-4</t>
         </is>
       </c>
       <c r="G49" s="34" t="inlineStr">
@@ -9882,22 +9902,22 @@
       </c>
       <c r="C50" s="33" t="inlineStr">
         <is>
-          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
+          <t>認知症対応型共同生活介護（村内27人分）の待機者数と、村外のグループホームを利用している方の人数</t>
         </is>
       </c>
       <c r="D50" s="33" t="inlineStr">
         <is>
-          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
+          <t>★施策3-2・5-4(7)の必要利用定員総数の判断に必須。認知症高齢者（自立度Ⅱ以上）は2年間で132人→161人と22.0%増えた一方、定員は平成28年度以降27人のまま。稼働率93%。増床の要否は待機と村外利用の実態がなければ判断できない。</t>
         </is>
       </c>
       <c r="E50" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc36§3,doc18 5-4(7)</t>
         </is>
       </c>
       <c r="G50" s="34" t="inlineStr">
@@ -9920,22 +9940,22 @@
       </c>
       <c r="C51" s="33" t="inlineStr">
         <is>
-          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
+          <t>認知症関連事業の実績（認知症カフェの箇所数、認知症初期集中支援推進事業の対象者数、認知症地域支援推進員の活動実績）</t>
         </is>
       </c>
       <c r="D51" s="33" t="inlineStr">
         <is>
-          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
+          <t>★素案5-5(1)の地域支援事業の量に認知症総合支援事業の行を新設したが、いずれも実績が未受領。国の様式では認知症総合支援事業の量を定めることが求められる。</t>
         </is>
       </c>
       <c r="E51" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-53,Ⅱ-68</t>
         </is>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc36§4,doc18 5-5(1)</t>
         </is>
       </c>
       <c r="G51" s="34" t="inlineStr">
@@ -9953,27 +9973,27 @@
       </c>
       <c r="B52" s="32" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C52" s="33" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
         </is>
       </c>
       <c r="D52" s="33" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
         </is>
       </c>
       <c r="E52" s="34" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G52" s="34" t="inlineStr">
@@ -9991,27 +10011,27 @@
       </c>
       <c r="B53" s="32" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C53" s="33" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
         </is>
       </c>
       <c r="D53" s="33" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
         </is>
       </c>
       <c r="E53" s="34" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G53" s="34" t="inlineStr">
@@ -10034,22 +10054,22 @@
       </c>
       <c r="C54" s="33" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D54" s="33" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E54" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-94</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G54" s="34" t="inlineStr">
@@ -10072,22 +10092,22 @@
       </c>
       <c r="C55" s="33" t="inlineStr">
         <is>
-          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D55" s="33" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。★9/25：案Bの採用により自由記述の全文を電子媒体に収録することとなったため、匿名化の対象は紙の「分類と主要意見」（資料2）と電子媒体の全文の双方に及ぶ。電子媒体に回しても匿名化は免除されない。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E55" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-44</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>doc24§12 K-89</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G55" s="34" t="inlineStr">
@@ -10110,22 +10130,22 @@
       </c>
       <c r="C56" s="33" t="inlineStr">
         <is>
-          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D56" s="33" t="inlineStr">
         <is>
-          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E56" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅰ-94</t>
         </is>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-97</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G56" s="34" t="inlineStr">
@@ -10148,27 +10168,27 @@
       </c>
       <c r="C57" s="33" t="inlineStr">
         <is>
-          <t>★見える化の「将来推計」メニューで在宅サービス利用率の分母を確認する</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D57" s="33" t="inlineStr">
         <is>
-          <t>★★見込量が数割変わる論点（要介護1で58.8%→86.1%、要介護2で107.7%と100%超）。村への依頼ではなく、当方が見える化にログインして推計方法の設定画面を開けば確かめられる見込み。他案件（大雪）は「画面の設定順からの推定［要確認］」としている。最優先で確認する。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。★9/25：案Bの採用により自由記述の全文を電子媒体に収録することとなったため、匿名化の対象は紙の「分類と主要意見」（資料2）と電子媒体の全文の双方に及ぶ。電子媒体に回しても匿名化は免除されない。</t>
         </is>
       </c>
       <c r="E57" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅰ-44</t>
         </is>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>doc38§C-1</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G57" s="34" t="inlineStr">
         <is>
-          <t>社内対応</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H57" s="33" t="inlineStr"/>
@@ -10181,27 +10201,27 @@
       </c>
       <c r="B58" s="32" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C58" s="33" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の集計設計（要介護度3区分×介護者勤務形態3区分のセル数）</t>
+          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
         </is>
       </c>
       <c r="D58" s="33" t="inlineStr">
         <is>
-          <t>★対象が118人（仕様書の想定150人）であることは村の了解を得て決着。残るのは集計設計の判断で、回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかを当方で決める。</t>
+          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
         </is>
       </c>
       <c r="E58" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-45</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>doc34§5-2</t>
+          <t>doc26§10 K-97</t>
         </is>
       </c>
       <c r="G58" s="34" t="inlineStr">
@@ -10219,32 +10239,32 @@
       </c>
       <c r="B59" s="32" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C59" s="33" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>★見える化の「将来推計」メニューで在宅サービス利用率の分母を確認する</t>
         </is>
       </c>
       <c r="D59" s="33" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>★★見込量が数割変わる論点（要介護1で58.8%→86.1%、要介護2で107.7%と100%超）。村への依頼ではなく、当方が見える化にログインして推計方法の設定画面を開けば確かめられる見込み。他案件（大雪）は「画面の設定順からの推定［要確認］」としている。最優先で確認する。</t>
         </is>
       </c>
       <c r="E59" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-95</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc38§C-1</t>
         </is>
       </c>
       <c r="G59" s="34" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>社内対応</t>
         </is>
       </c>
       <c r="H59" s="33" t="inlineStr"/>
@@ -10262,22 +10282,22 @@
       </c>
       <c r="C60" s="33" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>在宅介護実態調査の集計設計（要介護度3区分×介護者勤務形態3区分のセル数）</t>
         </is>
       </c>
       <c r="D60" s="33" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>★対象が118人（仕様書の想定150人）であることは村の了解を得て決着。残るのは集計設計の判断で、回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかを当方で決める。</t>
         </is>
       </c>
       <c r="E60" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅰ-45</t>
         </is>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc34§5-2</t>
         </is>
       </c>
       <c r="G60" s="34" t="inlineStr">
@@ -10300,22 +10320,22 @@
       </c>
       <c r="C61" s="33" t="inlineStr">
         <is>
-          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D61" s="33" t="inlineStr">
         <is>
-          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E61" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-46</t>
+          <t>Ⅰ-95</t>
         </is>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>doc25§4-2 K-91</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G61" s="34" t="inlineStr">
@@ -10333,27 +10353,27 @@
       </c>
       <c r="B62" s="32" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C62" s="33" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入の取組の実施可否（普及啓発・早期発見）</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D62" s="33" t="inlineStr">
         <is>
-          <t>★合わせて10点（全国68.9%・48.8%、県内48位・46位）。★9/25：素案の施策4-4に3つの取組（広報・健診案内・通いの場での周知／健診と通いの場での聞こえの確認／耳鼻咽喉科への受診勧奨と受診状況の把握）として反映し、指標表を普及啓発5点・早期発見5点・受診状況10点に分けた。実施の可否と現在の取組状況をご教示いただきたい。受診状況の把握と受診率50%以上は全国でも14.6%・4.8%と取得が少ないため第10期中の検討事項としている。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E62" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-65</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
-          <t>doc42§3</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G62" s="34" t="inlineStr">
@@ -10371,27 +10391,27 @@
       </c>
       <c r="B63" s="32" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C63" s="33" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の要綱の対象範囲（市町村長申立・生活保護受給者への限定を外す改正の可否）</t>
+          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
         </is>
       </c>
       <c r="D63" s="33" t="inlineStr">
         <is>
-          <t>★4点（全国78.1%・県内46位）。申立費用助成・報酬助成はいずれも整備済（doc28§3）であり、対象の限定を外す要綱改正のみで取得できる。新たな予算を要しない。★9/25：素案の施策4-7に取組として反映し、指標表に1行を追加した。現在の要綱が対象を市町村長申立てや生活保護受給者に限定しているかをご確認いただき、改正の可否をご判断いただきたい。</t>
+          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
         </is>
       </c>
       <c r="E63" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-69,Ⅱ-67</t>
+          <t>Ⅰ-46</t>
         </is>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>doc42§3-3</t>
+          <t>doc25§4-2 K-91</t>
         </is>
       </c>
       <c r="G63" s="34" t="inlineStr">
@@ -10414,22 +10434,22 @@
       </c>
       <c r="C64" s="33" t="inlineStr">
         <is>
-          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
+          <t>難聴高齢者の早期発見・早期介入の取組の実施可否（普及啓発・早期発見）</t>
         </is>
       </c>
       <c r="D64" s="33" t="inlineStr">
         <is>
-          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
+          <t>★合わせて10点（全国68.9%・48.8%、県内48位・46位）。★9/25：素案の施策4-4に3つの取組（広報・健診案内・通いの場での周知／健診と通いの場での聞こえの確認／耳鼻咽喉科への受診勧奨と受診状況の把握）として反映し、指標表を普及啓発5点・早期発見5点・受診状況10点に分けた。実施の可否と現在の取組状況をご教示いただきたい。受診状況の把握と受診率50%以上は全国でも14.6%・4.8%と取得が少ないため第10期中の検討事項としている。</t>
         </is>
       </c>
       <c r="E64" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-70,Ⅱ-71</t>
+          <t>Ⅱ-67,Ⅱ-65</t>
         </is>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc42§3</t>
         </is>
       </c>
       <c r="G64" s="34" t="inlineStr">
@@ -10447,27 +10467,27 @@
       </c>
       <c r="B65" s="32" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C65" s="33" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>成年後見制度利用支援事業の要綱の対象範囲（市町村長申立・生活保護受給者への限定を外す改正の可否）</t>
         </is>
       </c>
       <c r="D65" s="33" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★4点（全国78.1%・県内46位）。申立費用助成・報酬助成はいずれも整備済（doc28§3）であり、対象の限定を外す要綱改正のみで取得できる。新たな予算を要しない。★9/25：素案の施策4-7に取組として反映し、指標表に1行を追加した。現在の要綱が対象を市町村長申立てや生活保護受給者に限定しているかをご確認いただき、改正の可否をご判断いただきたい。</t>
         </is>
       </c>
       <c r="E65" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅱ-69,Ⅱ-67</t>
         </is>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc42§3-3</t>
         </is>
       </c>
       <c r="G65" s="34" t="inlineStr">
@@ -10485,27 +10505,27 @@
       </c>
       <c r="B66" s="32" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
         </is>
       </c>
       <c r="D66" s="33" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
         </is>
       </c>
       <c r="E66" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅱ-70,Ⅱ-71</t>
         </is>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G66" s="34" t="inlineStr">
@@ -10523,27 +10543,27 @@
       </c>
       <c r="B67" s="32" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D67" s="33" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E67" s="34" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G67" s="34" t="inlineStr">
@@ -10561,27 +10581,27 @@
       </c>
       <c r="B68" s="32" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C68" s="33" t="inlineStr">
         <is>
-          <t>★交付金で61点が取れる未得点項目11件の取組可否（計画への記載・要綱改正・手順の明文化のみで取得できるもの）</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D68" s="33" t="inlineStr">
         <is>
-          <t>★令和8年度の市町村分 全国一覧表と評価指標42頁を突合し、新たな予算や施設を要さず取得できる項目を61点分特定した（doc42§3）。447点→508点で全国1,005位→525位、県内34位→18位になる。内訳は認知症施策推進計画の策定着手5点／成年後見の要綱改正4点／難聴の普及啓発・早期発見10点／在宅医療連携の4場面の設定と対応策10点／相談内容の取りまとめ2点／給付適正化の福祉用具・住宅改修16点／ケアプラン点検の村外施設分8点／主要3事業の全実施6点。素案への反映には村の意向確認を要する。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E68" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-67,Ⅱ-109</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>doc42§3</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G68" s="34" t="inlineStr">
@@ -10599,27 +10619,27 @@
       </c>
       <c r="B69" s="32" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C69" s="33" t="inlineStr">
         <is>
-          <t>ケアプラン点検に村外の有料老人ホーム・サービス付き高齢者向け住宅の入居者分を含める体制の構築可否</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D69" s="33" t="inlineStr">
         <is>
-          <t>★評価指標の留意点により、管内に該当施設がない市町村でも、被保険者が他市町村の施設に入居して介護サービスを適正に利用しているかの実態を把握し、必要に応じ県・他市町村と連携して対応できる体制があれば8点の対象となる。素案5-8で「村内に該当施設がないため対象外」としていたのは誤りで訂正した。本村は給付費の58.7%が村外であり、利用実態の把握は得点にとどまらず計画上の課題である。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-109,Ⅱ-61</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>doc42§3-1</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G69" s="34" t="inlineStr">
@@ -10642,22 +10662,22 @@
       </c>
       <c r="C70" s="33" t="inlineStr">
         <is>
-          <t>福祉用具・住宅改修へのリハビリテーション専門職等の関与の仕組み（広域連携による整備の可否）</t>
+          <t>★交付金で61点が取れる未得点項目11件の取組可否（計画への記載・要綱改正・手順の明文化のみで取得できるもの）</t>
         </is>
       </c>
       <c r="D70" s="33" t="inlineStr">
         <is>
-          <t>★合わせて16点。評価指標の留意点により、関係団体や県・近隣市町村による広域団体と連携した仕組みでも対象となり、住宅改修費については建築専門職・福祉住環境コーディネーター検定試験2級以上も「リハビリテーション専門職等」に含まれる。購入費・改修費のいずれかで足りる。令和6・7年度は実施していたものが令和8年度に0点となっており、後退の原因もご教示いただきたい。</t>
+          <t>★令和8年度の市町村分 全国一覧表と評価指標42頁を突合し、新たな予算や施設を要さず取得できる項目を61点分特定した（doc42§3）。447点→508点で全国1,005位→525位、県内34位→18位になる。内訳は認知症施策推進計画の策定着手5点／成年後見の要綱改正4点／難聴の普及啓発・早期発見10点／在宅医療連携の4場面の設定と対応策10点／相談内容の取りまとめ2点／給付適正化の福祉用具・住宅改修16点／ケアプラン点検の村外施設分8点／主要3事業の全実施6点。素案への反映には村の意向確認を要する。</t>
         </is>
       </c>
       <c r="E70" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-109</t>
+          <t>Ⅱ-65,Ⅱ-67,Ⅱ-109</t>
         </is>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>doc42§3-1</t>
+          <t>doc42§3</t>
         </is>
       </c>
       <c r="G70" s="34" t="inlineStr">
@@ -10680,22 +10700,22 @@
       </c>
       <c r="C71" s="33" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
+          <t>ケアプラン点検に村外の有料老人ホーム・サービス付き高齢者向け住宅の入居者分を含める体制の構築可否</t>
         </is>
       </c>
       <c r="D71" s="33" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
+          <t>★評価指標の留意点により、管内に該当施設がない市町村でも、被保険者が他市町村の施設に入居して介護サービスを適正に利用しているかの実態を把握し、必要に応じ県・他市町村と連携して対応できる体制があれば8点の対象となる。素案5-8で「村内に該当施設がないため対象外」としていたのは誤りで訂正した。本村は給付費の58.7%が村外であり、利用実態の把握は得点にとどまらず計画上の課題である。</t>
         </is>
       </c>
       <c r="E71" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-109,Ⅱ-61</t>
         </is>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
-          <t>doc33§3-5</t>
+          <t>doc42§3-1</t>
         </is>
       </c>
       <c r="G71" s="34" t="inlineStr">
@@ -10718,22 +10738,22 @@
       </c>
       <c r="C72" s="33" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>福祉用具・住宅改修へのリハビリテーション専門職等の関与の仕組み（広域連携による整備の可否）</t>
         </is>
       </c>
       <c r="D72" s="33" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★合わせて16点。評価指標の留意点により、関係団体や県・近隣市町村による広域団体と連携した仕組みでも対象となり、住宅改修費については建築専門職・福祉住環境コーディネーター検定試験2級以上も「リハビリテーション専門職等」に含まれる。購入費・改修費のいずれかで足りる。令和6・7年度は実施していたものが令和8年度に0点となっており、後退の原因もご教示いただきたい。</t>
         </is>
       </c>
       <c r="E72" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-109</t>
         </is>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc42§3-1</t>
         </is>
       </c>
       <c r="G72" s="34" t="inlineStr">
@@ -10756,22 +10776,22 @@
       </c>
       <c r="C73" s="33" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
         </is>
       </c>
       <c r="D73" s="33" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
         </is>
       </c>
       <c r="E73" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc33§3-5</t>
         </is>
       </c>
       <c r="G73" s="34" t="inlineStr">
@@ -10794,22 +10814,22 @@
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D74" s="33" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E74" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G74" s="34" t="inlineStr">
@@ -10832,22 +10852,22 @@
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D75" s="33" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E75" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-99</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G75" s="34" t="inlineStr">
@@ -10870,22 +10890,22 @@
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D76" s="33" t="inlineStr">
         <is>
-          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E76" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>doc28§1-2 K-107</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G76" s="34" t="inlineStr">
@@ -10908,22 +10928,22 @@
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>認知症施策の実施状況の評価と公表の運用</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
         </is>
       </c>
       <c r="E77" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-71</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>doc36§10-1,doc18 4-7(6)</t>
+          <t>doc26§10 K-99</t>
         </is>
       </c>
       <c r="G77" s="34" t="inlineStr">
@@ -10946,22 +10966,22 @@
       </c>
       <c r="C78" s="33" t="inlineStr">
         <is>
-          <t>認知症の人およびご家族から意見を聴く方法</t>
+          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
         </is>
       </c>
       <c r="D78" s="33" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
+          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
         </is>
       </c>
       <c r="E78" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-71</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>doc36§5,doc18 4-7(4)</t>
+          <t>doc28§1-2 K-107</t>
         </is>
       </c>
       <c r="G78" s="34" t="inlineStr">
@@ -10984,22 +11004,22 @@
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
+          <t>認知症施策の実施状況の評価と公表の運用</t>
         </is>
       </c>
       <c r="D79" s="33" t="inlineStr">
         <is>
-          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
+          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
         </is>
       </c>
       <c r="E79" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§10-1,doc18 4-7(6)</t>
         </is>
       </c>
       <c r="G79" s="34" t="inlineStr">
@@ -11017,27 +11037,27 @@
       </c>
       <c r="B80" s="32" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C80" s="33" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>認知症の人およびご家族から意見を聴く方法</t>
         </is>
       </c>
       <c r="D80" s="33" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
         </is>
       </c>
       <c r="E80" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc36§5,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G80" s="34" t="inlineStr">
@@ -11055,27 +11075,27 @@
       </c>
       <c r="B81" s="32" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
         </is>
       </c>
       <c r="D81" s="33" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
         </is>
       </c>
       <c r="E81" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G81" s="34" t="inlineStr">
@@ -11093,27 +11113,27 @@
       </c>
       <c r="B82" s="32" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C82" s="33" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>★2つの名簿に重複して含まれる2人の扱い</t>
         </is>
       </c>
       <c r="D82" s="33" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>★ニーズ調査の対象者のうち2人が在宅介護実態調査の名簿にも含まれている（被保険者番号で突合。番号の値は当方で保持していない）。この2人には2種類の調査票が届く。ニーズ調査の対象には要支援認定者が、在宅調査の対象には在宅の要介護認定者が含まれるため本来は重ならない。抽出条件によるものか認定区分が変更になった方かは不明。発送済みの場合、回収時に同じ方の回答が2件計上されないようにする必要がある。</t>
         </is>
       </c>
       <c r="E82" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-24,Ⅰ-30,Ⅰ-36</t>
         </is>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc43§2-3</t>
         </is>
       </c>
       <c r="G82" s="34" t="inlineStr">
@@ -11131,32 +11151,32 @@
       </c>
       <c r="B83" s="32" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C83" s="33" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D83" s="33" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E83" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G83" s="34" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H83" s="33" t="inlineStr"/>
@@ -11169,27 +11189,27 @@
       </c>
       <c r="B84" s="32" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C84" s="33" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D84" s="33" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E84" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G84" s="34" t="inlineStr">
@@ -11207,27 +11227,27 @@
       </c>
       <c r="B85" s="32" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C85" s="33" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D85" s="33" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E85" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G85" s="34" t="inlineStr">
@@ -11250,27 +11270,27 @@
       </c>
       <c r="C86" s="33" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
       <c r="D86" s="33" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
       <c r="E86" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G86" s="34" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H86" s="33" t="inlineStr"/>
@@ -11288,144 +11308,144 @@
       </c>
       <c r="C87" s="33" t="inlineStr">
         <is>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+        </is>
+      </c>
+      <c r="D87" s="33" t="inlineStr">
+        <is>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+        </is>
+      </c>
+      <c r="E87" s="34" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F87" s="34" t="inlineStr">
+        <is>
+          <t>doc27§3-3</t>
+        </is>
+      </c>
+      <c r="G87" s="34" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H87" s="33" t="inlineStr"/>
+    </row>
+    <row r="88" ht="34" customHeight="1">
+      <c r="A88" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B88" s="32" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C88" s="33" t="inlineStr">
+        <is>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+        </is>
+      </c>
+      <c r="D88" s="33" t="inlineStr">
+        <is>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+        </is>
+      </c>
+      <c r="E88" s="34" t="inlineStr">
+        <is>
+          <t>Ⅰ-09,Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F88" s="34" t="inlineStr">
+        <is>
+          <t>doc27§5-2</t>
+        </is>
+      </c>
+      <c r="G88" s="34" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H88" s="33" t="inlineStr"/>
+    </row>
+    <row r="89" ht="34" customHeight="1">
+      <c r="A89" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B89" s="32" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C89" s="33" t="inlineStr">
+        <is>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+        </is>
+      </c>
+      <c r="D89" s="33" t="inlineStr">
+        <is>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+        </is>
+      </c>
+      <c r="E89" s="34" t="inlineStr">
+        <is>
+          <t>Ⅰ-10</t>
+        </is>
+      </c>
+      <c r="F89" s="34" t="inlineStr">
+        <is>
+          <t>doc27§5-3</t>
+        </is>
+      </c>
+      <c r="G89" s="34" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H89" s="33" t="inlineStr"/>
+    </row>
+    <row r="90" ht="34" customHeight="1">
+      <c r="A90" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B90" s="32" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C90" s="33" t="inlineStr">
+        <is>
           <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
-      <c r="D87" s="33" t="inlineStr">
+      <c r="D90" s="33" t="inlineStr">
         <is>
           <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
-      <c r="E87" s="34" t="inlineStr">
+      <c r="E90" s="34" t="inlineStr">
         <is>
           <t>Ⅰ-20</t>
         </is>
       </c>
-      <c r="F87" s="34" t="inlineStr">
+      <c r="F90" s="34" t="inlineStr">
         <is>
           <t>doc27§6</t>
         </is>
       </c>
-      <c r="G87" s="34" t="inlineStr">
+      <c r="G90" s="34" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H87" s="33" t="inlineStr"/>
-    </row>
-    <row r="88" ht="34" customHeight="1">
-      <c r="A88" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B88" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C88" s="25" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
-        </is>
-      </c>
-      <c r="D88" s="25" t="inlineStr">
-        <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
-        </is>
-      </c>
-      <c r="E88" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F88" s="23" t="inlineStr">
-        <is>
-          <t>doc02§22,doc08§8</t>
-        </is>
-      </c>
-      <c r="G88" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H88" s="25" t="inlineStr"/>
-    </row>
-    <row r="89" ht="34" customHeight="1">
-      <c r="A89" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B89" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C89" s="25" t="inlineStr">
-        <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
-        </is>
-      </c>
-      <c r="D89" s="25" t="inlineStr">
-        <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
-        </is>
-      </c>
-      <c r="E89" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
-        </is>
-      </c>
-      <c r="F89" s="23" t="inlineStr">
-        <is>
-          <t>doc08§8-1,doc30§2-4</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H89" s="25" t="inlineStr"/>
-    </row>
-    <row r="90" ht="34" customHeight="1">
-      <c r="A90" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B90" s="24" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C90" s="25" t="inlineStr">
-        <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
-        </is>
-      </c>
-      <c r="D90" s="25" t="inlineStr">
-        <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
-        </is>
-      </c>
-      <c r="E90" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-65</t>
-        </is>
-      </c>
-      <c r="F90" s="23" t="inlineStr">
-        <is>
-          <t>doc02§16,§22</t>
-        </is>
-      </c>
-      <c r="G90" s="23" t="inlineStr">
-        <is>
-          <t>一部回答</t>
-        </is>
-      </c>
-      <c r="H90" s="25" t="inlineStr"/>
+      <c r="H90" s="33" t="inlineStr"/>
     </row>
     <row r="91" ht="34" customHeight="1">
       <c r="A91" s="36" t="inlineStr">
@@ -11440,22 +11460,22 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc02§22,doc08§8</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
@@ -11478,22 +11498,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>訪問診療・訪問看護の提供実績（村内外の事業所別・令和6〜7年度）</t>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>★素案の施策4-3に在宅医療・介護連携の4場面ごとの目指すべき姿を新設し、①日常の療養支援の現状を【要確認】としている。村内は南東北裏磐梯診療所・桧原診療所の2か所で訪問看護事業所は村内にない。訪問診療の実施状況と村外からの訪問看護の提供量が分からないと、日常の療養支援の余力を示せない。県への提供依頼で把握できる範囲もあわせてご相談したい。</t>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-61</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc42§4,doc18 施策4-3</t>
+          <t>doc08§8-1,doc30§2-4</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -11516,27 +11536,27 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>急変時に本人の意思と医療情報を関係者間で共有する仕組みの有無（救急医療情報キット等）</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>★素案の施策4-3の4場面のうち③急変時の対応の現状を【要確認】としている。救急搬送先は村外の病院であり、本人の意思・服薬・既往の情報が救急隊と搬送先へ伝わる仕組みがあるかで、第10期の対応策（仕組みの導入を検討するか運用の改善にとどめるか）が変わる。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc42§4,doc18 施策4-3</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H93" s="25" t="inlineStr"/>
@@ -11554,22 +11574,22 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>介護人材の確保に関する福島県の事業（介護人材確保対策・修学資金貸付）の内容と本村からの利用実績</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>★令和8年度の交付金（都道府県分）により、介護人材の確保・サービス提供基盤の整備は福島県が全国平均を13.1点下回る県全体の課題であることが判明した（本村は▲4.8点）。本村単独では動かしにくいため、施策4-6は県の事業と定住自立圏（喜多方市・西会津町）の研修費用助成を活用する形に組み立てたい。県の事業の内容と本村からの利用実績をご教示いただきたい。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc41§3</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -11592,22 +11612,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>訪問診療・訪問看護の提供実績（村内外の事業所別・令和6〜7年度）</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>★素案の施策4-3に在宅医療・介護連携の4場面ごとの目指すべき姿を新設し、①日常の療養支援の現状を【要確認】としている。村内は南東北裏磐梯診療所・桧原診療所の2か所で訪問看護事業所は村内にない。訪問診療の実施状況と村外からの訪問看護の提供量が分からないと、日常の療養支援の余力を示せない。県への提供依頼で把握できる範囲もあわせてご相談したい。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-67,Ⅱ-61</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc42§4,doc18 施策4-3</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -11630,22 +11650,22 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>急変時に本人の意思と医療情報を関係者間で共有する仕組みの有無（救急医療情報キット等）</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>★素案の施策4-3の4場面のうち③急変時の対応の現状を【要確認】としている。救急搬送先は村外の病院であり、本人の意思・服薬・既往の情報が救急隊と搬送先へ伝わる仕組みがあるかで、第10期の対応策（仕組みの導入を検討するか運用の改善にとどめるか）が変わる。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-67</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc42§4,doc18 施策4-3</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -11668,22 +11688,22 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>介護人材の確保に関する福島県の事業（介護人材確保対策・修学資金貸付）の内容と本村からの利用実績</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>★令和8年度の交付金（都道府県分）により、介護人材の確保・サービス提供基盤の整備は福島県が全国平均を13.1点下回る県全体の課題であることが判明した（本村は▲4.8点）。本村単独では動かしにくいため、施策4-6は県の事業と定住自立圏（喜多方市・西会津町）の研修費用助成を活用する形に組み立てたい。県の事業の内容と本村からの利用実績をご教示いただきたい。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-67,Ⅱ-54</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc41§3</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -11706,22 +11726,22 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -11744,27 +11764,27 @@
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc38§A-2,doc18 5-4(9)</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H99" s="25" t="inlineStr"/>
@@ -11782,22 +11802,22 @@
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
@@ -11820,22 +11840,22 @@
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -11858,27 +11878,27 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc38§A-2,doc18 5-4(9)</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H102" s="25" t="inlineStr"/>
@@ -11896,12 +11916,12 @@
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
@@ -11911,7 +11931,7 @@
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -11934,22 +11954,22 @@
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11972,22 +11992,22 @@
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -12010,12 +12030,12 @@
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
@@ -12025,7 +12045,7 @@
       </c>
       <c r="F106" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
@@ -12048,12 +12068,12 @@
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
@@ -12063,7 +12083,7 @@
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -12086,22 +12106,22 @@
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -12124,22 +12144,22 @@
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -12162,12 +12182,12 @@
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
@@ -12177,7 +12197,7 @@
       </c>
       <c r="F110" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -12200,22 +12220,22 @@
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -12238,22 +12258,22 @@
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -12276,22 +12296,22 @@
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -12314,22 +12334,22 @@
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -12352,22 +12372,22 @@
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -12390,22 +12410,22 @@
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-107</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -12428,22 +12448,22 @@
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
+          <t>行政区コードの先頭の桁と地区の対応（推定の確認）および在宅調査「追加分」77件の位置づけ</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
+          <t>ニーズ調査の名簿の行政区コード（101〜407の23区分）について、先頭の桁が地区に対応するとみて第9期の対象者数と照合したところ4地区とも近い値となった（北山341対329、大塩185対200、桧原111対114、裏磐梯245対240、計882対883）。この対応で資料3の3-1の対象者数の欄を確定したため、推定が正しいかをご確認いただきたい。あわせて在宅調査の「追加分」77件の位置づけをご教示いただきたい（リスト66＋引き抜き52＝118で対象者数は足りており、ニーズ調査の「引き抜き」77件と同数である）。また、在宅介護実態調査の名簿の行政区は23区分あり10人以上は2区分のみであるため、そのままでは地区別の集計ができない。行政区名と地区（北山・大塩・桧原・裏磐梯）の対応表をご提供いただきたい。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅰ-24,Ⅰ-40</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc38§D</t>
+          <t>doc43§2-1,§2-4</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -12466,22 +12486,22 @@
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-4,doc18 4-7(3)</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -12504,22 +12524,22 @@
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(2),doc18 5-6</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -12537,27 +12557,27 @@
       </c>
       <c r="B120" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-107</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -12575,27 +12595,27 @@
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -12613,27 +12633,27 @@
       </c>
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc36§10-4,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -12651,27 +12671,27 @@
       </c>
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
+          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
+          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc35§7-3(2),doc18 5-6</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -12689,27 +12709,27 @@
       </c>
       <c r="B124" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>報告書に調査票を再掲しないことの村への事前説明（第9期の巻末の確認を含む）</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>★案Bを採用し、調査票の全文・単純集計表・自由記述の全文は紙の資料編から外して電子媒体に収録する（doc24§9）。doc01§5-5に記録した第9期報告書の構成に調査票の再掲はないが、目次の見出しのみの記録のため巻末に載っていた可能性がある。載っていた場合は前回からの変更にあたるため、納品時の齟齬を避けるため事前に説明しておきたい。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90,Ⅳ-114</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc24§1-3</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -12727,27 +12747,27 @@
       </c>
       <c r="B125" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>計画書・報告書の頁数の実測（当方では docx→PDF 変換ができず目視確認ができない）</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>★当方の推定では計画書は本文88頁＋前付4頁＝92頁で、仕様書の約100頁に8頁の余裕がある（レイアウト値からの積算・doc40§0）。字詰め・禁則・表の折り返しの実挙動で前後するため、村側で実際に開いて頁数をご確認いただきたい。余裕が確認できれば第3章の施策体系図（第9期にあり第10期素案にない）とSDGsの対応表を追加したい。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅳ-89</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc40§1-4</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -12765,27 +12785,27 @@
       </c>
       <c r="B126" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -12803,27 +12823,27 @@
       </c>
       <c r="B127" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-93</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -12841,27 +12861,27 @@
       </c>
       <c r="B128" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>報告書に調査票を再掲しないことの村への事前説明（第9期の巻末の確認を含む）</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>★案Bを採用し、調査票の全文・単純集計表・自由記述の全文は紙の資料編から外して電子媒体に収録する（doc24§9）。doc01§5-5に記録した第9期報告書の構成に調査票の再掲はないが、目次の見出しのみの記録のため巻末に載っていた可能性がある。載っていた場合は前回からの変更にあたるため、納品時の齟齬を避けるため事前に説明しておきたい。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅳ-90,Ⅳ-114</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc24§1-3</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -12879,27 +12899,27 @@
       </c>
       <c r="B129" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>計画書・報告書の頁数の実測（当方では docx→PDF 変換ができず目視確認ができない）</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>★当方の推定では計画書は本文88頁＋前付4頁＝92頁で、仕様書の約100頁に8頁の余裕がある（レイアウト値からの積算・doc40§0）。字詰め・禁則・表の折り返しの実挙動で前後するため、村側で実際に開いて頁数をご確認いただきたい。余裕が確認できれば第3章の施策体系図（第9期にあり第10期素案にない）とSDGsの対応表を追加したい。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc40§1-4</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -12917,27 +12937,27 @@
       </c>
       <c r="B130" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -12955,27 +12975,27 @@
       </c>
       <c r="B131" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-93</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -12998,22 +13018,22 @@
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -13036,22 +13056,22 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -13074,22 +13094,22 @@
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -13112,22 +13132,22 @@
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105,Ⅱ-67</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -13150,22 +13170,22 @@
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -13188,22 +13208,22 @@
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -13226,22 +13246,22 @@
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
@@ -13264,22 +13284,22 @@
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-105,Ⅱ-67</t>
         </is>
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
@@ -13302,22 +13322,22 @@
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
@@ -13340,22 +13360,22 @@
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E141" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>doc37§4,doc18 5-4(10)</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
@@ -13378,22 +13398,22 @@
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
-          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-2,doc18 4-7(4)</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G142" s="23" t="inlineStr">
@@ -13416,22 +13436,22 @@
       </c>
       <c r="C143" s="25" t="inlineStr">
         <is>
-          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E143" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-3,doc18 4-7(3)</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G143" s="23" t="inlineStr">
@@ -13454,22 +13474,22 @@
       </c>
       <c r="C144" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護を再開するかどうか</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F144" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 施策3-2</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G144" s="23" t="inlineStr">
@@ -13492,22 +13512,22 @@
       </c>
       <c r="C145" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
+          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
         </is>
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
+          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
         </is>
       </c>
       <c r="E145" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F145" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 4-7(2)</t>
+          <t>doc37§4,doc18 5-4(10)</t>
         </is>
       </c>
       <c r="G145" s="23" t="inlineStr">
@@ -13530,22 +13550,22 @@
       </c>
       <c r="C146" s="25" t="inlineStr">
         <is>
-          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
+          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
         </is>
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
+          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
         </is>
       </c>
       <c r="E146" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F146" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§10-2,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G146" s="23" t="inlineStr">
@@ -13568,22 +13588,22 @@
       </c>
       <c r="C147" s="25" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
         </is>
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
         </is>
       </c>
       <c r="E147" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F147" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc36§10-3,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G147" s="23" t="inlineStr">
@@ -13606,22 +13626,22 @@
       </c>
       <c r="C148" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>認知症対応型通所介護を再開するかどうか</t>
         </is>
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F148" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc36§3,doc18 施策3-2</t>
         </is>
       </c>
       <c r="G148" s="23" t="inlineStr">
@@ -13639,27 +13659,27 @@
       </c>
       <c r="B149" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C149" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
         </is>
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
         </is>
       </c>
       <c r="E149" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F149" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc36§3,doc18 4-7(2)</t>
         </is>
       </c>
       <c r="G149" s="23" t="inlineStr">
@@ -13677,27 +13697,27 @@
       </c>
       <c r="B150" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C150" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D150" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F150" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G150" s="23" t="inlineStr">
@@ -13715,27 +13735,27 @@
       </c>
       <c r="B151" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C151" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E151" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F151" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G151" s="23" t="inlineStr">
@@ -13753,27 +13773,27 @@
       </c>
       <c r="B152" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C152" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D152" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E152" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F152" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G152" s="23" t="inlineStr">
@@ -13796,22 +13816,22 @@
       </c>
       <c r="C153" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E153" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F153" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G153" s="23" t="inlineStr">
@@ -13834,27 +13854,27 @@
       </c>
       <c r="C154" s="25" t="inlineStr">
         <is>
-          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D154" s="25" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E154" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F154" s="23" t="inlineStr">
         <is>
-          <t>doc38§B-2</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G154" s="23" t="inlineStr">
         <is>
-          <t>社内対応</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H154" s="25" t="inlineStr"/>
@@ -13872,22 +13892,22 @@
       </c>
       <c r="C155" s="25" t="inlineStr">
         <is>
-          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D155" s="25" t="inlineStr">
         <is>
-          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E155" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F155" s="23" t="inlineStr">
         <is>
-          <t>doc37§3-2,doc18 5-4</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G155" s="23" t="inlineStr">
@@ -13910,22 +13930,22 @@
       </c>
       <c r="C156" s="25" t="inlineStr">
         <is>
-          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D156" s="25" t="inlineStr">
         <is>
-          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E156" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F156" s="23" t="inlineStr">
         <is>
-          <t>doc36§2,doc18 2-3</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G156" s="23" t="inlineStr">
@@ -13943,27 +13963,27 @@
       </c>
       <c r="B157" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C157" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D157" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E157" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F157" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G157" s="23" t="inlineStr">
@@ -13981,32 +14001,32 @@
       </c>
       <c r="B158" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C158" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
         </is>
       </c>
       <c r="D158" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
         </is>
       </c>
       <c r="E158" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F158" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc38§B-2</t>
         </is>
       </c>
       <c r="G158" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>社内対応</t>
         </is>
       </c>
       <c r="H158" s="25" t="inlineStr"/>
@@ -14019,27 +14039,27 @@
       </c>
       <c r="B159" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C159" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
         </is>
       </c>
       <c r="D159" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
         </is>
       </c>
       <c r="E159" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F159" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc37§3-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G159" s="23" t="inlineStr">
@@ -14057,27 +14077,27 @@
       </c>
       <c r="B160" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C160" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
         </is>
       </c>
       <c r="D160" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
         </is>
       </c>
       <c r="E160" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F160" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc36§2,doc18 2-3</t>
         </is>
       </c>
       <c r="G160" s="23" t="inlineStr">
@@ -14100,12 +14120,12 @@
       </c>
       <c r="C161" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D161" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E161" s="23" t="inlineStr">
@@ -14115,7 +14135,7 @@
       </c>
       <c r="F161" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G161" s="23" t="inlineStr">
@@ -14138,22 +14158,22 @@
       </c>
       <c r="C162" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D162" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E162" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F162" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G162" s="23" t="inlineStr">
@@ -14171,27 +14191,27 @@
       </c>
       <c r="B163" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C163" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D163" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E163" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F163" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G163" s="23" t="inlineStr">
@@ -14209,27 +14229,27 @@
       </c>
       <c r="B164" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C164" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D164" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E164" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F164" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G164" s="23" t="inlineStr">
@@ -14247,27 +14267,27 @@
       </c>
       <c r="B165" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C165" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D165" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E165" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F165" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G165" s="23" t="inlineStr">
@@ -14285,27 +14305,27 @@
       </c>
       <c r="B166" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C166" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D166" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E166" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F166" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G166" s="23" t="inlineStr">
@@ -14323,27 +14343,27 @@
       </c>
       <c r="B167" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C167" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D167" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E167" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F167" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G167" s="23" t="inlineStr">
@@ -14361,27 +14381,27 @@
       </c>
       <c r="B168" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C168" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D168" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E168" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F168" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G168" s="23" t="inlineStr">
@@ -14399,27 +14419,27 @@
       </c>
       <c r="B169" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C169" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D169" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E169" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F169" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G169" s="23" t="inlineStr">
@@ -14437,27 +14457,27 @@
       </c>
       <c r="B170" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C170" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D170" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E170" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F170" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G170" s="23" t="inlineStr">
@@ -14480,265 +14500,265 @@
       </c>
       <c r="C171" s="25" t="inlineStr">
         <is>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+        </is>
+      </c>
+      <c r="D171" s="25" t="inlineStr">
+        <is>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+        </is>
+      </c>
+      <c r="E171" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-31</t>
+        </is>
+      </c>
+      <c r="F171" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-6</t>
+        </is>
+      </c>
+      <c r="G171" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H171" s="25" t="inlineStr"/>
+    </row>
+    <row r="172" ht="34" customHeight="1">
+      <c r="A172" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B172" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C172" s="25" t="inlineStr">
+        <is>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+        </is>
+      </c>
+      <c r="D172" s="25" t="inlineStr">
+        <is>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+        </is>
+      </c>
+      <c r="E172" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-40,Ⅰ-42</t>
+        </is>
+      </c>
+      <c r="F172" s="23" t="inlineStr">
+        <is>
+          <t>doc19 追-7</t>
+        </is>
+      </c>
+      <c r="G172" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H172" s="25" t="inlineStr"/>
+    </row>
+    <row r="173" ht="34" customHeight="1">
+      <c r="A173" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B173" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C173" s="25" t="inlineStr">
+        <is>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+        </is>
+      </c>
+      <c r="D173" s="25" t="inlineStr">
+        <is>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+        </is>
+      </c>
+      <c r="E173" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-09</t>
+        </is>
+      </c>
+      <c r="F173" s="23" t="inlineStr">
+        <is>
+          <t>doc23§1-3</t>
+        </is>
+      </c>
+      <c r="G173" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H173" s="25" t="inlineStr"/>
+    </row>
+    <row r="174" ht="34" customHeight="1">
+      <c r="A174" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B174" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C174" s="25" t="inlineStr">
+        <is>
+          <t>送付状の個人情報に関する説明の補強</t>
+        </is>
+      </c>
+      <c r="D174" s="25" t="inlineStr">
+        <is>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+        </is>
+      </c>
+      <c r="E174" s="23" t="inlineStr">
+        <is>
+          <t>Ⅰ-14</t>
+        </is>
+      </c>
+      <c r="F174" s="23" t="inlineStr">
+        <is>
+          <t>doc27§5-1</t>
+        </is>
+      </c>
+      <c r="G174" s="23" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="H174" s="25" t="inlineStr"/>
+    </row>
+    <row r="175" ht="34" customHeight="1">
+      <c r="A175" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B175" s="24" t="inlineStr">
+        <is>
+          <t>調査設計</t>
+        </is>
+      </c>
+      <c r="C175" s="25" t="inlineStr">
+        <is>
           <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
-      <c r="D171" s="25" t="inlineStr">
+      <c r="D175" s="25" t="inlineStr">
         <is>
           <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
-      <c r="E171" s="23" t="inlineStr">
+      <c r="E175" s="23" t="inlineStr">
         <is>
           <t>Ⅰ-09</t>
         </is>
       </c>
-      <c r="F171" s="23" t="inlineStr">
+      <c r="F175" s="23" t="inlineStr">
         <is>
           <t>doc27§4</t>
         </is>
       </c>
-      <c r="G171" s="23" t="inlineStr">
+      <c r="G175" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H171" s="25" t="inlineStr"/>
-    </row>
-    <row r="172" ht="34" customHeight="1">
-      <c r="A172" s="37" t="inlineStr">
+      <c r="H175" s="25" t="inlineStr"/>
+    </row>
+    <row r="176" ht="34" customHeight="1">
+      <c r="A176" s="37" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B172" s="24" t="inlineStr">
+      <c r="B176" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C172" s="25" t="inlineStr">
+      <c r="C176" s="25" t="inlineStr">
         <is>
           <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
-      <c r="D172" s="25" t="inlineStr">
+      <c r="D176" s="25" t="inlineStr">
         <is>
           <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
-      <c r="E172" s="23" t="inlineStr">
+      <c r="E176" s="23" t="inlineStr">
         <is>
           <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
-      <c r="F172" s="23" t="inlineStr">
+      <c r="F176" s="23" t="inlineStr">
         <is>
           <t>doc01-10</t>
         </is>
       </c>
-      <c r="G172" s="23" t="inlineStr">
+      <c r="G176" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H172" s="25" t="inlineStr"/>
-    </row>
-    <row r="173" ht="34" customHeight="1">
-      <c r="A173" s="37" t="inlineStr">
+      <c r="H176" s="25" t="inlineStr"/>
+    </row>
+    <row r="177" ht="34" customHeight="1">
+      <c r="A177" s="37" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B173" s="24" t="inlineStr">
+      <c r="B177" s="24" t="inlineStr">
         <is>
           <t>成果品</t>
         </is>
       </c>
-      <c r="C173" s="25" t="inlineStr">
+      <c r="C177" s="25" t="inlineStr">
         <is>
           <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
-      <c r="D173" s="25" t="inlineStr">
+      <c r="D177" s="25" t="inlineStr">
         <is>
           <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
-      <c r="E173" s="23" t="inlineStr">
+      <c r="E177" s="23" t="inlineStr">
         <is>
           <t>Ⅳ-92</t>
         </is>
       </c>
-      <c r="F173" s="23" t="inlineStr">
+      <c r="F177" s="23" t="inlineStr">
         <is>
           <t>doc01-10,doc08</t>
         </is>
       </c>
-      <c r="G173" s="23" t="inlineStr">
+      <c r="G177" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H173" s="25" t="inlineStr"/>
-    </row>
-    <row r="175" ht="20" customHeight="1">
-      <c r="A175" s="38" t="inlineStr">
+      <c r="H177" s="25" t="inlineStr"/>
+    </row>
+    <row r="179" ht="20" customHeight="1">
+      <c r="A179" s="38" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
-    </row>
-    <row r="176" ht="34" customHeight="1">
-      <c r="A176" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B176" s="40" t="inlineStr">
-        <is>
-          <t>疑義</t>
-        </is>
-      </c>
-      <c r="C176" s="41" t="inlineStr">
-        <is>
-          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
-        </is>
-      </c>
-      <c r="D176" s="41" t="inlineStr">
-        <is>
-          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
-        </is>
-      </c>
-      <c r="E176" s="39" t="inlineStr">
-        <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F176" s="39" t="inlineStr">
-        <is>
-          <t>doc35§7-3(1)</t>
-        </is>
-      </c>
-      <c r="G176" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H176" s="41" t="inlineStr"/>
-    </row>
-    <row r="177" ht="34" customHeight="1">
-      <c r="A177" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B177" s="40" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C177" s="41" t="inlineStr">
-        <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
-        </is>
-      </c>
-      <c r="D177" s="41" t="inlineStr">
-        <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
-        </is>
-      </c>
-      <c r="E177" s="39" t="inlineStr">
-        <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
-        </is>
-      </c>
-      <c r="F177" s="39" t="inlineStr">
-        <is>
-          <t>doc28§3</t>
-        </is>
-      </c>
-      <c r="G177" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H177" s="41" t="inlineStr"/>
-    </row>
-    <row r="178" ht="34" customHeight="1">
-      <c r="A178" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B178" s="40" t="inlineStr">
-        <is>
-          <t>体制</t>
-        </is>
-      </c>
-      <c r="C178" s="41" t="inlineStr">
-        <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
-        </is>
-      </c>
-      <c r="D178" s="41" t="inlineStr">
-        <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
-        </is>
-      </c>
-      <c r="E178" s="39" t="inlineStr">
-        <is>
-          <t>０-04</t>
-        </is>
-      </c>
-      <c r="F178" s="39" t="inlineStr">
-        <is>
-          <t>doc28§4</t>
-        </is>
-      </c>
-      <c r="G178" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H178" s="41" t="inlineStr"/>
-    </row>
-    <row r="179" ht="34" customHeight="1">
-      <c r="A179" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B179" s="40" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C179" s="41" t="inlineStr">
-        <is>
-          <t>所得段階別の第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D179" s="41" t="inlineStr">
-        <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
-        </is>
-      </c>
-      <c r="E179" s="39" t="inlineStr">
-        <is>
-          <t>Ⅱ-64</t>
-        </is>
-      </c>
-      <c r="F179" s="39" t="inlineStr">
-        <is>
-          <t>doc28§2</t>
-        </is>
-      </c>
-      <c r="G179" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H179" s="41" t="inlineStr"/>
     </row>
     <row r="180" ht="34" customHeight="1">
       <c r="A180" s="39" t="inlineStr">
@@ -14748,27 +14768,27 @@
       </c>
       <c r="B180" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C180" s="41" t="inlineStr">
         <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
+          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
         </is>
       </c>
       <c r="D180" s="41" t="inlineStr">
         <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
+          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
         </is>
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F180" s="39" t="inlineStr">
         <is>
-          <t>doc28§1</t>
+          <t>doc35§7-3(1)</t>
         </is>
       </c>
       <c r="G180" s="39" t="inlineStr">
@@ -14786,32 +14806,32 @@
       </c>
       <c r="B181" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C181" s="41" t="inlineStr">
         <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
         </is>
       </c>
       <c r="D181" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
         </is>
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-68,Ⅱ-69</t>
         </is>
       </c>
       <c r="F181" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-1</t>
+          <t>doc28§3</t>
         </is>
       </c>
       <c r="G181" s="39" t="inlineStr">
         <is>
-          <t>解決済（一部再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H181" s="41" t="inlineStr"/>
@@ -14824,27 +14844,27 @@
       </c>
       <c r="B182" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C182" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D182" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E182" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F182" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G182" s="39" t="inlineStr">
@@ -14862,32 +14882,32 @@
       </c>
       <c r="B183" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C183" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D183" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E183" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F183" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G183" s="39" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H183" s="41" t="inlineStr"/>
@@ -14900,27 +14920,27 @@
       </c>
       <c r="B184" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C184" s="41" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D184" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E184" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F184" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G184" s="39" t="inlineStr">
@@ -14943,27 +14963,27 @@
       </c>
       <c r="C185" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D185" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E185" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F185" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G185" s="39" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H185" s="41" t="inlineStr"/>
@@ -14976,27 +14996,27 @@
       </c>
       <c r="B186" s="40" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C186" s="41" t="inlineStr">
         <is>
-          <t>施策体系図（基本理念→基本目標5→施策28の階層図）の計画書への掲載</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D186" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/25 作成して素案3-4と委員会資料4-4に掲載した。第9期が第3章に掲げていた施策体系とSDGsの対応を、体系図（3-4）と対応表（3-5）の2本立てに再構成したもの。3-4にあった同じ内容の平坦な表は図に置き換えて重複を解いた。計画書の推定は97頁で仕様書の約100頁に3頁の余裕がある。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E186" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅱ-71</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F186" s="39" t="inlineStr">
         <is>
-          <t>doc41§6</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G186" s="39" t="inlineStr">
@@ -15019,27 +15039,27 @@
       </c>
       <c r="C187" s="41" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D187" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E187" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F187" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G187" s="39" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H187" s="41" t="inlineStr"/>
@@ -15052,27 +15072,27 @@
       </c>
       <c r="B188" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C188" s="41" t="inlineStr">
         <is>
-          <t>配布用封筒の用意の主体（仕様書4Ⅰ(3)は受託者の印刷対象としている）</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D188" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：配布用封筒は村が用意し、費用は村側で請求処理する。受託者が印刷するのは返信用（回収用）のみ。仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消した。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E188" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-23,Ⅰ-26,Ⅰ-103</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F188" s="39" t="inlineStr">
         <is>
-          <t>doc39§5</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G188" s="39" t="inlineStr">
@@ -15090,27 +15110,27 @@
       </c>
       <c r="B189" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C189" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の対象者数（仕様書の約150人に対し118人）</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D189" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：118人で問題なし。仕様書4Ⅰ(1)の「約150人」との差異は解消した。集計設計上のセル数の扱いは当方の判断事項として継続。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E189" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24,Ⅰ-103</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F189" s="39" t="inlineStr">
         <is>
-          <t>doc39§5</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G189" s="39" t="inlineStr">
@@ -15133,22 +15153,22 @@
       </c>
       <c r="C190" s="41" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量（仕様書の約100頁に対し想定118頁）</t>
+          <t>施策体系図（基本理念→基本目標5→施策28の階層図）の計画書への掲載</t>
         </is>
       </c>
       <c r="D190" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：仕様書どおり約100頁に統一する。第Ⅱ部（分析編25頁）は計画の根拠のため維持し、第Ⅰ部（単純集計編）と資料編で18頁を圧縮する（doc24§1改訂）。部数は仕様書のとおり10部。</t>
+          <t>★2026/09/25 作成して素案3-4と委員会資料4-4に掲載した。第9期が第3章に掲げていた施策体系とSDGsの対応を、体系図（3-4）と対応表（3-5）の2本立てに再構成したもの。3-4にあった同じ内容の平坦な表は図に置き換えて重複を解いた。計画書の推定は97頁で仕様書の約100頁に3頁の余裕がある。</t>
         </is>
       </c>
       <c r="E190" s="39" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅱ-113,Ⅱ-71</t>
         </is>
       </c>
       <c r="F190" s="39" t="inlineStr">
         <is>
-          <t>doc39§5</t>
+          <t>doc41§6</t>
         </is>
       </c>
       <c r="G190" s="39" t="inlineStr">
@@ -15166,27 +15186,27 @@
       </c>
       <c r="B191" s="40" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C191" s="41" t="inlineStr">
         <is>
-          <t>100頁への圧縮の当て方（集計編を圧縮するか、調査票を電子媒体に移すか）</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D191" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/25 案Bを採用：調査票2種・単純集計表・自由記述の全文を電子媒体に収録し、資料編を25頁→6頁とする。浮いた頁を集計編に戻し第3章42頁・第4章21頁（計63頁・1頁1.7設問）とした。当初案118頁と同じ密度を100頁の枠内で保てる。案A（集計編を47頁に圧縮）は1頁2.3設問で第9期の2.5倍の密度となり、選択肢の多い設問が物理的に入らないため採らなかった。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E191" s="39" t="inlineStr">
         <is>
-          <t>Ⅳ-90,Ⅰ-48,Ⅳ-91,Ⅳ-114</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F191" s="39" t="inlineStr">
         <is>
-          <t>doc24§1-1,doc40§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G191" s="39" t="inlineStr">
@@ -15204,27 +15224,27 @@
       </c>
       <c r="B192" s="40" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C192" s="41" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>配布用封筒の用意の主体（仕様書4Ⅰ(3)は受託者の印刷対象としている）</t>
         </is>
       </c>
       <c r="D192" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>★2026/09/24 村の回答で決着：配布用封筒は村が用意し、費用は村側で請求処理する。受託者が印刷するのは返信用（回収用）のみ。仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消した。</t>
         </is>
       </c>
       <c r="E192" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-23,Ⅰ-26,Ⅰ-103</t>
         </is>
       </c>
       <c r="F192" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G192" s="39" t="inlineStr">
@@ -15242,27 +15262,27 @@
       </c>
       <c r="B193" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C193" s="41" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>在宅介護実態調査の対象者数（仕様書の約150人に対し118人）</t>
         </is>
       </c>
       <c r="D193" s="41" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>★2026/09/24 村の回答で決着：118人で問題なし。仕様書4Ⅰ(1)の「約150人」との差異は解消した。集計設計上のセル数の扱いは当方の判断事項として継続。</t>
         </is>
       </c>
       <c r="E193" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-08,Ⅰ-24,Ⅰ-103</t>
         </is>
       </c>
       <c r="F193" s="39" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G193" s="39" t="inlineStr">
@@ -15280,27 +15300,27 @@
       </c>
       <c r="B194" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C194" s="41" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>アンケート調査報告書の分量（仕様書の約100頁に対し想定118頁）</t>
         </is>
       </c>
       <c r="D194" s="41" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>★2026/09/24 村の回答で決着：仕様書どおり約100頁に統一する。第Ⅱ部（分析編25頁）は計画の根拠のため維持し、第Ⅰ部（単純集計編）と資料編で18頁を圧縮する（doc24§1改訂）。部数は仕様書のとおり10部。</t>
         </is>
       </c>
       <c r="E194" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F194" s="39" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G194" s="39" t="inlineStr">
@@ -15318,27 +15338,27 @@
       </c>
       <c r="B195" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C195" s="41" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>100頁への圧縮の当て方（集計編を圧縮するか、調査票を電子媒体に移すか）</t>
         </is>
       </c>
       <c r="D195" s="41" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>★2026/09/25 案Bを採用：調査票2種・単純集計表・自由記述の全文を電子媒体に収録し、資料編を25頁→6頁とする。浮いた頁を集計編に戻し第3章42頁・第4章21頁（計63頁・1頁1.7設問）とした。当初案118頁と同じ密度を100頁の枠内で保てる。案A（集計編を47頁に圧縮）は1頁2.3設問で第9期の2.5倍の密度となり、選択肢の多い設問が物理的に入らないため採らなかった。</t>
         </is>
       </c>
       <c r="E195" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅳ-90,Ⅰ-48,Ⅳ-91,Ⅳ-114</t>
         </is>
       </c>
       <c r="F195" s="39" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc24§1-1,doc40§2</t>
         </is>
       </c>
       <c r="G195" s="39" t="inlineStr">
@@ -15356,27 +15376,27 @@
       </c>
       <c r="B196" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C196" s="41" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D196" s="41" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E196" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F196" s="39" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G196" s="39" t="inlineStr">
@@ -15399,22 +15419,22 @@
       </c>
       <c r="C197" s="41" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D197" s="41" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E197" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F197" s="39" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G197" s="39" t="inlineStr">
@@ -15437,43 +15457,195 @@
       </c>
       <c r="C198" s="41" t="inlineStr">
         <is>
+          <t>交付要綱の配点表（満点）</t>
+        </is>
+      </c>
+      <c r="D198" s="41" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+        </is>
+      </c>
+      <c r="E198" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F198" s="39" t="inlineStr">
+        <is>
+          <t>doc20§2</t>
+        </is>
+      </c>
+      <c r="G198" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H198" s="41" t="inlineStr"/>
+    </row>
+    <row r="199" ht="34" customHeight="1">
+      <c r="A199" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B199" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C199" s="41" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
+        </is>
+      </c>
+      <c r="D199" s="41" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+        </is>
+      </c>
+      <c r="E199" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-65</t>
+        </is>
+      </c>
+      <c r="F199" s="39" t="inlineStr">
+        <is>
+          <t>doc20§3-1</t>
+        </is>
+      </c>
+      <c r="G199" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H199" s="41" t="inlineStr"/>
+    </row>
+    <row r="200" ht="34" customHeight="1">
+      <c r="A200" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B200" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C200" s="41" t="inlineStr">
+        <is>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+        </is>
+      </c>
+      <c r="D200" s="41" t="inlineStr">
+        <is>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+        </is>
+      </c>
+      <c r="E200" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-58</t>
+        </is>
+      </c>
+      <c r="F200" s="39" t="inlineStr">
+        <is>
+          <t>doc09</t>
+        </is>
+      </c>
+      <c r="G200" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H200" s="41" t="inlineStr"/>
+    </row>
+    <row r="201" ht="34" customHeight="1">
+      <c r="A201" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B201" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C201" s="41" t="inlineStr">
+        <is>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+        </is>
+      </c>
+      <c r="D201" s="41" t="inlineStr">
+        <is>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+        </is>
+      </c>
+      <c r="E201" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-59</t>
+        </is>
+      </c>
+      <c r="F201" s="39" t="inlineStr">
+        <is>
+          <t>doc02§20-2</t>
+        </is>
+      </c>
+      <c r="G201" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H201" s="41" t="inlineStr"/>
+    </row>
+    <row r="202" ht="34" customHeight="1">
+      <c r="A202" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B202" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C202" s="41" t="inlineStr">
+        <is>
           <t>国の指針・様式の更新有無</t>
         </is>
       </c>
-      <c r="D198" s="41" t="inlineStr">
+      <c r="D202" s="41" t="inlineStr">
         <is>
           <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
-      <c r="E198" s="39" t="inlineStr">
+      <c r="E202" s="39" t="inlineStr">
         <is>
           <t>Ⅰ-11</t>
         </is>
       </c>
-      <c r="F198" s="39" t="inlineStr">
+      <c r="F202" s="39" t="inlineStr">
         <is>
           <t>doc04,doc05</t>
         </is>
       </c>
-      <c r="G198" s="39" t="inlineStr">
+      <c r="G202" s="39" t="inlineStr">
         <is>
           <t>解決済</t>
         </is>
       </c>
-      <c r="H198" s="41" t="inlineStr"/>
+      <c r="H202" s="41" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H173"/>
+  <autoFilter ref="A4:H177"/>
   <mergeCells count="3">
-    <mergeCell ref="A175:H175"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A179:H179"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20114,7 +20286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -21384,39 +21556,99 @@
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="34" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>村データ</t>
         </is>
       </c>
-      <c r="B45" s="33" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>調査対象者名簿（ニーズ調査882人）</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>★個人情報を含む。属性の集計値のみ保存し原本は複製しない</t>
+        </is>
+      </c>
+      <c r="D45" s="46" t="n">
+        <v>46293</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/43_調査対象者データの確認.md</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>村データ</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>調査対象者名簿（在宅介護実態調査118人・要介護度を含む）</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>★個人情報を含む。要介護1が49人・2が30人・3が18人・4が14人・5が7人</t>
+        </is>
+      </c>
+      <c r="D46" s="46" t="n">
+        <v>46293</v>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>docs/…/43_調査対象者データの確認.md</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="34" t="inlineStr">
+        <is>
+          <t>村データ</t>
+        </is>
+      </c>
+      <c r="B47" s="33" t="inlineStr">
         <is>
           <t>★要介護認定データ（調査票との関連付け用）</t>
         </is>
       </c>
-      <c r="C45" s="33" t="inlineStr">
+      <c r="C47" s="33" t="inlineStr">
         <is>
           <t>仕様書4Ⅰ(5)。調査回収後に必要</t>
         </is>
       </c>
-      <c r="D45" s="34" t="inlineStr">
+      <c r="D47" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E45" s="33" t="inlineStr">
+      <c r="E47" s="33" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F45" s="34" t="inlineStr">
+      <c r="F47" s="34" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F45"/>
+  <autoFilter ref="A4:F47"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS・進捗管理'!$A$4:$P$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'村への確認事項'!$A$4:$H$175</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'仕様書対照'!$A$4:$H$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'受領資料・データ管理'!$A$4:$F$47</definedName>
   </definedNames>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="P32" s="13" t="inlineStr">
         <is>
-          <t>★名簿の管理番号はニーズ調査が数字のみ、在宅介護実態調査が英字＋数字であることを確認した。調査票の印字見本はどちらも「1」で、形式が食い違っている（doc43§2-4）。回収後に名簿と回答を突き合わせられなくなるため、優先度Sの確認事項として起票した。</t>
+          <t>★名簿の管理番号はニーズ調査が数字のみ、在宅介護実態調査が英字＋数字であることを確認した。調査票の印字見本がどちらも「1」であったことから形式の食い違いを疑い優先度Sで起票したが、印字見本は見本であり実物には名簿の形式のまま管理番号が入ることを村にご確認いただき解決した（doc43§2-4）。管理番号が欠損した場合は氏名でも突合できる。集計プログラムでは管理番号を数値ではなく文字列として扱う（在宅の英字＋数字が壊れるため）。</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8339,27 +8339,27 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
         <is>
-          <t>★在宅調査票の管理番号の印字形式（N付きか数字のみか）</t>
+          <t>★ICFを用いたクロス分析の具体的な期待像（軸・アウトプットのイメージ）</t>
         </is>
       </c>
       <c r="D9" s="33" t="inlineStr">
         <is>
-          <t>★対象者リストはニーズが1〜882の数字、在宅がN1〜N118。調査票の印字見本はどちらも「1」。食い違うと回収後に名簿と回答を突き合わせられない。</t>
+          <t>★議事録の新規要件。「元気な高齢者」×「地域のニーズ」で共助・互助の必要性を示す分析。調査票の設計段階でクロス軸を確保しないと後から分析できない。9/3の第1稿に影響。</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-18,Ⅰ-20</t>
+          <t>Ⅰ-95</t>
         </is>
       </c>
       <c r="F9" s="34" t="inlineStr">
         <is>
-          <t>doc34§5-3</t>
+          <t>doc22 K-77</t>
         </is>
       </c>
       <c r="G9" s="34" t="inlineStr">
@@ -8377,27 +8377,27 @@
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C10" s="33" t="inlineStr">
         <is>
-          <t>★ICFを用いたクロス分析の具体的な期待像（軸・アウトプットのイメージ）</t>
+          <t>★ニーズ調査 問4(15)(16)（社会的役割）を削除するかどうか</t>
         </is>
       </c>
       <c r="D10" s="33" t="inlineStr">
         <is>
-          <t>★議事録の新規要件。「元気な高齢者」×「地域のニーズ」で共助・互助の必要性を示す分析。調査票の設計段階でクロス軸を確保しないと後から分析できない。9/3の第1稿に影響。</t>
+          <t>★★印刷前に要決定。国の手引きは問4(13)〜(16)の4項目すべてが「いいえ」で「社会的役割の低下」と判定する。(16)は削除済み、(15)は0909校正で削除の指示。2項目が欠けるとR09が算出できず、見える化への登録も全国・県との比較も不可。R99が10領域→9領域に減るため第9期調査との比較も成立しない。左余白の「見える化関係」の書き込みは(10)〜(14)を指すとみられるが(15)(16)も登録対象である。</t>
         </is>
       </c>
       <c r="E10" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-95</t>
+          <t>Ⅰ-15,Ⅰ-102</t>
         </is>
       </c>
       <c r="F10" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-77</t>
+          <t>doc34§1-1</t>
         </is>
       </c>
       <c r="G10" s="34" t="inlineStr">
@@ -8420,22 +8420,22 @@
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
-          <t>★ニーズ調査 問4(15)(16)（社会的役割）を削除するかどうか</t>
+          <t>★基金取崩額の確認（第9期計画の24,000,000円と議事録の「800万円程度」の関係。年額か期間合計か）</t>
         </is>
       </c>
       <c r="D11" s="33" t="inlineStr">
         <is>
-          <t>★★印刷前に要決定。国の手引きは問4(13)〜(16)の4項目すべてが「いいえ」で「社会的役割の低下」と判定する。(16)は削除済み、(15)は0909校正で削除の指示。2項目が欠けるとR09が算出できず、見える化への登録も全国・県との比較も不可。R99が10領域→9領域に減るため第9期調査との比較も成立しない。左余白の「見える化関係」の書き込みは(10)〜(14)を指すとみられるが(15)(16)も登録対象である。</t>
+          <t>★保険料試算の前提が3倍変わる。議事録で基金取崩を視野に入れる方針が示されたため、正確な残高と取崩実績の確認が必須。</t>
         </is>
       </c>
       <c r="E11" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-15,Ⅰ-102</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F11" s="34" t="inlineStr">
         <is>
-          <t>doc34§1-1</t>
+          <t>doc22 K-74</t>
         </is>
       </c>
       <c r="G11" s="34" t="inlineStr">
@@ -8458,22 +8458,22 @@
       </c>
       <c r="C12" s="33" t="inlineStr">
         <is>
-          <t>★基金取崩額の確認（第9期計画の24,000,000円と議事録の「800万円程度」の関係。年額か期間合計か）</t>
+          <t>★第9期計画の第1号被保険者数の推計に用いたデータ（国配布の住基ベース推計か別の推計か）</t>
         </is>
       </c>
       <c r="D12" s="33" t="inlineStr">
         <is>
-          <t>★保険料試算の前提が3倍変わる。議事録で基金取崩を視野に入れる方針が示されたため、正確な残高と取崩実績の確認が必須。</t>
+          <t>★国の事務連絡により、福島県では社人研の市町村別推計が公表されておらず第9期でも住基ベース推計が配布されていたことが判明。当方が示してきた「社人研推計をそのまま用いたため6.6%ずれた」という説明の前提が崩れた。第10期の説明の組み立てに影響する。</t>
         </is>
       </c>
       <c r="E12" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F12" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-74</t>
+          <t>doc28§1-1 K-105</t>
         </is>
       </c>
       <c r="G12" s="34" t="inlineStr">
@@ -8496,22 +8496,22 @@
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
-          <t>★第9期計画の第1号被保険者数の推計に用いたデータ（国配布の住基ベース推計か別の推計か）</t>
+          <t>★第10期の第1号被保険者数をA案（配布データ）とB案（令和8年実績にリベース）のどちらで置くか</t>
         </is>
       </c>
       <c r="D13" s="33" t="inlineStr">
         <is>
-          <t>★国の事務連絡により、福島県では社人研の市町村別推計が公表されておらず第9期でも住基ベース推計が配布されていたことが判明。当方が示してきた「社人研推計をそのまま用いたため6.6%ずれた」という説明の前提が崩れた。第10期の説明の組み立てに影響する。</t>
+          <t>★配布データの推計値（令和8年954人）が実績（1,012人）を58人・5.7%下回っており、そのまま用いると第9期と同じ過少推計になる。第10期を通じて約57人・6%の差が生じ、保険料の基準額に直接影響する。県通知は「参考として適切に設定願います」としており配布データの使用を義務づけていない。</t>
         </is>
       </c>
       <c r="E13" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-59,Ⅱ-64</t>
         </is>
       </c>
       <c r="F13" s="34" t="inlineStr">
         <is>
-          <t>doc28§1-1 K-105</t>
+          <t>doc28§1-4 K-106</t>
         </is>
       </c>
       <c r="G13" s="34" t="inlineStr">
@@ -8529,27 +8529,27 @@
       </c>
       <c r="B14" s="32" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
-          <t>★第10期の第1号被保険者数をA案（配布データ）とB案（令和8年実績にリベース）のどちらで置くか</t>
+          <t>★調査票の印刷前修正5件（p2投函期限の空欄・問7-1の「問6」・問10の記号K L・A票問15の分岐・URLとQRコード）</t>
         </is>
       </c>
       <c r="D14" s="33" t="inlineStr">
         <is>
-          <t>★配布データの推計値（令和8年954人）が実績（1,012人）を58人・5.7%下回っており、そのまま用いると第9期と同じ過少推計になる。第10期を通じて約57人・6%の差が生じ、保険料の基準額に直接影響する。県通知は「参考として適切に設定願います」としており配布データの使用を義務づけていない。</t>
+          <t>★いずれも0909校正版で残っている。問7-1の参照先の誤りは分析編の中核クロス（X-15）に、A票問15の分岐はB票の回答対象者の確定に関わる。</t>
         </is>
       </c>
       <c r="E14" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-59,Ⅱ-64</t>
+          <t>Ⅰ-15,Ⅰ-102</t>
         </is>
       </c>
       <c r="F14" s="34" t="inlineStr">
         <is>
-          <t>doc28§1-4 K-106</t>
+          <t>doc34§1</t>
         </is>
       </c>
       <c r="G14" s="34" t="inlineStr">
@@ -8567,27 +8567,27 @@
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>★調査票の印刷前修正5件（p2投函期限の空欄・問7-1の「問6」・問10の記号K L・A票問15の分岐・URLとQRコード）</t>
+          <t>在宅介護実態調査の手法（手法Ⅲか、手法Ⅳ〈新版 在宅生活改善調査〉を加えるか）</t>
         </is>
       </c>
       <c r="D15" s="33" t="inlineStr">
         <is>
-          <t>★いずれも0909校正版で残っている。問7-1の参照先の誤りは分析編の中核クロス（X-15）に、A票問15の分岐はB票の回答対象者の確定に関わる。</t>
+          <t>調査票の設計・印刷頁数・集計方法がすべて決まる。第10期の新設手法。</t>
         </is>
       </c>
       <c r="E15" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-15,Ⅰ-102</t>
+          <t>Ⅰ-07,Ⅰ-10</t>
         </is>
       </c>
       <c r="F15" s="34" t="inlineStr">
         <is>
-          <t>doc34§1</t>
+          <t>doc03/doc05</t>
         </is>
       </c>
       <c r="G15" s="34" t="inlineStr">
@@ -8605,32 +8605,32 @@
       </c>
       <c r="B16" s="32" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>★★管理番号の形式の食い違い（名簿は英字＋数字、調査票の印字見本は数字のみ）</t>
+          <t>ニーズ調査 約850人の抽出基準（要支援認定者を含むか／第9期との対比）</t>
         </is>
       </c>
       <c r="D16" s="33" t="inlineStr">
         <is>
-          <t>★2026/09/28に受領した対象者名簿により確定した。在宅介護実態調査の名簿（リスト66件・引き抜き52件）の管理番号は英字＋数字、ニーズ調査の名簿（805件・77件）は数字のみである。一方doc34§5-3のとおり調査票の印字見本はどちらも「1」であった。形式が食い違うと回収後に名簿と回答を突き合わせられず、認定データとの関連付けも成立しない。発送済みの場合は回収時の読み替えの規則を決める必要がある。</t>
+          <t>議事録で在宅150件は「要支援1・2および要介護1〜5の在宅生活者等」と決着。ニーズ約850件の抽出基準（要支援を含むか）は未決着のため残置。</t>
         </is>
       </c>
       <c r="E16" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-18,Ⅰ-20,Ⅰ-38</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
         <is>
-          <t>doc43§2-4</t>
+          <t>doc01-2,3／doc22</t>
         </is>
       </c>
       <c r="G16" s="34" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H16" s="33" t="inlineStr"/>
@@ -8648,22 +8648,22 @@
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の手法（手法Ⅲか、手法Ⅳ〈新版 在宅生活改善調査〉を加えるか）</t>
+          <t>オプション項目の採否（「問6 就労について」ほか）</t>
         </is>
       </c>
       <c r="D17" s="33" t="inlineStr">
         <is>
-          <t>調査票の設計・印刷頁数・集計方法がすべて決まる。第10期の新設手法。</t>
+          <t>令和7年8月版で就労はオプションと確定。採否で頁数が変わる。</t>
         </is>
       </c>
       <c r="E17" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-07,Ⅰ-10</t>
+          <t>Ⅰ-12</t>
         </is>
       </c>
       <c r="F17" s="34" t="inlineStr">
         <is>
-          <t>doc03/doc05</t>
+          <t>doc05</t>
         </is>
       </c>
       <c r="G17" s="34" t="inlineStr">
@@ -8686,27 +8686,27 @@
       </c>
       <c r="C18" s="33" t="inlineStr">
         <is>
-          <t>ニーズ調査 約850人の抽出基準（要支援認定者を含むか／第9期との対比）</t>
+          <t>村独自設問の採否（除雪・在宅医療・成年後見・歯科受診・服薬ほか）</t>
         </is>
       </c>
       <c r="D18" s="33" t="inlineStr">
         <is>
-          <t>議事録で在宅150件は「要支援1・2および要介護1〜5の在宅生活者等」と決着。ニーズ約850件の抽出基準（要支援を含むか）は未決着のため残置。</t>
+          <t>第9期との時系列比較を優先するか、新規論点を入れるかの判断。</t>
         </is>
       </c>
       <c r="E18" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-13</t>
         </is>
       </c>
       <c r="F18" s="34" t="inlineStr">
         <is>
-          <t>doc01-2,3／doc22</t>
+          <t>doc03</t>
         </is>
       </c>
       <c r="G18" s="34" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H18" s="33" t="inlineStr"/>
@@ -8724,22 +8724,22 @@
       </c>
       <c r="C19" s="33" t="inlineStr">
         <is>
-          <t>オプション項目の採否（「問6 就労について」ほか）</t>
+          <t>ウェブ回答フォームの仕様（回答期限・村HP掲載の有無・二次元コード印字位置）</t>
         </is>
       </c>
       <c r="D19" s="33" t="inlineStr">
         <is>
-          <t>令和7年8月版で就労はオプションと確定。採否で頁数が変わる。</t>
+          <t>入稿データ作成の前提。</t>
         </is>
       </c>
       <c r="E19" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-12</t>
+          <t>Ⅰ-16,Ⅰ-17</t>
         </is>
       </c>
       <c r="F19" s="34" t="inlineStr">
         <is>
-          <t>doc05</t>
+          <t>doc01-8</t>
         </is>
       </c>
       <c r="G19" s="34" t="inlineStr">
@@ -8762,27 +8762,27 @@
       </c>
       <c r="C20" s="33" t="inlineStr">
         <is>
-          <t>村独自設問の採否（除雪・在宅医療・成年後見・歯科受診・服薬ほか）</t>
+          <t>★発送日の確定（9/17前倒し／9/18のまま／9/24後ろ倒し）と回収期限</t>
         </is>
       </c>
       <c r="D20" s="33" t="inlineStr">
         <is>
-          <t>第9期との時系列比較を優先するか、新規論点を入れるかの判断。</t>
+          <t>★議事録は「9月18日頃」とするのみで、5連休の論点に触れていない。9/17（木）への前倒し可否と回収期限を9/3の第1稿提出時に併せて提起する。</t>
         </is>
       </c>
       <c r="E20" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-13</t>
+          <t>Ⅰ-29,Ⅰ-32</t>
         </is>
       </c>
       <c r="F20" s="34" t="inlineStr">
         <is>
-          <t>doc03</t>
+          <t>doc19 指-1／doc22 A-4</t>
         </is>
       </c>
       <c r="G20" s="34" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>再提起</t>
         </is>
       </c>
       <c r="H20" s="33" t="inlineStr"/>
@@ -8800,22 +8800,22 @@
       </c>
       <c r="C21" s="33" t="inlineStr">
         <is>
-          <t>ウェブ回答フォームの仕様（回答期限・村HP掲載の有無・二次元コード印字位置）</t>
+          <t>★ウェブ回答フォームにGoogleフォームを用いることの可否</t>
         </is>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
-          <t>入稿データ作成の前提。</t>
+          <t>★通信の暗号化とデータの保存先は別の論点。回答データが村外サーバに保存される。個人情報保護条例上の取扱いと、重複排除の実装・エクスポート後の元データ削除・公開期間管理の確認が必要。</t>
         </is>
       </c>
       <c r="E21" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-16,Ⅰ-17</t>
+          <t>Ⅰ-16,Ⅰ-18</t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr">
         <is>
-          <t>doc01-8</t>
+          <t>doc19 追-3</t>
         </is>
       </c>
       <c r="G21" s="34" t="inlineStr">
@@ -8838,27 +8838,27 @@
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
-          <t>★発送日の確定（9/17前倒し／9/18のまま／9/24後ろ倒し）と回収期限</t>
+          <t>調査票の印刷頁数の調整方針（仕様書はニーズ約12頁／在宅約8頁）</t>
         </is>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
-          <t>★議事録は「9月18日頃」とするのみで、5連休の論点に触れていない。9/17（木）への前倒し可否と回収期限を9/3の第1稿提出時に併せて提起する。</t>
+          <t>現在の調査票案は設問数が多く、レイアウト調整か設問の絞り込みが必要になる可能性。オプション項目の採否と一体。</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-29,Ⅰ-32</t>
+          <t>Ⅰ-20,Ⅰ-21</t>
         </is>
       </c>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>doc19 指-1／doc22 A-4</t>
+          <t>doc19 S-5</t>
         </is>
       </c>
       <c r="G22" s="34" t="inlineStr">
         <is>
-          <t>再提起</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H22" s="33" t="inlineStr"/>
@@ -8876,27 +8876,27 @@
       </c>
       <c r="C23" s="33" t="inlineStr">
         <is>
-          <t>★ウェブ回答フォームにGoogleフォームを用いることの可否</t>
+          <t>依頼状の差出人名義（村名義／村長名）</t>
         </is>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
-          <t>★通信の暗号化とデータの保存先は別の論点。回答データが村外サーバに保存される。個人情報保護条例上の取扱いと、重複排除の実装・エクスポート後の元データ削除・公開期間管理の確認が必要。</t>
+          <t>★第1稿は「北塩原村長　遠藤　和夫」と村長名で作成済み。名義の可否と、あわせて現職の村長名が正しいかの確認が必要（当方が保有する平成30年の資料では別の方が村長）。</t>
         </is>
       </c>
       <c r="E23" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-16,Ⅰ-18</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>doc19 追-3</t>
+          <t>doc19 追-4／doc23§5</t>
         </is>
       </c>
       <c r="G23" s="34" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H23" s="33" t="inlineStr"/>
@@ -8914,22 +8914,22 @@
       </c>
       <c r="C24" s="33" t="inlineStr">
         <is>
-          <t>調査票の印刷頁数の調整方針（仕様書はニーズ約12頁／在宅約8頁）</t>
+          <t>調査票の印刷部数（予備を何部見込むか）</t>
         </is>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
-          <t>現在の調査票案は設問数が多く、レイアウト調整か設問の絞り込みが必要になる可能性。オプション項目の採否と一体。</t>
+          <t>約1,000部＋予備。発送後の追加印刷は工程上困難。</t>
         </is>
       </c>
       <c r="E24" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-20,Ⅰ-21</t>
+          <t>Ⅰ-21,Ⅰ-22</t>
         </is>
       </c>
       <c r="F24" s="34" t="inlineStr">
         <is>
-          <t>doc19 S-5</t>
+          <t>doc19 追-5</t>
         </is>
       </c>
       <c r="G24" s="34" t="inlineStr">
@@ -8952,27 +8952,27 @@
       </c>
       <c r="C25" s="33" t="inlineStr">
         <is>
-          <t>依頼状の差出人名義（村名義／村長名）</t>
+          <t>在宅介護実態調査 問8・問9の基準月</t>
         </is>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
-          <t>★第1稿は「北塩原村長　遠藤　和夫」と村長名で作成済み。名義の可否と、あわせて現職の村長名が正しいかの確認が必要（当方が保有する平成30年の資料では別の方が村長）。</t>
+          <t>発送月の前月が通常。発送日の確定とセット。</t>
         </is>
       </c>
       <c r="E25" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F25" s="34" t="inlineStr">
         <is>
-          <t>doc19 追-4／doc23§5</t>
+          <t>doc19 追-2</t>
         </is>
       </c>
       <c r="G25" s="34" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H25" s="33" t="inlineStr"/>
@@ -8990,22 +8990,22 @@
       </c>
       <c r="C26" s="33" t="inlineStr">
         <is>
-          <t>調査票の印刷部数（予備を何部見込むか）</t>
+          <t>★ニーズ調査 問7(7)「この1か月間に会った友人・知人の人数」の採用可否</t>
         </is>
       </c>
       <c r="D26" s="33" t="inlineStr">
         <is>
-          <t>約1,000部＋予備。発送後の追加印刷は工程上困難。</t>
+          <t>★第1稿では不採用のうえ以降の番号を繰り上げているため、見える化への入力時に設問の対応が崩れる。採用すれば番号ずれが解消し、かつICF分析の「参加」の量的指標としてそのまま使える。</t>
         </is>
       </c>
       <c r="E26" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-21,Ⅰ-22</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>doc19 追-5</t>
+          <t>doc23§1-2</t>
         </is>
       </c>
       <c r="G26" s="34" t="inlineStr">
@@ -9028,22 +9028,22 @@
       </c>
       <c r="C27" s="33" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 問8・問9の基準月</t>
+          <t>★ニーズ調査 村独自設問14問の採否と頁数（問3(10)の削除・問7(9)の簡素化）</t>
         </is>
       </c>
       <c r="D27" s="33" t="inlineStr">
         <is>
-          <t>発送月の前月が通常。発送日の確定とセット。</t>
+          <t>★標準約66問＋村独自14問＝約79問。仕様書の目安A4約12頁を超える見込み。削除を提案するのは問3(10)「1日に何回食事をとりますか」の1問のみ（低栄養は問3(1)(7)(8)で把握可能）。他13問は施策・交付金の指標と結びついており残すべき。</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-12,Ⅰ-13</t>
         </is>
       </c>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>doc19 追-2</t>
+          <t>doc23§4</t>
         </is>
       </c>
       <c r="G27" s="34" t="inlineStr">
@@ -9066,22 +9066,22 @@
       </c>
       <c r="C28" s="33" t="inlineStr">
         <is>
-          <t>★ニーズ調査 問7(7)「この1か月間に会った友人・知人の人数」の採用可否</t>
+          <t>★現職の村長名・所管課・役場の住所の確認</t>
         </is>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
-          <t>★第1稿では不採用のうえ以降の番号を繰り上げているため、見える化への入力時に設問の対応が崩れる。採用すれば番号ずれが解消し、かつICF分析の「参加」の量的指標としてそのまま使える。</t>
+          <t>★第1稿の依頼状に「北塩原村長 遠藤 和夫」「保健福祉課 福祉係」「大字北山字姥ヶ作3151番地」と記載。当方では現職の村長名を確認できない。所管課は住民課との別が未確認のまま（doc01 確認事項1）。</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>doc23§1-2</t>
+          <t>doc23§5</t>
         </is>
       </c>
       <c r="G28" s="34" t="inlineStr">
@@ -9104,22 +9104,22 @@
       </c>
       <c r="C29" s="33" t="inlineStr">
         <is>
-          <t>★ニーズ調査 村独自設問14問の採否と頁数（問3(10)の削除・問7(9)の簡素化）</t>
+          <t>★【必須】在宅A票 訪問診療の設問を問13に直す（問12が重複し問13が欠番）</t>
         </is>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
-          <t>★標準約66問＋村独自14問＝約79問。仕様書の目安A4約12頁を超える見込み。削除を提案するのは問3(10)「1日に何回食事をとりますか」の1問のみ（低栄養は問3(1)(7)(8)で把握可能）。他13問は施策・交付金の指標と結びついており残すべき。</t>
+          <t>★第2稿で訪問診療が復活したが番号が問12となり、今後必要と感じる支援（問12）と重複している。回答者が混乱し集計時に設問を特定できない。9/9の校了までに必ず修正。</t>
         </is>
       </c>
       <c r="E29" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-12,Ⅰ-13</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>doc23§4</t>
+          <t>doc27§3-1</t>
         </is>
       </c>
       <c r="G29" s="34" t="inlineStr">
@@ -9142,22 +9142,22 @@
       </c>
       <c r="C30" s="33" t="inlineStr">
         <is>
-          <t>★現職の村長名・所管課・役場の住所の確認</t>
+          <t>★【必須】在宅A票 問9の基準月を「令和8年8月」に修正</t>
         </is>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
-          <t>★第1稿の依頼状に「北塩原村長 遠藤 和夫」「保健福祉課 福祉係」「大字北山字姥ヶ作3151番地」と記載。当方では現職の村長名を確認できない。所管課は住民課との別が未確認のまま（doc01 確認事項1）。</t>
+          <t>★問8は修正されたが問9が「令和●年●月」のまま。</t>
         </is>
       </c>
       <c r="E30" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>doc23§5</t>
+          <t>doc27§3-2</t>
         </is>
       </c>
       <c r="G30" s="34" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="C31" s="33" t="inlineStr">
         <is>
-          <t>★【必須】在宅A票 訪問診療の設問を問13に直す（問12が重複し問13が欠番）</t>
+          <t>★【必須】ニーズ 問1(2)① 選択肢14・15を「14．その他／15．不明」に修正</t>
         </is>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
-          <t>★第2稿で訪問診療が復活したが番号が問12となり、今後必要と感じる支援（問12）と重複している。回答者が混乱し集計時に設問を特定できない。9/9の校了までに必ず修正。</t>
+          <t>★選択肢の順序の修正7か所のうち、この1か所のみ修正漏れ。標準は13．高齢による衰弱／14．その他（　）／15．不明。</t>
         </is>
       </c>
       <c r="E31" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F31" s="34" t="inlineStr">
         <is>
-          <t>doc27§3-1</t>
+          <t>doc27§2-1</t>
         </is>
       </c>
       <c r="G31" s="34" t="inlineStr">
@@ -9206,34 +9206,34 @@
       <c r="H31" s="33" t="inlineStr"/>
     </row>
     <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="31" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A32" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="C32" s="33" t="inlineStr">
         <is>
-          <t>★【必須】在宅A票 問9の基準月を「令和8年8月」に修正</t>
+          <t>★第2回策定委員会の開催日（11月のいつか）</t>
         </is>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
-          <t>★問8は修正されたが問9が「令和●年●月」のまま。</t>
+          <t>★資料の事前送付の期限が決まる。素案約90頁を当日配付では読めないため事前送付が前提。</t>
         </is>
       </c>
       <c r="E32" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F32" s="34" t="inlineStr">
         <is>
-          <t>doc27§3-2</t>
+          <t>doc26§10 K-95</t>
         </is>
       </c>
       <c r="G32" s="34" t="inlineStr">
@@ -9244,34 +9244,34 @@
       <c r="H32" s="33" t="inlineStr"/>
     </row>
     <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="A33" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B33" s="32" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C33" s="33" t="inlineStr">
         <is>
-          <t>★【必須】ニーズ 問1(2)① 選択肢14・15を「14．その他／15．不明」に修正</t>
+          <t>通いの場の参加者281人は実人数か延べ人数か（基準値の置き方）</t>
         </is>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
-          <t>★選択肢の順序の修正7か所のうち、この1か所のみ修正漏れ。標準は13．高齢による衰弱／14．その他（　）／15．不明。</t>
+          <t>★9/15：参加率の分母を検算し、見える化F1・F4系の定義が「参加者実人数÷65歳以上人口」であることを確認した（H30は306÷961＝31.8%で公表値と一致）。令和6年度は281÷1,009＝27.8%（週1回以上は123÷1,009＝12.2%）となり、素案の12.2%・5.3%を訂正した。一方、第9期アンケートの自己申告による参加率11.2%とは16.6ポイント開く。281人が複数の通いの場への参加を重複計上しているのであれば実人数はこれより少ない。第10期の活動指標の基準値をどちらに置くかは把握方法の確認が前提。</t>
         </is>
       </c>
       <c r="E33" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F33" s="34" t="inlineStr">
         <is>
-          <t>doc27§2-1</t>
+          <t>doc35§2</t>
         </is>
       </c>
       <c r="G33" s="34" t="inlineStr">
@@ -9289,27 +9289,27 @@
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>スケジュール</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C34" s="33" t="inlineStr">
         <is>
-          <t>★第2回策定委員会の開催日（11月のいつか）</t>
+          <t>★介護給付適正化の主要3事業のうち「要介護認定の適正化」の実施状況（令和8年度に0点となった原因）</t>
         </is>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
-          <t>★資料の事前送付の期限が決まる。素案約90頁を当日配付では読めないため事前送付が前提。</t>
+          <t>★主要3事業の全実施を問う指標（6点・全国96.9%が取得・県内55位／59）が0点である。適正化方策の策定は4項目すべて満点、ケアプラン点検と医療情報との突合は活動指標も満点であることから、残る「要介護認定の適正化」が実施されていない可能性が高い。取組が後退したのか、国への該当状況調査票の記載によるものかをご教示いただきたい。</t>
         </is>
       </c>
       <c r="E34" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅱ-109</t>
         </is>
       </c>
       <c r="F34" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-95</t>
+          <t>doc42§3</t>
         </is>
       </c>
       <c r="G34" s="34" t="inlineStr">
@@ -9332,22 +9332,22 @@
       </c>
       <c r="C35" s="33" t="inlineStr">
         <is>
-          <t>通いの場の参加者281人は実人数か延べ人数か（基準値の置き方）</t>
+          <t>国の介護保険事業計画作成支援ツール（将来推計総括表）の出力一式</t>
         </is>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
-          <t>★9/15：参加率の分母を検算し、見える化F1・F4系の定義が「参加者実人数÷65歳以上人口」であることを確認した（H30は306÷961＝31.8%で公表値と一致）。令和6年度は281÷1,009＝27.8%（週1回以上は123÷1,009＝12.2%）となり、素案の12.2%・5.3%を訂正した。一方、第9期アンケートの自己申告による参加率11.2%とは16.6ポイント開く。281人が複数の通いの場への参加を重複計上しているのであれば実人数はこれより少ない。第10期の活動指標の基準値をどちらに置くかは把握方法の確認が前提。</t>
+          <t>★★最優先。他案件（川崎町・金ケ崎町・大雪）はいずれも保険者が操作したツールの出力を受領し検証する立場にあるが、本村は見える化から独自算定しており国の様式との検算ができていない。他案件では令和8年度が実績でなく推計値、主要項目が未入力のまま保険料だけ数値が入る等の事例が実際に見つかっている。</t>
         </is>
       </c>
       <c r="E35" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-55,Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F35" s="34" t="inlineStr">
         <is>
-          <t>doc35§2</t>
+          <t>doc33§5-1</t>
         </is>
       </c>
       <c r="G35" s="34" t="inlineStr">
@@ -9370,22 +9370,22 @@
       </c>
       <c r="C36" s="33" t="inlineStr">
         <is>
-          <t>★介護給付適正化の主要3事業のうち「要介護認定の適正化」の実施状況（令和8年度に0点となった原因）</t>
+          <t>第9期計画の本文（サービス別見込量の表を含む全体）</t>
         </is>
       </c>
       <c r="D36" s="33" t="inlineStr">
         <is>
-          <t>★主要3事業の全実施を問う指標（6点・全国96.9%が取得・県内55位／59）が0点である。適正化方策の策定は4項目すべて満点、ケアプラン点検と医療情報との突合は活動指標も満点であることから、残る「要介護認定の適正化」が実施されていない可能性が高い。取組が後退したのか、国への該当状況調査票の記載によるものかをご教示いただきたい。</t>
+          <t>★★用途が2つある。①対計画比（サービス別の計画値と実績の対比）。他案件では総額が計画どおりでも内訳が11.5〜967.4％まで開くことが確認されており、本村は受給率を3か年平均で固定しているため偏りを持ち越す。②老人福祉事業の量の目標の記載位置の確認（doc32§4-1）。保有しているのは概要版のみでサービス別見込量がない。</t>
         </is>
       </c>
       <c r="E36" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-109</t>
+          <t>Ⅱ-53,Ⅱ-55</t>
         </is>
       </c>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>doc42§3</t>
+          <t>doc33§5-2</t>
         </is>
       </c>
       <c r="G36" s="34" t="inlineStr">
@@ -9408,22 +9408,22 @@
       </c>
       <c r="C37" s="33" t="inlineStr">
         <is>
-          <t>国の介護保険事業計画作成支援ツール（将来推計総括表）の出力一式</t>
+          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D37" s="33" t="inlineStr">
         <is>
-          <t>★★最優先。他案件（川崎町・金ケ崎町・大雪）はいずれも保険者が操作したツールの出力を受領し検証する立場にあるが、本村は見える化から独自算定しており国の様式との検算ができていない。他案件では令和8年度が実績でなく推計値、主要項目が未入力のまま保険料だけ数値が入る等の事例が実際に見つかっている。</t>
+          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
         </is>
       </c>
       <c r="E37" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F37" s="34" t="inlineStr">
         <is>
-          <t>doc33§5-1</t>
+          <t>doc20§8-2 K-61</t>
         </is>
       </c>
       <c r="G37" s="34" t="inlineStr">
@@ -9446,22 +9446,22 @@
       </c>
       <c r="C38" s="33" t="inlineStr">
         <is>
-          <t>第9期計画の本文（サービス別見込量の表を含む全体）</t>
+          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D38" s="33" t="inlineStr">
         <is>
-          <t>★★用途が2つある。①対計画比（サービス別の計画値と実績の対比）。他案件では総額が計画どおりでも内訳が11.5〜967.4％まで開くことが確認されており、本村は受給率を3か年平均で固定しているため偏りを持ち越す。②老人福祉事業の量の目標の記載位置の確認（doc32§4-1）。保有しているのは概要版のみでサービス別見込量がない。</t>
+          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
         </is>
       </c>
       <c r="E38" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-55</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>doc33§5-2</t>
+          <t>doc20§8-2 K-61b</t>
         </is>
       </c>
       <c r="G38" s="34" t="inlineStr">
@@ -9484,22 +9484,22 @@
       </c>
       <c r="C39" s="33" t="inlineStr">
         <is>
-          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
+          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
         </is>
       </c>
       <c r="D39" s="33" t="inlineStr">
         <is>
-          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
+          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
         </is>
       </c>
       <c r="E39" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61</t>
+          <t>doc20§6-2 K-62</t>
         </is>
       </c>
       <c r="G39" s="34" t="inlineStr">
@@ -9522,22 +9522,22 @@
       </c>
       <c r="C40" s="33" t="inlineStr">
         <is>
-          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
+          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
         </is>
       </c>
       <c r="D40" s="33" t="inlineStr">
         <is>
-          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
+          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
         </is>
       </c>
       <c r="E40" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61b</t>
+          <t>doc20§6-2 K-63</t>
         </is>
       </c>
       <c r="G40" s="34" t="inlineStr">
@@ -9560,22 +9560,22 @@
       </c>
       <c r="C41" s="33" t="inlineStr">
         <is>
-          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
+          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
         </is>
       </c>
       <c r="D41" s="33" t="inlineStr">
         <is>
-          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
+          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
         </is>
       </c>
       <c r="E41" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-62</t>
+          <t>doc20§6-2 K-64</t>
         </is>
       </c>
       <c r="G41" s="34" t="inlineStr">
@@ -9598,22 +9598,22 @@
       </c>
       <c r="C42" s="33" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
+          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
         </is>
       </c>
       <c r="D42" s="33" t="inlineStr">
         <is>
-          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
+          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
         </is>
       </c>
       <c r="E42" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-63</t>
+          <t>doc22 K-75</t>
         </is>
       </c>
       <c r="G42" s="34" t="inlineStr">
@@ -9636,22 +9636,22 @@
       </c>
       <c r="C43" s="33" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
+          <t>★ニーズ調査の対象者882人に対応する要介護認定データ（認定の有無・要介護度）</t>
         </is>
       </c>
       <c r="D43" s="33" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
+          <t>★2026/09/28に受領した名簿のうち、要介護度の列があるのは在宅介護実態調査の対象者118人分のみで、ニーズ調査の対象者882人分にはない。資料3の3-3（元気な軽度者）・3-4（生活機能からみた4つの層）・3-6（担い手の可能性）は、ニーズ調査の回答者一人ひとりの認定状況を必要とするため、このままでは作成できない。3-6は第10期に共助・互助の仕組みをどの規模で構想できるかを示す表であり、合意1・2の根拠でもある。</t>
         </is>
       </c>
       <c r="E43" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅰ-37,Ⅰ-38</t>
         </is>
       </c>
       <c r="F43" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-64</t>
+          <t>doc43§1</t>
         </is>
       </c>
       <c r="G43" s="34" t="inlineStr">
@@ -9674,22 +9674,22 @@
       </c>
       <c r="C44" s="33" t="inlineStr">
         <is>
-          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
+          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
         </is>
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
+          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
         </is>
       </c>
       <c r="E44" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅰ-37</t>
         </is>
       </c>
       <c r="F44" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-75</t>
+          <t>doc24§12 K-87</t>
         </is>
       </c>
       <c r="G44" s="34" t="inlineStr">
@@ -9712,22 +9712,22 @@
       </c>
       <c r="C45" s="33" t="inlineStr">
         <is>
-          <t>★ニーズ調査の対象者882人に対応する要介護認定データ（認定の有無・要介護度）</t>
+          <t>★会津権利擁護・成年後見センターへの相談が1年で件数−43%・時間−55%と減少した要因</t>
         </is>
       </c>
       <c r="D45" s="33" t="inlineStr">
         <is>
-          <t>★2026/09/28に受領した名簿のうち、要介護度の列があるのは在宅介護実態調査の対象者118人分のみで、ニーズ調査の対象者882人分にはない。資料3の3-3（元気な軽度者）・3-4（生活機能からみた4つの層）・3-6（担い手の可能性）は、ニーズ調査の回答者一人ひとりの認定状況を必要とするため、このままでは作成できない。3-6は第10期に共助・互助の仕組みをどの規模で構想できるかを示す表であり、合意1・2の根拠でもある。</t>
+          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
         </is>
       </c>
       <c r="E45" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-37,Ⅰ-38</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F45" s="34" t="inlineStr">
         <is>
-          <t>doc43§1</t>
+          <t>doc28§3-3 K-108</t>
         </is>
       </c>
       <c r="G45" s="34" t="inlineStr">
@@ -9750,22 +9750,22 @@
       </c>
       <c r="C46" s="33" t="inlineStr">
         <is>
-          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）</t>
+          <t>養護老人ホーム措置・軽費老人ホーム・老人クラブの実績は見える化に系列が一切ない</t>
         </is>
       </c>
       <c r="D46" s="33" t="inlineStr">
         <is>
-          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。</t>
+          <t>★老人福祉法第20条の8第2項が計画への記載を義務づける「老人福祉事業の量の目標」（素案4-6）の基礎。見える化に該当する系列がないため、村資料の受領が必須。代替手段はない。</t>
         </is>
       </c>
       <c r="E46" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-37</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>doc24§12 K-87</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G46" s="34" t="inlineStr">
@@ -9788,22 +9788,22 @@
       </c>
       <c r="C47" s="33" t="inlineStr">
         <is>
-          <t>★会津権利擁護・成年後見センターへの相談が1年で件数−43%・時間−55%と減少した要因</t>
+          <t>国の推計ワークシートが求める在宅サービス利用率の分母</t>
         </is>
       </c>
       <c r="D47" s="33" t="inlineStr">
         <is>
-          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
+          <t>★★他案件（大雪）の点検で「見込量の利用率の分母は認定者数であって第1号被保険者数ではない」ことが指摘された。本村の見える化のサービス利用率の分母は要介護度別認定者数であることを実データで確認済み（51件中21件が±0.6pt以内で一致、第1号被保険者数では0件）。ただし国の将来推計が在宅の分母を「認定者数−施設・居住系利用者数」とする場合、本村の率は要介護1で58.8%→86.1%、要介護4で26.8%→70.1%に変わり、要介護2では107.7%と100%を超える。分母の取り違えは見込量を数割動かす。</t>
         </is>
       </c>
       <c r="E47" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F47" s="34" t="inlineStr">
         <is>
-          <t>doc28§3-3 K-108</t>
+          <t>doc37§3,doc18 5-4</t>
         </is>
       </c>
       <c r="G47" s="34" t="inlineStr">
@@ -9826,22 +9826,22 @@
       </c>
       <c r="C48" s="33" t="inlineStr">
         <is>
-          <t>養護老人ホーム措置・軽費老人ホーム・老人クラブの実績は見える化に系列が一切ない</t>
+          <t>認知症対応型共同生活介護（村内27人分）の待機者数と、村外のグループホームを利用している方の人数</t>
         </is>
       </c>
       <c r="D48" s="33" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が計画への記載を義務づける「老人福祉事業の量の目標」（素案4-6）の基礎。見える化に該当する系列がないため、村資料の受領が必須。代替手段はない。</t>
+          <t>★施策3-2・5-4(7)の必要利用定員総数の判断に必須。認知症高齢者（自立度Ⅱ以上）は2年間で132人→161人と22.0%増えた一方、定員は平成28年度以降27人のまま。稼働率93%。増床の要否は待機と村外利用の実態がなければ判断できない。</t>
         </is>
       </c>
       <c r="E48" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>doc38§D</t>
+          <t>doc36§3,doc18 5-4(7)</t>
         </is>
       </c>
       <c r="G48" s="34" t="inlineStr">
@@ -9864,22 +9864,22 @@
       </c>
       <c r="C49" s="33" t="inlineStr">
         <is>
-          <t>国の推計ワークシートが求める在宅サービス利用率の分母</t>
+          <t>認知症関連事業の実績（認知症カフェの箇所数、認知症初期集中支援推進事業の対象者数、認知症地域支援推進員の活動実績）</t>
         </is>
       </c>
       <c r="D49" s="33" t="inlineStr">
         <is>
-          <t>★★他案件（大雪）の点検で「見込量の利用率の分母は認定者数であって第1号被保険者数ではない」ことが指摘された。本村の見える化のサービス利用率の分母は要介護度別認定者数であることを実データで確認済み（51件中21件が±0.6pt以内で一致、第1号被保険者数では0件）。ただし国の将来推計が在宅の分母を「認定者数−施設・居住系利用者数」とする場合、本村の率は要介護1で58.8%→86.1%、要介護4で26.8%→70.1%に変わり、要介護2では107.7%と100%を超える。分母の取り違えは見込量を数割動かす。</t>
+          <t>★素案5-5(1)の地域支援事業の量に認知症総合支援事業の行を新設したが、いずれも実績が未受領。国の様式では認知症総合支援事業の量を定めることが求められる。</t>
         </is>
       </c>
       <c r="E49" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-53,Ⅱ-68</t>
         </is>
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>doc37§3,doc18 5-4</t>
+          <t>doc36§4,doc18 5-5(1)</t>
         </is>
       </c>
       <c r="G49" s="34" t="inlineStr">
@@ -9902,22 +9902,22 @@
       </c>
       <c r="C50" s="33" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護（村内27人分）の待機者数と、村外のグループホームを利用している方の人数</t>
+          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
         </is>
       </c>
       <c r="D50" s="33" t="inlineStr">
         <is>
-          <t>★施策3-2・5-4(7)の必要利用定員総数の判断に必須。認知症高齢者（自立度Ⅱ以上）は2年間で132人→161人と22.0%増えた一方、定員は平成28年度以降27人のまま。稼働率93%。増床の要否は待機と村外利用の実態がなければ判断できない。</t>
+          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
         </is>
       </c>
       <c r="E50" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 5-4(7)</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G50" s="34" t="inlineStr">
@@ -9940,22 +9940,22 @@
       </c>
       <c r="C51" s="33" t="inlineStr">
         <is>
-          <t>認知症関連事業の実績（認知症カフェの箇所数、認知症初期集中支援推進事業の対象者数、認知症地域支援推進員の活動実績）</t>
+          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
         </is>
       </c>
       <c r="D51" s="33" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の地域支援事業の量に認知症総合支援事業の行を新設したが、いずれも実績が未受領。国の様式では認知症総合支援事業の量を定めることが求められる。</t>
+          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
         </is>
       </c>
       <c r="E51" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-68</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>doc36§4,doc18 5-5(1)</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G51" s="34" t="inlineStr">
@@ -9973,27 +9973,27 @@
       </c>
       <c r="B52" s="32" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C52" s="33" t="inlineStr">
         <is>
-          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
+          <t>契約締結日・契約書の取り交わし状況</t>
         </is>
       </c>
       <c r="D52" s="33" t="inlineStr">
         <is>
-          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
+          <t>業務開始日の確定。</t>
         </is>
       </c>
       <c r="E52" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>０-02</t>
         </is>
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G52" s="34" t="inlineStr">
@@ -10011,27 +10011,27 @@
       </c>
       <c r="B53" s="32" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C53" s="33" t="inlineStr">
         <is>
-          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D53" s="33" t="inlineStr">
         <is>
-          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
         </is>
       </c>
       <c r="E53" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc19 追-12</t>
         </is>
       </c>
       <c r="G53" s="34" t="inlineStr">
@@ -10054,22 +10054,22 @@
       </c>
       <c r="C54" s="33" t="inlineStr">
         <is>
-          <t>契約締結日・契約書の取り交わし状況</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D54" s="33" t="inlineStr">
         <is>
-          <t>業務開始日の確定。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E54" s="34" t="inlineStr">
         <is>
-          <t>０-02</t>
+          <t>Ⅰ-94</t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G54" s="34" t="inlineStr">
@@ -10092,22 +10092,22 @@
       </c>
       <c r="C55" s="33" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D55" s="33" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。★9/25：案Bの採用により自由記述の全文を電子媒体に収録することとなったため、匿名化の対象は紙の「分類と主要意見」（資料2）と電子媒体の全文の双方に及ぶ。電子媒体に回しても匿名化は免除されない。</t>
         </is>
       </c>
       <c r="E55" s="34" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>Ⅰ-44</t>
         </is>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>doc19 追-12</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G55" s="34" t="inlineStr">
@@ -10130,22 +10130,22 @@
       </c>
       <c r="C56" s="33" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
         </is>
       </c>
       <c r="D56" s="33" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
         </is>
       </c>
       <c r="E56" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-94</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>doc26§10 K-97</t>
         </is>
       </c>
       <c r="G56" s="34" t="inlineStr">
@@ -10168,27 +10168,27 @@
       </c>
       <c r="C57" s="33" t="inlineStr">
         <is>
-          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
+          <t>★見える化の「将来推計」メニューで在宅サービス利用率の分母を確認する</t>
         </is>
       </c>
       <c r="D57" s="33" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。★9/25：案Bの採用により自由記述の全文を電子媒体に収録することとなったため、匿名化の対象は紙の「分類と主要意見」（資料2）と電子媒体の全文の双方に及ぶ。電子媒体に回しても匿名化は免除されない。</t>
+          <t>★★見込量が数割変わる論点（要介護1で58.8%→86.1%、要介護2で107.7%と100%超）。村への依頼ではなく、当方が見える化にログインして推計方法の設定画面を開けば確かめられる見込み。他案件（大雪）は「画面の設定順からの推定［要確認］」としている。最優先で確認する。</t>
         </is>
       </c>
       <c r="E57" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-44</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>doc24§12 K-89</t>
+          <t>doc38§C-1</t>
         </is>
       </c>
       <c r="G57" s="34" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>社内対応</t>
         </is>
       </c>
       <c r="H57" s="33" t="inlineStr"/>
@@ -10201,27 +10201,27 @@
       </c>
       <c r="B58" s="32" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C58" s="33" t="inlineStr">
         <is>
-          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
+          <t>在宅介護実態調査の集計設計（要介護度3区分×介護者勤務形態3区分のセル数）</t>
         </is>
       </c>
       <c r="D58" s="33" t="inlineStr">
         <is>
-          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
+          <t>★対象が118人（仕様書の想定150人）であることは村の了解を得て決着。残るのは集計設計の判断で、回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかを当方で決める。</t>
         </is>
       </c>
       <c r="E58" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅰ-45</t>
         </is>
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-97</t>
+          <t>doc34§5-2</t>
         </is>
       </c>
       <c r="G58" s="34" t="inlineStr">
@@ -10239,32 +10239,32 @@
       </c>
       <c r="B59" s="32" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C59" s="33" t="inlineStr">
         <is>
-          <t>★見える化の「将来推計」メニューで在宅サービス利用率の分母を確認する</t>
+          <t>ICF分析は標準設問のみで完結することの確認</t>
         </is>
       </c>
       <c r="D59" s="33" t="inlineStr">
         <is>
-          <t>★★見込量が数割変わる論点（要介護1で58.8%→86.1%、要介護2で107.7%と100%超）。村への依頼ではなく、当方が見える化にログインして推計方法の設定画面を開けば確かめられる見込み。他案件（大雪）は「画面の設定順からの推定［要確認］」としている。最優先で確認する。</t>
+          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
         </is>
       </c>
       <c r="E59" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅰ-95</t>
         </is>
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
-          <t>doc38§C-1</t>
+          <t>doc23§3-4</t>
         </is>
       </c>
       <c r="G59" s="34" t="inlineStr">
         <is>
-          <t>社内対応</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H59" s="33" t="inlineStr"/>
@@ -10282,22 +10282,22 @@
       </c>
       <c r="C60" s="33" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の集計設計（要介護度3区分×介護者勤務形態3区分のセル数）</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D60" s="33" t="inlineStr">
         <is>
-          <t>★対象が118人（仕様書の想定150人）であることは村の了解を得て決着。残るのは集計設計の判断で、回収は70〜80件程度の見込み。要介護度3区分×介護者勤務形態3区分のクロス（X-16・X-17）は9セルで1セル平均8件前後になる。要介護度を2区分に束ねるか、比率を付さず実数で示すかを当方で決める。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E60" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-45</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>doc34§5-2</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G60" s="34" t="inlineStr">
@@ -10320,22 +10320,22 @@
       </c>
       <c r="C61" s="33" t="inlineStr">
         <is>
-          <t>ICF分析は標準設問のみで完結することの確認</t>
+          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
         </is>
       </c>
       <c r="D61" s="33" t="inlineStr">
         <is>
-          <t>★ICFの5領域（健康状態・心身機能・活動・参加・環境因子）はすべて標準の必須＋オプション項目で埋まる。分析のための独自設問の追加は不要。推奨対応は問7(7)の採用の1件のみ。</t>
+          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
         </is>
       </c>
       <c r="E61" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-95</t>
+          <t>Ⅰ-46</t>
         </is>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
-          <t>doc23§3-4</t>
+          <t>doc25§4-2 K-91</t>
         </is>
       </c>
       <c r="G61" s="34" t="inlineStr">
@@ -10353,27 +10353,27 @@
       </c>
       <c r="B62" s="32" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C62" s="33" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>難聴高齢者の早期発見・早期介入の取組の実施可否（普及啓発・早期発見）</t>
         </is>
       </c>
       <c r="D62" s="33" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>★合わせて10点（全国68.9%・48.8%、県内48位・46位）。★9/25：素案の施策4-4に3つの取組（広報・健診案内・通いの場での周知／健診と通いの場での聞こえの確認／耳鼻咽喉科への受診勧奨と受診状況の把握）として反映し、指標表を普及啓発5点・早期発見5点・受診状況10点に分けた。実施の可否と現在の取組状況をご教示いただきたい。受診状況の把握と受診率50%以上は全国でも14.6%・4.8%と取得が少ないため第10期中の検討事項としている。</t>
         </is>
       </c>
       <c r="E62" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-67,Ⅱ-65</t>
         </is>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc42§3</t>
         </is>
       </c>
       <c r="G62" s="34" t="inlineStr">
@@ -10391,27 +10391,27 @@
       </c>
       <c r="B63" s="32" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C63" s="33" t="inlineStr">
         <is>
-          <t>★リスク判定10種の該当基準（見える化システムの算出方法との突合）</t>
+          <t>成年後見制度利用支援事業の要綱の対象範囲（市町村長申立・生活保護受給者への限定を外す改正の可否）</t>
         </is>
       </c>
       <c r="D63" s="33" t="inlineStr">
         <is>
-          <t>★手引きに該当基準の明記があるのはBMI 18.5以下のみ。他9種は基本チェックリストに準じた案を置いているが、独自基準では全国・県と比較できない。手引きは算出方法が将来更新され得るとも記載しており、第9期の基準の流用も不可。</t>
+          <t>★4点（全国78.1%・県内46位）。申立費用助成・報酬助成はいずれも整備済（doc28§3）であり、対象の限定を外す要綱改正のみで取得できる。新たな予算を要しない。★9/25：素案の施策4-7に取組として反映し、指標表に1行を追加した。現在の要綱が対象を市町村長申立てや生活保護受給者に限定しているかをご確認いただき、改正の可否をご判断いただきたい。</t>
         </is>
       </c>
       <c r="E63" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-46</t>
+          <t>Ⅱ-69,Ⅱ-67</t>
         </is>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>doc25§4-2 K-91</t>
+          <t>doc42§3-3</t>
         </is>
       </c>
       <c r="G63" s="34" t="inlineStr">
@@ -10434,22 +10434,22 @@
       </c>
       <c r="C64" s="33" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入の取組の実施可否（普及啓発・早期発見）</t>
+          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
         </is>
       </c>
       <c r="D64" s="33" t="inlineStr">
         <is>
-          <t>★合わせて10点（全国68.9%・48.8%、県内48位・46位）。★9/25：素案の施策4-4に3つの取組（広報・健診案内・通いの場での周知／健診と通いの場での聞こえの確認／耳鼻咽喉科への受診勧奨と受診状況の把握）として反映し、指標表を普及啓発5点・早期発見5点・受診状況10点に分けた。実施の可否と現在の取組状況をご教示いただきたい。受診状況の把握と受診率50%以上は全国でも14.6%・4.8%と取得が少ないため第10期中の検討事項としている。</t>
+          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
         </is>
       </c>
       <c r="E64" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-65</t>
+          <t>Ⅱ-70,Ⅱ-71</t>
         </is>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
-          <t>doc42§3</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G64" s="34" t="inlineStr">
@@ -10467,27 +10467,27 @@
       </c>
       <c r="B65" s="32" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>委員会</t>
         </is>
       </c>
       <c r="C65" s="33" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の要綱の対象範囲（市町村長申立・生活保護受給者への限定を外す改正の可否）</t>
+          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
         </is>
       </c>
       <c r="D65" s="33" t="inlineStr">
         <is>
-          <t>★4点（全国78.1%・県内46位）。申立費用助成・報酬助成はいずれも整備済（doc28§3）であり、対象の限定を外す要綱改正のみで取得できる。新たな予算を要しない。★9/25：素案の施策4-7に取組として反映し、指標表に1行を追加した。現在の要綱が対象を市町村長申立てや生活保護受給者に限定しているかをご確認いただき、改正の可否をご判断いただきたい。</t>
+          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
         </is>
       </c>
       <c r="E65" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-69,Ⅱ-67</t>
+          <t>Ⅱ-80,Ⅱ-81</t>
         </is>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
-          <t>doc42§3-3</t>
+          <t>doc01-6,doc19 追-15</t>
         </is>
       </c>
       <c r="G65" s="34" t="inlineStr">
@@ -10505,27 +10505,27 @@
       </c>
       <c r="B66" s="32" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
-          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
+          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
         </is>
       </c>
       <c r="D66" s="33" t="inlineStr">
         <is>
-          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
+          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
         </is>
       </c>
       <c r="E66" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-70,Ⅱ-71</t>
+          <t>Ⅱ-76,Ⅱ-77</t>
         </is>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc01-7,doc19 指-3</t>
         </is>
       </c>
       <c r="G66" s="34" t="inlineStr">
@@ -10543,27 +10543,27 @@
       </c>
       <c r="B67" s="32" t="inlineStr">
         <is>
-          <t>委員会</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
-          <t>策定委員会の委員改選手続きの所要期間と第1回開催希望時期・開催形式</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D67" s="33" t="inlineStr">
         <is>
-          <t>★現委員の任期は令和8年9月30日満了。第1回を11月に開くには10月中の委嘱が必要。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
         </is>
       </c>
       <c r="E67" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-80,Ⅱ-81</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
-          <t>doc01-6,doc19 追-15</t>
+          <t>doc22 K-79</t>
         </is>
       </c>
       <c r="G67" s="34" t="inlineStr">
@@ -10581,27 +10581,27 @@
       </c>
       <c r="B68" s="32" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C68" s="33" t="inlineStr">
         <is>
-          <t>パブリックコメント（30日間）の実施時期・実施主体と庁内手続き日程</t>
+          <t>★交付金で61点が取れる未得点項目11件の取組可否（計画への記載・要綱改正・手順の明文化のみで取得できるもの）</t>
         </is>
       </c>
       <c r="D68" s="33" t="inlineStr">
         <is>
-          <t>★30日間必要。第2回策定委員会が1月にずれると第3回（2月）までに終わらず工程が破綻する。年末年始も挟む。</t>
+          <t>★令和8年度の市町村分 全国一覧表と評価指標42頁を突合し、新たな予算や施設を要さず取得できる項目を61点分特定した（doc42§3）。447点→508点で全国1,005位→525位、県内34位→18位になる。内訳は認知症施策推進計画の策定着手5点／成年後見の要綱改正4点／難聴の普及啓発・早期発見10点／在宅医療連携の4場面の設定と対応策10点／相談内容の取りまとめ2点／給付適正化の福祉用具・住宅改修16点／ケアプラン点検の村外施設分8点／主要3事業の全実施6点。素案への反映には村の意向確認を要する。</t>
         </is>
       </c>
       <c r="E68" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-76,Ⅱ-77</t>
+          <t>Ⅱ-65,Ⅱ-67,Ⅱ-109</t>
         </is>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
-          <t>doc01-7,doc19 指-3</t>
+          <t>doc42§3</t>
         </is>
       </c>
       <c r="G68" s="34" t="inlineStr">
@@ -10619,27 +10619,27 @@
       </c>
       <c r="B69" s="32" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C69" s="33" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>ケアプラン点検に村外の有料老人ホーム・サービス付き高齢者向け住宅の入居者分を含める体制の構築可否</t>
         </is>
       </c>
       <c r="D69" s="33" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。</t>
+          <t>★評価指標の留意点により、管内に該当施設がない市町村でも、被保険者が他市町村の施設に入居して介護サービスを適正に利用しているかの実態を把握し、必要に応じ県・他市町村と連携して対応できる体制があれば8点の対象となる。素案5-8で「村内に該当施設がないため対象外」としていたのは誤りで訂正した。本村は給付費の58.7%が村外であり、利用実態の把握は得点にとどまらず計画上の課題である。</t>
         </is>
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-109,Ⅱ-61</t>
         </is>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-79</t>
+          <t>doc42§3-1</t>
         </is>
       </c>
       <c r="G69" s="34" t="inlineStr">
@@ -10662,22 +10662,22 @@
       </c>
       <c r="C70" s="33" t="inlineStr">
         <is>
-          <t>★交付金で61点が取れる未得点項目11件の取組可否（計画への記載・要綱改正・手順の明文化のみで取得できるもの）</t>
+          <t>福祉用具・住宅改修へのリハビリテーション専門職等の関与の仕組み（広域連携による整備の可否）</t>
         </is>
       </c>
       <c r="D70" s="33" t="inlineStr">
         <is>
-          <t>★令和8年度の市町村分 全国一覧表と評価指標42頁を突合し、新たな予算や施設を要さず取得できる項目を61点分特定した（doc42§3）。447点→508点で全国1,005位→525位、県内34位→18位になる。内訳は認知症施策推進計画の策定着手5点／成年後見の要綱改正4点／難聴の普及啓発・早期発見10点／在宅医療連携の4場面の設定と対応策10点／相談内容の取りまとめ2点／給付適正化の福祉用具・住宅改修16点／ケアプラン点検の村外施設分8点／主要3事業の全実施6点。素案への反映には村の意向確認を要する。</t>
+          <t>★合わせて16点。評価指標の留意点により、関係団体や県・近隣市町村による広域団体と連携した仕組みでも対象となり、住宅改修費については建築専門職・福祉住環境コーディネーター検定試験2級以上も「リハビリテーション専門職等」に含まれる。購入費・改修費のいずれかで足りる。令和6・7年度は実施していたものが令和8年度に0点となっており、後退の原因もご教示いただきたい。</t>
         </is>
       </c>
       <c r="E70" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-67,Ⅱ-109</t>
+          <t>Ⅱ-109</t>
         </is>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>doc42§3</t>
+          <t>doc42§3-1</t>
         </is>
       </c>
       <c r="G70" s="34" t="inlineStr">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C71" s="33" t="inlineStr">
         <is>
-          <t>ケアプラン点検に村外の有料老人ホーム・サービス付き高齢者向け住宅の入居者分を含める体制の構築可否</t>
+          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
         </is>
       </c>
       <c r="D71" s="33" t="inlineStr">
         <is>
-          <t>★評価指標の留意点により、管内に該当施設がない市町村でも、被保険者が他市町村の施設に入居して介護サービスを適正に利用しているかの実態を把握し、必要に応じ県・他市町村と連携して対応できる体制があれば8点の対象となる。素案5-8で「村内に該当施設がないため対象外」としていたのは誤りで訂正した。本村は給付費の58.7%が村外であり、利用実態の把握は得点にとどまらず計画上の課題である。</t>
+          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
         </is>
       </c>
       <c r="E71" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-109,Ⅱ-61</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
-          <t>doc42§3-1</t>
+          <t>doc33§3-5</t>
         </is>
       </c>
       <c r="G71" s="34" t="inlineStr">
@@ -10738,22 +10738,22 @@
       </c>
       <c r="C72" s="33" t="inlineStr">
         <is>
-          <t>福祉用具・住宅改修へのリハビリテーション専門職等の関与の仕組み（広域連携による整備の可否）</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D72" s="33" t="inlineStr">
         <is>
-          <t>★合わせて16点。評価指標の留意点により、関係団体や県・近隣市町村による広域団体と連携した仕組みでも対象となり、住宅改修費については建築専門職・福祉住環境コーディネーター検定試験2級以上も「リハビリテーション専門職等」に含まれる。購入費・改修費のいずれかで足りる。令和6・7年度は実施していたものが令和8年度に0点となっており、後退の原因もご教示いただきたい。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E72" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-109</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>doc42§3-1</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G72" s="34" t="inlineStr">
@@ -10776,22 +10776,22 @@
       </c>
       <c r="C73" s="33" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D73" s="33" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E73" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>doc33§3-5</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G73" s="34" t="inlineStr">
@@ -10814,22 +10814,22 @@
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D74" s="33" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E74" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G74" s="34" t="inlineStr">
@@ -10852,22 +10852,22 @@
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D75" s="33" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
         </is>
       </c>
       <c r="E75" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc26§10 K-99</t>
         </is>
       </c>
       <c r="G75" s="34" t="inlineStr">
@@ -10890,22 +10890,22 @@
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
         </is>
       </c>
       <c r="D76" s="33" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
         </is>
       </c>
       <c r="E76" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc28§1-2 K-107</t>
         </is>
       </c>
       <c r="G76" s="34" t="inlineStr">
@@ -10928,22 +10928,22 @@
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>認知症施策の実施状況の評価と公表の運用</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。</t>
+          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
         </is>
       </c>
       <c r="E77" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
-          <t>doc26§10 K-99</t>
+          <t>doc36§10-1,doc18 4-7(6)</t>
         </is>
       </c>
       <c r="G77" s="34" t="inlineStr">
@@ -10966,22 +10966,22 @@
       </c>
       <c r="C78" s="33" t="inlineStr">
         <is>
-          <t>補正係数を①3区分と②前期・後期高齢者別のどちらで用いるか</t>
+          <t>認知症の人およびご家族から意見を聴く方法</t>
         </is>
       </c>
       <c r="D78" s="33" t="inlineStr">
         <is>
-          <t>国は小規模保険者では①の係数が不安定になるため②の選択を勧めている。本村の85歳以上は200人で係数0.03（差6人）と1人の増減の影響が大きい。当方は②を提案。</t>
+          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
         </is>
       </c>
       <c r="E78" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>doc28§1-2 K-107</t>
+          <t>doc36§5,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G78" s="34" t="inlineStr">
@@ -11004,22 +11004,22 @@
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>認知症施策の実施状況の評価と公表の運用</t>
+          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
         </is>
       </c>
       <c r="D79" s="33" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
+          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
         </is>
       </c>
       <c r="E79" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-71</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>doc36§10-1,doc18 4-7(6)</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G79" s="34" t="inlineStr">
@@ -11037,27 +11037,27 @@
       </c>
       <c r="B80" s="32" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C80" s="33" t="inlineStr">
         <is>
-          <t>認知症の人およびご家族から意見を聴く方法</t>
+          <t>★2つの名簿に重複して含まれる2人の扱い</t>
         </is>
       </c>
       <c r="D80" s="33" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
+          <t>★ニーズ調査の対象者のうち2人が在宅介護実態調査の名簿にも含まれている（被保険者番号で突合。番号の値は当方で保持していない）。この2人には2種類の調査票が届く。ニーズ調査の対象には要支援認定者が、在宅調査の対象には在宅の要介護認定者が含まれるため本来は重ならない。抽出条件によるものか認定区分が変更になった方かは不明。発送済みの場合、回収時に同じ方の回答が2件計上されないようにする必要がある。</t>
         </is>
       </c>
       <c r="E80" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-71</t>
+          <t>Ⅰ-24,Ⅰ-30,Ⅰ-36</t>
         </is>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>doc36§5,doc18 4-7(4)</t>
+          <t>doc43§2-3</t>
         </is>
       </c>
       <c r="G80" s="34" t="inlineStr">
@@ -11075,27 +11075,27 @@
       </c>
       <c r="B81" s="32" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
-          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D81" s="33" t="inlineStr">
         <is>
-          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E81" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G81" s="34" t="inlineStr">
@@ -11113,27 +11113,27 @@
       </c>
       <c r="B82" s="32" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C82" s="33" t="inlineStr">
         <is>
-          <t>★2つの名簿に重複して含まれる2人の扱い</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D82" s="33" t="inlineStr">
         <is>
-          <t>★ニーズ調査の対象者のうち2人が在宅介護実態調査の名簿にも含まれている（被保険者番号で突合。番号の値は当方で保持していない）。この2人には2種類の調査票が届く。ニーズ調査の対象には要支援認定者が、在宅調査の対象には在宅の要介護認定者が含まれるため本来は重ならない。抽出条件によるものか認定区分が変更になった方かは不明。発送済みの場合、回収時に同じ方の回答が2件計上されないようにする必要がある。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
         </is>
       </c>
       <c r="E82" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-24,Ⅰ-30,Ⅰ-36</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
-          <t>doc43§2-3</t>
+          <t>doc21§5 K-70</t>
         </is>
       </c>
       <c r="G82" s="34" t="inlineStr">
@@ -11156,12 +11156,12 @@
       </c>
       <c r="C83" s="33" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D83" s="33" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E83" s="34" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G83" s="34" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="B84" s="32" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C84" s="33" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
         </is>
       </c>
       <c r="D84" s="33" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。</t>
+          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
         </is>
       </c>
       <c r="E84" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-19,Ⅰ-25</t>
         </is>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>doc21§5 K-70</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G84" s="34" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H84" s="33" t="inlineStr"/>
@@ -11227,27 +11227,27 @@
       </c>
       <c r="B85" s="32" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C85" s="33" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
         </is>
       </c>
       <c r="D85" s="33" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
         </is>
       </c>
       <c r="E85" s="34" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-09,Ⅰ-10</t>
         </is>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc27§3-3</t>
         </is>
       </c>
       <c r="G85" s="34" t="inlineStr">
@@ -11270,27 +11270,27 @@
       </c>
       <c r="C86" s="33" t="inlineStr">
         <is>
-          <t>被保険者番号と照合可能な管理番号の形式（村のラベル作成仕様と一体）</t>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
         </is>
       </c>
       <c r="D86" s="33" t="inlineStr">
         <is>
-          <t>★議事録で方針決着：氏名は記載せず管理番号を付与し被保険者番号と紐付ける。具体的な番号形式は村のラベル作成仕様と一体で要調整。</t>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
         </is>
       </c>
       <c r="E86" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-19,Ⅰ-25</t>
+          <t>Ⅰ-09,Ⅰ-10</t>
         </is>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc27§5-2</t>
         </is>
       </c>
       <c r="G86" s="34" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H86" s="33" t="inlineStr"/>
@@ -11308,22 +11308,22 @@
       </c>
       <c r="C87" s="33" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
         </is>
       </c>
       <c r="D87" s="33" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
         </is>
       </c>
       <c r="E87" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc27§5-3</t>
         </is>
       </c>
       <c r="G87" s="34" t="inlineStr">
@@ -11346,22 +11346,22 @@
       </c>
       <c r="C88" s="33" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
       <c r="D88" s="33" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
       <c r="E88" s="34" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅰ-20</t>
         </is>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc27§6</t>
         </is>
       </c>
       <c r="G88" s="34" t="inlineStr">
@@ -11372,80 +11372,80 @@
       <c r="H88" s="33" t="inlineStr"/>
     </row>
     <row r="89" ht="34" customHeight="1">
-      <c r="A89" s="35" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B89" s="32" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C89" s="33" t="inlineStr">
-        <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
-        </is>
-      </c>
-      <c r="D89" s="33" t="inlineStr">
-        <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
-        </is>
-      </c>
-      <c r="E89" s="34" t="inlineStr">
-        <is>
-          <t>Ⅰ-10</t>
-        </is>
-      </c>
-      <c r="F89" s="34" t="inlineStr">
-        <is>
-          <t>doc27§5-3</t>
-        </is>
-      </c>
-      <c r="G89" s="34" t="inlineStr">
+      <c r="A89" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C89" s="25" t="inlineStr">
+        <is>
+          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
+        </is>
+      </c>
+      <c r="D89" s="25" t="inlineStr">
+        <is>
+          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
+        </is>
+      </c>
+      <c r="E89" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-63,Ⅱ-64</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>doc02§22,doc08§8</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H89" s="33" t="inlineStr"/>
+      <c r="H89" s="25" t="inlineStr"/>
     </row>
     <row r="90" ht="34" customHeight="1">
-      <c r="A90" s="35" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B90" s="32" t="inlineStr">
-        <is>
-          <t>調査設計</t>
-        </is>
-      </c>
-      <c r="C90" s="33" t="inlineStr">
-        <is>
-          <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
-        </is>
-      </c>
-      <c r="D90" s="33" t="inlineStr">
-        <is>
-          <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
-        </is>
-      </c>
-      <c r="E90" s="34" t="inlineStr">
-        <is>
-          <t>Ⅰ-20</t>
-        </is>
-      </c>
-      <c r="F90" s="34" t="inlineStr">
-        <is>
-          <t>doc27§6</t>
-        </is>
-      </c>
-      <c r="G90" s="34" t="inlineStr">
+      <c r="A90" s="36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B90" s="24" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C90" s="25" t="inlineStr">
+        <is>
+          <t>令和6年度決算および令和7年度の給付費見込</t>
+        </is>
+      </c>
+      <c r="D90" s="25" t="inlineStr">
+        <is>
+          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
+        </is>
+      </c>
+      <c r="E90" s="23" t="inlineStr">
+        <is>
+          <t>Ⅱ-55,Ⅱ-56</t>
+        </is>
+      </c>
+      <c r="F90" s="23" t="inlineStr">
+        <is>
+          <t>doc08§8-1,doc30§2-4</t>
+        </is>
+      </c>
+      <c r="G90" s="23" t="inlineStr">
         <is>
           <t>未依頼</t>
         </is>
       </c>
-      <c r="H90" s="33" t="inlineStr"/>
+      <c r="H90" s="25" t="inlineStr"/>
     </row>
     <row r="91" ht="34" customHeight="1">
       <c r="A91" s="36" t="inlineStr">
@@ -11460,27 +11460,27 @@
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の現在高（令和6年度末実績・令和7年度末見込）</t>
+          <t>通いの場の実数（令和3〜7年度）</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>保険料算定の前提。決算でR4年度1,700万円・R5年度810万円の積立を確認済。</t>
+          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>doc02§22,doc08§8</t>
+          <t>doc02§16,§22</t>
         </is>
       </c>
       <c r="G91" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H91" s="25" t="inlineStr"/>
@@ -11498,22 +11498,22 @@
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>令和6年度決算および令和7年度の給付費見込</t>
+          <t>高齢者福祉事業（村単独事業）の実績資料</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>第9期の計画値と実績の乖離を確定させるために必要。★9/8：見える化D48系に令和5年度までの決算（保険給付費の款項内訳・地域支援事業費）が収録されていることが判明したため、必要なのは令和6・7年度の2か年に縮小した。</t>
+          <t>現行計画の評価に必要。</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-1,doc30§2-4</t>
+          <t>doc01-11</t>
         </is>
       </c>
       <c r="G92" s="23" t="inlineStr">
@@ -11536,27 +11536,27 @@
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>通いの場の実数（令和3〜7年度）</t>
+          <t>訪問診療・訪問看護の提供実績（村内外の事業所別・令和6〜7年度）</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>見える化は令和2年度で更新停止。かつH25・H29・R2は未報告とみられる。活動指標の基準値に必須。★9/3：令和6年度分（23か所281人／週1回以上8か所123人）を受領。令和3〜5年度・令和7年度は未受領。</t>
+          <t>★素案の施策4-3に在宅医療・介護連携の4場面ごとの目指すべき姿を新設し、①日常の療養支援の現状を【要確認】としている。村内は南東北裏磐梯診療所・桧原診療所の2か所で訪問看護事業所は村内にない。訪問診療の実施状況と村外からの訪問看護の提供量が分からないと、日常の療養支援の余力を示せない。県への提供依頼で把握できる範囲もあわせてご相談したい。</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-67,Ⅱ-61</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>doc02§16,§22</t>
+          <t>doc42§4,doc18 施策4-3</t>
         </is>
       </c>
       <c r="G93" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H93" s="25" t="inlineStr"/>
@@ -11574,22 +11574,22 @@
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>高齢者福祉事業（村単独事業）の実績資料</t>
+          <t>急変時に本人の意思と医療情報を関係者間で共有する仕組みの有無（救急医療情報キット等）</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>現行計画の評価に必要。</t>
+          <t>★素案の施策4-3の4場面のうち③急変時の対応の現状を【要確認】としている。救急搬送先は村外の病院であり、本人の意思・服薬・既往の情報が救急隊と搬送先へ伝わる仕組みがあるかで、第10期の対応策（仕組みの導入を検討するか運用の改善にとどめるか）が変わる。</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-67</t>
         </is>
       </c>
       <c r="F94" s="23" t="inlineStr">
         <is>
-          <t>doc01-11</t>
+          <t>doc42§4,doc18 施策4-3</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -11612,22 +11612,22 @@
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>訪問診療・訪問看護の提供実績（村内外の事業所別・令和6〜7年度）</t>
+          <t>介護人材の確保に関する福島県の事業（介護人材確保対策・修学資金貸付）の内容と本村からの利用実績</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>★素案の施策4-3に在宅医療・介護連携の4場面ごとの目指すべき姿を新設し、①日常の療養支援の現状を【要確認】としている。村内は南東北裏磐梯診療所・桧原診療所の2か所で訪問看護事業所は村内にない。訪問診療の実施状況と村外からの訪問看護の提供量が分からないと、日常の療養支援の余力を示せない。県への提供依頼で把握できる範囲もあわせてご相談したい。</t>
+          <t>★令和8年度の交付金（都道府県分）により、介護人材の確保・サービス提供基盤の整備は福島県が全国平均を13.1点下回る県全体の課題であることが判明した（本村は▲4.8点）。本村単独では動かしにくいため、施策4-6は県の事業と定住自立圏（喜多方市・西会津町）の研修費用助成を活用する形に組み立てたい。県の事業の内容と本村からの利用実績をご教示いただきたい。</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-61</t>
+          <t>Ⅱ-67,Ⅱ-54</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>doc42§4,doc18 施策4-3</t>
+          <t>doc41§3</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
@@ -11650,22 +11650,22 @@
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>急変時に本人の意思と医療情報を関係者間で共有する仕組みの有無（救急医療情報キット等）</t>
+          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>★素案の施策4-3の4場面のうち③急変時の対応の現状を【要確認】としている。救急搬送先は村外の病院であり、本人の意思・服薬・既往の情報が救急隊と搬送先へ伝わる仕組みがあるかで、第10期の対応策（仕組みの導入を検討するか運用の改善にとどめるか）が変わる。</t>
+          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67</t>
+          <t>Ⅱ-58,Ⅱ-59</t>
         </is>
       </c>
       <c r="F96" s="23" t="inlineStr">
         <is>
-          <t>doc42§4,doc18 施策4-3</t>
+          <t>doc19 追-9</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -11688,22 +11688,22 @@
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>介護人材の確保に関する福島県の事業（介護人材確保対策・修学資金貸付）の内容と本村からの利用実績</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>★令和8年度の交付金（都道府県分）により、介護人材の確保・サービス提供基盤の整備は福島県が全国平均を13.1点下回る県全体の課題であることが判明した（本村は▲4.8点）。本村単独では動かしにくいため、施策4-6は県の事業と定住自立圏（喜多方市・西会津町）の研修費用助成を活用する形に組み立てたい。県の事業の内容と本村からの利用実績をご教示いただきたい。</t>
+          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-54</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t>doc41§3</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
@@ -11726,22 +11726,22 @@
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>人口データの出所の統一（住基／国勢調査／福島県現住人口調査）</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>計画書内で人口の数字が複数出ることを避ける。doc13は社人研＋住基の補正手法を採用。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-58,Ⅱ-59</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F98" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-9</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
@@ -11764,22 +11764,22 @@
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。施設サービス（特養・老健・介護医療院）と居住系サービス（GH・特定施設）は、見える化にサービス種類別の受給者数の系列がない。現在は給付費の構成比で按分した参考値を置いているが、種類ごとに単価が違うため実態とずれる。計画に載せる確定値にするには月報の実数が要る。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F99" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
@@ -11802,27 +11802,27 @@
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
         </is>
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F100" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc38§A-2,doc18 5-4(9)</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="H100" s="25" t="inlineStr"/>
@@ -11840,22 +11840,22 @@
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F101" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -11878,27 +11878,27 @@
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
+          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
         </is>
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
+          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F102" s="23" t="inlineStr">
         <is>
-          <t>doc38§A-2,doc18 5-4(9)</t>
+          <t>doc33§2</t>
         </is>
       </c>
       <c r="G102" s="23" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H102" s="25" t="inlineStr"/>
@@ -11916,22 +11916,22 @@
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F103" s="23" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -11954,22 +11954,22 @@
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>第10期（令和9〜11年度）の第1号被保険者負担割合を定める政令の公布状況</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>★第9期は23％。3年ごとに政令で定められ第1期17％から1ポイントずつ上がってきた。本村では1ポイントで保険料月額約294円。期限付きの軽減措置ではない。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t>doc33§2</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G104" s="23" t="inlineStr">
@@ -11992,22 +11992,22 @@
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F105" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>第9期計画の本文（第5章81〜92ページ）</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
@@ -12068,22 +12068,22 @@
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F107" s="23" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc32§3-3</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -12106,22 +12106,22 @@
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>第9期計画の本文（第5章81〜92ページ）</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>★老人福祉事業の量の目標を第9期計画のどこに記載していたかを確認し、第10期の配置を揃えるために必要。現在は第4章末（4-6）に置いている。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F108" s="23" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -12144,22 +12144,22 @@
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>福島県保健医療計画（第八次）の会津・南会津区域に関する記載</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第5項により本計画は医療計画と整合が図られたものでなければならない。素案1-4に整合の記述を追加したが内容が未確定。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F109" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-3</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
@@ -12220,22 +12220,22 @@
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F111" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -12258,22 +12258,22 @@
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E112" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F112" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -12296,22 +12296,22 @@
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E113" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F113" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -12334,22 +12334,22 @@
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E114" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F114" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>行政区コードの先頭の桁と地区の対応（推定の確認）および在宅調査「追加分」77件の位置づけ</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>ニーズ調査の名簿の行政区コード（101〜407の23区分）について、先頭の桁が地区に対応するとみて第9期の対象者数と照合したところ4地区とも近い値となった（北山341対329、大塩185対200、桧原111対114、裏磐梯245対240、計882対883）。この対応で資料3の3-1の対象者数の欄を確定したため、推定が正しいかをご確認いただきたい。あわせて在宅調査の「追加分」77件の位置づけをご教示いただきたい（リスト66＋引き抜き52＝118で対象者数は足りており、ニーズ調査の「引き抜き」77件と同数である）。また、在宅介護実態調査の名簿の行政区は23区分あり10人以上は2区分のみであるため、そのままでは地区別の集計ができない。行政区名と地区（北山・大塩・桧原・裏磐梯）の対応表をご提供いただきたい。</t>
         </is>
       </c>
       <c r="E115" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅰ-24,Ⅰ-40</t>
         </is>
       </c>
       <c r="F115" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc43§2-1,§2-4</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -12410,22 +12410,22 @@
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E116" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F116" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -12448,22 +12448,22 @@
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>行政区コードの先頭の桁と地区の対応（推定の確認）および在宅調査「追加分」77件の位置づけ</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査の名簿の行政区コード（101〜407の23区分）について、先頭の桁が地区に対応するとみて第9期の対象者数と照合したところ4地区とも近い値となった（北山341対329、大塩185対200、桧原111対114、裏磐梯245対240、計882対883）。この対応で資料3の3-1の対象者数の欄を確定したため、推定が正しいかをご確認いただきたい。あわせて在宅調査の「追加分」77件の位置づけをご教示いただきたい（リスト66＋引き抜き52＝118で対象者数は足りており、ニーズ調査の「引き抜き」77件と同数である）。また、在宅介護実態調査の名簿の行政区は23区分あり10人以上は2区分のみであるため、そのままでは地区別の集計ができない。行政区名と地区（北山・大塩・桧原・裏磐梯）の対応表をご提供いただきたい。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E117" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-24,Ⅰ-40</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>doc43§2-1,§2-4</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -12486,22 +12486,22 @@
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E118" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅱ-107</t>
         </is>
       </c>
       <c r="F118" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -12524,22 +12524,22 @@
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
         </is>
       </c>
       <c r="E119" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F119" s="23" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -12562,22 +12562,22 @@
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
         </is>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-107</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F120" s="23" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc36§10-4,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -12600,22 +12600,22 @@
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率は見える化に系列がない</t>
+          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>★施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
+          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
         </is>
       </c>
       <c r="E121" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F121" s="23" t="inlineStr">
         <is>
-          <t>doc38§D</t>
+          <t>doc35§7-3(2),doc18 5-6</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -12633,27 +12633,27 @@
       </c>
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E122" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F122" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-4,doc18 4-7(3)</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -12671,27 +12671,27 @@
       </c>
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E123" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F123" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(2),doc18 5-6</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -12714,22 +12714,22 @@
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E124" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F124" s="23" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -12747,27 +12747,27 @@
       </c>
       <c r="B125" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F125" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -12785,27 +12785,27 @@
       </c>
       <c r="B126" s="24" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>報告書に調査票を再掲しないことの村への事前説明（第9期の巻末の確認を含む）</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>★案Bを採用し、調査票の全文・単純集計表・自由記述の全文は紙の資料編から外して電子媒体に収録する（doc24§9）。doc01§5-5に記録した第9期報告書の構成に調査票の再掲はないが、目次の見出しのみの記録のため巻末に載っていた可能性がある。載っていた場合は前回からの変更にあたるため、納品時の齟齬を避けるため事前に説明しておきたい。</t>
         </is>
       </c>
       <c r="E126" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅳ-90,Ⅳ-114</t>
         </is>
       </c>
       <c r="F126" s="23" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc24§1-3</t>
         </is>
       </c>
       <c r="G126" s="23" t="inlineStr">
@@ -12823,27 +12823,27 @@
       </c>
       <c r="B127" s="24" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
+          <t>計画書・報告書の頁数の実測（当方では docx→PDF 変換ができず目視確認ができない）</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
+          <t>★当方の推定では計画書は本文88頁＋前付4頁＝92頁で、仕様書の約100頁に8頁の余裕がある（レイアウト値からの積算・doc40§0）。字詰め・禁則・表の折り返しの実挙動で前後するため、村側で実際に開いて頁数をご確認いただきたい。余裕が確認できれば第3章の施策体系図（第9期にあり第10期素案にない）とSDGsの対応表を追加したい。</t>
         </is>
       </c>
       <c r="E127" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc40§1-4</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -12866,22 +12866,22 @@
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>報告書に調査票を再掲しないことの村への事前説明（第9期の巻末の確認を含む）</t>
+          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>★案Bを採用し、調査票の全文・単純集計表・自由記述の全文は紙の資料編から外して電子媒体に収録する（doc24§9）。doc01§5-5に記録した第9期報告書の構成に調査票の再掲はないが、目次の見出しのみの記録のため巻末に載っていた可能性がある。載っていた場合は前回からの変更にあたるため、納品時の齟齬を避けるため事前に説明しておきたい。</t>
+          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
         </is>
       </c>
       <c r="E128" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-90,Ⅳ-114</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F128" s="23" t="inlineStr">
         <is>
-          <t>doc24§1-3</t>
+          <t>doc19 指-5</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
@@ -12904,22 +12904,22 @@
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>計画書・報告書の頁数の実測（当方では docx→PDF 変換ができず目視確認ができない）</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>★当方の推定では計画書は本文88頁＋前付4頁＝92頁で、仕様書の約100頁に8頁の余裕がある（レイアウト値からの積算・doc40§0）。字詰め・禁則・表の折り返しの実挙動で前後するため、村側で実際に開いて頁数をご確認いただきたい。余裕が確認できれば第3章の施策体系図（第9期にあり第10期素案にない）とSDGsの対応表を追加したい。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E129" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅳ-89</t>
+          <t>Ⅱ-93</t>
         </is>
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>doc40§1-4</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
@@ -12937,27 +12937,27 @@
       </c>
       <c r="B130" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>概要版の位置づけ（仕様の範囲内か追加対応か）</t>
+          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>仕様書に記載がなく成果品一覧にもないが、資料末尾に「必要に応じては概要版も作成致します」とある。第9期は2ページの概要版を作成。</t>
+          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
         </is>
       </c>
       <c r="E130" s="23" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F130" s="23" t="inlineStr">
         <is>
-          <t>doc19 指-5</t>
+          <t>doc09§4,§10</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
@@ -12975,27 +12975,27 @@
       </c>
       <c r="B131" s="24" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
         </is>
       </c>
       <c r="E131" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-93</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F131" s="23" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc09§8,§10</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
@@ -13018,22 +13018,22 @@
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数の推計を社人研ベースから補正して用いる方針の可否</t>
+          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>社人研推計は住基ベース実績より6〜8%少なく、第9期はこれで63人ずれた。手法変更のため村の合意が要る。</t>
+          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
         </is>
       </c>
       <c r="E132" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F132" s="23" t="inlineStr">
         <is>
-          <t>doc09§4,§10</t>
+          <t>doc02§17,doc07,doc18 4-1</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -13056,22 +13056,22 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>保険料が県・全国を上回る一方で費用額は下位である点の認識と説明方針</t>
+          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>保険料6,700円は県+360円・全国+475円。費用額は県内44/59位。説明ロジックの構築に関わる。</t>
+          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
         </is>
       </c>
       <c r="E133" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-56,Ⅱ-75</t>
         </is>
       </c>
       <c r="F133" s="23" t="inlineStr">
         <is>
-          <t>doc09§8,§10</t>
+          <t>doc17 C-1,doc02§20-2</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
@@ -13094,22 +13094,22 @@
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>総合事業のサービスA〜Dを第10期で立ち上げる意向の有無</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>従前相当サービス以外の事業費割合0.0%。要支援1急増（39→51人）の受け皿に直結。素案の施策1-2の成否を決める。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E134" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F134" s="23" t="inlineStr">
         <is>
-          <t>doc02§17,doc07,doc18 4-1</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G134" s="23" t="inlineStr">
@@ -13132,22 +13132,22 @@
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>認定率の分母をB1（第1号被保険者数）に統一することの可否</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>第9期は同一計画書内に19.0%（193/1,016）と19.7%（197/1,002）が併記されていた。統一すると第9期の公表値と異なる数値を示すことになる。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E135" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-75</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>doc17 C-1,doc02§20-2</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
@@ -13170,22 +13170,22 @@
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
         </is>
       </c>
       <c r="E136" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F136" s="23" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
@@ -13208,22 +13208,22 @@
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
         </is>
       </c>
       <c r="E137" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-105,Ⅱ-67</t>
         </is>
       </c>
       <c r="F137" s="23" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc32§3-1</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
@@ -13246,22 +13246,22 @@
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>★策定委員会の委員に認知症の本人・家族が含まれるかを確認する必要がある。含まれない場合は家族会・認知症カフェ等での意見聴取の機会が要る。記述の追加では埋まらず策定過程に関わるため、第2回策定委員会までに方針決定が必要。</t>
+          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
         </is>
       </c>
       <c r="E138" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F138" s="23" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc30§5-4</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
@@ -13284,22 +13284,22 @@
       </c>
       <c r="C139" s="25" t="inlineStr">
         <is>
-          <t>地域密着型サービスの必要利用定員総数（グループホーム27人を維持するか）</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>★介護保険法第117条第2項第1号の義務的記載事項。素案5-4(5)に27人維持で仮置きした。稼働率93%で第10期は増加見込みのため、増床・村外対応・在宅対応のいずれを取るかで数値が変わる。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
         </is>
       </c>
       <c r="E139" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-105,Ⅱ-67</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F139" s="23" t="inlineStr">
         <is>
-          <t>doc32§3-1</t>
+          <t>doc19 追-14</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
@@ -13322,22 +13322,22 @@
       </c>
       <c r="C140" s="25" t="inlineStr">
         <is>
-          <t>サービス見込量の前提（受給率を3か年平均とするか令和7年度水準とするか）</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>★3か年平均では令和9年度のサービス諸費が令和5年度決算比+1.8%にとどまるが、実績は令和4→5年度で+4.7%伸びている。前提の選び方で保険料が変わるため、委員会に感度分析を示して確認する。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E140" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F140" s="23" t="inlineStr">
         <is>
-          <t>doc30§5-4</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
@@ -13360,22 +13360,22 @@
       </c>
       <c r="C141" s="25" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E141" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F141" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-14</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
@@ -13398,22 +13398,22 @@
       </c>
       <c r="C142" s="25" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E142" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G142" s="23" t="inlineStr">
@@ -13436,22 +13436,22 @@
       </c>
       <c r="C143" s="25" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
         </is>
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
         </is>
       </c>
       <c r="E143" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56,Ⅱ-64</t>
         </is>
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc37§4,doc18 5-4(10)</t>
         </is>
       </c>
       <c r="G143" s="23" t="inlineStr">
@@ -13474,22 +13474,22 @@
       </c>
       <c r="C144" s="25" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
         </is>
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
         </is>
       </c>
       <c r="E144" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F144" s="23" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc36§10-2,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G144" s="23" t="inlineStr">
@@ -13512,22 +13512,22 @@
       </c>
       <c r="C145" s="25" t="inlineStr">
         <is>
-          <t>令和9年4月の介護報酬改定率が示された後の単価の扱い</t>
+          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
         </is>
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>★他案件（大雪）の点検で「改定率を乗じることと単価の趨勢を延ばすことを重ねると二重になる」ことが指摘された。本村の単価の趨勢（年1.30%）は連鎖ラスパイレス指数による実測値で、平成27年▲2.27%から令和6年+1.59%までの改定をすでに含む。改定率が示された時点で趨勢による補正（月額314円）を取り下げ、改定率のみを用いる。素案5-4(10)①に断りを入れたが、運用の確認を要する。</t>
+          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
         </is>
       </c>
       <c r="E145" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F145" s="23" t="inlineStr">
         <is>
-          <t>doc37§4,doc18 5-4(10)</t>
+          <t>doc36§10-3,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G145" s="23" t="inlineStr">
@@ -13550,22 +13550,22 @@
       </c>
       <c r="C146" s="25" t="inlineStr">
         <is>
-          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
+          <t>認知症対応型通所介護を再開するかどうか</t>
         </is>
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
+          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
         </is>
       </c>
       <c r="E146" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F146" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-2,doc18 4-7(4)</t>
+          <t>doc36§3,doc18 施策3-2</t>
         </is>
       </c>
       <c r="G146" s="23" t="inlineStr">
@@ -13588,12 +13588,12 @@
       </c>
       <c r="C147" s="25" t="inlineStr">
         <is>
-          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
+          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
         </is>
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
+          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
         </is>
       </c>
       <c r="E147" s="23" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="F147" s="23" t="inlineStr">
         <is>
-          <t>doc36§10-3,doc18 4-7(3)</t>
+          <t>doc36§3,doc18 4-7(2)</t>
         </is>
       </c>
       <c r="G147" s="23" t="inlineStr">
@@ -13626,22 +13626,22 @@
       </c>
       <c r="C148" s="25" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護を再開するかどうか</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E148" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F148" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 施策3-2</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G148" s="23" t="inlineStr">
@@ -13664,22 +13664,22 @@
       </c>
       <c r="C149" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E149" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F149" s="23" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 4-7(2)</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G149" s="23" t="inlineStr">
@@ -13702,12 +13702,12 @@
       </c>
       <c r="C150" s="25" t="inlineStr">
         <is>
-          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D150" s="25" t="inlineStr">
         <is>
-          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
         </is>
       </c>
       <c r="E150" s="23" t="inlineStr">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="F150" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc35§8,doc18 5-4(4)</t>
         </is>
       </c>
       <c r="G150" s="23" t="inlineStr">
@@ -13735,27 +13735,27 @@
       </c>
       <c r="B151" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C151" s="25" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
         </is>
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
         </is>
       </c>
       <c r="E151" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F151" s="23" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc07§4</t>
         </is>
       </c>
       <c r="G151" s="23" t="inlineStr">
@@ -13773,27 +13773,27 @@
       </c>
       <c r="B152" s="24" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C152" s="25" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
         </is>
       </c>
       <c r="D152" s="25" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。</t>
+          <t>評価指標の読み方に影響。</t>
         </is>
       </c>
       <c r="E152" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F152" s="23" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(4)</t>
+          <t>doc07§8-4</t>
         </is>
       </c>
       <c r="G152" s="23" t="inlineStr">
@@ -13816,22 +13816,22 @@
       </c>
       <c r="C153" s="25" t="inlineStr">
         <is>
-          <t>W125「第9期計画作成に向けた各種調査の実施」が4項目とも0点である理由</t>
+          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
         </is>
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>第9期報告書には調査結果が掲載されており、報告漏れの可能性が高い。第10期では確実に得点化したい。</t>
+          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
         </is>
       </c>
       <c r="E153" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F153" s="23" t="inlineStr">
         <is>
-          <t>doc07§4</t>
+          <t>doc08§4,§8-2</t>
         </is>
       </c>
       <c r="G153" s="23" t="inlineStr">
@@ -13854,22 +13854,22 @@
       </c>
       <c r="C154" s="25" t="inlineStr">
         <is>
-          <t>交付金「文書負担軽減」が11点→7点に低下した理由（取組の後退か判定基準の変更か）</t>
+          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
         </is>
       </c>
       <c r="D154" s="25" t="inlineStr">
         <is>
-          <t>評価指標の読み方に影響。</t>
+          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
         </is>
       </c>
       <c r="E154" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F154" s="23" t="inlineStr">
         <is>
-          <t>doc07§8-4</t>
+          <t>doc02§20-1</t>
         </is>
       </c>
       <c r="G154" s="23" t="inlineStr">
@@ -13892,22 +13892,22 @@
       </c>
       <c r="C155" s="25" t="inlineStr">
         <is>
-          <t>第9期概要版④「地域支援事業費」の集計範囲（任意事業の扱い）</t>
+          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
         </is>
       </c>
       <c r="D155" s="25" t="inlineStr">
         <is>
-          <t>決算と6,300〜10,100千円ずれる。揃えないと第10期が第9期と比較不能になる。</t>
+          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
         </is>
       </c>
       <c r="E155" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F155" s="23" t="inlineStr">
         <is>
-          <t>doc08§4,§8-2</t>
+          <t>doc32§1,§2</t>
         </is>
       </c>
       <c r="G155" s="23" t="inlineStr">
@@ -13930,27 +13930,27 @@
       </c>
       <c r="C156" s="25" t="inlineStr">
         <is>
-          <t>特別会計の歳入内訳の区分変更の有無（令和3→4年度）</t>
+          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
         </is>
       </c>
       <c r="D156" s="25" t="inlineStr">
         <is>
-          <t>総務費繰入金・低所得者保険料軽減繰入金が0になり一般会計繰入金が急増。時系列グラフが不連続になる。</t>
+          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
         </is>
       </c>
       <c r="E156" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F156" s="23" t="inlineStr">
         <is>
-          <t>doc02§20-1</t>
+          <t>doc38§B-2</t>
         </is>
       </c>
       <c r="G156" s="23" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>社内対応</t>
         </is>
       </c>
       <c r="H156" s="25" t="inlineStr"/>
@@ -13968,22 +13968,22 @@
       </c>
       <c r="C157" s="25" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項各号・第3項各号および基本指針の記載事項の条項番号の照合</t>
+          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
         </is>
       </c>
       <c r="D157" s="25" t="inlineStr">
         <is>
-          <t>★この作業環境ではe-Gov法令検索・厚労省サイトが外部接続ポリシーで遮断されており、条文本文を直接確認できていない。法令集または村・県への照会で照合が必要。給付適正化の条項を第3項第5号・第6号としていた誤りは訂正済（正しくは第2項第3号・第4号）。</t>
+          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
         </is>
       </c>
       <c r="E157" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F157" s="23" t="inlineStr">
         <is>
-          <t>doc32§1,§2</t>
+          <t>doc37§3-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G157" s="23" t="inlineStr">
@@ -14006,12 +14006,12 @@
       </c>
       <c r="C158" s="25" t="inlineStr">
         <is>
-          <t>総合事業の量（F29〜F40）は見える化そのものが令和3年3月で更新を止めている</t>
+          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
         </is>
       </c>
       <c r="D158" s="25" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の総合事業の量が空欄なのは村の未提供のためと整理していたが、見える化のF29〜F40（訪問型・通所型サービスA〜D・見守り・配食・介護予防ケアマネジメントの実施延べ件数）は令和2年3月・令和3年3月の2時点のみの収録で、本村の値は全て「-」。村の総合事業実施状況調査が唯一の出所である。素案5-12の記述を改める必要がある。</t>
+          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
         </is>
       </c>
       <c r="E158" s="23" t="inlineStr">
@@ -14021,12 +14021,12 @@
       </c>
       <c r="F158" s="23" t="inlineStr">
         <is>
-          <t>doc38§B-2</t>
+          <t>doc36§2,doc18 2-3</t>
         </is>
       </c>
       <c r="G158" s="23" t="inlineStr">
         <is>
-          <t>社内対応</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="H158" s="25" t="inlineStr"/>
@@ -14039,27 +14039,27 @@
       </c>
       <c r="B159" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C159" s="25" t="inlineStr">
         <is>
-          <t>要介護2の3区分の利用率の合計が101.5%となること</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D159" s="25" t="inlineStr">
         <is>
-          <t>★在宅73.5%＋居住系15.7%＋施設12.3%＝101.5%。年度の途中で在宅から施設へ移った方が両方に数えられているためとみられる（受給者数は年度の延べ）。重複は1.5%。給付実績により実人数を確認する。他の要介護度で100%に届かない分はサービスを使っていない方の割合（要介護1で13.1%、要介護5で21.0%）。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E159" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F159" s="23" t="inlineStr">
         <is>
-          <t>doc37§3-2,doc18 5-4</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G159" s="23" t="inlineStr">
@@ -14077,27 +14077,27 @@
       </c>
       <c r="B160" s="24" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C160" s="25" t="inlineStr">
         <is>
-          <t>認知症高齢者自立度（B7）の認定者数合計が認定者数（B4-a）と一致しない</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D160" s="25" t="inlineStr">
         <is>
-          <t>★B7の令和6年10月末の認定者数合計253人に対し、B4-aの令和7年3月末の認定者数は198人で55人の差。集計範囲が異なるとみられるが確認が取れていない。素案2-3では実数ではなく構成比（Ⅱ以上の割合63.6%）を中心に記載している。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E160" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F160" s="23" t="inlineStr">
         <is>
-          <t>doc36§2,doc18 2-3</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G160" s="23" t="inlineStr">
@@ -14120,22 +14120,22 @@
       </c>
       <c r="C161" s="25" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D161" s="25" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E161" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F161" s="23" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G161" s="23" t="inlineStr">
@@ -14158,22 +14158,22 @@
       </c>
       <c r="C162" s="25" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D162" s="25" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E162" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F162" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G162" s="23" t="inlineStr">
@@ -14196,22 +14196,22 @@
       </c>
       <c r="C163" s="25" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D163" s="25" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E163" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F163" s="23" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G163" s="23" t="inlineStr">
@@ -14234,22 +14234,22 @@
       </c>
       <c r="C164" s="25" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D164" s="25" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E164" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F164" s="23" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G164" s="23" t="inlineStr">
@@ -14267,27 +14267,27 @@
       </c>
       <c r="B165" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C165" s="25" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>北塩原村第六次総合振興計画の策定状況</t>
         </is>
       </c>
       <c r="D165" s="25" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
         </is>
       </c>
       <c r="E165" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F165" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc08§8-4</t>
         </is>
       </c>
       <c r="G165" s="23" t="inlineStr">
@@ -14305,27 +14305,27 @@
       </c>
       <c r="B166" s="24" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C166" s="25" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
         </is>
       </c>
       <c r="D166" s="25" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
         </is>
       </c>
       <c r="E166" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-73,Ⅱ-75</t>
         </is>
       </c>
       <c r="F166" s="23" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc01-5,doc18 1-2</t>
         </is>
       </c>
       <c r="G166" s="23" t="inlineStr">
@@ -14348,22 +14348,22 @@
       </c>
       <c r="C167" s="25" t="inlineStr">
         <is>
-          <t>北塩原村第六次総合振興計画の策定状況</t>
+          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
         </is>
       </c>
       <c r="D167" s="25" t="inlineStr">
         <is>
-          <t>第五次は2017〜2026。第10期（令和9〜11年度）の上位計画になる。</t>
+          <t>施策の書きぶりに影響。</t>
         </is>
       </c>
       <c r="E167" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-71,Ⅱ-72</t>
         </is>
       </c>
       <c r="F167" s="23" t="inlineStr">
         <is>
-          <t>doc08§8-4</t>
+          <t>doc01-12</t>
         </is>
       </c>
       <c r="G167" s="23" t="inlineStr">
@@ -14386,22 +14386,22 @@
       </c>
       <c r="C168" s="25" t="inlineStr">
         <is>
-          <t>認知症施策推進計画・成年後見制度利用促進基本計画の一体化を第10期も踏襲するか</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D168" s="25" t="inlineStr">
         <is>
-          <t>第9期は基本目標4に内包する構成。素案は踏襲を前提に1-2で法的根拠を記載している。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E168" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-73,Ⅱ-75</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F168" s="23" t="inlineStr">
         <is>
-          <t>doc01-5,doc18 1-2</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G168" s="23" t="inlineStr">
@@ -14419,27 +14419,27 @@
       </c>
       <c r="B169" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C169" s="25" t="inlineStr">
         <is>
-          <t>定住自立圏（喜多方市・西会津町）／会津権利擁護・成年後見センターとの広域連携の記載方針</t>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
         </is>
       </c>
       <c r="D169" s="25" t="inlineStr">
         <is>
-          <t>施策の書きぶりに影響。</t>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
         </is>
       </c>
       <c r="E169" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-72</t>
+          <t>Ⅰ-31</t>
         </is>
       </c>
       <c r="F169" s="23" t="inlineStr">
         <is>
-          <t>doc01-12</t>
+          <t>doc19 追-6</t>
         </is>
       </c>
       <c r="G169" s="23" t="inlineStr">
@@ -14457,27 +14457,27 @@
       </c>
       <c r="B170" s="24" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C170" s="25" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
         </is>
       </c>
       <c r="D170" s="25" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
         </is>
       </c>
       <c r="E170" s="23" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅰ-40,Ⅰ-42</t>
         </is>
       </c>
       <c r="F170" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc19 追-7</t>
         </is>
       </c>
       <c r="G170" s="23" t="inlineStr">
@@ -14500,22 +14500,22 @@
       </c>
       <c r="C171" s="25" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
         </is>
       </c>
       <c r="D171" s="25" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
         </is>
       </c>
       <c r="E171" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F171" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc23§1-3</t>
         </is>
       </c>
       <c r="G171" s="23" t="inlineStr">
@@ -14538,22 +14538,22 @@
       </c>
       <c r="C172" s="25" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>送付状の個人情報に関する説明の補強</t>
         </is>
       </c>
       <c r="D172" s="25" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
         </is>
       </c>
       <c r="E172" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F172" s="23" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc27§5-1</t>
         </is>
       </c>
       <c r="G172" s="23" t="inlineStr">
@@ -14576,12 +14576,12 @@
       </c>
       <c r="C173" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
       <c r="D173" s="25" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
       <c r="E173" s="23" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F173" s="23" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc27§4</t>
         </is>
       </c>
       <c r="G173" s="23" t="inlineStr">
@@ -14602,34 +14602,34 @@
       <c r="H173" s="25" t="inlineStr"/>
     </row>
     <row r="174" ht="34" customHeight="1">
-      <c r="A174" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A174" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B174" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C174" s="25" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
       <c r="D174" s="25" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
       <c r="E174" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
       <c r="F174" s="23" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc01-10</t>
         </is>
       </c>
       <c r="G174" s="23" t="inlineStr">
@@ -14640,34 +14640,34 @@
       <c r="H174" s="25" t="inlineStr"/>
     </row>
     <row r="175" ht="34" customHeight="1">
-      <c r="A175" s="36" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A175" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B175" s="24" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C175" s="25" t="inlineStr">
         <is>
-          <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
+          <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
         </is>
       </c>
       <c r="D175" s="25" t="inlineStr">
         <is>
-          <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
+          <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
         </is>
       </c>
       <c r="E175" s="23" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F175" s="23" t="inlineStr">
         <is>
-          <t>doc27§4</t>
+          <t>doc01-10,doc08</t>
         </is>
       </c>
       <c r="G175" s="23" t="inlineStr">
@@ -14677,88 +14677,88 @@
       </c>
       <c r="H175" s="25" t="inlineStr"/>
     </row>
-    <row r="176" ht="34" customHeight="1">
-      <c r="A176" s="37" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B176" s="24" t="inlineStr">
-        <is>
-          <t>成果品</t>
-        </is>
-      </c>
-      <c r="C176" s="25" t="inlineStr">
-        <is>
-          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
-        </is>
-      </c>
-      <c r="D176" s="25" t="inlineStr">
-        <is>
-          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
-        </is>
-      </c>
-      <c r="E176" s="23" t="inlineStr">
-        <is>
-          <t>Ⅱ-113,Ⅳ-89</t>
-        </is>
-      </c>
-      <c r="F176" s="23" t="inlineStr">
-        <is>
-          <t>doc01-10</t>
-        </is>
-      </c>
-      <c r="G176" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H176" s="25" t="inlineStr"/>
-    </row>
-    <row r="177" ht="34" customHeight="1">
-      <c r="A177" s="37" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B177" s="24" t="inlineStr">
-        <is>
-          <t>成果品</t>
-        </is>
-      </c>
-      <c r="C177" s="25" t="inlineStr">
-        <is>
-          <t>概要版の要否（仕様書に記載なし。第9期は概要版を作成している）</t>
-        </is>
-      </c>
-      <c r="D177" s="25" t="inlineStr">
-        <is>
-          <t>★第9期概要版（2ページ）の現物を受領し存在を確認。仕様書に記載がないため別途対応か要確認。</t>
-        </is>
-      </c>
-      <c r="E177" s="23" t="inlineStr">
-        <is>
-          <t>Ⅳ-92</t>
-        </is>
-      </c>
-      <c r="F177" s="23" t="inlineStr">
-        <is>
-          <t>doc01-10,doc08</t>
-        </is>
-      </c>
-      <c r="G177" s="23" t="inlineStr">
-        <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="H177" s="25" t="inlineStr"/>
-    </row>
-    <row r="179" ht="20" customHeight="1">
-      <c r="A179" s="38" t="inlineStr">
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="38" t="inlineStr">
         <is>
           <t>■ 解決済み（記録）</t>
         </is>
       </c>
+    </row>
+    <row r="178" ht="34" customHeight="1">
+      <c r="A178" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B178" s="40" t="inlineStr">
+        <is>
+          <t>疑義</t>
+        </is>
+      </c>
+      <c r="C178" s="41" t="inlineStr">
+        <is>
+          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
+        </is>
+      </c>
+      <c r="D178" s="41" t="inlineStr">
+        <is>
+          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
+        </is>
+      </c>
+      <c r="E178" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-56,Ⅱ-64</t>
+        </is>
+      </c>
+      <c r="F178" s="39" t="inlineStr">
+        <is>
+          <t>doc35§7-3(1)</t>
+        </is>
+      </c>
+      <c r="G178" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H178" s="41" t="inlineStr"/>
+    </row>
+    <row r="179" ht="34" customHeight="1">
+      <c r="A179" s="39" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="B179" s="40" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C179" s="41" t="inlineStr">
+        <is>
+          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
+        </is>
+      </c>
+      <c r="D179" s="41" t="inlineStr">
+        <is>
+          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
+        </is>
+      </c>
+      <c r="E179" s="39" t="inlineStr">
+        <is>
+          <t>Ⅱ-68,Ⅱ-69</t>
+        </is>
+      </c>
+      <c r="F179" s="39" t="inlineStr">
+        <is>
+          <t>doc28§3</t>
+        </is>
+      </c>
+      <c r="G179" s="39" t="inlineStr">
+        <is>
+          <t>解決済</t>
+        </is>
+      </c>
+      <c r="H179" s="41" t="inlineStr"/>
     </row>
     <row r="180" ht="34" customHeight="1">
       <c r="A180" s="39" t="inlineStr">
@@ -14768,27 +14768,27 @@
       </c>
       <c r="B180" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C180" s="41" t="inlineStr">
         <is>
-          <t>第1号被保険者数・認定者数の推計に2系列が併存していた（社内・解消済）</t>
+          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
         </is>
       </c>
       <c r="D180" s="41" t="inlineStr">
         <is>
-          <t>★素案5-2・5-3が社人研推計（国勢調査ベース）、5-4以降が厚生労働省配布の推計用人口（住民基本台帳ベース）を用いており、令和11年の認定者数が230人と220人で食い違っていた。厚生労働省配布の系列（B案）に統一し、5-1・5-2・5-3を全面的に書き改めた。介護保険の第1号被保険者数が住民基本台帳を基礎とすること、国の推計ワークシートが同じ配布データを用いることによる。</t>
+          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
         </is>
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-64</t>
+          <t>０-04</t>
         </is>
       </c>
       <c r="F180" s="39" t="inlineStr">
         <is>
-          <t>doc35§7-3(1)</t>
+          <t>doc28§4</t>
         </is>
       </c>
       <c r="G180" s="39" t="inlineStr">
@@ -14811,22 +14811,22 @@
       </c>
       <c r="C181" s="41" t="inlineStr">
         <is>
-          <t>成年後見制度（市民後見人養成含む）の利用実態・実績</t>
+          <t>所得段階別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D181" s="41" t="inlineStr">
         <is>
-          <t>令和7・8年度の成年後見制度利用促進施策に係る取組状況調査（市町村票）と会津権利擁護・成年後見センターの相談件数の受領により解決。利用者4人、市町村長申立て0件、市民後見人の登録0人・受任0件、中核機関・協議会・申立費用助成・報酬助成はいずれも整備済。</t>
+          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
         </is>
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-69</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F181" s="39" t="inlineStr">
         <is>
-          <t>doc28§3</t>
+          <t>doc28§2</t>
         </is>
       </c>
       <c r="G181" s="39" t="inlineStr">
@@ -14844,27 +14844,27 @@
       </c>
       <c r="B182" s="40" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C182" s="41" t="inlineStr">
         <is>
-          <t>所管課・窓口の確認（住民課→保健福祉課の変更の有無、担当者体制）</t>
+          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
         </is>
       </c>
       <c r="D182" s="41" t="inlineStr">
         <is>
-          <t>成年後見の調査票により解決。報告担当課・主管課とも保健福祉課、担当は小林 洋一様、電話0241-23-3113、メールfukushi01@vill.kitashiobara.fukushima.jp。調査票の問合せ先表記も裏づけられた。</t>
+          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
         </is>
       </c>
       <c r="E182" s="39" t="inlineStr">
         <is>
-          <t>０-04</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F182" s="39" t="inlineStr">
         <is>
-          <t>doc28§4</t>
+          <t>doc28§1</t>
         </is>
       </c>
       <c r="G182" s="39" t="inlineStr">
@@ -14882,32 +14882,32 @@
       </c>
       <c r="B183" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C183" s="41" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数</t>
+          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
         </is>
       </c>
       <c r="D183" s="41" t="inlineStr">
         <is>
-          <t>令和8年度合計所得金額分布調査の入力済み調査票により解決。13段階・合計1,015人。非課税層60.3%、第1〜3段階だけで346人・34.1%。10万円刻みの分布も入手。</t>
+          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
         </is>
       </c>
       <c r="E183" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F183" s="39" t="inlineStr">
         <is>
-          <t>doc28§2</t>
+          <t>doc27§1-1</t>
         </is>
       </c>
       <c r="G183" s="39" t="inlineStr">
         <is>
-          <t>解決済</t>
+          <t>解決済（一部再掲）</t>
         </is>
       </c>
       <c r="H183" s="41" t="inlineStr"/>
@@ -14920,27 +14920,27 @@
       </c>
       <c r="B184" s="40" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C184" s="41" t="inlineStr">
         <is>
-          <t>第10期の将来推計人口・第1号被保険者数の推計データ</t>
+          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
         </is>
       </c>
       <c r="D184" s="41" t="inlineStr">
         <is>
-          <t>厚労省配布の第10期将来推計用人口推計（住基ベース）と補正係数の受領により解決。補正後の第1号被保険者数は令和9年946人／令和10年939人／令和11年931人。ただし直近実績を約6%下回る論点あり（K-106）。</t>
+          <t>第2稿（0904版）で両方とも修正済。</t>
         </is>
       </c>
       <c r="E184" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F184" s="39" t="inlineStr">
         <is>
-          <t>doc28§1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G184" s="39" t="inlineStr">
@@ -14963,27 +14963,27 @@
       </c>
       <c r="C185" s="41" t="inlineStr">
         <is>
-          <t>ニーズ調査 選択肢の順序が標準と逆になっている7か所の修正</t>
+          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
         </is>
       </c>
       <c r="D185" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で問7の6か所を修正済。誤植2件（「そのような人はいないその他」「いないその他」）も解消。★問1(2)①の1か所が未修正のため別項目として再掲。</t>
+          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
         </is>
       </c>
       <c r="E185" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F185" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-1</t>
+          <t>doc27§1-2</t>
         </is>
       </c>
       <c r="G185" s="39" t="inlineStr">
         <is>
-          <t>解決済（一部再掲）</t>
+          <t>解決済（番号は再掲）</t>
         </is>
       </c>
       <c r="H185" s="41" t="inlineStr"/>
@@ -15001,22 +15001,22 @@
       </c>
       <c r="C186" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 前回指摘2件の反映（介護療養型医療施設の削除／傷病の選択肢13・14の入替）</t>
+          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
         </is>
       </c>
       <c r="D186" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で両方とも修正済。</t>
+          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
         </is>
       </c>
       <c r="E186" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F186" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G186" s="39" t="inlineStr">
@@ -15039,27 +15039,27 @@
       </c>
       <c r="C187" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 標準の問13「訪問診療」の復活</t>
+          <t>在宅介護実態調査 約150人の抽出基準</t>
         </is>
       </c>
       <c r="D187" s="41" t="inlineStr">
         <is>
-          <t>第2稿（0904版）で復活。★ただし番号が問12として付されており問13が欠番。番号の修正を別項目として再掲。</t>
+          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
         </is>
       </c>
       <c r="E187" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-08,Ⅰ-24</t>
         </is>
       </c>
       <c r="F187" s="39" t="inlineStr">
         <is>
-          <t>doc27§1-2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G187" s="39" t="inlineStr">
         <is>
-          <t>解決済（番号は再掲）</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="H187" s="41" t="inlineStr"/>
@@ -15072,27 +15072,27 @@
       </c>
       <c r="B188" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C188" s="41" t="inlineStr">
         <is>
-          <t>調査の基準日（ニーズ調査・在宅介護実態調査）</t>
+          <t>施策体系図（基本理念→基本目標5→施策28の階層図）の計画書への掲載</t>
         </is>
       </c>
       <c r="D188" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議（令和8年9月1日）で決着：令和8年9月1日を基準日とする。</t>
+          <t>★2026/09/25 作成して素案3-4と委員会資料4-4に掲載した。第9期が第3章に掲げていた施策体系とSDGsの対応を、体系図（3-4）と対応表（3-5）の2本立てに再構成したもの。3-4にあった同じ内容の平坦な表は図に置き換えて重複を解いた。計画書の推定は97頁で仕様書の約100頁に3頁の余裕がある。</t>
         </is>
       </c>
       <c r="E188" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅱ-113,Ⅱ-71</t>
         </is>
       </c>
       <c r="F188" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc41§6</t>
         </is>
       </c>
       <c r="G188" s="39" t="inlineStr">
@@ -15110,27 +15110,27 @@
       </c>
       <c r="B189" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C189" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 約150人の抽出基準</t>
+          <t>在宅調査票の管理番号の印字形式（N付きか数字のみか）</t>
         </is>
       </c>
       <c r="D189" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：要支援1・2および要介護1〜5の在宅生活者等、150件。</t>
+          <t>★2026/09/28 決着：調査票の印字見本の「1」はあくまで見本であり、実物には対象者ごとの管理番号が入る。名簿の形式（ニーズは数字のみ、在宅は英字＋数字）がそのまま印字される。当方が印字見本を実物と取り違えて優先度Sとしていたもので、問題は生じない。なお回収後の突合は管理番号によるが、万一欠損した場合は氏名で突合できることを村にご確認いただいた。</t>
         </is>
       </c>
       <c r="E189" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24</t>
+          <t>Ⅰ-18,Ⅰ-20,Ⅰ-38</t>
         </is>
       </c>
       <c r="F189" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc34§5-3,doc43§2-4</t>
         </is>
       </c>
       <c r="G189" s="39" t="inlineStr">
@@ -15148,27 +15148,27 @@
       </c>
       <c r="B190" s="40" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C190" s="41" t="inlineStr">
         <is>
-          <t>施策体系図（基本理念→基本目標5→施策28の階層図）の計画書への掲載</t>
+          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
         </is>
       </c>
       <c r="D190" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/25 作成して素案3-4と委員会資料4-4に掲載した。第9期が第3章に掲げていた施策体系とSDGsの対応を、体系図（3-4）と対応表（3-5）の2本立てに再構成したもの。3-4にあった同じ内容の平坦な表は図に置き換えて重複を解いた。計画書の推定は97頁で仕様書の約100頁に3頁の余裕がある。</t>
+          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
         </is>
       </c>
       <c r="E190" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅱ-71</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F190" s="39" t="inlineStr">
         <is>
-          <t>doc41§6</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G190" s="39" t="inlineStr">
@@ -15186,27 +15186,27 @@
       </c>
       <c r="B191" s="40" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C191" s="41" t="inlineStr">
         <is>
-          <t>配布・回収方法と宛名ラベル・封筒の用意</t>
+          <t>配布用封筒の用意の主体（仕様書4Ⅰ(3)は受託者の印刷対象としている）</t>
         </is>
       </c>
       <c r="D191" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：郵送（紙）とWeb回答（QRコード）の併用。宛名ラベル・封筒は北塩原村が用意。回収は村で100件程度集まるごとに随時受託者へ小分け送付。</t>
+          <t>★2026/09/24 村の回答で決着：配布用封筒は村が用意し、費用は村側で請求処理する。受託者が印刷するのは返信用（回収用）のみ。仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消した。</t>
         </is>
       </c>
       <c r="E191" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-23,Ⅰ-26,Ⅰ-103</t>
         </is>
       </c>
       <c r="F191" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc39§5</t>
         </is>
       </c>
       <c r="G191" s="39" t="inlineStr">
@@ -15229,17 +15229,17 @@
       </c>
       <c r="C192" s="41" t="inlineStr">
         <is>
-          <t>配布用封筒の用意の主体（仕様書4Ⅰ(3)は受託者の印刷対象としている）</t>
+          <t>在宅介護実態調査の対象者数（仕様書の約150人に対し118人）</t>
         </is>
       </c>
       <c r="D192" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：配布用封筒は村が用意し、費用は村側で請求処理する。受託者が印刷するのは返信用（回収用）のみ。仕様書4Ⅰ(3)の「封筒（配布用・回収用）」との差異は解消した。</t>
+          <t>★2026/09/24 村の回答で決着：118人で問題なし。仕様書4Ⅰ(1)の「約150人」との差異は解消した。集計設計上のセル数の扱いは当方の判断事項として継続。</t>
         </is>
       </c>
       <c r="E192" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-23,Ⅰ-26,Ⅰ-103</t>
+          <t>Ⅰ-08,Ⅰ-24,Ⅰ-103</t>
         </is>
       </c>
       <c r="F192" s="39" t="inlineStr">
@@ -15262,22 +15262,22 @@
       </c>
       <c r="B193" s="40" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C193" s="41" t="inlineStr">
         <is>
-          <t>在宅介護実態調査の対象者数（仕様書の約150人に対し118人）</t>
+          <t>アンケート調査報告書の分量（仕様書の約100頁に対し想定118頁）</t>
         </is>
       </c>
       <c r="D193" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：118人で問題なし。仕様書4Ⅰ(1)の「約150人」との差異は解消した。集計設計上のセル数の扱いは当方の判断事項として継続。</t>
+          <t>★2026/09/24 村の回答で決着：仕様書どおり約100頁に統一する。第Ⅱ部（分析編25頁）は計画の根拠のため維持し、第Ⅰ部（単純集計編）と資料編で18頁を圧縮する（doc24§1改訂）。部数は仕様書のとおり10部。</t>
         </is>
       </c>
       <c r="E193" s="39" t="inlineStr">
         <is>
-          <t>Ⅰ-08,Ⅰ-24,Ⅰ-103</t>
+          <t>Ⅳ-90</t>
         </is>
       </c>
       <c r="F193" s="39" t="inlineStr">
@@ -15305,22 +15305,22 @@
       </c>
       <c r="C194" s="41" t="inlineStr">
         <is>
-          <t>アンケート調査報告書の分量（仕様書の約100頁に対し想定118頁）</t>
+          <t>100頁への圧縮の当て方（集計編を圧縮するか、調査票を電子媒体に移すか）</t>
         </is>
       </c>
       <c r="D194" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/24 村の回答で決着：仕様書どおり約100頁に統一する。第Ⅱ部（分析編25頁）は計画の根拠のため維持し、第Ⅰ部（単純集計編）と資料編で18頁を圧縮する（doc24§1改訂）。部数は仕様書のとおり10部。</t>
+          <t>★2026/09/25 案Bを採用：調査票2種・単純集計表・自由記述の全文を電子媒体に収録し、資料編を25頁→6頁とする。浮いた頁を集計編に戻し第3章42頁・第4章21頁（計63頁・1頁1.7設問）とした。当初案118頁と同じ密度を100頁の枠内で保てる。案A（集計編を47頁に圧縮）は1頁2.3設問で第9期の2.5倍の密度となり、選択肢の多い設問が物理的に入らないため採らなかった。</t>
         </is>
       </c>
       <c r="E194" s="39" t="inlineStr">
         <is>
-          <t>Ⅳ-90</t>
+          <t>Ⅳ-90,Ⅰ-48,Ⅳ-91,Ⅳ-114</t>
         </is>
       </c>
       <c r="F194" s="39" t="inlineStr">
         <is>
-          <t>doc39§5</t>
+          <t>doc24§1-1,doc40§2</t>
         </is>
       </c>
       <c r="G194" s="39" t="inlineStr">
@@ -15338,27 +15338,27 @@
       </c>
       <c r="B195" s="40" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C195" s="41" t="inlineStr">
         <is>
-          <t>100頁への圧縮の当て方（集計編を圧縮するか、調査票を電子媒体に移すか）</t>
+          <t>整合を図る関連計画の範囲</t>
         </is>
       </c>
       <c r="D195" s="41" t="inlineStr">
         <is>
-          <t>★2026/09/25 案Bを採用：調査票2種・単純集計表・自由記述の全文を電子媒体に収録し、資料編を25頁→6頁とする。浮いた頁を集計編に戻し第3章42頁・第4章21頁（計63頁・1頁1.7設問）とした。当初案118頁と同じ密度を100頁の枠内で保てる。案A（集計編を47頁に圧縮）は1頁2.3設問で第9期の2.5倍の密度となり、選択肢の多い設問が物理的に入らないため採らなかった。</t>
+          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
         </is>
       </c>
       <c r="E195" s="39" t="inlineStr">
         <is>
-          <t>Ⅳ-90,Ⅰ-48,Ⅳ-91,Ⅳ-114</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F195" s="39" t="inlineStr">
         <is>
-          <t>doc24§1-1,doc40§2</t>
+          <t>doc22 §1</t>
         </is>
       </c>
       <c r="G195" s="39" t="inlineStr">
@@ -15376,27 +15376,27 @@
       </c>
       <c r="B196" s="40" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C196" s="41" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の範囲</t>
+          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
         </is>
       </c>
       <c r="D196" s="41" t="inlineStr">
         <is>
-          <t>キックオフ会議で決着：国の基本方針・総合計画・障がい福祉計画・地域福祉計画・グッドヘルスプラン（21計画）・生涯学習計画。</t>
+          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
         </is>
       </c>
       <c r="E196" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F196" s="39" t="inlineStr">
         <is>
-          <t>doc22 §1</t>
+          <t>doc20§3,§4</t>
         </is>
       </c>
       <c r="G196" s="39" t="inlineStr">
@@ -15419,12 +15419,12 @@
       </c>
       <c r="C197" s="41" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金（W系）の福島県平均・全国平均</t>
+          <t>交付要綱の配点表（満点）</t>
         </is>
       </c>
       <c r="D197" s="41" t="inlineStr">
         <is>
-          <t>厚労省の全国集計表（令和6・7・8年度）の受領により解決。全国平均・中央値・標準偏差・該当率・全国順位を取得し、県内59市町村の生データから県平均・県内順位も算出。</t>
+          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
         </is>
       </c>
       <c r="E197" s="39" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="F197" s="39" t="inlineStr">
         <is>
-          <t>doc20§3,§4</t>
+          <t>doc20§2</t>
         </is>
       </c>
       <c r="G197" s="39" t="inlineStr">
@@ -15457,12 +15457,12 @@
       </c>
       <c r="C198" s="41" t="inlineStr">
         <is>
-          <t>交付要綱の配点表（満点）</t>
+          <t>令和6年度・令和7年度の交付金評価結果</t>
         </is>
       </c>
       <c r="D198" s="41" t="inlineStr">
         <is>
-          <t>令和8年度評価指標（市町村分）の配点表を受領し解決。推進交付金400点・支援交付金400点、目標Ⅰ〜Ⅳ各100点と判明。</t>
+          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
         </is>
       </c>
       <c r="E198" s="39" t="inlineStr">
@@ -15472,7 +15472,7 @@
       </c>
       <c r="F198" s="39" t="inlineStr">
         <is>
-          <t>doc20§2</t>
+          <t>doc20§3-1</t>
         </is>
       </c>
       <c r="G198" s="39" t="inlineStr">
@@ -15495,22 +15495,22 @@
       </c>
       <c r="C199" s="41" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の交付金評価結果</t>
+          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
         </is>
       </c>
       <c r="D199" s="41" t="inlineStr">
         <is>
-          <t>令和6・7・8年度の3か年を指標単位で取得し解決。合計295→339→447点。第10期の基準値は令和8年度447点/800点に置く。</t>
+          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
         </is>
       </c>
       <c r="E199" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-56,Ⅱ-58</t>
         </is>
       </c>
       <c r="F199" s="39" t="inlineStr">
         <is>
-          <t>doc20§3-1</t>
+          <t>doc09</t>
         </is>
       </c>
       <c r="G199" s="39" t="inlineStr">
@@ -15533,22 +15533,22 @@
       </c>
       <c r="C200" s="41" t="inlineStr">
         <is>
-          <t>高齢化率・認定率・費用額・保険料の福島県平均／全国平均</t>
+          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
         </is>
       </c>
       <c r="D200" s="41" t="inlineStr">
         <is>
-          <t>地域分析P1〜P4の受領により解決。県内順位・全国順位も入手。</t>
+          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
         </is>
       </c>
       <c r="E200" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-58</t>
+          <t>Ⅱ-59</t>
         </is>
       </c>
       <c r="F200" s="39" t="inlineStr">
         <is>
-          <t>doc09</t>
+          <t>doc02§20-2</t>
         </is>
       </c>
       <c r="G200" s="39" t="inlineStr">
@@ -15571,22 +15571,22 @@
       </c>
       <c r="C201" s="41" t="inlineStr">
         <is>
-          <t>1人あたり指標に用いる高齢者人口の分母の統一</t>
+          <t>国の指針・様式の更新有無</t>
         </is>
       </c>
       <c r="D201" s="41" t="inlineStr">
         <is>
-          <t>C1系の分母がB1第1号被保険者数であることを確認し解決。計画書はB1に統一。</t>
+          <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
         </is>
       </c>
       <c r="E201" s="39" t="inlineStr">
         <is>
-          <t>Ⅱ-59</t>
+          <t>Ⅰ-11</t>
         </is>
       </c>
       <c r="F201" s="39" t="inlineStr">
         <is>
-          <t>doc02§20-2</t>
+          <t>doc04,doc05</t>
         </is>
       </c>
       <c r="G201" s="39" t="inlineStr">
@@ -15596,56 +15596,18 @@
       </c>
       <c r="H201" s="41" t="inlineStr"/>
     </row>
-    <row r="202" ht="34" customHeight="1">
-      <c r="A202" s="39" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="B202" s="40" t="inlineStr">
-        <is>
-          <t>データ</t>
-        </is>
-      </c>
-      <c r="C202" s="41" t="inlineStr">
-        <is>
-          <t>国の指針・様式の更新有無</t>
-        </is>
-      </c>
-      <c r="D202" s="41" t="inlineStr">
-        <is>
-          <t>令和7年8月版の標準様式を入手し逐条突合を完了（要確認0件）。</t>
-        </is>
-      </c>
-      <c r="E202" s="39" t="inlineStr">
-        <is>
-          <t>Ⅰ-11</t>
-        </is>
-      </c>
-      <c r="F202" s="39" t="inlineStr">
-        <is>
-          <t>doc04,doc05</t>
-        </is>
-      </c>
-      <c r="G202" s="39" t="inlineStr">
-        <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="H202" s="41" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:H177"/>
+  <autoFilter ref="A4:H175"/>
   <mergeCells count="3">
+    <mergeCell ref="A177:H177"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A179:H179"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未依頼,依頼済,回答待ち,回答済,解決済"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/05_北塩原村第10期_WBS進捗管理表.xlsx
+++ b/output/05_北塩原村第10期_WBS進捗管理表.xlsx
@@ -6474,7 +6474,7 @@
       </c>
       <c r="P92" s="13" t="inlineStr">
         <is>
-          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。★9/15：見込量算定の第1次概算を反映（doc35）。あわせて素案の記述を令和8年度の交付金評価指標で検算し、複数の訂正を行った。(1)中長期の保険料を算定し5-11の【要確認】を解消（αを23%据え置くと令和22年度6,883円、3年ごとに1ポイント上がると8,379円）。(2)標準給付費の様式を埋め5-6を確定（3か年854,014千円）。5-7と完全に一致。(3)交付金の評価指標を令和8年度で検算したところ、素案の記述の多くが令和6年度または令和4年度の評価に基づいており実態と食い違っていた。通いの場への参加率は0→8点満点（最上位の段階は全国で約10%）、参加促進のアウトリーチは9点満点、地域リハビリテーションの推進は0→7点満点、計画の進捗管理（目標Ⅰの3項目）は0→48点満点。一方、要介護3〜5の状態の変化は2指標とも0点（35点減）、認知症サポーター数は12点中0点、難聴は20点中0点。施策1-1を「通いの場の再構築と参加率の向上」から「通いの場の開催頻度の向上と地区差の是正」に改称し、課題3の見出しも改めた。(4)6-3の成果目標・活動指標に令和8年度の得点と全国平均を併記し、維持6指標・引上げ5指標に整理。(5)認知症基本法13条1項・成年後見促進法14条1項を確認し1-2の【要確認】を解消。素案は2,197行→2,341行。★9/15：3次にわたり修正。(1)見込量算定の第1次概算を反映（doc35）。(2)令和8年度の交付金評価指標で全記述を検算し、施策1-1の名称と課題3の見出しを改めた。(3)推計の系列を統一し、介護給付費と予防給付費を分離、見込量の自己点検を実施。5-12（据え置き項目31件）を新設。素案は約115頁→2,449行（段落約4,400・表約125・図20）。残る空欄は交付金の交付見込額、高齢者福祉サービスの量の目標の一部、委員名簿・パブコメなど確定後に記入するもの。★9/16：交付金の目標別に全国平均と対比したところ、素案2-8の「認知症総合支援が全国平均を下回る唯一の目標」が誤りと判明（上回るのは3目標、下回るのは5目標。認知症総合支援は差が最大の▲19.1点）。2-8に目標別の対比表を新設し関係箇所を訂正した。あわせて薄い節を埋めた（1-5日常生活圏域・4-2〜4-4基本目標の導入・5-10低所得者）。6-4に乖離の検証の見直しの目安（±5%以内／±5〜12%／±12%超）を、6-5に計画期間中に確定する5項目を新設。±12%は推計の誤差の絶対値の平均11.9%（保険料月額約700円）によるもので、この幅を超える乖離は基金の取崩しでは吸収できない。素案は2,449行→2,509行。★9/16：認知症施策推進計画としての検討（doc36）。本計画は認知症基本法第13条第1項の市町村計画を兼ねるが、認知症施策は施策4-4の1本のみで基本法の基本的施策との対応が示されていなかった。第4章に4-7「認知症施策推進計画としての位置づけ」を新設し、3つの基本的な考え方（新しい認知症観・本人および家族等の参画・共生社会）、基本法第14〜23条の10項目と本計画の施策との対応表、本村の状況、本人・家族の参画の方法、指標8件を掲載した。2-3に認知症高齢者の状況（自立度Ⅱ以上161人・2年間で22.0%増・認定者に占める割合63.6%）を新設。あわせて第4章の施策番号に「施策」を冠し、基本目標の節番号との衝突（4-4が基本目標4と施策4-4の両方を指す状態）を解消した。素案は2,509行→2,633行。★9/16（第2次）：認知症基本法の条文（令和5年法律第65号）と厚生労働省の概要資料を受領し、素案4-7を検算した。3件の誤りを訂正——(1)市町村が計画に位置づけるのは第14〜23条の10項目ではなく第14〜21条の8項目（第22条以降は主語が「国は」）、(2)意見聴取の根拠は第13条第3項ではなく「第13条第3項において準用する第12条第3項」、(3)第15条バリアフリー化の対応施策は住まい・除雪ではなく移動・見守り（条文の例示による）。あわせて条文から新たに4件を素案に追加——第13条第3項が準用する第12条第4〜7項（計画の公表・実施状況の評価と公表・5年ごとの検討・評価結果の取りまとめ時の意見聴取）、第9条（認知症の日9月21日・認知症月間9月）、第7条（公共交通・金融機関・小売業者等の合理的配慮）、第16条第2項（若年性認知症の雇用継続）。4-7を全面改訂し8つの見出しに再構成した。素案は2,633行→2,677行。★9/24：素案の自己点検16件を新設（verify_soan.py）。全件適合で終了コード0、不適合なら1。素案の数値は算定スクリプトの出力を手書きで書き写しているため、算定を改めたときの乖離を検出する。大雪は素案の生成が算定をrunpyで直接読む形に改めたが、本村は構造を変える工数が大きいため点検で代替する。点検項目は人口・認定者数・区分別受給者数・標準給付費の内部整合・給付費の分離・地域支援事業費・年度別保険料・中長期保険料・定員到達率・利用率の分母・二重計上の注記・乖離の目安・認知症基本法の条項・節番号の重複・据え置き一覧の16件。素案は2,715行→2,758行。★9/24（第2次）：未解決の確認事項46件を見える化での確認可否により4分類し（doc38）、取得済みでありながら素案で使っていなかった2件を投入した。(1)介護サービス自給率（δ2系）を2-5に新設。全体46.5%・訪問系41.1%・通所系79.3%・短期入所系0%・施設居住系41.3%（令和7年度）。訪問系は令和3年度62.7%から21.6pt低下しており村内の供給力の低下が疑われる。施設居住系は給付の58.7%が村外。(2)居宅介護支援・介護予防支援の受給者数を5-4(9)に投入。見える化の2系列から逆算し（D13-r×B1÷D17-l）、令和3〜7年度の値が在宅サービス受給者数と0.1人以内で一致することを確認した。従前は全て空欄であった。素案は2,758行→2,787行。</t>
+          <t>doc18／output/06_計画素案.docx として全6章・65節・73表・図20点を作成。第2章の図はモノクロ印刷を前提に明度差＋線種＋マーカー＋ハッチングで識別。施策2-6「冬期の生活支援（除雪）」を新設し施策26本。サービス区分別分析（訪問系−50.8%）を追加。★9/8：第5章5-4・5-5・5-6にサービス見込量と給付費の暫定推計値を投入（doc30）。あわせて資料編（策定経過・委員名簿・アンケート調査の概要・パブリックコメント・用語の解説69語）を新設。★9/8：第5章の章題を仕様書・第9期の構成に合わせ「介護保険料の設定」に変更し、5-8介護給付適正化計画・5-9保険者機能強化推進交付金等の活用の2節を新設（第9期の並びに沿わせた）。★9/10：法定記載事項をチェックし（doc32）、欠落5件を反映——地域密着型サービスの必要利用定員総数（介保法117条2項1号・義務）、老人福祉事業の量の目標（老福法20条の8第2項・義務、第4章4-6を新設）、地域支援事業の量の見込み（同117条2項2号・義務）、医療計画との整合（同117条5項）、高齢者虐待の防止・BCP・避難確保計画（基本指針）。あわせて給付適正化の根拠を「117条3項5号6号（努力義務）」から「117条2項3号4号（義務）」に訂正。全6章＋資料編・約115頁。残る空欄は地域支援事業費の事業別内訳、交付金の交付見込額、および確定後に記入する日付・名簿。★9/15：見込量算定の第1次概算を反映（doc35）。あわせて素案の記述を令和8年度の交付金評価指標で検算し、複数の訂正を行った。(1)中長期の保険料を算定し5-11の【要確認】を解消（αを23%据え置くと令和22年度6,883円、3年ごとに1ポイント上がると8,379円）。(2)標準給付費の様式を埋め5-6を確定（3か年854,014千円）。5-7と完全に一致。(3)交付金の評価指標を令和8年度で検算したところ、素案の記述の多くが令和6年度または令和4年度の評価に基づいており実態と食い違っていた。通いの場への参加率は0→8点満点（最上位の段階は全国で約10%）、参加促進のアウトリーチは9点満点、地域リハビリテーションの推進は0→7点満点、計画の進捗管理（目標Ⅰの3項目）は0→48点満点。一方、要介護3〜5の状態の変化は2指標とも0点（35点減）、認知症サポーター数は12点中0点、難聴は20点中0点。施策1-1を「通いの場の再構築と参加率の向上」から「通いの場の開催頻度の向上と地区差の是正」に改称し、課題3の見出しも改めた。(4)6-3の成果目標・活動指標に令和8年度の得点と全国平均を併記し、維持6指標・引上げ5指標に整理。(5)認知症基本法13条1項・成年後見促進法14条1項を確認し1-2の【要確認】を解消。素案は2,197行→2,341行。★9/15：3次にわたり修正。(1)見込量算定の第1次概算を反映（doc35）。(2)令和8年度の交付金評価指標で全記述を検算し、施策1-1の名称と課題3の見出しを改めた。(3)推計の系列を統一し、介護給付費と予防給付費を分離、見込量の自己点検を実施。5-12（据え置き項目31件）を新設。素案は約115頁→2,449行（段落約4,400・表約125・図20）。残る空欄は交付金の交付見込額、高齢者福祉サービスの量の目標の一部、委員名簿・パブコメなど確定後に記入するもの。★9/16：交付金の目標別に全国平均と対比したところ、素案2-8の「認知症総合支援が全国平均を下回る唯一の目標」が誤りと判明（上回るのは3目標、下回るのは5目標。認知症総合支援は差が最大の▲19.1点）。2-8に目標別の対比表を新設し関係箇所を訂正した。あわせて薄い節を埋めた（1-5日常生活圏域・4-2〜4-4基本目標の導入・5-10低所得者）。6-4に乖離の検証の見直しの目安（±5%以内／±5〜12%／±12%超）を、6-5に計画期間中に確定する5項目を新設。±12%は推計の誤差の絶対値の平均11.9%（保険料月額約700円）によるもので、この幅を超える乖離は基金の取崩しでは吸収できない。素案は2,449行→2,509行。★9/16：認知症施策推進計画としての検討（doc36）。本計画は認知症基本法第13条第1項の市町村計画を兼ねるが、認知症施策は施